--- a/IV_2.5K_T1.xlsx
+++ b/IV_2.5K_T1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Superconductivity\Nb\Mn3Pt_Nb\Queries\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -2737,7 +2737,7 @@
         <v>23.4375</v>
       </c>
       <c r="B20">
-        <v>8.8100000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="C20">
         <v>23.4375</v>
@@ -2877,7 +2877,7 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>3.245E-2</v>
+        <v>0</v>
       </c>
       <c r="C21">
         <v>25</v>
@@ -3017,7 +3017,7 @@
         <v>26.5625</v>
       </c>
       <c r="B22">
-        <v>3.4500000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="C22">
         <v>26.5625</v>
@@ -3157,7 +3157,7 @@
         <v>28.125</v>
       </c>
       <c r="B23">
-        <v>3.6540000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="C23">
         <v>28.125</v>
@@ -3297,7 +3297,7 @@
         <v>29.6875</v>
       </c>
       <c r="B24">
-        <v>3.8600000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="C24">
         <v>29.6875</v>
@@ -3436,8 +3436,8 @@
       <c r="A25">
         <v>31.25</v>
       </c>
-      <c r="B25">
-        <v>4.0640000000000003E-2</v>
+      <c r="B25" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="C25">
         <v>31.25</v>
@@ -3577,7 +3577,7 @@
         <v>32.8125</v>
       </c>
       <c r="B26">
-        <v>4.267E-2</v>
+        <v>0</v>
       </c>
       <c r="C26">
         <v>32.8125</v>
@@ -3679,7 +3679,7 @@
         <v>32.8125</v>
       </c>
       <c r="AJ26">
-        <v>4.4650000000000002E-2</v>
+        <v>4.4670000000000001E-2</v>
       </c>
       <c r="AK26">
         <v>32.8125</v>
@@ -3717,7 +3717,7 @@
         <v>34.375</v>
       </c>
       <c r="B27">
-        <v>4.4699999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="C27">
         <v>34.375</v>
@@ -3857,7 +3857,7 @@
         <v>35.9375</v>
       </c>
       <c r="B28">
-        <v>4.6760000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="C28">
         <v>35.9375</v>
@@ -3977,7 +3977,7 @@
         <v>35.9375</v>
       </c>
       <c r="AP28">
-        <v>4.8899999999999999E-2</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="AQ28">
         <v>35.9375</v>
@@ -3997,7 +3997,7 @@
         <v>37.5</v>
       </c>
       <c r="B29">
-        <v>4.8800000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="C29">
         <v>37.5</v>
@@ -4117,7 +4117,7 @@
         <v>37.5</v>
       </c>
       <c r="AP29">
-        <v>5.1029999999999999E-2</v>
+        <v>5.1020000000000003E-2</v>
       </c>
       <c r="AQ29">
         <v>37.5</v>
@@ -4137,7 +4137,7 @@
         <v>39.0625</v>
       </c>
       <c r="B30">
-        <v>5.0860000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="C30">
         <v>39.0625</v>
@@ -4257,7 +4257,7 @@
         <v>39.0625</v>
       </c>
       <c r="AP30">
-        <v>5.314E-2</v>
+        <v>5.3150000000000003E-2</v>
       </c>
       <c r="AQ30">
         <v>39.0625</v>
@@ -4277,7 +4277,7 @@
         <v>40.625</v>
       </c>
       <c r="B31" s="1">
-        <v>5.289E-2</v>
+        <v>0</v>
       </c>
       <c r="C31">
         <v>40.625</v>
@@ -4397,7 +4397,7 @@
         <v>40.625</v>
       </c>
       <c r="AP31">
-        <v>5.5280000000000003E-2</v>
+        <v>5.5300000000000002E-2</v>
       </c>
       <c r="AQ31">
         <v>40.625</v>
@@ -4417,7 +4417,7 @@
         <v>42.1875</v>
       </c>
       <c r="B32">
-        <v>5.4940000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="C32">
         <v>42.1875</v>
@@ -4513,13 +4513,13 @@
         <v>42.1875</v>
       </c>
       <c r="AH32">
-        <v>5.7419999999999999E-2</v>
+        <v>5.7450000000000001E-2</v>
       </c>
       <c r="AI32">
         <v>42.1875</v>
       </c>
       <c r="AJ32">
-        <v>5.7389999999999997E-2</v>
+        <v>5.7410000000000003E-2</v>
       </c>
       <c r="AK32">
         <v>42.1875</v>
@@ -4537,7 +4537,7 @@
         <v>42.1875</v>
       </c>
       <c r="AP32">
-        <v>5.7410000000000003E-2</v>
+        <v>5.74E-2</v>
       </c>
       <c r="AQ32">
         <v>42.1875</v>
@@ -4557,7 +4557,7 @@
         <v>43.75</v>
       </c>
       <c r="B33">
-        <v>5.6980000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="C33">
         <v>43.75</v>
@@ -4659,7 +4659,7 @@
         <v>43.75</v>
       </c>
       <c r="AJ33">
-        <v>5.9520000000000003E-2</v>
+        <v>5.9499999999999997E-2</v>
       </c>
       <c r="AK33">
         <v>43.75</v>
@@ -4677,7 +4677,7 @@
         <v>43.75</v>
       </c>
       <c r="AP33">
-        <v>5.9520000000000003E-2</v>
+        <v>5.953E-2</v>
       </c>
       <c r="AQ33">
         <v>43.75</v>
@@ -4697,7 +4697,7 @@
         <v>45.3125</v>
       </c>
       <c r="B34">
-        <v>5.901E-2</v>
+        <v>0</v>
       </c>
       <c r="C34">
         <v>45.3125</v>
@@ -4781,7 +4781,7 @@
         <v>45.3125</v>
       </c>
       <c r="AD34">
-        <v>6.164E-2</v>
+        <v>6.1650000000000003E-2</v>
       </c>
       <c r="AE34">
         <v>45.3125</v>
@@ -4837,7 +4837,7 @@
         <v>46.875</v>
       </c>
       <c r="B35">
-        <v>6.105E-2</v>
+        <v>0</v>
       </c>
       <c r="C35">
         <v>46.875</v>
@@ -4921,7 +4921,7 @@
         <v>46.875</v>
       </c>
       <c r="AD35">
-        <v>6.3769999999999993E-2</v>
+        <v>6.3780000000000003E-2</v>
       </c>
       <c r="AE35">
         <v>46.875</v>
@@ -4939,7 +4939,7 @@
         <v>46.875</v>
       </c>
       <c r="AJ35">
-        <v>6.3769999999999993E-2</v>
+        <v>6.3759999999999997E-2</v>
       </c>
       <c r="AK35">
         <v>46.875</v>
@@ -4977,7 +4977,7 @@
         <v>48.4375</v>
       </c>
       <c r="B36">
-        <v>6.3109999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="C36" s="1">
         <v>48.4375</v>
@@ -5031,7 +5031,7 @@
         <v>48.4375</v>
       </c>
       <c r="T36">
-        <v>6.5909999999999996E-2</v>
+        <v>6.6009999999999999E-2</v>
       </c>
       <c r="U36">
         <v>48.4375</v>
@@ -5061,7 +5061,7 @@
         <v>48.4375</v>
       </c>
       <c r="AD36">
-        <v>6.5909999999999996E-2</v>
+        <v>6.5920000000000006E-2</v>
       </c>
       <c r="AE36">
         <v>48.4375</v>
@@ -5117,7 +5117,7 @@
         <v>50</v>
       </c>
       <c r="B37">
-        <v>6.5140000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="C37">
         <v>50</v>
@@ -5171,7 +5171,7 @@
         <v>50</v>
       </c>
       <c r="T37">
-        <v>6.8099999999999994E-2</v>
+        <v>6.83E-2</v>
       </c>
       <c r="U37">
         <v>50</v>
@@ -5237,7 +5237,7 @@
         <v>50</v>
       </c>
       <c r="AP37">
-        <v>6.8099999999999994E-2</v>
+        <v>6.8199999999999997E-2</v>
       </c>
       <c r="AQ37">
         <v>50</v>
@@ -5257,7 +5257,7 @@
         <v>51.5625</v>
       </c>
       <c r="B38">
-        <v>6.7250000000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="C38" s="1">
         <v>51.5625</v>
@@ -5311,7 +5311,7 @@
         <v>51.5625</v>
       </c>
       <c r="T38">
-        <v>7.0230000000000001E-2</v>
+        <v>7.0430000000000006E-2</v>
       </c>
       <c r="U38">
         <v>51.5625</v>
@@ -5397,7 +5397,7 @@
         <v>53.125</v>
       </c>
       <c r="B39">
-        <v>6.9290000000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="C39" s="1">
         <v>53.125</v>
@@ -5451,7 +5451,7 @@
         <v>53.125</v>
       </c>
       <c r="T39">
-        <v>7.2370000000000004E-2</v>
+        <v>7.2169999999999998E-2</v>
       </c>
       <c r="U39">
         <v>53.125</v>
@@ -5481,7 +5481,7 @@
         <v>53.125</v>
       </c>
       <c r="AD39">
-        <v>7.2349999999999998E-2</v>
+        <v>7.2340000000000002E-2</v>
       </c>
       <c r="AE39">
         <v>53.125</v>
@@ -5517,7 +5517,7 @@
         <v>53.125</v>
       </c>
       <c r="AP39">
-        <v>7.2349999999999998E-2</v>
+        <v>7.2400000000000006E-2</v>
       </c>
       <c r="AQ39">
         <v>53.125</v>
@@ -5537,7 +5537,7 @@
         <v>54.6875</v>
       </c>
       <c r="B40">
-        <v>7.1349999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="C40" s="1">
         <v>54.6875</v>
@@ -5591,7 +5591,7 @@
         <v>54.6875</v>
       </c>
       <c r="T40">
-        <v>7.4499999999999997E-2</v>
+        <v>7.4399999999999994E-2</v>
       </c>
       <c r="U40">
         <v>54.6875</v>
@@ -5677,7 +5677,7 @@
         <v>56.25</v>
       </c>
       <c r="B41">
-        <v>7.3380000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="C41" s="1">
         <v>56.25</v>
@@ -5731,7 +5731,7 @@
         <v>56.25</v>
       </c>
       <c r="T41">
-        <v>7.6630000000000004E-2</v>
+        <v>7.6829999999999996E-2</v>
       </c>
       <c r="U41">
         <v>56.25</v>
@@ -5749,7 +5749,7 @@
         <v>56.25</v>
       </c>
       <c r="Z41">
-        <v>7.6630000000000004E-2</v>
+        <v>7.6609999999999998E-2</v>
       </c>
       <c r="AA41">
         <v>56.25</v>
@@ -5779,7 +5779,7 @@
         <v>56.25</v>
       </c>
       <c r="AJ41">
-        <v>7.6609999999999998E-2</v>
+        <v>7.664E-2</v>
       </c>
       <c r="AK41">
         <v>56.25</v>
@@ -5817,7 +5817,7 @@
         <v>57.8125</v>
       </c>
       <c r="B42">
-        <v>7.5439999999999993E-2</v>
+        <v>0</v>
       </c>
       <c r="C42" s="1">
         <v>57.8125</v>
@@ -5847,7 +5847,7 @@
         <v>57.8125</v>
       </c>
       <c r="L42">
-        <v>7.8750000000000001E-2</v>
+        <v>7.8950000000000006E-2</v>
       </c>
       <c r="M42">
         <v>57.8125</v>
@@ -5871,7 +5871,7 @@
         <v>57.8125</v>
       </c>
       <c r="T42">
-        <v>7.8759999999999997E-2</v>
+        <v>7.8560000000000005E-2</v>
       </c>
       <c r="U42">
         <v>57.8125</v>
@@ -5889,7 +5889,7 @@
         <v>57.8125</v>
       </c>
       <c r="Z42">
-        <v>7.8759999999999997E-2</v>
+        <v>7.8750000000000001E-2</v>
       </c>
       <c r="AA42">
         <v>57.8125</v>
@@ -5901,7 +5901,7 @@
         <v>57.8125</v>
       </c>
       <c r="AD42">
-        <v>7.8750000000000001E-2</v>
+        <v>7.8799999999999995E-2</v>
       </c>
       <c r="AE42">
         <v>57.8125</v>
@@ -5937,7 +5937,7 @@
         <v>57.8125</v>
       </c>
       <c r="AP42">
-        <v>7.8750000000000001E-2</v>
+        <v>7.8740000000000004E-2</v>
       </c>
       <c r="AQ42">
         <v>57.8125</v>
@@ -5957,7 +5957,7 @@
         <v>59.375</v>
       </c>
       <c r="B43">
-        <v>7.7469999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="C43" s="1">
         <v>59.375</v>
@@ -5987,7 +5987,7 @@
         <v>59.375</v>
       </c>
       <c r="L43">
-        <v>8.09E-2</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="M43">
         <v>59.375</v>
@@ -6011,7 +6011,7 @@
         <v>59.375</v>
       </c>
       <c r="T43">
-        <v>8.0909999999999996E-2</v>
+        <v>8.0810000000000007E-2</v>
       </c>
       <c r="U43">
         <v>59.375</v>
@@ -6029,7 +6029,7 @@
         <v>59.375</v>
       </c>
       <c r="Z43">
-        <v>8.0909999999999996E-2</v>
+        <v>8.09E-2</v>
       </c>
       <c r="AA43">
         <v>59.375</v>
@@ -6077,7 +6077,7 @@
         <v>59.375</v>
       </c>
       <c r="AP43">
-        <v>8.09E-2</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="AQ43">
         <v>59.375</v>
@@ -6097,7 +6097,7 @@
         <v>60.9375</v>
       </c>
       <c r="B44">
-        <v>7.9519999999999993E-2</v>
+        <v>0</v>
       </c>
       <c r="C44" s="1">
         <v>60.9375</v>
@@ -6127,7 +6127,7 @@
         <v>60.9375</v>
       </c>
       <c r="L44">
-        <v>8.3040000000000003E-2</v>
+        <v>8.2839999999999997E-2</v>
       </c>
       <c r="M44">
         <v>60.9375</v>
@@ -6151,7 +6151,7 @@
         <v>60.9375</v>
       </c>
       <c r="T44">
-        <v>8.3040000000000003E-2</v>
+        <v>8.3239999999999995E-2</v>
       </c>
       <c r="U44">
         <v>60.9375</v>
@@ -6181,7 +6181,7 @@
         <v>60.9375</v>
       </c>
       <c r="AD44">
-        <v>8.3040000000000003E-2</v>
+        <v>8.301E-2</v>
       </c>
       <c r="AE44">
         <v>60.9375</v>
@@ -6193,13 +6193,13 @@
         <v>60.9375</v>
       </c>
       <c r="AH44">
-        <v>8.3080000000000001E-2</v>
+        <v>8.3070000000000005E-2</v>
       </c>
       <c r="AI44">
         <v>60.9375</v>
       </c>
       <c r="AJ44">
-        <v>8.3030000000000007E-2</v>
+        <v>8.3049999999999999E-2</v>
       </c>
       <c r="AK44">
         <v>60.9375</v>
@@ -6217,7 +6217,7 @@
         <v>60.9375</v>
       </c>
       <c r="AP44">
-        <v>8.3040000000000003E-2</v>
+        <v>8.3019999999999997E-2</v>
       </c>
       <c r="AQ44">
         <v>60.9375</v>
@@ -6237,7 +6237,7 @@
         <v>62.5</v>
       </c>
       <c r="B45">
-        <v>8.1570000000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="C45" s="1">
         <v>62.5</v>
@@ -6267,7 +6267,7 @@
         <v>62.5</v>
       </c>
       <c r="L45">
-        <v>8.5190000000000002E-2</v>
+        <v>8.5089999999999999E-2</v>
       </c>
       <c r="M45">
         <v>62.5</v>
@@ -6309,7 +6309,7 @@
         <v>62.5</v>
       </c>
       <c r="Z45">
-        <v>8.5209999999999994E-2</v>
+        <v>8.5199999999999998E-2</v>
       </c>
       <c r="AA45">
         <v>62.5</v>
@@ -6321,7 +6321,7 @@
         <v>62.5</v>
       </c>
       <c r="AD45">
-        <v>8.5190000000000002E-2</v>
+        <v>8.5199999999999998E-2</v>
       </c>
       <c r="AE45">
         <v>62.5</v>
@@ -6357,7 +6357,7 @@
         <v>62.5</v>
       </c>
       <c r="AP45">
-        <v>8.5190000000000002E-2</v>
+        <v>8.5209999999999994E-2</v>
       </c>
       <c r="AQ45">
         <v>62.5</v>
@@ -6377,7 +6377,7 @@
         <v>64.0625</v>
       </c>
       <c r="B46">
-        <v>8.362E-2</v>
+        <v>0</v>
       </c>
       <c r="C46" s="1">
         <v>64.0625</v>
@@ -6407,7 +6407,7 @@
         <v>64.0625</v>
       </c>
       <c r="L46">
-        <v>8.7340000000000001E-2</v>
+        <v>8.7239999999999998E-2</v>
       </c>
       <c r="M46">
         <v>64.0625</v>
@@ -6431,7 +6431,7 @@
         <v>64.0625</v>
       </c>
       <c r="T46">
-        <v>8.7340000000000001E-2</v>
+        <v>8.7540000000000007E-2</v>
       </c>
       <c r="U46">
         <v>64.0625</v>
@@ -6461,7 +6461,7 @@
         <v>64.0625</v>
       </c>
       <c r="AD46">
-        <v>8.7340000000000001E-2</v>
+        <v>8.7349999999999997E-2</v>
       </c>
       <c r="AE46">
         <v>64.0625</v>
@@ -6497,7 +6497,7 @@
         <v>64.0625</v>
       </c>
       <c r="AP46">
-        <v>8.7340000000000001E-2</v>
+        <v>8.7359999999999993E-2</v>
       </c>
       <c r="AQ46">
         <v>64.0625</v>
@@ -6517,7 +6517,7 @@
         <v>65.625</v>
       </c>
       <c r="B47">
-        <v>8.5669999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="C47" s="1">
         <v>65.625</v>
@@ -6547,7 +6547,7 @@
         <v>65.625</v>
       </c>
       <c r="L47">
-        <v>8.949E-2</v>
+        <v>8.9590000000000003E-2</v>
       </c>
       <c r="M47">
         <v>65.625</v>
@@ -6571,7 +6571,7 @@
         <v>65.625</v>
       </c>
       <c r="T47">
-        <v>8.949E-2</v>
+        <v>8.9690000000000006E-2</v>
       </c>
       <c r="U47">
         <v>65.625</v>
@@ -6589,7 +6589,7 @@
         <v>65.625</v>
       </c>
       <c r="Z47">
-        <v>8.949E-2</v>
+        <v>8.9450000000000002E-2</v>
       </c>
       <c r="AA47">
         <v>65.625</v>
@@ -6601,7 +6601,7 @@
         <v>65.625</v>
       </c>
       <c r="AD47">
-        <v>8.949E-2</v>
+        <v>8.9499999999999996E-2</v>
       </c>
       <c r="AE47">
         <v>65.625</v>
@@ -6637,7 +6637,7 @@
         <v>65.625</v>
       </c>
       <c r="AP47">
-        <v>8.949E-2</v>
+        <v>8.9480000000000004E-2</v>
       </c>
       <c r="AQ47">
         <v>65.625</v>
@@ -6657,7 +6657,7 @@
         <v>67.1875</v>
       </c>
       <c r="B48">
-        <v>8.7730000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="C48" s="1">
         <v>67.1875</v>
@@ -6687,7 +6687,7 @@
         <v>67.1875</v>
       </c>
       <c r="L48">
-        <v>9.1639999999999999E-2</v>
+        <v>9.1439999999999994E-2</v>
       </c>
       <c r="M48">
         <v>67.1875</v>
@@ -6711,7 +6711,7 @@
         <v>67.1875</v>
       </c>
       <c r="T48">
-        <v>9.1639999999999999E-2</v>
+        <v>9.1539999999999996E-2</v>
       </c>
       <c r="U48">
         <v>67.1875</v>
@@ -6729,7 +6729,7 @@
         <v>67.1875</v>
       </c>
       <c r="Z48">
-        <v>9.1639999999999999E-2</v>
+        <v>9.1619999999999993E-2</v>
       </c>
       <c r="AA48">
         <v>67.1875</v>
@@ -6741,7 +6741,7 @@
         <v>67.1875</v>
       </c>
       <c r="AD48">
-        <v>9.1639999999999999E-2</v>
+        <v>9.1670000000000001E-2</v>
       </c>
       <c r="AE48">
         <v>67.1875</v>
@@ -6777,7 +6777,7 @@
         <v>67.1875</v>
       </c>
       <c r="AP48">
-        <v>9.1639999999999999E-2</v>
+        <v>9.1649999999999995E-2</v>
       </c>
       <c r="AQ48">
         <v>67.1875</v>
@@ -6794,10 +6794,10 @@
     </row>
     <row r="49" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>68.75</v>
+        <v>70.3125</v>
       </c>
       <c r="B49">
-        <v>8.9779999999999999E-2</v>
+        <v>9.2020000000000005E-2</v>
       </c>
       <c r="C49" s="1">
         <v>68.75</v>
@@ -6827,7 +6827,7 @@
         <v>68.75</v>
       </c>
       <c r="L49">
-        <v>9.3789999999999998E-2</v>
+        <v>9.3890000000000001E-2</v>
       </c>
       <c r="M49">
         <v>68.75</v>
@@ -6851,7 +6851,7 @@
         <v>68.75</v>
       </c>
       <c r="T49">
-        <v>9.3799999999999994E-2</v>
+        <v>9.3600000000000003E-2</v>
       </c>
       <c r="U49">
         <v>68.75</v>
@@ -6869,7 +6869,7 @@
         <v>68.75</v>
       </c>
       <c r="Z49">
-        <v>9.3799999999999994E-2</v>
+        <v>9.375E-2</v>
       </c>
       <c r="AA49">
         <v>68.75</v>
@@ -6881,7 +6881,7 @@
         <v>68.75</v>
       </c>
       <c r="AD49">
-        <v>9.3789999999999998E-2</v>
+        <v>9.3799999999999994E-2</v>
       </c>
       <c r="AE49">
         <v>68.75</v>
@@ -6917,7 +6917,7 @@
         <v>68.75</v>
       </c>
       <c r="AP49">
-        <v>9.3789999999999998E-2</v>
+        <v>9.3780000000000002E-2</v>
       </c>
       <c r="AQ49">
         <v>68.75</v>
@@ -6934,10 +6934,10 @@
     </row>
     <row r="50" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>70.3125</v>
+        <v>71.875</v>
       </c>
       <c r="B50">
-        <v>9.1829999999999995E-2</v>
+        <v>9.4079999999999997E-2</v>
       </c>
       <c r="C50" s="1">
         <v>70.3125</v>
@@ -6967,7 +6967,7 @@
         <v>70.3125</v>
       </c>
       <c r="L50">
-        <v>9.5930000000000001E-2</v>
+        <v>9.6129999999999993E-2</v>
       </c>
       <c r="M50">
         <v>70.3125</v>
@@ -6991,7 +6991,7 @@
         <v>70.3125</v>
       </c>
       <c r="T50">
-        <v>9.5930000000000001E-2</v>
+        <v>9.5729999999999996E-2</v>
       </c>
       <c r="U50">
         <v>70.3125</v>
@@ -7009,7 +7009,7 @@
         <v>70.3125</v>
       </c>
       <c r="Z50">
-        <v>9.5930000000000001E-2</v>
+        <v>9.5949999999999994E-2</v>
       </c>
       <c r="AA50">
         <v>70.3125</v>
@@ -7021,7 +7021,7 @@
         <v>70.3125</v>
       </c>
       <c r="AD50">
-        <v>9.5930000000000001E-2</v>
+        <v>9.5920000000000005E-2</v>
       </c>
       <c r="AE50">
         <v>70.3125</v>
@@ -7039,7 +7039,7 @@
         <v>70.3125</v>
       </c>
       <c r="AJ50">
-        <v>9.5920000000000005E-2</v>
+        <v>9.5939999999999998E-2</v>
       </c>
       <c r="AK50">
         <v>70.3125</v>
@@ -7057,7 +7057,7 @@
         <v>70.3125</v>
       </c>
       <c r="AP50">
-        <v>9.5930000000000001E-2</v>
+        <v>9.5909999999999995E-2</v>
       </c>
       <c r="AQ50">
         <v>70.3125</v>
@@ -7074,10 +7074,10 @@
     </row>
     <row r="51" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>71.875</v>
+        <v>73.4375</v>
       </c>
       <c r="B51">
-        <v>9.3869999999999995E-2</v>
+        <v>9.6129999999999993E-2</v>
       </c>
       <c r="C51" s="1">
         <v>71.875</v>
@@ -7107,7 +7107,7 @@
         <v>71.875</v>
       </c>
       <c r="L51">
-        <v>9.8080000000000001E-2</v>
+        <v>9.7879999999999995E-2</v>
       </c>
       <c r="M51">
         <v>71.875</v>
@@ -7131,7 +7131,7 @@
         <v>71.875</v>
       </c>
       <c r="T51">
-        <v>9.8100000000000007E-2</v>
+        <v>9.8299999999999998E-2</v>
       </c>
       <c r="U51">
         <v>71.875</v>
@@ -7149,7 +7149,7 @@
         <v>71.875</v>
       </c>
       <c r="Z51">
-        <v>9.8100000000000007E-2</v>
+        <v>9.8119999999999999E-2</v>
       </c>
       <c r="AA51">
         <v>71.875</v>
@@ -7161,7 +7161,7 @@
         <v>71.875</v>
       </c>
       <c r="AD51">
-        <v>9.8080000000000001E-2</v>
+        <v>9.8070000000000004E-2</v>
       </c>
       <c r="AE51">
         <v>71.875</v>
@@ -7197,7 +7197,7 @@
         <v>71.875</v>
       </c>
       <c r="AP51">
-        <v>9.8080000000000001E-2</v>
+        <v>9.8059999999999994E-2</v>
       </c>
       <c r="AQ51">
         <v>71.875</v>
@@ -7214,10 +7214,10 @@
     </row>
     <row r="52" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>73.4375</v>
+        <v>75</v>
       </c>
       <c r="B52">
-        <v>9.5930000000000001E-2</v>
+        <v>9.819E-2</v>
       </c>
       <c r="C52" s="1">
         <v>73.4375</v>
@@ -7247,7 +7247,7 @@
         <v>73.4375</v>
       </c>
       <c r="L52">
-        <v>0.10025000000000001</v>
+        <v>0.10045</v>
       </c>
       <c r="M52">
         <v>73.4375</v>
@@ -7271,7 +7271,7 @@
         <v>73.4375</v>
       </c>
       <c r="T52">
-        <v>0.10026</v>
+        <v>0.10036</v>
       </c>
       <c r="U52">
         <v>73.4375</v>
@@ -7289,7 +7289,7 @@
         <v>73.4375</v>
       </c>
       <c r="Z52">
-        <v>0.10026</v>
+        <v>0.10024</v>
       </c>
       <c r="AA52">
         <v>73.4375</v>
@@ -7301,7 +7301,7 @@
         <v>73.4375</v>
       </c>
       <c r="AD52">
-        <v>0.10025000000000001</v>
+        <v>0.10024</v>
       </c>
       <c r="AE52">
         <v>73.4375</v>
@@ -7337,7 +7337,7 @@
         <v>73.4375</v>
       </c>
       <c r="AP52">
-        <v>0.10025000000000001</v>
+        <v>0.10020999999999999</v>
       </c>
       <c r="AQ52">
         <v>73.4375</v>
@@ -7354,10 +7354,10 @@
     </row>
     <row r="53" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>75</v>
+        <v>76.5625</v>
       </c>
       <c r="B53">
-        <v>9.7979999999999998E-2</v>
+        <v>0.10024</v>
       </c>
       <c r="C53">
         <v>75</v>
@@ -7387,7 +7387,7 @@
         <v>75</v>
       </c>
       <c r="L53">
-        <v>0.10241</v>
+        <v>0.10221</v>
       </c>
       <c r="M53">
         <v>75</v>
@@ -7411,7 +7411,7 @@
         <v>75</v>
       </c>
       <c r="T53">
-        <v>0.10241</v>
+        <v>0.10231</v>
       </c>
       <c r="U53">
         <v>75</v>
@@ -7441,7 +7441,7 @@
         <v>75</v>
       </c>
       <c r="AD53">
-        <v>0.10241</v>
+        <v>0.1024</v>
       </c>
       <c r="AE53">
         <v>75</v>
@@ -7477,7 +7477,7 @@
         <v>75</v>
       </c>
       <c r="AP53">
-        <v>0.10241</v>
+        <v>0.10242</v>
       </c>
       <c r="AQ53">
         <v>75</v>
@@ -7494,10 +7494,10 @@
     </row>
     <row r="54" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>76.5625</v>
+        <v>78.125</v>
       </c>
       <c r="B54">
-        <v>0.10004</v>
+        <v>0.10231</v>
       </c>
       <c r="C54">
         <v>76.5625</v>
@@ -7527,7 +7527,7 @@
         <v>76.5625</v>
       </c>
       <c r="L54">
-        <v>0.10458000000000001</v>
+        <v>0.10438</v>
       </c>
       <c r="M54">
         <v>76.5625</v>
@@ -7569,7 +7569,7 @@
         <v>76.5625</v>
       </c>
       <c r="Z54">
-        <v>0.10458000000000001</v>
+        <v>0.10453999999999999</v>
       </c>
       <c r="AA54">
         <v>76.5625</v>
@@ -7581,7 +7581,7 @@
         <v>76.5625</v>
       </c>
       <c r="AD54">
-        <v>0.10458000000000001</v>
+        <v>0.1046</v>
       </c>
       <c r="AE54">
         <v>76.5625</v>
@@ -7599,7 +7599,7 @@
         <v>76.5625</v>
       </c>
       <c r="AJ54">
-        <v>0.10458000000000001</v>
+        <v>0.10457</v>
       </c>
       <c r="AK54">
         <v>76.5625</v>
@@ -7617,7 +7617,7 @@
         <v>76.5625</v>
       </c>
       <c r="AP54">
-        <v>0.10458000000000001</v>
+        <v>0.10456</v>
       </c>
       <c r="AQ54">
         <v>76.5625</v>
@@ -7634,10 +7634,10 @@
     </row>
     <row r="55" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>78.125</v>
+        <v>79.6875</v>
       </c>
       <c r="B55">
-        <v>0.10208</v>
+        <v>0.10437</v>
       </c>
       <c r="C55">
         <v>78.125</v>
@@ -7667,7 +7667,7 @@
         <v>78.125</v>
       </c>
       <c r="L55">
-        <v>0.10674</v>
+        <v>0.10664</v>
       </c>
       <c r="M55">
         <v>78.125</v>
@@ -7709,7 +7709,7 @@
         <v>78.125</v>
       </c>
       <c r="Z55">
-        <v>0.10675999999999999</v>
+        <v>0.10675</v>
       </c>
       <c r="AA55">
         <v>78.125</v>
@@ -7721,7 +7721,7 @@
         <v>78.125</v>
       </c>
       <c r="AD55">
-        <v>0.10674</v>
+        <v>0.10678</v>
       </c>
       <c r="AE55">
         <v>78.125</v>
@@ -7739,7 +7739,7 @@
         <v>78.125</v>
       </c>
       <c r="AJ55">
-        <v>0.10675999999999999</v>
+        <v>0.10677</v>
       </c>
       <c r="AK55">
         <v>78.125</v>
@@ -7757,7 +7757,7 @@
         <v>78.125</v>
       </c>
       <c r="AP55">
-        <v>0.10674</v>
+        <v>0.10675999999999999</v>
       </c>
       <c r="AQ55">
         <v>78.125</v>
@@ -7774,10 +7774,10 @@
     </row>
     <row r="56" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>79.6875</v>
+        <v>81.25</v>
       </c>
       <c r="B56">
-        <v>0.10415000000000001</v>
+        <v>0.10644000000000001</v>
       </c>
       <c r="C56">
         <v>79.6875</v>
@@ -7807,7 +7807,7 @@
         <v>79.6875</v>
       </c>
       <c r="L56">
-        <v>0.10892</v>
+        <v>0.10911999999999999</v>
       </c>
       <c r="M56">
         <v>79.6875</v>
@@ -7831,7 +7831,7 @@
         <v>79.6875</v>
       </c>
       <c r="T56">
-        <v>0.10892</v>
+        <v>0.10911999999999999</v>
       </c>
       <c r="U56">
         <v>79.6875</v>
@@ -7849,7 +7849,7 @@
         <v>79.6875</v>
       </c>
       <c r="Z56">
-        <v>0.10892</v>
+        <v>0.10891000000000001</v>
       </c>
       <c r="AA56">
         <v>79.6875</v>
@@ -7861,7 +7861,7 @@
         <v>79.6875</v>
       </c>
       <c r="AD56">
-        <v>0.10892</v>
+        <v>0.10893</v>
       </c>
       <c r="AE56">
         <v>79.6875</v>
@@ -7879,7 +7879,7 @@
         <v>79.6875</v>
       </c>
       <c r="AJ56">
-        <v>0.10894</v>
+        <v>0.10897999999999999</v>
       </c>
       <c r="AK56">
         <v>79.6875</v>
@@ -7897,7 +7897,7 @@
         <v>79.6875</v>
       </c>
       <c r="AP56">
-        <v>0.10892</v>
+        <v>0.10891000000000001</v>
       </c>
       <c r="AQ56">
         <v>79.6875</v>
@@ -7914,16 +7914,16 @@
     </row>
     <row r="57" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>81.25</v>
+        <v>82.8125</v>
       </c>
       <c r="B57">
-        <v>0.10619000000000001</v>
+        <v>0.1085</v>
       </c>
       <c r="C57">
         <v>81.25</v>
       </c>
       <c r="D57" s="1">
-        <v>0.11115</v>
+        <v>0.11115999999999999</v>
       </c>
       <c r="E57">
         <v>81.25</v>
@@ -7947,7 +7947,7 @@
         <v>81.25</v>
       </c>
       <c r="L57">
-        <v>0.1111</v>
+        <v>0.1113</v>
       </c>
       <c r="M57">
         <v>81.25</v>
@@ -7971,7 +7971,7 @@
         <v>81.25</v>
       </c>
       <c r="T57">
-        <v>0.1111</v>
+        <v>0.1113</v>
       </c>
       <c r="U57">
         <v>81.25</v>
@@ -7989,7 +7989,7 @@
         <v>81.25</v>
       </c>
       <c r="Z57">
-        <v>0.1111</v>
+        <v>0.11119999999999999</v>
       </c>
       <c r="AA57">
         <v>81.25</v>
@@ -8001,7 +8001,7 @@
         <v>81.25</v>
       </c>
       <c r="AD57">
-        <v>0.1111</v>
+        <v>0.11119999999999999</v>
       </c>
       <c r="AE57">
         <v>81.25</v>
@@ -8013,13 +8013,13 @@
         <v>81.25</v>
       </c>
       <c r="AH57">
-        <v>0.11115</v>
+        <v>0.11112</v>
       </c>
       <c r="AI57">
         <v>81.25</v>
       </c>
       <c r="AJ57">
-        <v>0.1111</v>
+        <v>0.11119999999999999</v>
       </c>
       <c r="AK57">
         <v>81.25</v>
@@ -8037,7 +8037,7 @@
         <v>81.25</v>
       </c>
       <c r="AP57">
-        <v>0.1111</v>
+        <v>0.1115</v>
       </c>
       <c r="AQ57">
         <v>81.25</v>
@@ -8054,16 +8054,16 @@
     </row>
     <row r="58" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>82.8125</v>
+        <v>84.375</v>
       </c>
       <c r="B58">
-        <v>0.10825</v>
+        <v>0.11058</v>
       </c>
       <c r="C58">
         <v>82.8125</v>
       </c>
       <c r="D58" s="1">
-        <v>0.11333</v>
+        <v>0.11334</v>
       </c>
       <c r="E58">
         <v>82.8125</v>
@@ -8087,7 +8087,7 @@
         <v>82.8125</v>
       </c>
       <c r="L58">
-        <v>0.11328000000000001</v>
+        <v>0.11318</v>
       </c>
       <c r="M58">
         <v>82.8125</v>
@@ -8111,7 +8111,7 @@
         <v>82.8125</v>
       </c>
       <c r="T58">
-        <v>0.11328000000000001</v>
+        <v>0.11348</v>
       </c>
       <c r="U58">
         <v>82.8125</v>
@@ -8129,7 +8129,7 @@
         <v>82.8125</v>
       </c>
       <c r="Z58">
-        <v>0.11328000000000001</v>
+        <v>0.11327</v>
       </c>
       <c r="AA58">
         <v>82.8125</v>
@@ -8141,7 +8141,7 @@
         <v>82.8125</v>
       </c>
       <c r="AD58">
-        <v>0.11328000000000001</v>
+        <v>0.11329</v>
       </c>
       <c r="AE58">
         <v>82.8125</v>
@@ -8159,7 +8159,7 @@
         <v>82.8125</v>
       </c>
       <c r="AJ58">
-        <v>0.11328000000000001</v>
+        <v>0.11327</v>
       </c>
       <c r="AK58">
         <v>82.8125</v>
@@ -8177,7 +8177,7 @@
         <v>82.8125</v>
       </c>
       <c r="AP58">
-        <v>0.11328000000000001</v>
+        <v>0.1133</v>
       </c>
       <c r="AQ58">
         <v>82.8125</v>
@@ -8194,16 +8194,16 @@
     </row>
     <row r="59" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>84.375</v>
+        <v>85.9375</v>
       </c>
       <c r="B59">
-        <v>0.1103</v>
+        <v>0.11265</v>
       </c>
       <c r="C59">
         <v>84.375</v>
       </c>
       <c r="D59">
-        <v>0.11552999999999999</v>
+        <v>0.11552</v>
       </c>
       <c r="E59">
         <v>84.375</v>
@@ -8227,7 +8227,7 @@
         <v>84.375</v>
       </c>
       <c r="L59">
-        <v>0.11548</v>
+        <v>0.11527999999999999</v>
       </c>
       <c r="M59">
         <v>84.375</v>
@@ -8251,7 +8251,7 @@
         <v>84.375</v>
       </c>
       <c r="T59">
-        <v>0.11550000000000001</v>
+        <v>0.11559999999999999</v>
       </c>
       <c r="U59">
         <v>84.375</v>
@@ -8281,7 +8281,7 @@
         <v>84.375</v>
       </c>
       <c r="AD59">
-        <v>0.11548</v>
+        <v>0.11547</v>
       </c>
       <c r="AE59">
         <v>84.375</v>
@@ -8299,7 +8299,7 @@
         <v>84.375</v>
       </c>
       <c r="AJ59">
-        <v>0.11550000000000001</v>
+        <v>0.1153</v>
       </c>
       <c r="AK59">
         <v>84.375</v>
@@ -8317,7 +8317,7 @@
         <v>84.375</v>
       </c>
       <c r="AP59">
-        <v>0.11548</v>
+        <v>0.11549</v>
       </c>
       <c r="AQ59">
         <v>84.375</v>
@@ -8334,16 +8334,16 @@
     </row>
     <row r="60" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>85.9375</v>
+        <v>87.5</v>
       </c>
       <c r="B60">
-        <v>0.11237</v>
+        <v>0.11473999999999999</v>
       </c>
       <c r="C60">
         <v>85.9375</v>
       </c>
       <c r="D60">
-        <v>0.11772000000000001</v>
+        <v>0.11771</v>
       </c>
       <c r="E60">
         <v>85.9375</v>
@@ -8391,7 +8391,7 @@
         <v>85.9375</v>
       </c>
       <c r="T60">
-        <v>0.11768000000000001</v>
+        <v>0.11748</v>
       </c>
       <c r="U60">
         <v>85.9375</v>
@@ -8409,7 +8409,7 @@
         <v>85.9375</v>
       </c>
       <c r="Z60">
-        <v>0.11768000000000001</v>
+        <v>0.1177</v>
       </c>
       <c r="AA60">
         <v>85.9375</v>
@@ -8421,7 +8421,7 @@
         <v>85.9375</v>
       </c>
       <c r="AD60">
-        <v>0.11766</v>
+        <v>0.11767</v>
       </c>
       <c r="AE60">
         <v>85.9375</v>
@@ -8439,7 +8439,7 @@
         <v>85.9375</v>
       </c>
       <c r="AJ60">
-        <v>0.11768000000000001</v>
+        <v>0.1177</v>
       </c>
       <c r="AK60">
         <v>85.9375</v>
@@ -8457,7 +8457,7 @@
         <v>85.9375</v>
       </c>
       <c r="AP60">
-        <v>0.11766</v>
+        <v>0.11768000000000001</v>
       </c>
       <c r="AQ60">
         <v>85.9375</v>
@@ -8474,10 +8474,10 @@
     </row>
     <row r="61" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>87.5</v>
+        <v>89.0625</v>
       </c>
       <c r="B61">
-        <v>0.11443</v>
+        <v>0.1168</v>
       </c>
       <c r="C61">
         <v>87.5</v>
@@ -8507,7 +8507,7 @@
         <v>87.5</v>
       </c>
       <c r="L61">
-        <v>0.11987</v>
+        <v>0.11967</v>
       </c>
       <c r="M61">
         <v>87.5</v>
@@ -8531,7 +8531,7 @@
         <v>87.5</v>
       </c>
       <c r="T61">
-        <v>0.11989</v>
+        <v>0.11999</v>
       </c>
       <c r="U61">
         <v>87.5</v>
@@ -8549,7 +8549,7 @@
         <v>87.5</v>
       </c>
       <c r="Z61">
-        <v>0.11989</v>
+        <v>0.11990000000000001</v>
       </c>
       <c r="AA61">
         <v>87.5</v>
@@ -8561,7 +8561,7 @@
         <v>87.5</v>
       </c>
       <c r="AD61">
-        <v>0.11987</v>
+        <v>0.11985999999999999</v>
       </c>
       <c r="AE61">
         <v>87.5</v>
@@ -8579,7 +8579,7 @@
         <v>87.5</v>
       </c>
       <c r="AJ61">
-        <v>0.11989</v>
+        <v>0.11991</v>
       </c>
       <c r="AK61">
         <v>87.5</v>
@@ -8597,7 +8597,7 @@
         <v>87.5</v>
       </c>
       <c r="AP61">
-        <v>0.11987</v>
+        <v>0.11985</v>
       </c>
       <c r="AQ61">
         <v>87.5</v>
@@ -8614,10 +8614,10 @@
     </row>
     <row r="62" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>89.0625</v>
+        <v>90.625</v>
       </c>
       <c r="B62">
-        <v>0.11651</v>
+        <v>0.11888</v>
       </c>
       <c r="C62">
         <v>89.0625</v>
@@ -8689,7 +8689,7 @@
         <v>89.0625</v>
       </c>
       <c r="Z62">
-        <v>0.12209</v>
+        <v>0.1221</v>
       </c>
       <c r="AA62">
         <v>89.0625</v>
@@ -8701,7 +8701,7 @@
         <v>89.0625</v>
       </c>
       <c r="AD62">
-        <v>0.12209</v>
+        <v>0.12207999999999999</v>
       </c>
       <c r="AE62">
         <v>89.0625</v>
@@ -8719,7 +8719,7 @@
         <v>89.0625</v>
       </c>
       <c r="AJ62">
-        <v>0.12209</v>
+        <v>0.1221</v>
       </c>
       <c r="AK62">
         <v>89.0625</v>
@@ -8737,7 +8737,7 @@
         <v>89.0625</v>
       </c>
       <c r="AP62">
-        <v>0.12209</v>
+        <v>0.12206</v>
       </c>
       <c r="AQ62">
         <v>89.0625</v>
@@ -8754,10 +8754,10 @@
     </row>
     <row r="63" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>90.625</v>
+        <v>92.1875</v>
       </c>
       <c r="B63">
-        <v>0.11856999999999999</v>
+        <v>0.12096</v>
       </c>
       <c r="C63">
         <v>90.625</v>
@@ -8787,7 +8787,7 @@
         <v>90.625</v>
       </c>
       <c r="L63">
-        <v>0.12429999999999999</v>
+        <v>0.1245</v>
       </c>
       <c r="M63">
         <v>90.625</v>
@@ -8829,7 +8829,7 @@
         <v>90.625</v>
       </c>
       <c r="Z63">
-        <v>0.12432</v>
+        <v>0.12429999999999999</v>
       </c>
       <c r="AA63">
         <v>90.625</v>
@@ -8841,7 +8841,7 @@
         <v>90.625</v>
       </c>
       <c r="AD63">
-        <v>0.12429999999999999</v>
+        <v>0.12431</v>
       </c>
       <c r="AE63">
         <v>90.625</v>
@@ -8877,7 +8877,7 @@
         <v>90.625</v>
       </c>
       <c r="AP63">
-        <v>0.12429999999999999</v>
+        <v>0.12432</v>
       </c>
       <c r="AQ63">
         <v>90.625</v>
@@ -8894,10 +8894,10 @@
     </row>
     <row r="64" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>92.1875</v>
+        <v>93.75</v>
       </c>
       <c r="B64">
-        <v>0.12064</v>
+        <v>0.12302</v>
       </c>
       <c r="C64">
         <v>92.1875</v>
@@ -8951,7 +8951,7 @@
         <v>92.1875</v>
       </c>
       <c r="T64">
-        <v>0.12653</v>
+        <v>0.12633</v>
       </c>
       <c r="U64">
         <v>92.1875</v>
@@ -8969,7 +8969,7 @@
         <v>92.1875</v>
       </c>
       <c r="Z64">
-        <v>0.12653</v>
+        <v>0.12651999999999999</v>
       </c>
       <c r="AA64">
         <v>92.1875</v>
@@ -8999,7 +8999,7 @@
         <v>92.1875</v>
       </c>
       <c r="AJ64">
-        <v>0.12653</v>
+        <v>0.12655</v>
       </c>
       <c r="AK64">
         <v>92.1875</v>
@@ -9034,10 +9034,10 @@
     </row>
     <row r="65" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>93.75</v>
+        <v>95.3125</v>
       </c>
       <c r="B65">
-        <v>0.12272</v>
+        <v>0.12509000000000001</v>
       </c>
       <c r="C65">
         <v>93.75</v>
@@ -9091,7 +9091,7 @@
         <v>93.75</v>
       </c>
       <c r="T65">
-        <v>0.12873000000000001</v>
+        <v>0.12862999999999999</v>
       </c>
       <c r="U65">
         <v>93.75</v>
@@ -9109,7 +9109,7 @@
         <v>93.75</v>
       </c>
       <c r="Z65">
-        <v>0.12873000000000001</v>
+        <v>0.12872</v>
       </c>
       <c r="AA65">
         <v>93.75</v>
@@ -9121,7 +9121,7 @@
         <v>93.75</v>
       </c>
       <c r="AD65">
-        <v>0.12873000000000001</v>
+        <v>0.12872</v>
       </c>
       <c r="AE65">
         <v>93.75</v>
@@ -9139,7 +9139,7 @@
         <v>93.75</v>
       </c>
       <c r="AJ65">
-        <v>0.12873999999999999</v>
+        <v>0.12875</v>
       </c>
       <c r="AK65">
         <v>93.75</v>
@@ -9157,7 +9157,7 @@
         <v>93.75</v>
       </c>
       <c r="AP65">
-        <v>0.12873000000000001</v>
+        <v>0.12872</v>
       </c>
       <c r="AQ65">
         <v>93.75</v>
@@ -9174,10 +9174,10 @@
     </row>
     <row r="66" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>95.3125</v>
+        <v>96.875</v>
       </c>
       <c r="B66">
-        <v>0.12479999999999999</v>
+        <v>0.12717000000000001</v>
       </c>
       <c r="C66">
         <v>95.3125</v>
@@ -9207,7 +9207,7 @@
         <v>95.3125</v>
       </c>
       <c r="L66">
-        <v>0.13095000000000001</v>
+        <v>0.13075000000000001</v>
       </c>
       <c r="M66">
         <v>95.3125</v>
@@ -9249,7 +9249,7 @@
         <v>95.3125</v>
       </c>
       <c r="Z66">
-        <v>0.13095000000000001</v>
+        <v>0.13092000000000001</v>
       </c>
       <c r="AA66">
         <v>95.3125</v>
@@ -9261,7 +9261,7 @@
         <v>95.3125</v>
       </c>
       <c r="AD66">
-        <v>0.13095000000000001</v>
+        <v>0.13094</v>
       </c>
       <c r="AE66">
         <v>95.3125</v>
@@ -9279,7 +9279,7 @@
         <v>95.3125</v>
       </c>
       <c r="AJ66">
-        <v>0.13097</v>
+        <v>0.13099</v>
       </c>
       <c r="AK66">
         <v>95.3125</v>
@@ -9297,7 +9297,7 @@
         <v>95.3125</v>
       </c>
       <c r="AP66">
-        <v>0.13095000000000001</v>
+        <v>0.13091</v>
       </c>
       <c r="AQ66">
         <v>95.3125</v>
@@ -9314,10 +9314,10 @@
     </row>
     <row r="67" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>96.875</v>
+        <v>98.4375</v>
       </c>
       <c r="B67">
-        <v>0.12687000000000001</v>
+        <v>0.12923000000000001</v>
       </c>
       <c r="C67">
         <v>96.875</v>
@@ -9389,7 +9389,7 @@
         <v>96.875</v>
       </c>
       <c r="Z67">
-        <v>0.13320000000000001</v>
+        <v>0.13321</v>
       </c>
       <c r="AA67">
         <v>96.875</v>
@@ -9401,7 +9401,7 @@
         <v>96.875</v>
       </c>
       <c r="AD67">
-        <v>0.13320000000000001</v>
+        <v>0.1331</v>
       </c>
       <c r="AE67">
         <v>96.875</v>
@@ -9454,16 +9454,16 @@
     </row>
     <row r="68" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>98.4375</v>
+        <v>100</v>
       </c>
       <c r="B68">
-        <v>0.12895999999999999</v>
+        <v>0.13102</v>
       </c>
       <c r="C68">
         <v>98.4375</v>
       </c>
       <c r="D68">
-        <v>0.13549</v>
+        <v>0.13550000000000001</v>
       </c>
       <c r="E68">
         <v>98.4375</v>
@@ -9487,7 +9487,7 @@
         <v>98.4375</v>
       </c>
       <c r="L68">
-        <v>0.13544</v>
+        <v>0.13553999999999999</v>
       </c>
       <c r="M68">
         <v>98.4375</v>
@@ -9511,7 +9511,7 @@
         <v>98.4375</v>
       </c>
       <c r="T68">
-        <v>0.13544</v>
+        <v>0.13533999999999999</v>
       </c>
       <c r="U68">
         <v>98.4375</v>
@@ -9529,7 +9529,7 @@
         <v>98.4375</v>
       </c>
       <c r="Z68">
-        <v>0.13544</v>
+        <v>0.13541</v>
       </c>
       <c r="AA68">
         <v>98.4375</v>
@@ -9541,7 +9541,7 @@
         <v>98.4375</v>
       </c>
       <c r="AD68">
-        <v>0.13544</v>
+        <v>0.13541</v>
       </c>
       <c r="AE68">
         <v>98.4375</v>
@@ -9559,7 +9559,7 @@
         <v>98.4375</v>
       </c>
       <c r="AJ68">
-        <v>0.13544</v>
+        <v>0.13542999999999999</v>
       </c>
       <c r="AK68">
         <v>98.4375</v>
@@ -9577,7 +9577,7 @@
         <v>98.4375</v>
       </c>
       <c r="AP68">
-        <v>0.13544</v>
+        <v>0.13542000000000001</v>
       </c>
       <c r="AQ68">
         <v>98.4375</v>
@@ -9594,16 +9594,16 @@
     </row>
     <row r="69" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>100</v>
+        <v>98.4375</v>
       </c>
       <c r="B69">
-        <v>0.13102</v>
+        <v>0.12895999999999999</v>
       </c>
       <c r="C69">
         <v>100</v>
       </c>
       <c r="D69">
-        <v>0.13744999999999999</v>
+        <v>0.13744000000000001</v>
       </c>
       <c r="E69">
         <v>100</v>
@@ -9627,7 +9627,7 @@
         <v>100</v>
       </c>
       <c r="L69">
-        <v>0.13739999999999999</v>
+        <v>0.13741999999999999</v>
       </c>
       <c r="M69">
         <v>100</v>
@@ -9651,7 +9651,7 @@
         <v>100</v>
       </c>
       <c r="T69">
-        <v>0.13739999999999999</v>
+        <v>0.13719999999999999</v>
       </c>
       <c r="U69">
         <v>100</v>
@@ -9669,7 +9669,7 @@
         <v>100</v>
       </c>
       <c r="Z69">
-        <v>0.13739999999999999</v>
+        <v>0.13738</v>
       </c>
       <c r="AA69">
         <v>100</v>
@@ -9681,7 +9681,7 @@
         <v>100</v>
       </c>
       <c r="AD69">
-        <v>0.13739999999999999</v>
+        <v>0.13741</v>
       </c>
       <c r="AE69">
         <v>100</v>
@@ -9693,13 +9693,13 @@
         <v>100</v>
       </c>
       <c r="AH69">
-        <v>0.13744999999999999</v>
+        <v>0.13744000000000001</v>
       </c>
       <c r="AI69">
         <v>100</v>
       </c>
       <c r="AJ69">
-        <v>0.13743</v>
+        <v>0.13744000000000001</v>
       </c>
       <c r="AK69">
         <v>100</v>
@@ -9717,7 +9717,7 @@
         <v>100</v>
       </c>
       <c r="AP69">
-        <v>0.13739999999999999</v>
+        <v>0.13741999999999999</v>
       </c>
       <c r="AQ69">
         <v>100</v>
@@ -9734,10 +9734,10 @@
     </row>
     <row r="70" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>98.4375</v>
+        <v>96.875</v>
       </c>
       <c r="B70">
-        <v>0.12923000000000001</v>
+        <v>0.12687000000000001</v>
       </c>
       <c r="C70">
         <v>98.4375</v>
@@ -9767,7 +9767,7 @@
         <v>98.4375</v>
       </c>
       <c r="L70">
-        <v>0.13525000000000001</v>
+        <v>0.13544999999999999</v>
       </c>
       <c r="M70">
         <v>98.4375</v>
@@ -9791,7 +9791,7 @@
         <v>98.4375</v>
       </c>
       <c r="T70">
-        <v>0.13525000000000001</v>
+        <v>0.13535</v>
       </c>
       <c r="U70">
         <v>98.4375</v>
@@ -9809,7 +9809,7 @@
         <v>98.4375</v>
       </c>
       <c r="Z70">
-        <v>0.13525000000000001</v>
+        <v>0.13524</v>
       </c>
       <c r="AA70">
         <v>98.4375</v>
@@ -9821,7 +9821,7 @@
         <v>98.4375</v>
       </c>
       <c r="AD70">
-        <v>0.13525000000000001</v>
+        <v>0.13524</v>
       </c>
       <c r="AE70">
         <v>98.4375</v>
@@ -9833,13 +9833,13 @@
         <v>98.4375</v>
       </c>
       <c r="AH70">
-        <v>0.13532</v>
+        <v>0.13531000000000001</v>
       </c>
       <c r="AI70">
         <v>98.4375</v>
       </c>
       <c r="AJ70">
-        <v>0.13528000000000001</v>
+        <v>0.13528999999999999</v>
       </c>
       <c r="AK70">
         <v>98.4375</v>
@@ -9857,7 +9857,7 @@
         <v>98.4375</v>
       </c>
       <c r="AP70">
-        <v>0.13525000000000001</v>
+        <v>0.13525999999999999</v>
       </c>
       <c r="AQ70">
         <v>98.4375</v>
@@ -9874,10 +9874,10 @@
     </row>
     <row r="71" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>96.875</v>
+        <v>95.3125</v>
       </c>
       <c r="B71">
-        <v>0.12717000000000001</v>
+        <v>0.12479999999999999</v>
       </c>
       <c r="C71">
         <v>96.875</v>
@@ -9931,7 +9931,7 @@
         <v>96.875</v>
       </c>
       <c r="T71">
-        <v>0.13303999999999999</v>
+        <v>0.13294</v>
       </c>
       <c r="U71">
         <v>96.875</v>
@@ -9949,7 +9949,7 @@
         <v>96.875</v>
       </c>
       <c r="Z71">
-        <v>0.13303999999999999</v>
+        <v>0.13303000000000001</v>
       </c>
       <c r="AA71">
         <v>96.875</v>
@@ -9961,7 +9961,7 @@
         <v>96.875</v>
       </c>
       <c r="AD71">
-        <v>0.13303999999999999</v>
+        <v>0.13302</v>
       </c>
       <c r="AE71">
         <v>96.875</v>
@@ -9973,13 +9973,13 @@
         <v>96.875</v>
       </c>
       <c r="AH71">
-        <v>0.13309000000000001</v>
+        <v>0.1331</v>
       </c>
       <c r="AI71">
         <v>96.875</v>
       </c>
       <c r="AJ71">
-        <v>0.13305</v>
+        <v>0.13306000000000001</v>
       </c>
       <c r="AK71">
         <v>96.875</v>
@@ -10014,16 +10014,16 @@
     </row>
     <row r="72" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>95.3125</v>
+        <v>93.75</v>
       </c>
       <c r="B72">
-        <v>0.12509000000000001</v>
+        <v>0.12272</v>
       </c>
       <c r="C72">
         <v>95.3125</v>
       </c>
       <c r="D72">
-        <v>0.13086</v>
+        <v>0.13084000000000001</v>
       </c>
       <c r="E72">
         <v>95.3125</v>
@@ -10047,7 +10047,7 @@
         <v>95.3125</v>
       </c>
       <c r="L72">
-        <v>0.13081000000000001</v>
+        <v>0.13100999999999999</v>
       </c>
       <c r="M72">
         <v>95.3125</v>
@@ -10071,7 +10071,7 @@
         <v>95.3125</v>
       </c>
       <c r="T72">
-        <v>0.13081000000000001</v>
+        <v>0.13100999999999999</v>
       </c>
       <c r="U72">
         <v>95.3125</v>
@@ -10089,7 +10089,7 @@
         <v>95.3125</v>
       </c>
       <c r="Z72">
-        <v>0.13081000000000001</v>
+        <v>0.13081999999999999</v>
       </c>
       <c r="AA72">
         <v>95.3125</v>
@@ -10101,7 +10101,7 @@
         <v>95.3125</v>
       </c>
       <c r="AD72">
-        <v>0.13081000000000001</v>
+        <v>0.13081999999999999</v>
       </c>
       <c r="AE72">
         <v>95.3125</v>
@@ -10137,7 +10137,7 @@
         <v>95.3125</v>
       </c>
       <c r="AP72">
-        <v>0.13081000000000001</v>
+        <v>0.13084000000000001</v>
       </c>
       <c r="AQ72">
         <v>95.3125</v>
@@ -10154,16 +10154,16 @@
     </row>
     <row r="73" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>93.75</v>
+        <v>92.1875</v>
       </c>
       <c r="B73">
-        <v>0.12302</v>
+        <v>0.12064</v>
       </c>
       <c r="C73">
         <v>93.75</v>
       </c>
       <c r="D73">
-        <v>0.12862999999999999</v>
+        <v>0.12862000000000001</v>
       </c>
       <c r="E73">
         <v>93.75</v>
@@ -10187,7 +10187,7 @@
         <v>93.75</v>
       </c>
       <c r="L73">
-        <v>0.12858</v>
+        <v>0.12848000000000001</v>
       </c>
       <c r="M73">
         <v>93.75</v>
@@ -10241,7 +10241,7 @@
         <v>93.75</v>
       </c>
       <c r="AD73">
-        <v>0.12858</v>
+        <v>0.12859999999999999</v>
       </c>
       <c r="AE73">
         <v>93.75</v>
@@ -10277,7 +10277,7 @@
         <v>93.75</v>
       </c>
       <c r="AP73">
-        <v>0.12858</v>
+        <v>0.12853999999999999</v>
       </c>
       <c r="AQ73">
         <v>93.75</v>
@@ -10294,16 +10294,16 @@
     </row>
     <row r="74" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>92.1875</v>
+        <v>90.625</v>
       </c>
       <c r="B74">
-        <v>0.12096</v>
+        <v>0.11856999999999999</v>
       </c>
       <c r="C74">
         <v>92.1875</v>
       </c>
       <c r="D74">
-        <v>0.12640000000000001</v>
+        <v>0.12640999999999999</v>
       </c>
       <c r="E74">
         <v>92.1875</v>
@@ -10351,7 +10351,7 @@
         <v>92.1875</v>
       </c>
       <c r="T74">
-        <v>0.12634999999999999</v>
+        <v>0.12655</v>
       </c>
       <c r="U74">
         <v>92.1875</v>
@@ -10381,7 +10381,7 @@
         <v>92.1875</v>
       </c>
       <c r="AD74">
-        <v>0.12634999999999999</v>
+        <v>0.12640000000000001</v>
       </c>
       <c r="AE74">
         <v>92.1875</v>
@@ -10399,7 +10399,7 @@
         <v>92.1875</v>
       </c>
       <c r="AJ74">
-        <v>0.12637999999999999</v>
+        <v>0.12634999999999999</v>
       </c>
       <c r="AK74">
         <v>92.1875</v>
@@ -10417,7 +10417,7 @@
         <v>92.1875</v>
       </c>
       <c r="AP74">
-        <v>0.12634999999999999</v>
+        <v>0.12631999999999999</v>
       </c>
       <c r="AQ74">
         <v>92.1875</v>
@@ -10434,16 +10434,16 @@
     </row>
     <row r="75" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>90.625</v>
+        <v>89.0625</v>
       </c>
       <c r="B75">
-        <v>0.11888</v>
+        <v>0.11651</v>
       </c>
       <c r="C75">
         <v>90.625</v>
       </c>
       <c r="D75">
-        <v>0.12417</v>
+        <v>0.12418</v>
       </c>
       <c r="E75">
         <v>90.625</v>
@@ -10467,7 +10467,7 @@
         <v>90.625</v>
       </c>
       <c r="L75">
-        <v>0.12411999999999999</v>
+        <v>0.12432</v>
       </c>
       <c r="M75">
         <v>90.625</v>
@@ -10491,7 +10491,7 @@
         <v>90.625</v>
       </c>
       <c r="T75">
-        <v>0.12411999999999999</v>
+        <v>0.12422</v>
       </c>
       <c r="U75">
         <v>90.625</v>
@@ -10509,7 +10509,7 @@
         <v>90.625</v>
       </c>
       <c r="Z75">
-        <v>0.12411999999999999</v>
+        <v>0.12415</v>
       </c>
       <c r="AA75">
         <v>90.625</v>
@@ -10521,7 +10521,7 @@
         <v>90.625</v>
       </c>
       <c r="AD75">
-        <v>0.12411999999999999</v>
+        <v>0.12411</v>
       </c>
       <c r="AE75">
         <v>90.625</v>
@@ -10557,7 +10557,7 @@
         <v>90.625</v>
       </c>
       <c r="AP75">
-        <v>0.12411999999999999</v>
+        <v>0.12413</v>
       </c>
       <c r="AQ75">
         <v>90.625</v>
@@ -10574,10 +10574,10 @@
     </row>
     <row r="76" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>89.0625</v>
+        <v>87.5</v>
       </c>
       <c r="B76">
-        <v>0.1168</v>
+        <v>0.11443</v>
       </c>
       <c r="C76">
         <v>89.0625</v>
@@ -10631,7 +10631,7 @@
         <v>89.0625</v>
       </c>
       <c r="T76">
-        <v>0.12192</v>
+        <v>0.12202</v>
       </c>
       <c r="U76">
         <v>89.0625</v>
@@ -10661,7 +10661,7 @@
         <v>89.0625</v>
       </c>
       <c r="AD76">
-        <v>0.12191</v>
+        <v>0.12189999999999999</v>
       </c>
       <c r="AE76">
         <v>89.0625</v>
@@ -10697,7 +10697,7 @@
         <v>89.0625</v>
       </c>
       <c r="AP76">
-        <v>0.12191</v>
+        <v>0.12192</v>
       </c>
       <c r="AQ76">
         <v>89.0625</v>
@@ -10714,10 +10714,10 @@
     </row>
     <row r="77" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>87.5</v>
+        <v>85.9375</v>
       </c>
       <c r="B77">
-        <v>0.11473999999999999</v>
+        <v>0.11237</v>
       </c>
       <c r="C77">
         <v>87.5</v>
@@ -10747,7 +10747,7 @@
         <v>87.5</v>
       </c>
       <c r="L77" s="1">
-        <v>0.11967999999999999</v>
+        <v>0.11958000000000001</v>
       </c>
       <c r="M77">
         <v>87.5</v>
@@ -10771,7 +10771,7 @@
         <v>87.5</v>
       </c>
       <c r="T77" s="1">
-        <v>0.11967999999999999</v>
+        <v>0.11978</v>
       </c>
       <c r="U77">
         <v>87.5</v>
@@ -10789,7 +10789,7 @@
         <v>87.5</v>
       </c>
       <c r="Z77">
-        <v>0.11967999999999999</v>
+        <v>0.11967</v>
       </c>
       <c r="AA77">
         <v>87.5</v>
@@ -10801,7 +10801,7 @@
         <v>87.5</v>
       </c>
       <c r="AD77">
-        <v>0.11967999999999999</v>
+        <v>0.11967</v>
       </c>
       <c r="AE77">
         <v>87.5</v>
@@ -10819,7 +10819,7 @@
         <v>87.5</v>
       </c>
       <c r="AJ77">
-        <v>0.11971</v>
+        <v>0.11973</v>
       </c>
       <c r="AK77">
         <v>87.5</v>
@@ -10837,7 +10837,7 @@
         <v>87.5</v>
       </c>
       <c r="AP77">
-        <v>0.11967999999999999</v>
+        <v>0.11965000000000001</v>
       </c>
       <c r="AQ77">
         <v>87.5</v>
@@ -10854,16 +10854,16 @@
     </row>
     <row r="78" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>85.9375</v>
+        <v>84.375</v>
       </c>
       <c r="B78">
-        <v>0.11265</v>
+        <v>0.1103</v>
       </c>
       <c r="C78">
         <v>85.9375</v>
       </c>
       <c r="D78" s="1">
-        <v>0.11753</v>
+        <v>0.11752</v>
       </c>
       <c r="E78">
         <v>85.9375</v>
@@ -10887,7 +10887,7 @@
         <v>85.9375</v>
       </c>
       <c r="L78" s="1">
-        <v>0.11748</v>
+        <v>0.11768000000000001</v>
       </c>
       <c r="M78">
         <v>85.9375</v>
@@ -10911,7 +10911,7 @@
         <v>85.9375</v>
       </c>
       <c r="T78" s="1">
-        <v>0.11748</v>
+        <v>0.11768000000000001</v>
       </c>
       <c r="U78">
         <v>85.9375</v>
@@ -10941,7 +10941,7 @@
         <v>85.9375</v>
       </c>
       <c r="AD78">
-        <v>0.11748</v>
+        <v>0.11749</v>
       </c>
       <c r="AE78">
         <v>85.9375</v>
@@ -10959,7 +10959,7 @@
         <v>85.9375</v>
       </c>
       <c r="AJ78">
-        <v>0.11749999999999999</v>
+        <v>0.1176</v>
       </c>
       <c r="AK78">
         <v>85.9375</v>
@@ -10977,7 +10977,7 @@
         <v>85.9375</v>
       </c>
       <c r="AP78">
-        <v>0.11748</v>
+        <v>0.11747</v>
       </c>
       <c r="AQ78">
         <v>85.9375</v>
@@ -10994,16 +10994,16 @@
     </row>
     <row r="79" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>84.375</v>
+        <v>82.8125</v>
       </c>
       <c r="B79">
-        <v>0.11058</v>
+        <v>0.10825</v>
       </c>
       <c r="C79">
         <v>84.375</v>
       </c>
       <c r="D79" s="1">
-        <v>0.11533</v>
+        <v>0.11534</v>
       </c>
       <c r="E79">
         <v>84.375</v>
@@ -11027,7 +11027,7 @@
         <v>84.375</v>
       </c>
       <c r="L79" s="1">
-        <v>0.11527</v>
+        <v>0.11507000000000001</v>
       </c>
       <c r="M79">
         <v>84.375</v>
@@ -11051,7 +11051,7 @@
         <v>84.375</v>
       </c>
       <c r="T79" s="1">
-        <v>0.11527</v>
+        <v>0.11537</v>
       </c>
       <c r="U79">
         <v>84.375</v>
@@ -11069,7 +11069,7 @@
         <v>84.375</v>
       </c>
       <c r="Z79" s="1">
-        <v>0.11527</v>
+        <v>0.11527999999999999</v>
       </c>
       <c r="AA79">
         <v>84.375</v>
@@ -11093,7 +11093,7 @@
         <v>84.375</v>
       </c>
       <c r="AH79">
-        <v>0.11533</v>
+        <v>0.11532000000000001</v>
       </c>
       <c r="AI79">
         <v>84.375</v>
@@ -11117,7 +11117,7 @@
         <v>84.375</v>
       </c>
       <c r="AP79">
-        <v>0.11527</v>
+        <v>0.11525000000000001</v>
       </c>
       <c r="AQ79">
         <v>84.375</v>
@@ -11134,10 +11134,10 @@
     </row>
     <row r="80" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>82.8125</v>
+        <v>81.25</v>
       </c>
       <c r="B80">
-        <v>0.1085</v>
+        <v>0.10619000000000001</v>
       </c>
       <c r="C80">
         <v>82.8125</v>
@@ -11167,7 +11167,7 @@
         <v>82.8125</v>
       </c>
       <c r="L80">
-        <v>0.11309</v>
+        <v>0.11289</v>
       </c>
       <c r="M80">
         <v>82.8125</v>
@@ -11191,7 +11191,7 @@
         <v>82.8125</v>
       </c>
       <c r="T80" s="1">
-        <v>0.11309</v>
+        <v>0.11298999999999999</v>
       </c>
       <c r="U80">
         <v>82.8125</v>
@@ -11221,7 +11221,7 @@
         <v>82.8125</v>
       </c>
       <c r="AD80" s="1">
-        <v>0.11309</v>
+        <v>0.11308</v>
       </c>
       <c r="AE80">
         <v>82.8125</v>
@@ -11274,10 +11274,10 @@
     </row>
     <row r="81" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>81.25</v>
+        <v>79.6875</v>
       </c>
       <c r="B81">
-        <v>0.10644000000000001</v>
+        <v>0.10415000000000001</v>
       </c>
       <c r="C81">
         <v>81.25</v>
@@ -11307,7 +11307,7 @@
         <v>81.25</v>
       </c>
       <c r="L81" s="1">
-        <v>0.11090999999999999</v>
+        <v>0.11071</v>
       </c>
       <c r="M81">
         <v>81.25</v>
@@ -11361,7 +11361,7 @@
         <v>81.25</v>
       </c>
       <c r="AD81">
-        <v>0.11090999999999999</v>
+        <v>0.11092</v>
       </c>
       <c r="AE81">
         <v>81.25</v>
@@ -11397,7 +11397,7 @@
         <v>81.25</v>
       </c>
       <c r="AP81">
-        <v>0.11090999999999999</v>
+        <v>0.1109</v>
       </c>
       <c r="AQ81">
         <v>81.25</v>
@@ -11414,10 +11414,10 @@
     </row>
     <row r="82" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>79.6875</v>
+        <v>78.125</v>
       </c>
       <c r="B82">
-        <v>0.10437</v>
+        <v>0.10208</v>
       </c>
       <c r="C82">
         <v>79.6875</v>
@@ -11447,7 +11447,7 @@
         <v>79.6875</v>
       </c>
       <c r="L82" s="1">
-        <v>0.10871</v>
+        <v>0.10891000000000001</v>
       </c>
       <c r="M82">
         <v>79.6875</v>
@@ -11471,7 +11471,7 @@
         <v>79.6875</v>
       </c>
       <c r="T82" s="1">
-        <v>0.10871</v>
+        <v>0.10861</v>
       </c>
       <c r="U82">
         <v>79.6875</v>
@@ -11501,7 +11501,7 @@
         <v>79.6875</v>
       </c>
       <c r="AD82">
-        <v>0.10871</v>
+        <v>0.10872</v>
       </c>
       <c r="AE82">
         <v>79.6875</v>
@@ -11519,7 +11519,7 @@
         <v>79.6875</v>
       </c>
       <c r="AJ82">
-        <v>0.10876</v>
+        <v>0.10877000000000001</v>
       </c>
       <c r="AK82">
         <v>79.6875</v>
@@ -11537,7 +11537,7 @@
         <v>79.6875</v>
       </c>
       <c r="AP82">
-        <v>0.10871</v>
+        <v>0.1087</v>
       </c>
       <c r="AQ82">
         <v>79.6875</v>
@@ -11554,10 +11554,10 @@
     </row>
     <row r="83" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>78.125</v>
+        <v>76.5625</v>
       </c>
       <c r="B83">
-        <v>0.10231</v>
+        <v>0.10004</v>
       </c>
       <c r="C83">
         <v>78.125</v>
@@ -11587,7 +11587,7 @@
         <v>78.125</v>
       </c>
       <c r="L83" s="1">
-        <v>0.10653</v>
+        <v>0.10673000000000001</v>
       </c>
       <c r="M83">
         <v>78.125</v>
@@ -11611,7 +11611,7 @@
         <v>78.125</v>
       </c>
       <c r="T83" s="1">
-        <v>0.10653</v>
+        <v>0.10663</v>
       </c>
       <c r="U83">
         <v>78.125</v>
@@ -11629,7 +11629,7 @@
         <v>78.125</v>
       </c>
       <c r="Z83">
-        <v>0.10653</v>
+        <v>0.10655000000000001</v>
       </c>
       <c r="AA83">
         <v>78.125</v>
@@ -11641,7 +11641,7 @@
         <v>78.125</v>
       </c>
       <c r="AD83">
-        <v>0.10653</v>
+        <v>0.10650999999999999</v>
       </c>
       <c r="AE83">
         <v>78.125</v>
@@ -11677,7 +11677,7 @@
         <v>78.125</v>
       </c>
       <c r="AP83">
-        <v>0.10653</v>
+        <v>0.10652</v>
       </c>
       <c r="AQ83">
         <v>78.125</v>
@@ -11694,10 +11694,10 @@
     </row>
     <row r="84" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>76.5625</v>
+        <v>75</v>
       </c>
       <c r="B84">
-        <v>0.10024</v>
+        <v>9.7979999999999998E-2</v>
       </c>
       <c r="C84">
         <v>76.5625</v>
@@ -11751,7 +11751,7 @@
         <v>76.5625</v>
       </c>
       <c r="T84" s="1">
-        <v>0.10437</v>
+        <v>0.10427</v>
       </c>
       <c r="U84">
         <v>76.5625</v>
@@ -11769,7 +11769,7 @@
         <v>76.5625</v>
       </c>
       <c r="Z84">
-        <v>0.10437</v>
+        <v>0.10440000000000001</v>
       </c>
       <c r="AA84">
         <v>76.5625</v>
@@ -11781,7 +11781,7 @@
         <v>76.5625</v>
       </c>
       <c r="AD84">
-        <v>0.10435</v>
+        <v>0.10432</v>
       </c>
       <c r="AE84">
         <v>76.5625</v>
@@ -11817,7 +11817,7 @@
         <v>76.5625</v>
       </c>
       <c r="AP84">
-        <v>0.10435</v>
+        <v>0.10435999999999999</v>
       </c>
       <c r="AQ84">
         <v>76.5625</v>
@@ -11834,10 +11834,10 @@
     </row>
     <row r="85" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>75</v>
+        <v>73.4375</v>
       </c>
       <c r="B85">
-        <v>9.819E-2</v>
+        <v>9.5930000000000001E-2</v>
       </c>
       <c r="C85">
         <v>75</v>
@@ -11891,7 +11891,7 @@
         <v>75</v>
       </c>
       <c r="T85" s="1">
-        <v>0.1022</v>
+        <v>0.1024</v>
       </c>
       <c r="U85">
         <v>75</v>
@@ -11921,7 +11921,7 @@
         <v>75</v>
       </c>
       <c r="AD85">
-        <v>0.1022</v>
+        <v>0.1024</v>
       </c>
       <c r="AE85">
         <v>75</v>
@@ -11957,7 +11957,7 @@
         <v>75</v>
       </c>
       <c r="AP85">
-        <v>0.1022</v>
+        <v>0.1023</v>
       </c>
       <c r="AQ85">
         <v>75</v>
@@ -11974,10 +11974,10 @@
     </row>
     <row r="86" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>73.4375</v>
+        <v>71.875</v>
       </c>
       <c r="B86">
-        <v>9.6129999999999993E-2</v>
+        <v>9.3869999999999995E-2</v>
       </c>
       <c r="C86">
         <v>73.4375</v>
@@ -12007,7 +12007,7 @@
         <v>73.4375</v>
       </c>
       <c r="L86" s="1">
-        <v>0.10002</v>
+        <v>0.10012</v>
       </c>
       <c r="M86">
         <v>73.4375</v>
@@ -12031,7 +12031,7 @@
         <v>73.4375</v>
       </c>
       <c r="T86" s="1">
-        <v>0.10004</v>
+        <v>0.10014000000000001</v>
       </c>
       <c r="U86">
         <v>73.4375</v>
@@ -12049,7 +12049,7 @@
         <v>73.4375</v>
       </c>
       <c r="Z86">
-        <v>0.10004</v>
+        <v>0.10001</v>
       </c>
       <c r="AA86">
         <v>73.4375</v>
@@ -12061,7 +12061,7 @@
         <v>73.4375</v>
       </c>
       <c r="AD86">
-        <v>0.10002</v>
+        <v>0.10001</v>
       </c>
       <c r="AE86">
         <v>73.4375</v>
@@ -12079,7 +12079,7 @@
         <v>73.4375</v>
       </c>
       <c r="AJ86">
-        <v>0.10007000000000001</v>
+        <v>0.10008</v>
       </c>
       <c r="AK86">
         <v>73.4375</v>
@@ -12097,7 +12097,7 @@
         <v>73.4375</v>
       </c>
       <c r="AP86">
-        <v>0.10002</v>
+        <v>0.1</v>
       </c>
       <c r="AQ86">
         <v>73.4375</v>
@@ -12114,10 +12114,10 @@
     </row>
     <row r="87" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>71.875</v>
+        <v>70.3125</v>
       </c>
       <c r="B87">
-        <v>9.4079999999999997E-2</v>
+        <v>9.1829999999999995E-2</v>
       </c>
       <c r="C87">
         <v>71.875</v>
@@ -12147,7 +12147,7 @@
         <v>71.875</v>
       </c>
       <c r="L87" s="1">
-        <v>9.7860000000000003E-2</v>
+        <v>9.7659999999999997E-2</v>
       </c>
       <c r="M87">
         <v>71.875</v>
@@ -12171,7 +12171,7 @@
         <v>71.875</v>
       </c>
       <c r="T87" s="1">
-        <v>9.7869999999999999E-2</v>
+        <v>9.7670000000000007E-2</v>
       </c>
       <c r="U87">
         <v>71.875</v>
@@ -12201,7 +12201,7 @@
         <v>71.875</v>
       </c>
       <c r="AD87">
-        <v>9.7860000000000003E-2</v>
+        <v>9.7850000000000006E-2</v>
       </c>
       <c r="AE87">
         <v>71.875</v>
@@ -12237,7 +12237,7 @@
         <v>71.875</v>
       </c>
       <c r="AP87">
-        <v>9.7860000000000003E-2</v>
+        <v>9.7900000000000001E-2</v>
       </c>
       <c r="AQ87">
         <v>71.875</v>
@@ -12254,10 +12254,10 @@
     </row>
     <row r="88" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>70.3125</v>
+        <v>68.75</v>
       </c>
       <c r="B88">
-        <v>9.2020000000000005E-2</v>
+        <v>8.9779999999999999E-2</v>
       </c>
       <c r="C88">
         <v>70.3125</v>
@@ -12287,7 +12287,7 @@
         <v>70.3125</v>
       </c>
       <c r="L88">
-        <v>9.5710000000000003E-2</v>
+        <v>9.5509999999999998E-2</v>
       </c>
       <c r="M88">
         <v>70.3125</v>
@@ -12311,7 +12311,7 @@
         <v>70.3125</v>
       </c>
       <c r="T88" s="1">
-        <v>9.5710000000000003E-2</v>
+        <v>9.5810000000000006E-2</v>
       </c>
       <c r="U88">
         <v>70.3125</v>
@@ -12329,7 +12329,7 @@
         <v>70.3125</v>
       </c>
       <c r="Z88">
-        <v>9.5710000000000003E-2</v>
+        <v>9.5699999999999993E-2</v>
       </c>
       <c r="AA88">
         <v>70.3125</v>
@@ -12341,7 +12341,7 @@
         <v>70.3125</v>
       </c>
       <c r="AD88">
-        <v>9.5710000000000003E-2</v>
+        <v>9.5699999999999993E-2</v>
       </c>
       <c r="AE88">
         <v>70.3125</v>
@@ -12397,7 +12397,7 @@
         <v>67.1875</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>8.7730000000000002E-2</v>
       </c>
       <c r="C89">
         <v>68.75</v>
@@ -12427,7 +12427,7 @@
         <v>68.75</v>
       </c>
       <c r="L89">
-        <v>9.3560000000000004E-2</v>
+        <v>9.3759999999999996E-2</v>
       </c>
       <c r="M89">
         <v>68.75</v>
@@ -12451,7 +12451,7 @@
         <v>68.75</v>
       </c>
       <c r="T89" s="1">
-        <v>9.3560000000000004E-2</v>
+        <v>9.3359999999999999E-2</v>
       </c>
       <c r="U89">
         <v>68.75</v>
@@ -12469,7 +12469,7 @@
         <v>68.75</v>
       </c>
       <c r="Z89" s="1">
-        <v>9.3560000000000004E-2</v>
+        <v>9.3549999999999994E-2</v>
       </c>
       <c r="AA89">
         <v>68.75</v>
@@ -12481,7 +12481,7 @@
         <v>68.75</v>
       </c>
       <c r="AD89">
-        <v>9.3560000000000004E-2</v>
+        <v>9.3579999999999997E-2</v>
       </c>
       <c r="AE89">
         <v>68.75</v>
@@ -12517,7 +12517,7 @@
         <v>68.75</v>
       </c>
       <c r="AP89">
-        <v>9.3560000000000004E-2</v>
+        <v>9.357E-2</v>
       </c>
       <c r="AQ89">
         <v>68.75</v>
@@ -12537,7 +12537,7 @@
         <v>65.625</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>8.5669999999999996E-2</v>
       </c>
       <c r="C90">
         <v>67.1875</v>
@@ -12567,7 +12567,7 @@
         <v>67.1875</v>
       </c>
       <c r="L90">
-        <v>9.1410000000000005E-2</v>
+        <v>9.1509999999999994E-2</v>
       </c>
       <c r="M90">
         <v>67.1875</v>
@@ -12609,7 +12609,7 @@
         <v>67.1875</v>
       </c>
       <c r="Z90" s="1">
-        <v>9.1410000000000005E-2</v>
+        <v>9.1399999999999995E-2</v>
       </c>
       <c r="AA90">
         <v>67.1875</v>
@@ -12621,7 +12621,7 @@
         <v>67.1875</v>
       </c>
       <c r="AD90" s="1">
-        <v>9.1410000000000005E-2</v>
+        <v>9.1420000000000001E-2</v>
       </c>
       <c r="AE90">
         <v>67.1875</v>
@@ -12639,7 +12639,7 @@
         <v>67.1875</v>
       </c>
       <c r="AJ90">
-        <v>9.1429999999999997E-2</v>
+        <v>9.146E-2</v>
       </c>
       <c r="AK90">
         <v>67.1875</v>
@@ -12657,7 +12657,7 @@
         <v>67.1875</v>
       </c>
       <c r="AP90">
-        <v>9.1410000000000005E-2</v>
+        <v>9.1450000000000004E-2</v>
       </c>
       <c r="AQ90">
         <v>67.1875</v>
@@ -12677,7 +12677,7 @@
         <v>64.0625</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>8.362E-2</v>
       </c>
       <c r="C91">
         <v>65.625</v>
@@ -12707,7 +12707,7 @@
         <v>65.625</v>
       </c>
       <c r="L91">
-        <v>8.9249999999999996E-2</v>
+        <v>8.9149999999999993E-2</v>
       </c>
       <c r="M91">
         <v>65.625</v>
@@ -12749,7 +12749,7 @@
         <v>65.625</v>
       </c>
       <c r="Z91" s="1">
-        <v>8.9260000000000006E-2</v>
+        <v>8.9289999999999994E-2</v>
       </c>
       <c r="AA91">
         <v>65.625</v>
@@ -12797,7 +12797,7 @@
         <v>65.625</v>
       </c>
       <c r="AP91">
-        <v>8.9249999999999996E-2</v>
+        <v>8.924E-2</v>
       </c>
       <c r="AQ91">
         <v>65.625</v>
@@ -12817,7 +12817,7 @@
         <v>62.5</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>8.1570000000000004E-2</v>
       </c>
       <c r="C92">
         <v>64.0625</v>
@@ -12847,7 +12847,7 @@
         <v>64.0625</v>
       </c>
       <c r="L92">
-        <v>8.7099999999999997E-2</v>
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="M92">
         <v>64.0625</v>
@@ -12871,7 +12871,7 @@
         <v>64.0625</v>
       </c>
       <c r="T92">
-        <v>8.7099999999999997E-2</v>
+        <v>8.7300000000000003E-2</v>
       </c>
       <c r="U92">
         <v>64.0625</v>
@@ -12901,7 +12901,7 @@
         <v>64.0625</v>
       </c>
       <c r="AD92">
-        <v>8.7099999999999997E-2</v>
+        <v>8.72E-2</v>
       </c>
       <c r="AE92">
         <v>64.0625</v>
@@ -12957,7 +12957,7 @@
         <v>60.9375</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>7.9519999999999993E-2</v>
       </c>
       <c r="C93">
         <v>62.5</v>
@@ -13011,7 +13011,7 @@
         <v>62.5</v>
       </c>
       <c r="T93" s="1">
-        <v>8.4949999999999998E-2</v>
+        <v>8.4750000000000006E-2</v>
       </c>
       <c r="U93">
         <v>62.5</v>
@@ -13041,7 +13041,7 @@
         <v>62.5</v>
       </c>
       <c r="AD93">
-        <v>8.4949999999999998E-2</v>
+        <v>8.4959999999999994E-2</v>
       </c>
       <c r="AE93">
         <v>62.5</v>
@@ -13077,7 +13077,7 @@
         <v>62.5</v>
       </c>
       <c r="AP93">
-        <v>8.4949999999999998E-2</v>
+        <v>8.4900000000000003E-2</v>
       </c>
       <c r="AQ93">
         <v>62.5</v>
@@ -13097,7 +13097,7 @@
         <v>59.375</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>7.7469999999999997E-2</v>
       </c>
       <c r="C94">
         <v>60.9375</v>
@@ -13127,7 +13127,7 @@
         <v>60.9375</v>
       </c>
       <c r="L94">
-        <v>8.2799999999999999E-2</v>
+        <v>8.2699999999999996E-2</v>
       </c>
       <c r="M94">
         <v>60.9375</v>
@@ -13151,7 +13151,7 @@
         <v>60.9375</v>
       </c>
       <c r="T94" s="1">
-        <v>8.2799999999999999E-2</v>
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="U94">
         <v>60.9375</v>
@@ -13169,7 +13169,7 @@
         <v>60.9375</v>
       </c>
       <c r="Z94">
-        <v>8.2799999999999999E-2</v>
+        <v>8.2790000000000002E-2</v>
       </c>
       <c r="AA94">
         <v>60.9375</v>
@@ -13181,7 +13181,7 @@
         <v>60.9375</v>
       </c>
       <c r="AD94">
-        <v>8.2799999999999999E-2</v>
+        <v>8.2809999999999995E-2</v>
       </c>
       <c r="AE94">
         <v>60.9375</v>
@@ -13217,7 +13217,7 @@
         <v>60.9375</v>
       </c>
       <c r="AP94">
-        <v>8.2799999999999999E-2</v>
+        <v>8.2820000000000005E-2</v>
       </c>
       <c r="AQ94">
         <v>60.9375</v>
@@ -13237,7 +13237,7 @@
         <v>57.8125</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>7.5439999999999993E-2</v>
       </c>
       <c r="C95">
         <v>59.375</v>
@@ -13267,7 +13267,7 @@
         <v>59.375</v>
       </c>
       <c r="L95">
-        <v>8.0649999999999999E-2</v>
+        <v>8.0449999999999994E-2</v>
       </c>
       <c r="M95">
         <v>59.375</v>
@@ -13291,7 +13291,7 @@
         <v>59.375</v>
       </c>
       <c r="T95" s="1">
-        <v>8.0670000000000006E-2</v>
+        <v>8.0869999999999997E-2</v>
       </c>
       <c r="U95">
         <v>59.375</v>
@@ -13321,7 +13321,7 @@
         <v>59.375</v>
       </c>
       <c r="AD95">
-        <v>8.0649999999999999E-2</v>
+        <v>8.0640000000000003E-2</v>
       </c>
       <c r="AE95">
         <v>59.375</v>
@@ -13333,7 +13333,7 @@
         <v>59.375</v>
       </c>
       <c r="AH95">
-        <v>8.0689999999999998E-2</v>
+        <v>8.0710000000000004E-2</v>
       </c>
       <c r="AI95">
         <v>59.375</v>
@@ -13357,7 +13357,7 @@
         <v>59.375</v>
       </c>
       <c r="AP95">
-        <v>8.0649999999999999E-2</v>
+        <v>8.0619999999999997E-2</v>
       </c>
       <c r="AQ95">
         <v>59.375</v>
@@ -13377,7 +13377,7 @@
         <v>56.25</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>7.3380000000000001E-2</v>
       </c>
       <c r="C96">
         <v>57.8125</v>
@@ -13407,7 +13407,7 @@
         <v>57.8125</v>
       </c>
       <c r="L96">
-        <v>7.8520000000000006E-2</v>
+        <v>7.8320000000000001E-2</v>
       </c>
       <c r="M96">
         <v>57.8125</v>
@@ -13431,7 +13431,7 @@
         <v>57.8125</v>
       </c>
       <c r="T96">
-        <v>7.8520000000000006E-2</v>
+        <v>7.8320000000000001E-2</v>
       </c>
       <c r="U96">
         <v>57.8125</v>
@@ -13461,7 +13461,7 @@
         <v>57.8125</v>
       </c>
       <c r="AD96">
-        <v>7.8520000000000006E-2</v>
+        <v>7.8549999999999995E-2</v>
       </c>
       <c r="AE96">
         <v>57.8125</v>
@@ -13473,7 +13473,7 @@
         <v>57.8125</v>
       </c>
       <c r="AH96">
-        <v>7.8549999999999995E-2</v>
+        <v>7.8560000000000005E-2</v>
       </c>
       <c r="AI96">
         <v>57.8125</v>
@@ -13497,7 +13497,7 @@
         <v>57.8125</v>
       </c>
       <c r="AP96">
-        <v>7.8520000000000006E-2</v>
+        <v>7.8600000000000003E-2</v>
       </c>
       <c r="AQ96">
         <v>57.8125</v>
@@ -13517,7 +13517,7 @@
         <v>54.6875</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>7.1349999999999997E-2</v>
       </c>
       <c r="C97">
         <v>56.25</v>
@@ -13547,7 +13547,7 @@
         <v>56.25</v>
       </c>
       <c r="L97">
-        <v>7.639E-2</v>
+        <v>7.6189999999999994E-2</v>
       </c>
       <c r="M97">
         <v>56.25</v>
@@ -13571,7 +13571,7 @@
         <v>56.25</v>
       </c>
       <c r="T97">
-        <v>7.639E-2</v>
+        <v>7.6590000000000005E-2</v>
       </c>
       <c r="U97">
         <v>56.25</v>
@@ -13589,7 +13589,7 @@
         <v>56.25</v>
       </c>
       <c r="Z97">
-        <v>7.639E-2</v>
+        <v>7.6340000000000005E-2</v>
       </c>
       <c r="AA97">
         <v>56.25</v>
@@ -13601,7 +13601,7 @@
         <v>56.25</v>
       </c>
       <c r="AD97">
-        <v>7.639E-2</v>
+        <v>7.6350000000000001E-2</v>
       </c>
       <c r="AE97">
         <v>56.25</v>
@@ -13613,7 +13613,7 @@
         <v>56.25</v>
       </c>
       <c r="AH97">
-        <v>7.6399999999999996E-2</v>
+        <v>7.6420000000000002E-2</v>
       </c>
       <c r="AI97">
         <v>56.25</v>
@@ -13637,7 +13637,7 @@
         <v>56.25</v>
       </c>
       <c r="AP97">
-        <v>7.639E-2</v>
+        <v>7.6399999999999996E-2</v>
       </c>
       <c r="AQ97">
         <v>56.25</v>
@@ -13657,7 +13657,7 @@
         <v>53.125</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>6.9290000000000004E-2</v>
       </c>
       <c r="C98">
         <v>54.6875</v>
@@ -13687,7 +13687,7 @@
         <v>54.6875</v>
       </c>
       <c r="L98">
-        <v>7.4260000000000007E-2</v>
+        <v>7.4459999999999998E-2</v>
       </c>
       <c r="M98">
         <v>54.6875</v>
@@ -13711,7 +13711,7 @@
         <v>54.6875</v>
       </c>
       <c r="T98">
-        <v>7.4260000000000007E-2</v>
+        <v>7.4359999999999996E-2</v>
       </c>
       <c r="U98">
         <v>54.6875</v>
@@ -13741,7 +13741,7 @@
         <v>54.6875</v>
       </c>
       <c r="AD98">
-        <v>7.4260000000000007E-2</v>
+        <v>7.4249999999999997E-2</v>
       </c>
       <c r="AE98">
         <v>54.6875</v>
@@ -13777,7 +13777,7 @@
         <v>54.6875</v>
       </c>
       <c r="AP98">
-        <v>7.4260000000000007E-2</v>
+        <v>7.4279999999999999E-2</v>
       </c>
       <c r="AQ98">
         <v>54.6875</v>
@@ -13797,7 +13797,7 @@
         <v>51.5625</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>6.7250000000000004E-2</v>
       </c>
       <c r="C99">
         <v>53.125</v>
@@ -13827,7 +13827,7 @@
         <v>53.125</v>
       </c>
       <c r="L99">
-        <v>7.2120000000000004E-2</v>
+        <v>7.2319999999999995E-2</v>
       </c>
       <c r="M99">
         <v>53.125</v>
@@ -13851,7 +13851,7 @@
         <v>53.125</v>
       </c>
       <c r="T99">
-        <v>7.2120000000000004E-2</v>
+        <v>7.1919999999999998E-2</v>
       </c>
       <c r="U99">
         <v>53.125</v>
@@ -13881,7 +13881,7 @@
         <v>53.125</v>
       </c>
       <c r="AD99">
-        <v>7.2120000000000004E-2</v>
+        <v>7.2150000000000006E-2</v>
       </c>
       <c r="AE99">
         <v>53.125</v>
@@ -13899,7 +13899,7 @@
         <v>53.125</v>
       </c>
       <c r="AJ99">
-        <v>7.2139999999999996E-2</v>
+        <v>7.2150000000000006E-2</v>
       </c>
       <c r="AK99">
         <v>53.125</v>
@@ -13917,7 +13917,7 @@
         <v>53.125</v>
       </c>
       <c r="AP99">
-        <v>7.2120000000000004E-2</v>
+        <v>7.2109999999999994E-2</v>
       </c>
       <c r="AQ99">
         <v>53.125</v>
@@ -13937,7 +13937,7 @@
         <v>50</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>6.5140000000000003E-2</v>
       </c>
       <c r="C100">
         <v>51.5625</v>
@@ -13991,7 +13991,7 @@
         <v>51.5625</v>
       </c>
       <c r="T100">
-        <v>6.9989999999999997E-2</v>
+        <v>7.0190000000000002E-2</v>
       </c>
       <c r="U100">
         <v>51.5625</v>
@@ -14009,7 +14009,7 @@
         <v>51.5625</v>
       </c>
       <c r="Z100">
-        <v>6.9989999999999997E-2</v>
+        <v>6.9940000000000002E-2</v>
       </c>
       <c r="AA100">
         <v>51.5625</v>
@@ -14021,7 +14021,7 @@
         <v>51.5625</v>
       </c>
       <c r="AD100">
-        <v>6.9989999999999997E-2</v>
+        <v>6.9980000000000001E-2</v>
       </c>
       <c r="AE100">
         <v>51.5625</v>
@@ -14057,7 +14057,7 @@
         <v>51.5625</v>
       </c>
       <c r="AP100">
-        <v>6.9989999999999997E-2</v>
+        <v>6.9959999999999994E-2</v>
       </c>
       <c r="AQ100">
         <v>51.5625</v>
@@ -14077,7 +14077,7 @@
         <v>48.4375</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>6.3109999999999999E-2</v>
       </c>
       <c r="C101">
         <v>50</v>
@@ -14107,7 +14107,7 @@
         <v>50</v>
       </c>
       <c r="L101" s="1">
-        <v>6.7799999999999999E-2</v>
+        <v>6.7699999999999996E-2</v>
       </c>
       <c r="M101">
         <v>50</v>
@@ -14131,7 +14131,7 @@
         <v>50</v>
       </c>
       <c r="T101">
-        <v>6.7799999999999999E-2</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="U101">
         <v>50</v>
@@ -14161,7 +14161,7 @@
         <v>50</v>
       </c>
       <c r="AD101">
-        <v>6.7799999999999999E-2</v>
+        <v>6.7809999999999995E-2</v>
       </c>
       <c r="AE101">
         <v>50</v>
@@ -14173,7 +14173,7 @@
         <v>50</v>
       </c>
       <c r="AH101">
-        <v>6.7809999999999995E-2</v>
+        <v>6.7820000000000005E-2</v>
       </c>
       <c r="AI101">
         <v>50</v>
@@ -14197,7 +14197,7 @@
         <v>50</v>
       </c>
       <c r="AP101">
-        <v>6.7799999999999999E-2</v>
+        <v>6.7820000000000005E-2</v>
       </c>
       <c r="AQ101">
         <v>50</v>
@@ -14217,7 +14217,7 @@
         <v>46.875</v>
       </c>
       <c r="B102">
-        <v>0</v>
+        <v>6.105E-2</v>
       </c>
       <c r="C102">
         <v>48.4375</v>
@@ -14247,7 +14247,7 @@
         <v>48.4375</v>
       </c>
       <c r="L102">
-        <v>6.5659999999999996E-2</v>
+        <v>6.5460000000000004E-2</v>
       </c>
       <c r="M102">
         <v>48.4375</v>
@@ -14271,7 +14271,7 @@
         <v>48.4375</v>
       </c>
       <c r="T102">
-        <v>6.5659999999999996E-2</v>
+        <v>6.5559999999999993E-2</v>
       </c>
       <c r="U102">
         <v>48.4375</v>
@@ -14301,7 +14301,7 @@
         <v>48.4375</v>
       </c>
       <c r="AD102">
-        <v>6.5659999999999996E-2</v>
+        <v>6.5670000000000006E-2</v>
       </c>
       <c r="AE102">
         <v>48.4375</v>
@@ -14337,7 +14337,7 @@
         <v>48.4375</v>
       </c>
       <c r="AP102">
-        <v>6.5659999999999996E-2</v>
+        <v>6.5699999999999995E-2</v>
       </c>
       <c r="AQ102">
         <v>48.4375</v>
@@ -14357,7 +14357,7 @@
         <v>45.3125</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>5.901E-2</v>
       </c>
       <c r="C103">
         <v>46.875</v>
@@ -14387,7 +14387,7 @@
         <v>46.875</v>
       </c>
       <c r="L103">
-        <v>6.3530000000000003E-2</v>
+        <v>6.3630000000000006E-2</v>
       </c>
       <c r="M103">
         <v>46.875</v>
@@ -14411,7 +14411,7 @@
         <v>46.875</v>
       </c>
       <c r="T103">
-        <v>6.3509999999999997E-2</v>
+        <v>6.3409999999999994E-2</v>
       </c>
       <c r="U103">
         <v>46.875</v>
@@ -14441,7 +14441,7 @@
         <v>46.875</v>
       </c>
       <c r="AD103">
-        <v>6.3530000000000003E-2</v>
+        <v>6.3539999999999999E-2</v>
       </c>
       <c r="AE103">
         <v>46.875</v>
@@ -14477,7 +14477,7 @@
         <v>46.875</v>
       </c>
       <c r="AP103">
-        <v>6.3530000000000003E-2</v>
+        <v>6.3500000000000001E-2</v>
       </c>
       <c r="AQ103">
         <v>46.875</v>
@@ -14497,7 +14497,7 @@
         <v>43.75</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>5.6980000000000003E-2</v>
       </c>
       <c r="C104">
         <v>45.3125</v>
@@ -14527,7 +14527,7 @@
         <v>45.3125</v>
       </c>
       <c r="L104">
-        <v>6.1400000000000003E-2</v>
+        <v>6.13E-2</v>
       </c>
       <c r="M104">
         <v>45.3125</v>
@@ -14551,7 +14551,7 @@
         <v>45.3125</v>
       </c>
       <c r="T104">
-        <v>6.1400000000000003E-2</v>
+        <v>6.1499999999999999E-2</v>
       </c>
       <c r="U104">
         <v>45.3125</v>
@@ -14569,7 +14569,7 @@
         <v>45.3125</v>
       </c>
       <c r="Z104">
-        <v>6.1400000000000003E-2</v>
+        <v>6.1199999999999997E-2</v>
       </c>
       <c r="AA104">
         <v>45.3125</v>
@@ -14617,7 +14617,7 @@
         <v>45.3125</v>
       </c>
       <c r="AP104">
-        <v>6.1400000000000003E-2</v>
+        <v>6.1199999999999997E-2</v>
       </c>
       <c r="AQ104">
         <v>45.3125</v>
@@ -14637,7 +14637,7 @@
         <v>42.1875</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>5.4940000000000003E-2</v>
       </c>
       <c r="C105" s="1">
         <v>43.75</v>
@@ -14667,7 +14667,7 @@
         <v>43.75</v>
       </c>
       <c r="L105">
-        <v>5.9279999999999999E-2</v>
+        <v>5.9080000000000001E-2</v>
       </c>
       <c r="M105">
         <v>43.75</v>
@@ -14691,7 +14691,7 @@
         <v>43.75</v>
       </c>
       <c r="T105">
-        <v>5.9279999999999999E-2</v>
+        <v>5.9080000000000001E-2</v>
       </c>
       <c r="U105">
         <v>43.75</v>
@@ -14709,7 +14709,7 @@
         <v>43.75</v>
       </c>
       <c r="Z105">
-        <v>5.9279999999999999E-2</v>
+        <v>5.9290000000000002E-2</v>
       </c>
       <c r="AA105">
         <v>43.75</v>
@@ -14721,7 +14721,7 @@
         <v>43.75</v>
       </c>
       <c r="AD105">
-        <v>5.9279999999999999E-2</v>
+        <v>5.9290000000000002E-2</v>
       </c>
       <c r="AE105">
         <v>43.75</v>
@@ -14757,7 +14757,7 @@
         <v>43.75</v>
       </c>
       <c r="AP105">
-        <v>5.9279999999999999E-2</v>
+        <v>5.9270000000000003E-2</v>
       </c>
       <c r="AQ105">
         <v>43.75</v>
@@ -14777,7 +14777,7 @@
         <v>40.625</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>5.289E-2</v>
       </c>
       <c r="C106" s="1">
         <v>42.1875</v>
@@ -14807,7 +14807,7 @@
         <v>42.1875</v>
       </c>
       <c r="L106">
-        <v>5.7149999999999999E-2</v>
+        <v>5.7349999999999998E-2</v>
       </c>
       <c r="M106">
         <v>42.1875</v>
@@ -14831,7 +14831,7 @@
         <v>42.1875</v>
       </c>
       <c r="T106">
-        <v>5.7149999999999999E-2</v>
+        <v>5.7250000000000002E-2</v>
       </c>
       <c r="U106">
         <v>42.1875</v>
@@ -14861,7 +14861,7 @@
         <v>42.1875</v>
       </c>
       <c r="AD106">
-        <v>5.7149999999999999E-2</v>
+        <v>5.7140000000000003E-2</v>
       </c>
       <c r="AE106">
         <v>42.1875</v>
@@ -14873,13 +14873,13 @@
         <v>42.1875</v>
       </c>
       <c r="AH106">
-        <v>5.7169999999999999E-2</v>
+        <v>5.7149999999999999E-2</v>
       </c>
       <c r="AI106">
         <v>42.1875</v>
       </c>
       <c r="AJ106">
-        <v>5.7169999999999999E-2</v>
+        <v>5.7180000000000002E-2</v>
       </c>
       <c r="AK106">
         <v>42.1875</v>
@@ -14897,7 +14897,7 @@
         <v>42.1875</v>
       </c>
       <c r="AP106">
-        <v>5.7149999999999999E-2</v>
+        <v>5.7119999999999997E-2</v>
       </c>
       <c r="AQ106">
         <v>42.1875</v>
@@ -14917,7 +14917,7 @@
         <v>39.0625</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>5.0860000000000002E-2</v>
       </c>
       <c r="C107">
         <v>40.625</v>
@@ -14971,7 +14971,7 @@
         <v>40.625</v>
       </c>
       <c r="T107">
-        <v>5.5019999999999999E-2</v>
+        <v>5.5219999999999998E-2</v>
       </c>
       <c r="U107">
         <v>40.625</v>
@@ -14989,7 +14989,7 @@
         <v>40.625</v>
       </c>
       <c r="Z107">
-        <v>5.5019999999999999E-2</v>
+        <v>5.5030000000000003E-2</v>
       </c>
       <c r="AA107">
         <v>40.625</v>
@@ -15001,7 +15001,7 @@
         <v>40.625</v>
       </c>
       <c r="AD107">
-        <v>5.5019999999999999E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="AE107">
         <v>40.625</v>
@@ -15037,7 +15037,7 @@
         <v>40.625</v>
       </c>
       <c r="AP107">
-        <v>5.5019999999999999E-2</v>
+        <v>5.5050000000000002E-2</v>
       </c>
       <c r="AQ107">
         <v>40.625</v>
@@ -15057,7 +15057,7 @@
         <v>37.5</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>4.8800000000000003E-2</v>
       </c>
       <c r="C108">
         <v>39.0625</v>
@@ -15111,7 +15111,7 @@
         <v>39.0625</v>
       </c>
       <c r="T108">
-        <v>5.2900000000000003E-2</v>
+        <v>5.2699999999999997E-2</v>
       </c>
       <c r="U108">
         <v>39.0625</v>
@@ -15129,7 +15129,7 @@
         <v>39.0625</v>
       </c>
       <c r="Z108">
-        <v>5.2900000000000003E-2</v>
+        <v>5.2920000000000002E-2</v>
       </c>
       <c r="AA108">
         <v>39.0625</v>
@@ -15141,7 +15141,7 @@
         <v>39.0625</v>
       </c>
       <c r="AD108">
-        <v>5.2900000000000003E-2</v>
+        <v>5.2909999999999999E-2</v>
       </c>
       <c r="AE108">
         <v>39.0625</v>
@@ -15177,7 +15177,7 @@
         <v>39.0625</v>
       </c>
       <c r="AP108">
-        <v>5.2900000000000003E-2</v>
+        <v>5.2920000000000002E-2</v>
       </c>
       <c r="AQ108">
         <v>39.0625</v>
@@ -15197,7 +15197,7 @@
         <v>35.9375</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>4.6760000000000003E-2</v>
       </c>
       <c r="C109" s="1">
         <v>37.5</v>
@@ -15281,7 +15281,7 @@
         <v>37.5</v>
       </c>
       <c r="AD109">
-        <v>5.0770000000000003E-2</v>
+        <v>5.0799999999999998E-2</v>
       </c>
       <c r="AE109">
         <v>37.5</v>
@@ -15293,7 +15293,7 @@
         <v>37.5</v>
       </c>
       <c r="AH109">
-        <v>5.0790000000000002E-2</v>
+        <v>5.0779999999999999E-2</v>
       </c>
       <c r="AI109">
         <v>37.5</v>
@@ -15317,7 +15317,7 @@
         <v>37.5</v>
       </c>
       <c r="AP109">
-        <v>5.0770000000000003E-2</v>
+        <v>5.0790000000000002E-2</v>
       </c>
       <c r="AQ109">
         <v>37.5</v>
@@ -15337,7 +15337,7 @@
         <v>34.375</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>4.4699999999999997E-2</v>
       </c>
       <c r="C110" s="1">
         <v>35.9375</v>
@@ -15367,7 +15367,7 @@
         <v>35.9375</v>
       </c>
       <c r="L110">
-        <v>4.8649999999999999E-2</v>
+        <v>4.8550000000000003E-2</v>
       </c>
       <c r="M110">
         <v>35.9375</v>
@@ -15409,7 +15409,7 @@
         <v>35.9375</v>
       </c>
       <c r="Z110">
-        <v>4.8640000000000003E-2</v>
+        <v>4.8649999999999999E-2</v>
       </c>
       <c r="AA110">
         <v>35.9375</v>
@@ -15457,7 +15457,7 @@
         <v>35.9375</v>
       </c>
       <c r="AP110">
-        <v>4.8649999999999999E-2</v>
+        <v>4.8669999999999998E-2</v>
       </c>
       <c r="AQ110">
         <v>35.9375</v>
@@ -15477,7 +15477,7 @@
         <v>32.8125</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>4.267E-2</v>
       </c>
       <c r="C111" s="1">
         <v>34.375</v>
@@ -15507,7 +15507,7 @@
         <v>34.375</v>
       </c>
       <c r="L111">
-        <v>4.6510000000000003E-2</v>
+        <v>4.6309999999999997E-2</v>
       </c>
       <c r="M111">
         <v>34.375</v>
@@ -15531,7 +15531,7 @@
         <v>34.375</v>
       </c>
       <c r="T111">
-        <v>4.6510000000000003E-2</v>
+        <v>4.6309999999999997E-2</v>
       </c>
       <c r="U111">
         <v>34.375</v>
@@ -15561,7 +15561,7 @@
         <v>34.375</v>
       </c>
       <c r="AD111">
-        <v>4.6510000000000003E-2</v>
+        <v>4.6519999999999999E-2</v>
       </c>
       <c r="AE111">
         <v>34.375</v>
@@ -15579,7 +15579,7 @@
         <v>34.375</v>
       </c>
       <c r="AJ111">
-        <v>4.6519999999999999E-2</v>
+        <v>4.6539999999999998E-2</v>
       </c>
       <c r="AK111">
         <v>34.375</v>
@@ -15617,7 +15617,7 @@
         <v>31.25</v>
       </c>
       <c r="B112" s="1">
-        <v>1.11676E-5</v>
+        <v>4.0640000000000003E-2</v>
       </c>
       <c r="C112" s="1">
         <v>32.8125</v>
@@ -15647,7 +15647,7 @@
         <v>32.8125</v>
       </c>
       <c r="L112">
-        <v>4.4389999999999999E-2</v>
+        <v>4.419E-2</v>
       </c>
       <c r="M112">
         <v>32.8125</v>
@@ -15671,7 +15671,7 @@
         <v>32.8125</v>
       </c>
       <c r="T112">
-        <v>4.4389999999999999E-2</v>
+        <v>4.4490000000000002E-2</v>
       </c>
       <c r="U112">
         <v>32.8125</v>
@@ -15689,7 +15689,7 @@
         <v>32.8125</v>
       </c>
       <c r="Z112">
-        <v>4.4389999999999999E-2</v>
+        <v>4.437E-2</v>
       </c>
       <c r="AA112">
         <v>32.8125</v>
@@ -15701,7 +15701,7 @@
         <v>32.8125</v>
       </c>
       <c r="AD112">
-        <v>4.4389999999999999E-2</v>
+        <v>4.4359999999999997E-2</v>
       </c>
       <c r="AE112">
         <v>32.8125</v>
@@ -15737,7 +15737,7 @@
         <v>32.8125</v>
       </c>
       <c r="AP112">
-        <v>4.4389999999999999E-2</v>
+        <v>4.4380000000000003E-2</v>
       </c>
       <c r="AQ112">
         <v>32.8125</v>
@@ -15757,7 +15757,7 @@
         <v>29.6875</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>3.8600000000000002E-2</v>
       </c>
       <c r="C113" s="1">
         <v>31.25</v>
@@ -15787,7 +15787,7 @@
         <v>31.25</v>
       </c>
       <c r="L113">
-        <v>4.2270000000000002E-2</v>
+        <v>4.2070000000000003E-2</v>
       </c>
       <c r="M113">
         <v>31.25</v>
@@ -15811,7 +15811,7 @@
         <v>31.25</v>
       </c>
       <c r="T113">
-        <v>4.2270000000000002E-2</v>
+        <v>4.2470000000000001E-2</v>
       </c>
       <c r="U113">
         <v>31.25</v>
@@ -15841,7 +15841,7 @@
         <v>31.25</v>
       </c>
       <c r="AD113">
-        <v>4.2270000000000002E-2</v>
+        <v>4.2250000000000003E-2</v>
       </c>
       <c r="AE113">
         <v>31.25</v>
@@ -15877,7 +15877,7 @@
         <v>31.25</v>
       </c>
       <c r="AP113">
-        <v>4.2270000000000002E-2</v>
+        <v>4.2250000000000003E-2</v>
       </c>
       <c r="AQ113">
         <v>31.25</v>
@@ -15897,7 +15897,7 @@
         <v>28.125</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>3.6540000000000003E-2</v>
       </c>
       <c r="C114" s="1">
         <v>29.6875</v>
@@ -15927,7 +15927,7 @@
         <v>29.6875</v>
       </c>
       <c r="L114">
-        <v>4.0160000000000001E-2</v>
+        <v>4.0059999999999998E-2</v>
       </c>
       <c r="M114">
         <v>29.6875</v>
@@ -15951,7 +15951,7 @@
         <v>29.6875</v>
       </c>
       <c r="T114">
-        <v>4.0160000000000001E-2</v>
+        <v>4.0059999999999998E-2</v>
       </c>
       <c r="U114">
         <v>29.6875</v>
@@ -15969,7 +15969,7 @@
         <v>29.6875</v>
       </c>
       <c r="Z114">
-        <v>4.0160000000000001E-2</v>
+        <v>4.0149999999999998E-2</v>
       </c>
       <c r="AA114">
         <v>29.6875</v>
@@ -15981,7 +15981,7 @@
         <v>29.6875</v>
       </c>
       <c r="AD114">
-        <v>4.0160000000000001E-2</v>
+        <v>4.0149999999999998E-2</v>
       </c>
       <c r="AE114">
         <v>29.6875</v>
@@ -16017,7 +16017,7 @@
         <v>29.6875</v>
       </c>
       <c r="AP114">
-        <v>4.0160000000000001E-2</v>
+        <v>4.0120000000000003E-2</v>
       </c>
       <c r="AQ114">
         <v>29.6875</v>
@@ -16037,7 +16037,7 @@
         <v>26.5625</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>3.4500000000000003E-2</v>
       </c>
       <c r="C115" s="1">
         <v>28.125</v>
@@ -16067,7 +16067,7 @@
         <v>28.125</v>
       </c>
       <c r="L115">
-        <v>3.8019999999999998E-2</v>
+        <v>3.7819999999999999E-2</v>
       </c>
       <c r="M115">
         <v>28.125</v>
@@ -16091,7 +16091,7 @@
         <v>28.125</v>
       </c>
       <c r="T115">
-        <v>3.8019999999999998E-2</v>
+        <v>3.8219999999999997E-2</v>
       </c>
       <c r="U115">
         <v>28.125</v>
@@ -16121,7 +16121,7 @@
         <v>28.125</v>
       </c>
       <c r="AD115">
-        <v>3.8019999999999998E-2</v>
+        <v>3.8010000000000002E-2</v>
       </c>
       <c r="AE115">
         <v>28.125</v>
@@ -16157,7 +16157,7 @@
         <v>28.125</v>
       </c>
       <c r="AP115">
-        <v>3.8019999999999998E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="AQ115">
         <v>28.125</v>
@@ -16177,7 +16177,7 @@
         <v>25</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>3.245E-2</v>
       </c>
       <c r="C116" s="1">
         <v>26.5625</v>
@@ -16207,7 +16207,7 @@
         <v>26.5625</v>
       </c>
       <c r="L116">
-        <v>3.5909999999999997E-2</v>
+        <v>3.5709999999999999E-2</v>
       </c>
       <c r="M116">
         <v>26.5625</v>
@@ -16231,7 +16231,7 @@
         <v>26.5625</v>
       </c>
       <c r="T116">
-        <v>3.5909999999999997E-2</v>
+        <v>3.5709999999999999E-2</v>
       </c>
       <c r="U116">
         <v>26.5625</v>
@@ -16261,7 +16261,7 @@
         <v>26.5625</v>
       </c>
       <c r="AD116">
-        <v>3.5909999999999997E-2</v>
+        <v>3.5900000000000001E-2</v>
       </c>
       <c r="AE116">
         <v>26.5625</v>
@@ -16297,7 +16297,7 @@
         <v>26.5625</v>
       </c>
       <c r="AP116">
-        <v>3.5909999999999997E-2</v>
+        <v>3.5920000000000001E-2</v>
       </c>
       <c r="AQ116">
         <v>26.5625</v>
@@ -16317,7 +16317,7 @@
         <v>23.4375</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>8.8100000000000001E-3</v>
       </c>
       <c r="C117" s="1">
         <v>25</v>
@@ -16347,7 +16347,7 @@
         <v>25</v>
       </c>
       <c r="L117">
-        <v>3.3790000000000001E-2</v>
+        <v>3.3890000000000003E-2</v>
       </c>
       <c r="M117">
         <v>25</v>
@@ -16371,7 +16371,7 @@
         <v>25</v>
       </c>
       <c r="T117">
-        <v>3.3790000000000001E-2</v>
+        <v>3.3890000000000003E-2</v>
       </c>
       <c r="U117">
         <v>25</v>
@@ -16389,7 +16389,7 @@
         <v>25</v>
       </c>
       <c r="Z117">
-        <v>3.3790000000000001E-2</v>
+        <v>3.3779999999999998E-2</v>
       </c>
       <c r="AA117">
         <v>25</v>
@@ -16401,7 +16401,7 @@
         <v>25</v>
       </c>
       <c r="AD117">
-        <v>3.3790000000000001E-2</v>
+        <v>3.3799999999999997E-2</v>
       </c>
       <c r="AE117">
         <v>25</v>
@@ -16413,7 +16413,7 @@
         <v>25</v>
       </c>
       <c r="AH117">
-        <v>3.3790000000000001E-2</v>
+        <v>3.3799999999999997E-2</v>
       </c>
       <c r="AI117">
         <v>25</v>
@@ -16437,7 +16437,7 @@
         <v>25</v>
       </c>
       <c r="AP117">
-        <v>3.3790000000000001E-2</v>
+        <v>3.3759999999999998E-2</v>
       </c>
       <c r="AQ117">
         <v>25</v>
@@ -16487,7 +16487,7 @@
         <v>23.4375</v>
       </c>
       <c r="L118">
-        <v>3.168E-2</v>
+        <v>3.1480000000000001E-2</v>
       </c>
       <c r="M118">
         <v>23.4375</v>
@@ -16511,7 +16511,7 @@
         <v>23.4375</v>
       </c>
       <c r="T118">
-        <v>3.1660000000000001E-2</v>
+        <v>3.1460000000000002E-2</v>
       </c>
       <c r="U118">
         <v>23.4375</v>
@@ -16541,7 +16541,7 @@
         <v>23.4375</v>
       </c>
       <c r="AD118">
-        <v>3.168E-2</v>
+        <v>3.1669999999999997E-2</v>
       </c>
       <c r="AE118">
         <v>23.4375</v>
@@ -16577,7 +16577,7 @@
         <v>23.4375</v>
       </c>
       <c r="AP118">
-        <v>3.168E-2</v>
+        <v>3.1660000000000001E-2</v>
       </c>
       <c r="AQ118">
         <v>23.4375</v>
@@ -16627,7 +16627,7 @@
         <v>21.875</v>
       </c>
       <c r="L119">
-        <v>2.954E-2</v>
+        <v>2.9440000000000001E-2</v>
       </c>
       <c r="M119">
         <v>21.875</v>
@@ -16651,7 +16651,7 @@
         <v>21.875</v>
       </c>
       <c r="T119">
-        <v>2.954E-2</v>
+        <v>2.9739999999999999E-2</v>
       </c>
       <c r="U119">
         <v>21.875</v>
@@ -16681,7 +16681,7 @@
         <v>21.875</v>
       </c>
       <c r="AD119">
-        <v>2.954E-2</v>
+        <v>2.9510000000000002E-2</v>
       </c>
       <c r="AE119">
         <v>21.875</v>
@@ -16717,7 +16717,7 @@
         <v>21.875</v>
       </c>
       <c r="AP119">
-        <v>2.954E-2</v>
+        <v>2.9520000000000001E-2</v>
       </c>
       <c r="AQ119">
         <v>21.875</v>
@@ -16767,7 +16767,7 @@
         <v>20.3125</v>
       </c>
       <c r="L120">
-        <v>2.741E-2</v>
+        <v>2.7210000000000002E-2</v>
       </c>
       <c r="M120">
         <v>20.3125</v>
@@ -16809,7 +16809,7 @@
         <v>20.3125</v>
       </c>
       <c r="Z120">
-        <v>2.741E-2</v>
+        <v>2.7449999999999999E-2</v>
       </c>
       <c r="AA120">
         <v>20.3125</v>
@@ -16821,7 +16821,7 @@
         <v>20.3125</v>
       </c>
       <c r="AD120">
-        <v>2.741E-2</v>
+        <v>2.7400000000000001E-2</v>
       </c>
       <c r="AE120">
         <v>20.3125</v>
@@ -16857,7 +16857,7 @@
         <v>20.3125</v>
       </c>
       <c r="AP120">
-        <v>2.741E-2</v>
+        <v>2.7449999999999999E-2</v>
       </c>
       <c r="AQ120">
         <v>20.3125</v>
@@ -16931,7 +16931,7 @@
         <v>18.75</v>
       </c>
       <c r="T121">
-        <v>2.53E-2</v>
+        <v>2.5499999999999998E-2</v>
       </c>
       <c r="U121">
         <v>18.75</v>
@@ -16961,7 +16961,7 @@
         <v>18.75</v>
       </c>
       <c r="AD121">
-        <v>2.528E-2</v>
+        <v>2.529E-2</v>
       </c>
       <c r="AE121">
         <v>18.75</v>
@@ -16997,7 +16997,7 @@
         <v>18.75</v>
       </c>
       <c r="AP121">
-        <v>2.528E-2</v>
+        <v>2.5270000000000001E-2</v>
       </c>
       <c r="AQ121">
         <v>18.75</v>
@@ -17047,7 +17047,7 @@
         <v>17.1875</v>
       </c>
       <c r="L122">
-        <v>2.29E-2</v>
+        <v>2.2700000000000001E-2</v>
       </c>
       <c r="M122">
         <v>17.1875</v>
@@ -17071,7 +17071,7 @@
         <v>17.1875</v>
       </c>
       <c r="T122">
-        <v>2.232E-2</v>
+        <v>2.222E-2</v>
       </c>
       <c r="U122">
         <v>17.1875</v>
@@ -17089,7 +17089,7 @@
         <v>17.1875</v>
       </c>
       <c r="Z122">
-        <v>2.307E-2</v>
+        <v>2.3040000000000001E-2</v>
       </c>
       <c r="AA122">
         <v>17.1875</v>
@@ -17101,7 +17101,7 @@
         <v>17.1875</v>
       </c>
       <c r="AD122">
-        <v>2.2450000000000001E-2</v>
+        <v>2.2419999999999999E-2</v>
       </c>
       <c r="AE122">
         <v>17.1875</v>
@@ -17137,7 +17137,7 @@
         <v>17.1875</v>
       </c>
       <c r="AP122">
-        <v>2.2450000000000001E-2</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="AQ122">
         <v>17.1875</v>
@@ -17187,7 +17187,7 @@
         <v>15.625</v>
       </c>
       <c r="L123">
-        <v>1.873E-2</v>
+        <v>1.8630000000000001E-2</v>
       </c>
       <c r="M123">
         <v>15.625</v>
@@ -17211,7 +17211,7 @@
         <v>15.625</v>
       </c>
       <c r="T123">
-        <v>1.5509999999999999E-2</v>
+        <v>1.5310000000000001E-2</v>
       </c>
       <c r="U123">
         <v>15.625</v>
@@ -17241,7 +17241,7 @@
         <v>15.625</v>
       </c>
       <c r="AD123">
-        <v>1.601E-2</v>
+        <v>1.602E-2</v>
       </c>
       <c r="AE123">
         <v>15.625</v>
@@ -17327,7 +17327,7 @@
         <v>14.0625</v>
       </c>
       <c r="L124">
-        <v>1.1350000000000001E-2</v>
+        <v>1.125E-2</v>
       </c>
       <c r="M124">
         <v>14.0625</v>
@@ -17467,7 +17467,7 @@
         <v>12.5</v>
       </c>
       <c r="L125" s="1">
-        <v>4.6060799999999999E-4</v>
+        <v>6.6060800000000003E-4</v>
       </c>
       <c r="M125">
         <v>12.5</v>
@@ -18554,7 +18554,7 @@
     </row>
     <row r="133" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>-1.5625</v>
+        <v>0</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -18694,7 +18694,7 @@
     </row>
     <row r="134" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>-3.125</v>
+        <v>-1.5625</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -18834,7 +18834,7 @@
     </row>
     <row r="135" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>-4.6875</v>
+        <v>-3.125</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -18974,7 +18974,7 @@
     </row>
     <row r="136" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>-6.25</v>
+        <v>-4.6875</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -19114,7 +19114,7 @@
     </row>
     <row r="137" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>-7.8125</v>
+        <v>-6.25</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -19254,7 +19254,7 @@
     </row>
     <row r="138" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>-9.375</v>
+        <v>-7.8125</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -19394,7 +19394,7 @@
     </row>
     <row r="139" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>-10.9375</v>
+        <v>-9.375</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -19534,7 +19534,7 @@
     </row>
     <row r="140" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>-12.5</v>
+        <v>-10.9375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -19674,7 +19674,7 @@
     </row>
     <row r="141" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>-14.0625</v>
+        <v>-12.5</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -19814,7 +19814,7 @@
     </row>
     <row r="142" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>-15.625</v>
+        <v>-14.0625</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -19954,7 +19954,7 @@
     </row>
     <row r="143" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>-17.1875</v>
+        <v>-15.625</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -20094,7 +20094,7 @@
     </row>
     <row r="144" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>-18.75</v>
+        <v>-17.1875</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -20234,7 +20234,7 @@
     </row>
     <row r="145" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>-20.3125</v>
+        <v>-18.75</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -20374,7 +20374,7 @@
     </row>
     <row r="146" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>-21.875</v>
+        <v>-20.3125</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -20514,10 +20514,10 @@
     </row>
     <row r="147" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>-23.4375</v>
+        <v>-21.875</v>
       </c>
       <c r="B147">
-        <v>-2.4410000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="C147">
         <v>-21.875</v>
@@ -20654,10 +20654,10 @@
     </row>
     <row r="148" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>-25</v>
+        <v>-23.4375</v>
       </c>
       <c r="B148">
-        <v>-3.243E-2</v>
+        <v>0</v>
       </c>
       <c r="C148">
         <v>-23.4375</v>
@@ -20794,10 +20794,10 @@
     </row>
     <row r="149" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>-26.5625</v>
+        <v>-25</v>
       </c>
       <c r="B149">
-        <v>-3.4470000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="C149">
         <v>-25</v>
@@ -20934,10 +20934,10 @@
     </row>
     <row r="150" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>-28.125</v>
+        <v>-26.5625</v>
       </c>
       <c r="B150">
-        <v>-3.6519999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="C150">
         <v>-26.5625</v>
@@ -21057,7 +21057,7 @@
         <v>-26.5625</v>
       </c>
       <c r="AP150">
-        <v>-3.6130000000000002E-2</v>
+        <v>-3.6139999999999999E-2</v>
       </c>
       <c r="AQ150">
         <v>-26.5625</v>
@@ -21074,10 +21074,10 @@
     </row>
     <row r="151" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>-29.6875</v>
+        <v>-28.125</v>
       </c>
       <c r="B151">
-        <v>-3.857E-2</v>
+        <v>0</v>
       </c>
       <c r="C151">
         <v>-28.125</v>
@@ -21197,7 +21197,7 @@
         <v>-28.125</v>
       </c>
       <c r="AP151">
-        <v>-3.8249999999999999E-2</v>
+        <v>-3.8260000000000002E-2</v>
       </c>
       <c r="AQ151">
         <v>-28.125</v>
@@ -21214,10 +21214,10 @@
     </row>
     <row r="152" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>-31.25</v>
+        <v>-29.6875</v>
       </c>
       <c r="B152">
-        <v>-4.0620000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="C152">
         <v>-29.6875</v>
@@ -21337,7 +21337,7 @@
         <v>-29.6875</v>
       </c>
       <c r="AP152">
-        <v>-4.0379999999999999E-2</v>
+        <v>-4.0399999999999998E-2</v>
       </c>
       <c r="AQ152">
         <v>-29.6875</v>
@@ -21354,10 +21354,10 @@
     </row>
     <row r="153" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>-32.8125</v>
+        <v>-31.25</v>
       </c>
       <c r="B153">
-        <v>-4.265E-2</v>
+        <v>0</v>
       </c>
       <c r="C153">
         <v>-31.25</v>
@@ -21494,10 +21494,10 @@
     </row>
     <row r="154" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>-34.375</v>
+        <v>-32.8125</v>
       </c>
       <c r="B154">
-        <v>-4.4690000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="C154">
         <v>-32.8125</v>
@@ -21599,7 +21599,7 @@
         <v>-32.8125</v>
       </c>
       <c r="AJ154">
-        <v>-4.4650000000000002E-2</v>
+        <v>-4.4609999999999997E-2</v>
       </c>
       <c r="AK154">
         <v>-32.8125</v>
@@ -21617,7 +21617,7 @@
         <v>-32.8125</v>
       </c>
       <c r="AP154">
-        <v>-4.462E-2</v>
+        <v>-4.4609999999999997E-2</v>
       </c>
       <c r="AQ154">
         <v>-32.8125</v>
@@ -21634,10 +21634,10 @@
     </row>
     <row r="155" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>-35.9375</v>
+        <v>-34.375</v>
       </c>
       <c r="B155">
-        <v>-4.6739999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="C155">
         <v>-34.375</v>
@@ -21733,7 +21733,7 @@
         <v>-34.375</v>
       </c>
       <c r="AH155">
-        <v>-4.675E-2</v>
+        <v>-4.6789999999999998E-2</v>
       </c>
       <c r="AI155">
         <v>-34.375</v>
@@ -21774,10 +21774,10 @@
     </row>
     <row r="156" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>-37.5</v>
+        <v>-35.9375</v>
       </c>
       <c r="B156">
-        <v>-4.8779999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="C156">
         <v>-35.9375</v>
@@ -21831,7 +21831,7 @@
         <v>-35.9375</v>
       </c>
       <c r="T156">
-        <v>-4.8860000000000001E-2</v>
+        <v>-4.8660000000000002E-2</v>
       </c>
       <c r="U156">
         <v>-35.9375</v>
@@ -21897,7 +21897,7 @@
         <v>-35.9375</v>
       </c>
       <c r="AP156">
-        <v>-4.888E-2</v>
+        <v>-4.8890000000000003E-2</v>
       </c>
       <c r="AQ156">
         <v>-35.9375</v>
@@ -21914,10 +21914,10 @@
     </row>
     <row r="157" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>-39.0625</v>
+        <v>-37.5</v>
       </c>
       <c r="B157">
-        <v>-5.083E-2</v>
+        <v>0</v>
       </c>
       <c r="C157">
         <v>-37.5</v>
@@ -22054,10 +22054,10 @@
     </row>
     <row r="158" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>-40.625</v>
+        <v>-39.0625</v>
       </c>
       <c r="B158">
-        <v>-5.2880000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="C158">
         <v>-39.0625</v>
@@ -22111,7 +22111,7 @@
         <v>-39.0625</v>
       </c>
       <c r="T158" s="1">
-        <v>-5.3109999999999997E-2</v>
+        <v>-5.3010000000000002E-2</v>
       </c>
       <c r="U158">
         <v>-39.0625</v>
@@ -22177,7 +22177,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AP158">
-        <v>-5.3129999999999997E-2</v>
+        <v>-5.314E-2</v>
       </c>
       <c r="AQ158">
         <v>-39.0625</v>
@@ -22194,10 +22194,10 @@
     </row>
     <row r="159" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>-42.1875</v>
+        <v>-40.625</v>
       </c>
       <c r="B159">
-        <v>-5.4919999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="C159">
         <v>-40.625</v>
@@ -22227,7 +22227,7 @@
         <v>-40.625</v>
       </c>
       <c r="L159" s="1">
-        <v>-1.1307299999999999E-5</v>
+        <v>-1.11307E-4</v>
       </c>
       <c r="M159">
         <v>-40.625</v>
@@ -22251,7 +22251,7 @@
         <v>-40.625</v>
       </c>
       <c r="T159">
-        <v>-5.5239999999999997E-2</v>
+        <v>-5.5140000000000002E-2</v>
       </c>
       <c r="U159">
         <v>-40.625</v>
@@ -22293,13 +22293,13 @@
         <v>-40.625</v>
       </c>
       <c r="AH159">
-        <v>-5.5259999999999997E-2</v>
+        <v>-5.527E-2</v>
       </c>
       <c r="AI159">
         <v>-40.625</v>
       </c>
       <c r="AJ159">
-        <v>-5.5280000000000003E-2</v>
+        <v>-5.5309999999999998E-2</v>
       </c>
       <c r="AK159">
         <v>-40.625</v>
@@ -22334,10 +22334,10 @@
     </row>
     <row r="160" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>-43.75</v>
+        <v>-42.1875</v>
       </c>
       <c r="B160">
-        <v>-5.6950000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="C160">
         <v>-42.1875</v>
@@ -22409,7 +22409,7 @@
         <v>-42.1875</v>
       </c>
       <c r="Z160" s="1">
-        <v>-5.738E-2</v>
+        <v>-5.7360000000000001E-2</v>
       </c>
       <c r="AA160">
         <v>-42.1875</v>
@@ -22433,7 +22433,7 @@
         <v>-42.1875</v>
       </c>
       <c r="AH160">
-        <v>-5.7389999999999997E-2</v>
+        <v>-5.74E-2</v>
       </c>
       <c r="AI160">
         <v>-42.1875</v>
@@ -22474,10 +22474,10 @@
     </row>
     <row r="161" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>-45.3125</v>
+        <v>-43.75</v>
       </c>
       <c r="B161">
-        <v>-5.8999999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="C161">
         <v>-43.75</v>
@@ -22531,7 +22531,7 @@
         <v>-43.75</v>
       </c>
       <c r="T161" s="1">
-        <v>-5.9490000000000001E-2</v>
+        <v>-5.9290000000000002E-2</v>
       </c>
       <c r="U161">
         <v>-43.75</v>
@@ -22597,7 +22597,7 @@
         <v>-43.75</v>
       </c>
       <c r="AP161">
-        <v>-5.9490000000000001E-2</v>
+        <v>-5.9499999999999997E-2</v>
       </c>
       <c r="AQ161">
         <v>-43.75</v>
@@ -22614,10 +22614,10 @@
     </row>
     <row r="162" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>-46.875</v>
+        <v>-45.3125</v>
       </c>
       <c r="B162">
-        <v>-6.1039999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="C162">
         <v>-45.3125</v>
@@ -22647,7 +22647,7 @@
         <v>-45.3125</v>
       </c>
       <c r="L162">
-        <v>-6.1620000000000001E-2</v>
+        <v>-6.182E-2</v>
       </c>
       <c r="M162">
         <v>-45.3125</v>
@@ -22671,7 +22671,7 @@
         <v>-45.3125</v>
       </c>
       <c r="T162" s="1">
-        <v>-6.1620000000000001E-2</v>
+        <v>-6.182E-2</v>
       </c>
       <c r="U162">
         <v>-45.3125</v>
@@ -22719,7 +22719,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AJ162" s="1">
-        <v>-6.166E-2</v>
+        <v>-6.1670000000000003E-2</v>
       </c>
       <c r="AK162">
         <v>-45.3125</v>
@@ -22737,7 +22737,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AP162">
-        <v>-6.1620000000000001E-2</v>
+        <v>-6.1609999999999998E-2</v>
       </c>
       <c r="AQ162">
         <v>-45.3125</v>
@@ -22754,10 +22754,10 @@
     </row>
     <row r="163" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>-48.4375</v>
+        <v>-46.875</v>
       </c>
       <c r="B163">
-        <v>-6.3089999999999993E-2</v>
+        <v>0</v>
       </c>
       <c r="C163">
         <v>-46.875</v>
@@ -22811,7 +22811,7 @@
         <v>-46.875</v>
       </c>
       <c r="T163">
-        <v>-6.3740000000000005E-2</v>
+        <v>-6.3640000000000002E-2</v>
       </c>
       <c r="U163">
         <v>-46.875</v>
@@ -22829,7 +22829,7 @@
         <v>-46.875</v>
       </c>
       <c r="Z163">
-        <v>-6.3740000000000005E-2</v>
+        <v>-6.3750000000000001E-2</v>
       </c>
       <c r="AA163">
         <v>-46.875</v>
@@ -22894,10 +22894,10 @@
     </row>
     <row r="164" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>-50</v>
+        <v>-48.4375</v>
       </c>
       <c r="B164">
-        <v>-6.5129999999999993E-2</v>
+        <v>0</v>
       </c>
       <c r="C164">
         <v>-48.4375</v>
@@ -22951,7 +22951,7 @@
         <v>-48.4375</v>
       </c>
       <c r="T164">
-        <v>-6.5869999999999998E-2</v>
+        <v>-6.5970000000000001E-2</v>
       </c>
       <c r="U164">
         <v>-48.4375</v>
@@ -23017,7 +23017,7 @@
         <v>-48.4375</v>
       </c>
       <c r="AP164">
-        <v>-6.5869999999999998E-2</v>
+        <v>-6.59E-2</v>
       </c>
       <c r="AQ164">
         <v>-48.4375</v>
@@ -23034,10 +23034,10 @@
     </row>
     <row r="165" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>-51.5625</v>
+        <v>-50</v>
       </c>
       <c r="B165">
-        <v>-6.7239999999999994E-2</v>
+        <v>0</v>
       </c>
       <c r="C165">
         <v>-50</v>
@@ -23091,7 +23091,7 @@
         <v>-50</v>
       </c>
       <c r="T165">
-        <v>-6.8010000000000001E-2</v>
+        <v>-6.8210000000000007E-2</v>
       </c>
       <c r="U165">
         <v>-50</v>
@@ -23174,10 +23174,10 @@
     </row>
     <row r="166" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>-53.125</v>
+        <v>-51.5625</v>
       </c>
       <c r="B166">
-        <v>-6.9269999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="C166">
         <v>-51.5625</v>
@@ -23207,7 +23207,7 @@
         <v>-51.5625</v>
       </c>
       <c r="L166">
-        <v>-7.0199999999999999E-2</v>
+        <v>-7.0400000000000004E-2</v>
       </c>
       <c r="M166">
         <v>-51.5625</v>
@@ -23231,7 +23231,7 @@
         <v>-51.5625</v>
       </c>
       <c r="T166">
-        <v>-7.0190000000000002E-2</v>
+        <v>-7.0389999999999994E-2</v>
       </c>
       <c r="U166">
         <v>-51.5625</v>
@@ -23261,7 +23261,7 @@
         <v>-51.5625</v>
       </c>
       <c r="AD166">
-        <v>-7.0199999999999999E-2</v>
+        <v>-7.0190000000000002E-2</v>
       </c>
       <c r="AE166">
         <v>-51.5625</v>
@@ -23297,7 +23297,7 @@
         <v>-51.5625</v>
       </c>
       <c r="AP166">
-        <v>-7.0199999999999999E-2</v>
+        <v>-7.0209999999999995E-2</v>
       </c>
       <c r="AQ166">
         <v>-51.5625</v>
@@ -23314,10 +23314,10 @@
     </row>
     <row r="167" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>-54.6875</v>
+        <v>-53.125</v>
       </c>
       <c r="B167">
-        <v>-7.1330000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="C167">
         <v>-53.125</v>
@@ -23347,7 +23347,7 @@
         <v>-53.125</v>
       </c>
       <c r="L167">
-        <v>-7.2319999999999995E-2</v>
+        <v>-7.2419999999999998E-2</v>
       </c>
       <c r="M167">
         <v>-53.125</v>
@@ -23371,7 +23371,7 @@
         <v>-53.125</v>
       </c>
       <c r="T167">
-        <v>-7.2319999999999995E-2</v>
+        <v>-7.2419999999999998E-2</v>
       </c>
       <c r="U167">
         <v>-53.125</v>
@@ -23401,7 +23401,7 @@
         <v>-53.125</v>
       </c>
       <c r="AD167">
-        <v>-7.2319999999999995E-2</v>
+        <v>-7.2349999999999998E-2</v>
       </c>
       <c r="AE167">
         <v>-53.125</v>
@@ -23437,7 +23437,7 @@
         <v>-53.125</v>
       </c>
       <c r="AP167">
-        <v>-7.2319999999999995E-2</v>
+        <v>-7.2340000000000002E-2</v>
       </c>
       <c r="AQ167">
         <v>-53.125</v>
@@ -23454,10 +23454,10 @@
     </row>
     <row r="168" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>-56.25</v>
+        <v>-54.6875</v>
       </c>
       <c r="B168">
-        <v>-7.3370000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="C168">
         <v>-54.6875</v>
@@ -23487,7 +23487,7 @@
         <v>-54.6875</v>
       </c>
       <c r="L168">
-        <v>-7.4469999999999995E-2</v>
+        <v>-7.4270000000000003E-2</v>
       </c>
       <c r="M168">
         <v>-54.6875</v>
@@ -23529,7 +23529,7 @@
         <v>-54.6875</v>
       </c>
       <c r="Z168">
-        <v>-7.4450000000000002E-2</v>
+        <v>-7.4399999999999994E-2</v>
       </c>
       <c r="AA168">
         <v>-54.6875</v>
@@ -23541,7 +23541,7 @@
         <v>-54.6875</v>
       </c>
       <c r="AD168">
-        <v>-7.4469999999999995E-2</v>
+        <v>-7.4499999999999997E-2</v>
       </c>
       <c r="AE168">
         <v>-54.6875</v>
@@ -23577,7 +23577,7 @@
         <v>-54.6875</v>
       </c>
       <c r="AP168">
-        <v>-7.4469999999999995E-2</v>
+        <v>-7.4480000000000005E-2</v>
       </c>
       <c r="AQ168">
         <v>-54.6875</v>
@@ -23594,10 +23594,10 @@
     </row>
     <row r="169" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>-57.8125</v>
+        <v>-56.25</v>
       </c>
       <c r="B169">
-        <v>-7.5410000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="C169">
         <v>-56.25</v>
@@ -23627,7 +23627,7 @@
         <v>-56.25</v>
       </c>
       <c r="L169">
-        <v>-7.6600000000000001E-2</v>
+        <v>-7.6399999999999996E-2</v>
       </c>
       <c r="M169">
         <v>-56.25</v>
@@ -23651,7 +23651,7 @@
         <v>-56.25</v>
       </c>
       <c r="T169">
-        <v>-7.6579999999999995E-2</v>
+        <v>-7.6780000000000001E-2</v>
       </c>
       <c r="U169">
         <v>-56.25</v>
@@ -23669,7 +23669,7 @@
         <v>-56.25</v>
       </c>
       <c r="Z169">
-        <v>-7.6579999999999995E-2</v>
+        <v>-7.6569999999999999E-2</v>
       </c>
       <c r="AA169">
         <v>-56.25</v>
@@ -23681,7 +23681,7 @@
         <v>-56.25</v>
       </c>
       <c r="AD169">
-        <v>-7.6600000000000001E-2</v>
+        <v>-7.6499999999999999E-2</v>
       </c>
       <c r="AE169">
         <v>-56.25</v>
@@ -23734,10 +23734,10 @@
     </row>
     <row r="170" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>-59.375</v>
+        <v>-57.8125</v>
       </c>
       <c r="B170">
-        <v>-7.7460000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="C170">
         <v>-57.8125</v>
@@ -23767,7 +23767,7 @@
         <v>-57.8125</v>
       </c>
       <c r="L170">
-        <v>-7.8729999999999994E-2</v>
+        <v>-7.8630000000000005E-2</v>
       </c>
       <c r="M170">
         <v>-57.8125</v>
@@ -23791,7 +23791,7 @@
         <v>-57.8125</v>
       </c>
       <c r="T170">
-        <v>-7.8710000000000002E-2</v>
+        <v>-7.8509999999999996E-2</v>
       </c>
       <c r="U170">
         <v>-57.8125</v>
@@ -23821,7 +23821,7 @@
         <v>-57.8125</v>
       </c>
       <c r="AD170">
-        <v>-7.8729999999999994E-2</v>
+        <v>-7.8740000000000004E-2</v>
       </c>
       <c r="AE170">
         <v>-57.8125</v>
@@ -23857,7 +23857,7 @@
         <v>-57.8125</v>
       </c>
       <c r="AP170">
-        <v>-7.8729999999999994E-2</v>
+        <v>-7.8740000000000004E-2</v>
       </c>
       <c r="AQ170">
         <v>-57.8125</v>
@@ -23874,10 +23874,10 @@
     </row>
     <row r="171" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>-60.9375</v>
+        <v>-59.375</v>
       </c>
       <c r="B171">
-        <v>-7.9509999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="C171">
         <v>-59.375</v>
@@ -23907,7 +23907,7 @@
         <v>-59.375</v>
       </c>
       <c r="L171">
-        <v>-8.0860000000000001E-2</v>
+        <v>-8.0759999999999998E-2</v>
       </c>
       <c r="M171">
         <v>-59.375</v>
@@ -23931,7 +23931,7 @@
         <v>-59.375</v>
       </c>
       <c r="T171">
-        <v>-8.0850000000000005E-2</v>
+        <v>-8.0649999999999999E-2</v>
       </c>
       <c r="U171">
         <v>-59.375</v>
@@ -23949,7 +23949,7 @@
         <v>-59.375</v>
       </c>
       <c r="Z171">
-        <v>-8.0850000000000005E-2</v>
+        <v>-8.0820000000000003E-2</v>
       </c>
       <c r="AA171">
         <v>-59.375</v>
@@ -23961,7 +23961,7 @@
         <v>-59.375</v>
       </c>
       <c r="AD171">
-        <v>-8.0860000000000001E-2</v>
+        <v>-8.0839999999999995E-2</v>
       </c>
       <c r="AE171">
         <v>-59.375</v>
@@ -23979,7 +23979,7 @@
         <v>-59.375</v>
       </c>
       <c r="AJ171">
-        <v>-8.09E-2</v>
+        <v>-8.0909999999999996E-2</v>
       </c>
       <c r="AK171">
         <v>-59.375</v>
@@ -23997,7 +23997,7 @@
         <v>-59.375</v>
       </c>
       <c r="AP171">
-        <v>-8.0860000000000001E-2</v>
+        <v>-8.0839999999999995E-2</v>
       </c>
       <c r="AQ171">
         <v>-59.375</v>
@@ -24014,10 +24014,10 @@
     </row>
     <row r="172" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>-62.5</v>
+        <v>-60.9375</v>
       </c>
       <c r="B172">
-        <v>-8.1549999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="C172">
         <v>-60.9375</v>
@@ -24047,7 +24047,7 @@
         <v>-60.9375</v>
       </c>
       <c r="L172">
-        <v>-8.301E-2</v>
+        <v>-8.2909999999999998E-2</v>
       </c>
       <c r="M172">
         <v>-60.9375</v>
@@ -24071,7 +24071,7 @@
         <v>-60.9375</v>
       </c>
       <c r="T172">
-        <v>-8.3000000000000004E-2</v>
+        <v>-8.2900000000000001E-2</v>
       </c>
       <c r="U172">
         <v>-60.9375</v>
@@ -24101,7 +24101,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AD172">
-        <v>-8.301E-2</v>
+        <v>-8.3019999999999997E-2</v>
       </c>
       <c r="AE172">
         <v>-60.9375</v>
@@ -24113,7 +24113,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AH172">
-        <v>-8.3030000000000007E-2</v>
+        <v>-8.3049999999999999E-2</v>
       </c>
       <c r="AI172">
         <v>-60.9375</v>
@@ -24137,7 +24137,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AP172">
-        <v>-8.301E-2</v>
+        <v>-8.3000000000000004E-2</v>
       </c>
       <c r="AQ172">
         <v>-60.9375</v>
@@ -24154,10 +24154,10 @@
     </row>
     <row r="173" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>-64.0625</v>
+        <v>-62.5</v>
       </c>
       <c r="B173">
-        <v>-8.3610000000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="C173">
         <v>-62.5</v>
@@ -24187,7 +24187,7 @@
         <v>-62.5</v>
       </c>
       <c r="L173">
-        <v>-8.5139999999999993E-2</v>
+        <v>-8.5339999999999999E-2</v>
       </c>
       <c r="M173">
         <v>-62.5</v>
@@ -24211,7 +24211,7 @@
         <v>-62.5</v>
       </c>
       <c r="T173">
-        <v>-8.5139999999999993E-2</v>
+        <v>-8.5339999999999999E-2</v>
       </c>
       <c r="U173">
         <v>-62.5</v>
@@ -24241,7 +24241,7 @@
         <v>-62.5</v>
       </c>
       <c r="AD173">
-        <v>-8.5139999999999993E-2</v>
+        <v>-8.5150000000000003E-2</v>
       </c>
       <c r="AE173">
         <v>-62.5</v>
@@ -24253,7 +24253,7 @@
         <v>-62.5</v>
       </c>
       <c r="AH173">
-        <v>-8.5180000000000006E-2</v>
+        <v>-8.5169999999999996E-2</v>
       </c>
       <c r="AI173">
         <v>-62.5</v>
@@ -24277,7 +24277,7 @@
         <v>-62.5</v>
       </c>
       <c r="AP173">
-        <v>-8.5139999999999993E-2</v>
+        <v>-8.5120000000000001E-2</v>
       </c>
       <c r="AQ173">
         <v>-62.5</v>
@@ -24294,10 +24294,10 @@
     </row>
     <row r="174" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>-65.625</v>
+        <v>-64.0625</v>
       </c>
       <c r="B174">
-        <v>-8.566E-2</v>
+        <v>0</v>
       </c>
       <c r="C174">
         <v>-64.0625</v>
@@ -24327,7 +24327,7 @@
         <v>-64.0625</v>
       </c>
       <c r="L174">
-        <v>-8.7309999999999999E-2</v>
+        <v>-8.7209999999999996E-2</v>
       </c>
       <c r="M174">
         <v>-64.0625</v>
@@ -24351,7 +24351,7 @@
         <v>-64.0625</v>
       </c>
       <c r="T174">
-        <v>-8.7290000000000006E-2</v>
+        <v>-8.7389999999999995E-2</v>
       </c>
       <c r="U174">
         <v>-64.0625</v>
@@ -24381,7 +24381,7 @@
         <v>-64.0625</v>
       </c>
       <c r="AD174">
-        <v>-8.7309999999999999E-2</v>
+        <v>-8.7300000000000003E-2</v>
       </c>
       <c r="AE174">
         <v>-64.0625</v>
@@ -24393,7 +24393,7 @@
         <v>-64.0625</v>
       </c>
       <c r="AH174">
-        <v>-8.7319999999999995E-2</v>
+        <v>-8.7330000000000005E-2</v>
       </c>
       <c r="AI174">
         <v>-64.0625</v>
@@ -24417,7 +24417,7 @@
         <v>-64.0625</v>
       </c>
       <c r="AP174">
-        <v>-8.7309999999999999E-2</v>
+        <v>-8.7319999999999995E-2</v>
       </c>
       <c r="AQ174">
         <v>-64.0625</v>
@@ -24434,10 +24434,10 @@
     </row>
     <row r="175" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>-67.1875</v>
+        <v>-65.625</v>
       </c>
       <c r="B175">
-        <v>-8.7720000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="C175">
         <v>-65.625</v>
@@ -24467,7 +24467,7 @@
         <v>-65.625</v>
       </c>
       <c r="L175">
-        <v>-8.9440000000000006E-2</v>
+        <v>-8.9539999999999995E-2</v>
       </c>
       <c r="M175">
         <v>-65.625</v>
@@ -24491,7 +24491,7 @@
         <v>-65.625</v>
       </c>
       <c r="T175">
-        <v>-8.9440000000000006E-2</v>
+        <v>-8.9639999999999997E-2</v>
       </c>
       <c r="U175">
         <v>-65.625</v>
@@ -24521,7 +24521,7 @@
         <v>-65.625</v>
       </c>
       <c r="AD175">
-        <v>-8.9440000000000006E-2</v>
+        <v>-8.949E-2</v>
       </c>
       <c r="AE175">
         <v>-65.625</v>
@@ -24533,13 +24533,13 @@
         <v>-65.625</v>
       </c>
       <c r="AH175">
-        <v>-8.9469999999999994E-2</v>
+        <v>-8.9480000000000004E-2</v>
       </c>
       <c r="AI175">
         <v>-65.625</v>
       </c>
       <c r="AJ175">
-        <v>-8.9469999999999994E-2</v>
+        <v>-8.9480000000000004E-2</v>
       </c>
       <c r="AK175">
         <v>-65.625</v>
@@ -24557,7 +24557,7 @@
         <v>-65.625</v>
       </c>
       <c r="AP175">
-        <v>-8.9440000000000006E-2</v>
+        <v>-8.9419999999999999E-2</v>
       </c>
       <c r="AQ175">
         <v>-65.625</v>
@@ -24577,7 +24577,7 @@
         <v>-68.75</v>
       </c>
       <c r="B176">
-        <v>-8.9770000000000003E-2</v>
+        <v>-8.9990000000000001E-2</v>
       </c>
       <c r="C176">
         <v>-67.1875</v>
@@ -24607,7 +24607,7 @@
         <v>-67.1875</v>
       </c>
       <c r="L176">
-        <v>-9.1590000000000005E-2</v>
+        <v>-9.1689999999999994E-2</v>
       </c>
       <c r="M176">
         <v>-67.1875</v>
@@ -24631,7 +24631,7 @@
         <v>-67.1875</v>
       </c>
       <c r="T176">
-        <v>-9.1590000000000005E-2</v>
+        <v>-9.1389999999999999E-2</v>
       </c>
       <c r="U176">
         <v>-67.1875</v>
@@ -24649,7 +24649,7 @@
         <v>-67.1875</v>
       </c>
       <c r="Z176">
-        <v>-9.1590000000000005E-2</v>
+        <v>-9.1550000000000006E-2</v>
       </c>
       <c r="AA176">
         <v>-67.1875</v>
@@ -24661,7 +24661,7 @@
         <v>-67.1875</v>
       </c>
       <c r="AD176">
-        <v>-9.1590000000000005E-2</v>
+        <v>-9.1600000000000001E-2</v>
       </c>
       <c r="AE176">
         <v>-67.1875</v>
@@ -24697,7 +24697,7 @@
         <v>-67.1875</v>
       </c>
       <c r="AP176">
-        <v>-9.1590000000000005E-2</v>
+        <v>-9.1579999999999995E-2</v>
       </c>
       <c r="AQ176">
         <v>-67.1875</v>
@@ -24717,7 +24717,7 @@
         <v>-70.3125</v>
       </c>
       <c r="B177">
-        <v>-9.1810000000000003E-2</v>
+        <v>-9.2030000000000001E-2</v>
       </c>
       <c r="C177">
         <v>-68.75</v>
@@ -24747,7 +24747,7 @@
         <v>-68.75</v>
       </c>
       <c r="L177">
-        <v>-9.3740000000000004E-2</v>
+        <v>-9.3640000000000001E-2</v>
       </c>
       <c r="M177">
         <v>-68.75</v>
@@ -24771,7 +24771,7 @@
         <v>-68.75</v>
       </c>
       <c r="T177">
-        <v>-9.3740000000000004E-2</v>
+        <v>-9.3840000000000007E-2</v>
       </c>
       <c r="U177">
         <v>-68.75</v>
@@ -24801,7 +24801,7 @@
         <v>-68.75</v>
       </c>
       <c r="AD177">
-        <v>-9.3740000000000004E-2</v>
+        <v>-9.3719999999999998E-2</v>
       </c>
       <c r="AE177">
         <v>-68.75</v>
@@ -24837,7 +24837,7 @@
         <v>-68.75</v>
       </c>
       <c r="AP177">
-        <v>-9.3740000000000004E-2</v>
+        <v>-9.3700000000000006E-2</v>
       </c>
       <c r="AQ177">
         <v>-68.75</v>
@@ -24857,7 +24857,7 @@
         <v>-71.875</v>
       </c>
       <c r="B178">
-        <v>-9.3859999999999999E-2</v>
+        <v>-9.4079999999999997E-2</v>
       </c>
       <c r="C178">
         <v>-70.3125</v>
@@ -24887,7 +24887,7 @@
         <v>-70.3125</v>
       </c>
       <c r="L178">
-        <v>-9.5890000000000003E-2</v>
+        <v>-9.5990000000000006E-2</v>
       </c>
       <c r="M178">
         <v>-70.3125</v>
@@ -24911,7 +24911,7 @@
         <v>-70.3125</v>
       </c>
       <c r="T178">
-        <v>-9.5890000000000003E-2</v>
+        <v>-9.6089999999999995E-2</v>
       </c>
       <c r="U178">
         <v>-70.3125</v>
@@ -24941,7 +24941,7 @@
         <v>-70.3125</v>
       </c>
       <c r="AD178">
-        <v>-9.5890000000000003E-2</v>
+        <v>-9.5899999999999999E-2</v>
       </c>
       <c r="AE178">
         <v>-70.3125</v>
@@ -24959,7 +24959,7 @@
         <v>-70.3125</v>
       </c>
       <c r="AJ178">
-        <v>-9.5920000000000005E-2</v>
+        <v>-9.5899999999999999E-2</v>
       </c>
       <c r="AK178">
         <v>-70.3125</v>
@@ -24977,7 +24977,7 @@
         <v>-70.3125</v>
       </c>
       <c r="AP178">
-        <v>-9.5890000000000003E-2</v>
+        <v>-9.5850000000000005E-2</v>
       </c>
       <c r="AQ178">
         <v>-70.3125</v>
@@ -24997,7 +24997,7 @@
         <v>-73.4375</v>
       </c>
       <c r="B179">
-        <v>-9.5920000000000005E-2</v>
+        <v>-9.6140000000000003E-2</v>
       </c>
       <c r="C179">
         <v>-71.875</v>
@@ -25027,7 +25027,7 @@
         <v>-71.875</v>
       </c>
       <c r="L179">
-        <v>-9.8030000000000006E-2</v>
+        <v>-9.8129999999999995E-2</v>
       </c>
       <c r="M179">
         <v>-71.875</v>
@@ -25081,7 +25081,7 @@
         <v>-71.875</v>
       </c>
       <c r="AD179">
-        <v>-9.8030000000000006E-2</v>
+        <v>-9.8019999999999996E-2</v>
       </c>
       <c r="AE179">
         <v>-71.875</v>
@@ -25099,7 +25099,7 @@
         <v>-71.875</v>
       </c>
       <c r="AJ179">
-        <v>-9.8070000000000004E-2</v>
+        <v>-9.8049999999999998E-2</v>
       </c>
       <c r="AK179">
         <v>-71.875</v>
@@ -25117,7 +25117,7 @@
         <v>-71.875</v>
       </c>
       <c r="AP179">
-        <v>-9.8030000000000006E-2</v>
+        <v>-9.801E-2</v>
       </c>
       <c r="AQ179">
         <v>-71.875</v>
@@ -25137,7 +25137,7 @@
         <v>-75</v>
       </c>
       <c r="B180">
-        <v>-9.7970000000000002E-2</v>
+        <v>-9.8199999999999996E-2</v>
       </c>
       <c r="C180">
         <v>-73.4375</v>
@@ -25167,7 +25167,7 @@
         <v>-73.4375</v>
       </c>
       <c r="L180">
-        <v>-0.1002</v>
+        <v>-0.10009999999999999</v>
       </c>
       <c r="M180">
         <v>-73.4375</v>
@@ -25191,7 +25191,7 @@
         <v>-73.4375</v>
       </c>
       <c r="T180">
-        <v>-0.1002</v>
+        <v>-0.1004</v>
       </c>
       <c r="U180">
         <v>-73.4375</v>
@@ -25209,7 +25209,7 @@
         <v>-73.4375</v>
       </c>
       <c r="Z180">
-        <v>-0.1002</v>
+        <v>-0.10009999999999999</v>
       </c>
       <c r="AA180">
         <v>-73.4375</v>
@@ -25221,7 +25221,7 @@
         <v>-73.4375</v>
       </c>
       <c r="AD180">
-        <v>-0.1002</v>
+        <v>-0.10009999999999999</v>
       </c>
       <c r="AE180">
         <v>-73.4375</v>
@@ -25239,7 +25239,7 @@
         <v>-73.4375</v>
       </c>
       <c r="AJ180">
-        <v>-0.10023</v>
+        <v>-0.10024</v>
       </c>
       <c r="AK180">
         <v>-73.4375</v>
@@ -25257,7 +25257,7 @@
         <v>-73.4375</v>
       </c>
       <c r="AP180">
-        <v>-0.1002</v>
+        <v>-0.10009999999999999</v>
       </c>
       <c r="AQ180">
         <v>-73.4375</v>
@@ -25277,7 +25277,7 @@
         <v>-76.5625</v>
       </c>
       <c r="B181">
-        <v>-0.10002999999999999</v>
+        <v>-0.10026</v>
       </c>
       <c r="C181">
         <v>-75</v>
@@ -25331,7 +25331,7 @@
         <v>-75</v>
       </c>
       <c r="T181">
-        <v>-0.10235</v>
+        <v>-0.10255</v>
       </c>
       <c r="U181">
         <v>-75</v>
@@ -25349,7 +25349,7 @@
         <v>-75</v>
       </c>
       <c r="Z181">
-        <v>-0.10235</v>
+        <v>-0.10231999999999999</v>
       </c>
       <c r="AA181">
         <v>-75</v>
@@ -25361,7 +25361,7 @@
         <v>-75</v>
       </c>
       <c r="AD181">
-        <v>-0.10235</v>
+        <v>-0.10231</v>
       </c>
       <c r="AE181">
         <v>-75</v>
@@ -25417,7 +25417,7 @@
         <v>-78.125</v>
       </c>
       <c r="B182">
-        <v>-0.10206999999999999</v>
+        <v>-0.10231999999999999</v>
       </c>
       <c r="C182">
         <v>-76.5625</v>
@@ -25447,7 +25447,7 @@
         <v>-76.5625</v>
       </c>
       <c r="L182">
-        <v>-0.10451000000000001</v>
+        <v>-0.10431</v>
       </c>
       <c r="M182">
         <v>-76.5625</v>
@@ -25489,7 +25489,7 @@
         <v>-76.5625</v>
       </c>
       <c r="Z182">
-        <v>-0.1045</v>
+        <v>-0.10451000000000001</v>
       </c>
       <c r="AA182">
         <v>-76.5625</v>
@@ -25501,7 +25501,7 @@
         <v>-76.5625</v>
       </c>
       <c r="AD182">
-        <v>-0.10451000000000001</v>
+        <v>-0.10452</v>
       </c>
       <c r="AE182">
         <v>-76.5625</v>
@@ -25537,7 +25537,7 @@
         <v>-76.5625</v>
       </c>
       <c r="AP182">
-        <v>-0.10451000000000001</v>
+        <v>-0.1045</v>
       </c>
       <c r="AQ182">
         <v>-76.5625</v>
@@ -25557,7 +25557,7 @@
         <v>-79.6875</v>
       </c>
       <c r="B183">
-        <v>-0.10414</v>
+        <v>-0.10439</v>
       </c>
       <c r="C183">
         <v>-78.125</v>
@@ -25611,7 +25611,7 @@
         <v>-78.125</v>
       </c>
       <c r="T183">
-        <v>-0.10668</v>
+        <v>-0.10648000000000001</v>
       </c>
       <c r="U183">
         <v>-78.125</v>
@@ -25629,7 +25629,7 @@
         <v>-78.125</v>
       </c>
       <c r="Z183">
-        <v>-0.10668</v>
+        <v>-0.10668999999999999</v>
       </c>
       <c r="AA183">
         <v>-78.125</v>
@@ -25641,7 +25641,7 @@
         <v>-78.125</v>
       </c>
       <c r="AD183">
-        <v>-0.10668</v>
+        <v>-0.10667</v>
       </c>
       <c r="AE183">
         <v>-78.125</v>
@@ -25659,7 +25659,7 @@
         <v>-78.125</v>
       </c>
       <c r="AJ183">
-        <v>-0.10671</v>
+        <v>-0.10668999999999999</v>
       </c>
       <c r="AK183">
         <v>-78.125</v>
@@ -25697,7 +25697,7 @@
         <v>-81.25</v>
       </c>
       <c r="B184">
-        <v>-0.10619000000000001</v>
+        <v>-0.10646</v>
       </c>
       <c r="C184">
         <v>-79.6875</v>
@@ -25727,7 +25727,7 @@
         <v>-79.6875</v>
       </c>
       <c r="L184">
-        <v>-0.10884000000000001</v>
+        <v>-0.10894</v>
       </c>
       <c r="M184">
         <v>-79.6875</v>
@@ -25781,7 +25781,7 @@
         <v>-79.6875</v>
       </c>
       <c r="AD184">
-        <v>-0.10884000000000001</v>
+        <v>-0.10882</v>
       </c>
       <c r="AE184">
         <v>-79.6875</v>
@@ -25793,7 +25793,7 @@
         <v>-79.6875</v>
       </c>
       <c r="AH184">
-        <v>-0.10889</v>
+        <v>-0.10888</v>
       </c>
       <c r="AI184">
         <v>-79.6875</v>
@@ -25817,7 +25817,7 @@
         <v>-79.6875</v>
       </c>
       <c r="AP184">
-        <v>-0.10884000000000001</v>
+        <v>-0.10883</v>
       </c>
       <c r="AQ184">
         <v>-79.6875</v>
@@ -25837,7 +25837,7 @@
         <v>-82.8125</v>
       </c>
       <c r="B185">
-        <v>-0.10824</v>
+        <v>-0.10853</v>
       </c>
       <c r="C185">
         <v>-81.25</v>
@@ -25867,7 +25867,7 @@
         <v>-81.25</v>
       </c>
       <c r="L185">
-        <v>-0.11101999999999999</v>
+        <v>-0.11112</v>
       </c>
       <c r="M185">
         <v>-81.25</v>
@@ -25891,7 +25891,7 @@
         <v>-81.25</v>
       </c>
       <c r="T185">
-        <v>-0.11101999999999999</v>
+        <v>-0.11092</v>
       </c>
       <c r="U185">
         <v>-81.25</v>
@@ -25921,7 +25921,7 @@
         <v>-81.25</v>
       </c>
       <c r="AD185">
-        <v>-0.11101999999999999</v>
+        <v>-0.111</v>
       </c>
       <c r="AE185">
         <v>-81.25</v>
@@ -25957,7 +25957,7 @@
         <v>-81.25</v>
       </c>
       <c r="AP185">
-        <v>-0.11101999999999999</v>
+        <v>-0.11103</v>
       </c>
       <c r="AQ185">
         <v>-81.25</v>
@@ -25977,7 +25977,7 @@
         <v>-84.375</v>
       </c>
       <c r="B186">
-        <v>-0.1103</v>
+        <v>-0.11058999999999999</v>
       </c>
       <c r="C186">
         <v>-82.8125</v>
@@ -26007,7 +26007,7 @@
         <v>-82.8125</v>
       </c>
       <c r="L186">
-        <v>-0.1132</v>
+        <v>-0.1134</v>
       </c>
       <c r="M186">
         <v>-82.8125</v>
@@ -26031,7 +26031,7 @@
         <v>-82.8125</v>
       </c>
       <c r="T186">
-        <v>-0.11319</v>
+        <v>-0.11298999999999999</v>
       </c>
       <c r="U186">
         <v>-82.8125</v>
@@ -26061,7 +26061,7 @@
         <v>-82.8125</v>
       </c>
       <c r="AD186">
-        <v>-0.1132</v>
+        <v>-0.11310000000000001</v>
       </c>
       <c r="AE186">
         <v>-82.8125</v>
@@ -26117,7 +26117,7 @@
         <v>-85.9375</v>
       </c>
       <c r="B187">
-        <v>-0.11237</v>
+        <v>-0.11268</v>
       </c>
       <c r="C187">
         <v>-84.375</v>
@@ -26147,7 +26147,7 @@
         <v>-84.375</v>
       </c>
       <c r="L187">
-        <v>-0.11538</v>
+        <v>-0.11527999999999999</v>
       </c>
       <c r="M187">
         <v>-84.375</v>
@@ -26171,7 +26171,7 @@
         <v>-84.375</v>
       </c>
       <c r="T187">
-        <v>-0.11537</v>
+        <v>-0.11527</v>
       </c>
       <c r="U187">
         <v>-84.375</v>
@@ -26201,7 +26201,7 @@
         <v>-84.375</v>
       </c>
       <c r="AD187">
-        <v>-0.11538</v>
+        <v>-0.11537</v>
       </c>
       <c r="AE187">
         <v>-84.375</v>
@@ -26237,7 +26237,7 @@
         <v>-84.375</v>
       </c>
       <c r="AP187">
-        <v>-0.11538</v>
+        <v>-0.1154</v>
       </c>
       <c r="AQ187">
         <v>-84.375</v>
@@ -26257,7 +26257,7 @@
         <v>-87.5</v>
       </c>
       <c r="B188">
-        <v>-0.11445</v>
+        <v>-0.11475</v>
       </c>
       <c r="C188">
         <v>-85.9375</v>
@@ -26287,7 +26287,7 @@
         <v>-85.9375</v>
       </c>
       <c r="L188">
-        <v>-0.11758</v>
+        <v>-0.11768000000000001</v>
       </c>
       <c r="M188">
         <v>-85.9375</v>
@@ -26311,7 +26311,7 @@
         <v>-85.9375</v>
       </c>
       <c r="T188">
-        <v>-0.11756</v>
+        <v>-0.11745999999999999</v>
       </c>
       <c r="U188">
         <v>-85.9375</v>
@@ -26341,7 +26341,7 @@
         <v>-85.9375</v>
       </c>
       <c r="AD188">
-        <v>-0.11758</v>
+        <v>-0.11756</v>
       </c>
       <c r="AE188">
         <v>-85.9375</v>
@@ -26353,7 +26353,7 @@
         <v>-85.9375</v>
       </c>
       <c r="AH188">
-        <v>-0.11763999999999999</v>
+        <v>-0.11765</v>
       </c>
       <c r="AI188">
         <v>-85.9375</v>
@@ -26377,7 +26377,7 @@
         <v>-85.9375</v>
       </c>
       <c r="AP188">
-        <v>-0.11758</v>
+        <v>-0.1176</v>
       </c>
       <c r="AQ188">
         <v>-85.9375</v>
@@ -26397,7 +26397,7 @@
         <v>-89.0625</v>
       </c>
       <c r="B189">
-        <v>-0.11654</v>
+        <v>-0.11684</v>
       </c>
       <c r="C189">
         <v>-87.5</v>
@@ -26427,7 +26427,7 @@
         <v>-87.5</v>
       </c>
       <c r="L189">
-        <v>-0.11978</v>
+        <v>-0.11988</v>
       </c>
       <c r="M189">
         <v>-87.5</v>
@@ -26451,7 +26451,7 @@
         <v>-87.5</v>
       </c>
       <c r="T189">
-        <v>-0.11978</v>
+        <v>-0.11988</v>
       </c>
       <c r="U189">
         <v>-87.5</v>
@@ -26481,7 +26481,7 @@
         <v>-87.5</v>
       </c>
       <c r="AD189">
-        <v>-0.11978</v>
+        <v>-0.11977</v>
       </c>
       <c r="AE189">
         <v>-87.5</v>
@@ -26517,7 +26517,7 @@
         <v>-87.5</v>
       </c>
       <c r="AP189">
-        <v>-0.11978</v>
+        <v>-0.11976000000000001</v>
       </c>
       <c r="AQ189">
         <v>-87.5</v>
@@ -26537,7 +26537,7 @@
         <v>-90.625</v>
       </c>
       <c r="B190">
-        <v>-0.1186</v>
+        <v>-0.11890000000000001</v>
       </c>
       <c r="C190">
         <v>-89.0625</v>
@@ -26567,7 +26567,7 @@
         <v>-89.0625</v>
       </c>
       <c r="L190">
-        <v>-0.12199</v>
+        <v>-0.12179</v>
       </c>
       <c r="M190">
         <v>-89.0625</v>
@@ -26591,7 +26591,7 @@
         <v>-89.0625</v>
       </c>
       <c r="T190">
-        <v>-0.12199</v>
+        <v>-0.12189</v>
       </c>
       <c r="U190">
         <v>-89.0625</v>
@@ -26621,7 +26621,7 @@
         <v>-89.0625</v>
       </c>
       <c r="AD190">
-        <v>-0.12199</v>
+        <v>-0.12198000000000001</v>
       </c>
       <c r="AE190">
         <v>-89.0625</v>
@@ -26657,7 +26657,7 @@
         <v>-89.0625</v>
       </c>
       <c r="AP190">
-        <v>-0.12199</v>
+        <v>-0.12198000000000001</v>
       </c>
       <c r="AQ190">
         <v>-89.0625</v>
@@ -26677,7 +26677,7 @@
         <v>-92.1875</v>
       </c>
       <c r="B191">
-        <v>-0.12068</v>
+        <v>-0.12098</v>
       </c>
       <c r="C191">
         <v>-90.625</v>
@@ -26707,7 +26707,7 @@
         <v>-90.625</v>
       </c>
       <c r="L191">
-        <v>-0.12418999999999999</v>
+        <v>-0.12429</v>
       </c>
       <c r="M191">
         <v>-90.625</v>
@@ -26761,7 +26761,7 @@
         <v>-90.625</v>
       </c>
       <c r="AD191">
-        <v>-0.12418999999999999</v>
+        <v>-0.12411999999999999</v>
       </c>
       <c r="AE191">
         <v>-90.625</v>
@@ -26779,7 +26779,7 @@
         <v>-90.625</v>
       </c>
       <c r="AJ191">
-        <v>-0.12422</v>
+        <v>-0.12421</v>
       </c>
       <c r="AK191">
         <v>-90.625</v>
@@ -26817,7 +26817,7 @@
         <v>-93.75</v>
       </c>
       <c r="B192">
-        <v>-0.12275</v>
+        <v>-0.12304</v>
       </c>
       <c r="C192">
         <v>-92.1875</v>
@@ -26871,7 +26871,7 @@
         <v>-92.1875</v>
       </c>
       <c r="T192">
-        <v>-0.12642</v>
+        <v>-0.12651999999999999</v>
       </c>
       <c r="U192">
         <v>-92.1875</v>
@@ -26889,7 +26889,7 @@
         <v>-92.1875</v>
       </c>
       <c r="Z192">
-        <v>-0.12642</v>
+        <v>-0.12640999999999999</v>
       </c>
       <c r="AA192">
         <v>-92.1875</v>
@@ -26937,7 +26937,7 @@
         <v>-92.1875</v>
       </c>
       <c r="AP192">
-        <v>-0.12640000000000001</v>
+        <v>-0.12609999999999999</v>
       </c>
       <c r="AQ192">
         <v>-92.1875</v>
@@ -26957,7 +26957,7 @@
         <v>-95.3125</v>
       </c>
       <c r="B193">
-        <v>-0.12484000000000001</v>
+        <v>-0.12512000000000001</v>
       </c>
       <c r="C193">
         <v>-93.75</v>
@@ -27011,7 +27011,7 @@
         <v>-93.75</v>
       </c>
       <c r="T193">
-        <v>-0.12861</v>
+        <v>-0.12870999999999999</v>
       </c>
       <c r="U193">
         <v>-93.75</v>
@@ -27041,7 +27041,7 @@
         <v>-93.75</v>
       </c>
       <c r="AD193">
-        <v>-0.12862999999999999</v>
+        <v>-0.12862000000000001</v>
       </c>
       <c r="AE193">
         <v>-93.75</v>
@@ -27053,7 +27053,7 @@
         <v>-93.75</v>
       </c>
       <c r="AH193">
-        <v>-0.12867999999999999</v>
+        <v>-0.12867000000000001</v>
       </c>
       <c r="AI193">
         <v>-93.75</v>
@@ -27097,7 +27097,7 @@
         <v>-96.875</v>
       </c>
       <c r="B194">
-        <v>-0.12691</v>
+        <v>-0.12719</v>
       </c>
       <c r="C194">
         <v>-95.3125</v>
@@ -27127,7 +27127,7 @@
         <v>-95.3125</v>
       </c>
       <c r="L194">
-        <v>-0.13084000000000001</v>
+        <v>-0.13103999999999999</v>
       </c>
       <c r="M194">
         <v>-95.3125</v>
@@ -27181,7 +27181,7 @@
         <v>-95.3125</v>
       </c>
       <c r="AD194">
-        <v>-0.13084000000000001</v>
+        <v>-0.13084999999999999</v>
       </c>
       <c r="AE194">
         <v>-95.3125</v>
@@ -27217,7 +27217,7 @@
         <v>-95.3125</v>
       </c>
       <c r="AP194">
-        <v>-0.13084000000000001</v>
+        <v>-0.13081999999999999</v>
       </c>
       <c r="AQ194">
         <v>-95.3125</v>
@@ -27237,7 +27237,7 @@
         <v>-98.4375</v>
       </c>
       <c r="B195">
-        <v>-0.129</v>
+        <v>-0.12925</v>
       </c>
       <c r="C195">
         <v>-96.875</v>
@@ -27267,7 +27267,7 @@
         <v>-96.875</v>
       </c>
       <c r="L195">
-        <v>-0.13305</v>
+        <v>-0.13325000000000001</v>
       </c>
       <c r="M195">
         <v>-96.875</v>
@@ -27291,7 +27291,7 @@
         <v>-96.875</v>
       </c>
       <c r="T195">
-        <v>-0.13306999999999999</v>
+        <v>-0.13297</v>
       </c>
       <c r="U195">
         <v>-96.875</v>
@@ -27321,7 +27321,7 @@
         <v>-96.875</v>
       </c>
       <c r="AD195">
-        <v>-0.13305</v>
+        <v>-0.13306000000000001</v>
       </c>
       <c r="AE195">
         <v>-96.875</v>
@@ -27407,7 +27407,7 @@
         <v>-98.4375</v>
       </c>
       <c r="L196">
-        <v>-0.13532</v>
+        <v>-0.13552</v>
       </c>
       <c r="M196">
         <v>-98.4375</v>
@@ -27431,7 +27431,7 @@
         <v>-98.4375</v>
       </c>
       <c r="T196">
-        <v>-0.13532</v>
+        <v>-0.13511999999999999</v>
       </c>
       <c r="U196">
         <v>-98.4375</v>
@@ -27461,7 +27461,7 @@
         <v>-98.4375</v>
       </c>
       <c r="AD196">
-        <v>-0.13532</v>
+        <v>-0.13531000000000001</v>
       </c>
       <c r="AE196">
         <v>-98.4375</v>
@@ -27517,13 +27517,13 @@
         <v>-98.4375</v>
       </c>
       <c r="B197">
-        <v>-0.12925</v>
+        <v>-0.129</v>
       </c>
       <c r="C197">
         <v>-100</v>
       </c>
       <c r="D197">
-        <v>-0.13733000000000001</v>
+        <v>-0.13730000000000001</v>
       </c>
       <c r="E197">
         <v>-100</v>
@@ -27547,7 +27547,7 @@
         <v>-100</v>
       </c>
       <c r="L197">
-        <v>-0.13729</v>
+        <v>-0.13739000000000001</v>
       </c>
       <c r="M197">
         <v>-100</v>
@@ -27571,7 +27571,7 @@
         <v>-100</v>
       </c>
       <c r="T197">
-        <v>-0.13730000000000001</v>
+        <v>-0.13719999999999999</v>
       </c>
       <c r="U197">
         <v>-100</v>
@@ -27637,7 +27637,7 @@
         <v>-100</v>
       </c>
       <c r="AP197">
-        <v>-0.13729</v>
+        <v>-0.13728000000000001</v>
       </c>
       <c r="AQ197">
         <v>-100</v>
@@ -27657,13 +27657,13 @@
         <v>-96.875</v>
       </c>
       <c r="B198">
-        <v>-0.12719</v>
+        <v>-0.12691</v>
       </c>
       <c r="C198">
         <v>-98.4375</v>
       </c>
       <c r="D198">
-        <v>-0.13519999999999999</v>
+        <v>-0.13521</v>
       </c>
       <c r="E198">
         <v>-98.4375</v>
@@ -27687,7 +27687,7 @@
         <v>-98.4375</v>
       </c>
       <c r="L198">
-        <v>-0.13514000000000001</v>
+        <v>-0.13503999999999999</v>
       </c>
       <c r="M198">
         <v>-98.4375</v>
@@ -27711,7 +27711,7 @@
         <v>-98.4375</v>
       </c>
       <c r="T198">
-        <v>-0.13514000000000001</v>
+        <v>-0.13503999999999999</v>
       </c>
       <c r="U198">
         <v>-98.4375</v>
@@ -27741,7 +27741,7 @@
         <v>-98.4375</v>
       </c>
       <c r="AD198">
-        <v>-0.13514000000000001</v>
+        <v>-0.13513</v>
       </c>
       <c r="AE198">
         <v>-98.4375</v>
@@ -27777,7 +27777,7 @@
         <v>-98.4375</v>
       </c>
       <c r="AP198">
-        <v>-0.13514000000000001</v>
+        <v>-0.13511999999999999</v>
       </c>
       <c r="AQ198">
         <v>-98.4375</v>
@@ -27797,7 +27797,7 @@
         <v>-95.3125</v>
       </c>
       <c r="B199">
-        <v>-0.12512000000000001</v>
+        <v>-0.12484000000000001</v>
       </c>
       <c r="C199">
         <v>-96.875</v>
@@ -27851,7 +27851,7 @@
         <v>-96.875</v>
       </c>
       <c r="T199">
-        <v>-0.13291</v>
+        <v>-0.13270999999999999</v>
       </c>
       <c r="U199">
         <v>-96.875</v>
@@ -27869,7 +27869,7 @@
         <v>-96.875</v>
       </c>
       <c r="Z199">
-        <v>-0.13291</v>
+        <v>-0.13292000000000001</v>
       </c>
       <c r="AA199">
         <v>-96.875</v>
@@ -27937,13 +27937,13 @@
         <v>-93.75</v>
       </c>
       <c r="B200">
-        <v>-0.12304</v>
+        <v>-0.12275</v>
       </c>
       <c r="C200">
         <v>-95.3125</v>
       </c>
       <c r="D200">
-        <v>-0.13075999999999999</v>
+        <v>-0.13075000000000001</v>
       </c>
       <c r="E200">
         <v>-95.3125</v>
@@ -27967,7 +27967,7 @@
         <v>-95.3125</v>
       </c>
       <c r="L200">
-        <v>-0.13070000000000001</v>
+        <v>-0.1308</v>
       </c>
       <c r="M200">
         <v>-95.3125</v>
@@ -27991,7 +27991,7 @@
         <v>-95.3125</v>
       </c>
       <c r="T200">
-        <v>-0.13070000000000001</v>
+        <v>-0.13089999999999999</v>
       </c>
       <c r="U200">
         <v>-95.3125</v>
@@ -28021,7 +28021,7 @@
         <v>-95.3125</v>
       </c>
       <c r="AD200">
-        <v>-0.13070000000000001</v>
+        <v>-0.1308</v>
       </c>
       <c r="AE200">
         <v>-95.3125</v>
@@ -28033,7 +28033,7 @@
         <v>-95.3125</v>
       </c>
       <c r="AH200">
-        <v>-0.13075999999999999</v>
+        <v>-0.13075000000000001</v>
       </c>
       <c r="AI200">
         <v>-95.3125</v>
@@ -28057,7 +28057,7 @@
         <v>-95.3125</v>
       </c>
       <c r="AP200">
-        <v>-0.13070000000000001</v>
+        <v>-0.13009999999999999</v>
       </c>
       <c r="AQ200">
         <v>-95.3125</v>
@@ -28077,13 +28077,13 @@
         <v>-92.1875</v>
       </c>
       <c r="B201">
-        <v>-0.12098</v>
+        <v>-0.12068</v>
       </c>
       <c r="C201">
         <v>-93.75</v>
       </c>
       <c r="D201">
-        <v>-0.12852</v>
+        <v>-0.12851000000000001</v>
       </c>
       <c r="E201">
         <v>-93.75</v>
@@ -28107,7 +28107,7 @@
         <v>-93.75</v>
       </c>
       <c r="L201">
-        <v>-0.12848000000000001</v>
+        <v>-0.12858</v>
       </c>
       <c r="M201">
         <v>-93.75</v>
@@ -28131,7 +28131,7 @@
         <v>-93.75</v>
       </c>
       <c r="T201">
-        <v>-0.12847</v>
+        <v>-0.12827</v>
       </c>
       <c r="U201">
         <v>-93.75</v>
@@ -28149,7 +28149,7 @@
         <v>-93.75</v>
       </c>
       <c r="Z201">
-        <v>-0.12847</v>
+        <v>-0.12848000000000001</v>
       </c>
       <c r="AA201">
         <v>-93.75</v>
@@ -28161,7 +28161,7 @@
         <v>-93.75</v>
       </c>
       <c r="AD201">
-        <v>-0.12848000000000001</v>
+        <v>-0.1285</v>
       </c>
       <c r="AE201">
         <v>-93.75</v>
@@ -28179,7 +28179,7 @@
         <v>-93.75</v>
       </c>
       <c r="AJ201">
-        <v>-0.12852</v>
+        <v>-0.12853000000000001</v>
       </c>
       <c r="AK201">
         <v>-93.75</v>
@@ -28197,7 +28197,7 @@
         <v>-93.75</v>
       </c>
       <c r="AP201">
-        <v>-0.12848000000000001</v>
+        <v>-0.12845000000000001</v>
       </c>
       <c r="AQ201">
         <v>-93.75</v>
@@ -28217,13 +28217,13 @@
         <v>-90.625</v>
       </c>
       <c r="B202">
-        <v>-0.11890000000000001</v>
+        <v>-0.1186</v>
       </c>
       <c r="C202">
         <v>-92.1875</v>
       </c>
       <c r="D202">
-        <v>-0.1263</v>
+        <v>-0.12631000000000001</v>
       </c>
       <c r="E202">
         <v>-92.1875</v>
@@ -28247,7 +28247,7 @@
         <v>-92.1875</v>
       </c>
       <c r="L202">
-        <v>-0.12626999999999999</v>
+        <v>-0.12617</v>
       </c>
       <c r="M202">
         <v>-92.1875</v>
@@ -28271,7 +28271,7 @@
         <v>-92.1875</v>
       </c>
       <c r="T202">
-        <v>-0.12625</v>
+        <v>-0.12615000000000001</v>
       </c>
       <c r="U202">
         <v>-92.1875</v>
@@ -28301,7 +28301,7 @@
         <v>-92.1875</v>
       </c>
       <c r="AD202">
-        <v>-0.12626999999999999</v>
+        <v>-0.12626000000000001</v>
       </c>
       <c r="AE202">
         <v>-92.1875</v>
@@ -28357,13 +28357,13 @@
         <v>-89.0625</v>
       </c>
       <c r="B203">
-        <v>-0.11684</v>
+        <v>-0.11654</v>
       </c>
       <c r="C203">
         <v>-90.625</v>
       </c>
       <c r="D203">
-        <v>-0.12409000000000001</v>
+        <v>-0.12408</v>
       </c>
       <c r="E203">
         <v>-90.625</v>
@@ -28387,7 +28387,7 @@
         <v>-90.625</v>
       </c>
       <c r="L203">
-        <v>-0.12404</v>
+        <v>-0.12424</v>
       </c>
       <c r="M203">
         <v>-90.625</v>
@@ -28411,7 +28411,7 @@
         <v>-90.625</v>
       </c>
       <c r="T203">
-        <v>-0.12402000000000001</v>
+        <v>-0.12411999999999999</v>
       </c>
       <c r="U203">
         <v>-90.625</v>
@@ -28441,7 +28441,7 @@
         <v>-90.625</v>
       </c>
       <c r="AD203">
-        <v>-0.12404</v>
+        <v>-0.12401</v>
       </c>
       <c r="AE203">
         <v>-90.625</v>
@@ -28477,7 +28477,7 @@
         <v>-90.625</v>
       </c>
       <c r="AP203">
-        <v>-0.12404</v>
+        <v>-0.12402000000000001</v>
       </c>
       <c r="AQ203">
         <v>-90.625</v>
@@ -28497,13 +28497,13 @@
         <v>-87.5</v>
       </c>
       <c r="B204">
-        <v>-0.11475</v>
+        <v>-0.11445</v>
       </c>
       <c r="C204">
         <v>-89.0625</v>
       </c>
       <c r="D204">
-        <v>-0.12186</v>
+        <v>-0.12185</v>
       </c>
       <c r="E204">
         <v>-89.0625</v>
@@ -28527,7 +28527,7 @@
         <v>-89.0625</v>
       </c>
       <c r="L204">
-        <v>-0.12182999999999999</v>
+        <v>-0.12193</v>
       </c>
       <c r="M204">
         <v>-89.0625</v>
@@ -28551,7 +28551,7 @@
         <v>-89.0625</v>
       </c>
       <c r="T204">
-        <v>-0.12181</v>
+        <v>-0.12191</v>
       </c>
       <c r="U204">
         <v>-89.0625</v>
@@ -28581,7 +28581,7 @@
         <v>-89.0625</v>
       </c>
       <c r="AD204">
-        <v>-0.12182999999999999</v>
+        <v>-0.12182</v>
       </c>
       <c r="AE204">
         <v>-89.0625</v>
@@ -28617,7 +28617,7 @@
         <v>-89.0625</v>
       </c>
       <c r="AP204">
-        <v>-0.12182999999999999</v>
+        <v>-0.12181</v>
       </c>
       <c r="AQ204">
         <v>-89.0625</v>
@@ -28637,13 +28637,13 @@
         <v>-85.9375</v>
       </c>
       <c r="B205">
-        <v>-0.11268</v>
+        <v>-0.11237</v>
       </c>
       <c r="C205">
         <v>-87.5</v>
       </c>
       <c r="D205">
-        <v>-0.11965000000000001</v>
+        <v>-0.11966</v>
       </c>
       <c r="E205">
         <v>-87.5</v>
@@ -28667,7 +28667,7 @@
         <v>-87.5</v>
       </c>
       <c r="L205">
-        <v>-0.11960999999999999</v>
+        <v>-0.11971</v>
       </c>
       <c r="M205">
         <v>-87.5</v>
@@ -28691,7 +28691,7 @@
         <v>-87.5</v>
       </c>
       <c r="T205">
-        <v>-0.11958000000000001</v>
+        <v>-0.11948</v>
       </c>
       <c r="U205">
         <v>-87.5</v>
@@ -28721,7 +28721,7 @@
         <v>-87.5</v>
       </c>
       <c r="AD205">
-        <v>-0.11960999999999999</v>
+        <v>-0.1196</v>
       </c>
       <c r="AE205">
         <v>-87.5</v>
@@ -28757,7 +28757,7 @@
         <v>-87.5</v>
       </c>
       <c r="AP205">
-        <v>-0.11960999999999999</v>
+        <v>-0.11962</v>
       </c>
       <c r="AQ205">
         <v>-87.5</v>
@@ -28777,13 +28777,13 @@
         <v>-84.375</v>
       </c>
       <c r="B206">
-        <v>-0.11058999999999999</v>
+        <v>-0.1103</v>
       </c>
       <c r="C206">
         <v>-85.9375</v>
       </c>
       <c r="D206">
-        <v>-0.11747</v>
+        <v>-0.11745</v>
       </c>
       <c r="E206">
         <v>-85.9375</v>
@@ -28807,7 +28807,7 @@
         <v>-85.9375</v>
       </c>
       <c r="L206">
-        <v>-0.11742</v>
+        <v>-0.11722</v>
       </c>
       <c r="M206">
         <v>-85.9375</v>
@@ -28831,7 +28831,7 @@
         <v>-85.9375</v>
       </c>
       <c r="T206">
-        <v>-0.11738999999999999</v>
+        <v>-0.11729000000000001</v>
       </c>
       <c r="U206">
         <v>-85.9375</v>
@@ -28861,7 +28861,7 @@
         <v>-85.9375</v>
       </c>
       <c r="AD206">
-        <v>-0.11742</v>
+        <v>-0.11743000000000001</v>
       </c>
       <c r="AE206">
         <v>-85.9375</v>
@@ -28873,7 +28873,7 @@
         <v>-85.9375</v>
       </c>
       <c r="AH206">
-        <v>-0.11747</v>
+        <v>-0.11742</v>
       </c>
       <c r="AI206">
         <v>-85.9375</v>
@@ -28897,7 +28897,7 @@
         <v>-85.9375</v>
       </c>
       <c r="AP206">
-        <v>-0.11742</v>
+        <v>-0.1174</v>
       </c>
       <c r="AQ206">
         <v>-85.9375</v>
@@ -28917,13 +28917,13 @@
         <v>-82.8125</v>
       </c>
       <c r="B207">
-        <v>-0.10853</v>
+        <v>-0.10824</v>
       </c>
       <c r="C207">
         <v>-84.375</v>
       </c>
       <c r="D207">
-        <v>-0.11525000000000001</v>
+        <v>-0.11524</v>
       </c>
       <c r="E207">
         <v>-84.375</v>
@@ -28947,7 +28947,7 @@
         <v>-84.375</v>
       </c>
       <c r="L207">
-        <v>-0.11522</v>
+        <v>-0.11502</v>
       </c>
       <c r="M207">
         <v>-84.375</v>
@@ -28971,7 +28971,7 @@
         <v>-84.375</v>
       </c>
       <c r="T207">
-        <v>-0.11519</v>
+        <v>-0.11529</v>
       </c>
       <c r="U207">
         <v>-84.375</v>
@@ -29057,13 +29057,13 @@
         <v>-81.25</v>
       </c>
       <c r="B208">
-        <v>-0.10646</v>
+        <v>-0.10619000000000001</v>
       </c>
       <c r="C208">
         <v>-82.8125</v>
       </c>
       <c r="D208">
-        <v>-0.11307</v>
+        <v>-0.11305999999999999</v>
       </c>
       <c r="E208">
         <v>-82.8125</v>
@@ -29087,7 +29087,7 @@
         <v>-82.8125</v>
       </c>
       <c r="L208">
-        <v>-0.11302</v>
+        <v>-0.11282</v>
       </c>
       <c r="M208">
         <v>-82.8125</v>
@@ -29111,7 +29111,7 @@
         <v>-82.8125</v>
       </c>
       <c r="T208">
-        <v>-0.11301</v>
+        <v>-0.11291</v>
       </c>
       <c r="U208">
         <v>-82.8125</v>
@@ -29197,13 +29197,13 @@
         <v>-79.6875</v>
       </c>
       <c r="B209">
-        <v>-0.10439</v>
+        <v>-0.10414</v>
       </c>
       <c r="C209">
         <v>-81.25</v>
       </c>
       <c r="D209">
-        <v>-0.11088000000000001</v>
+        <v>-0.11089</v>
       </c>
       <c r="E209">
         <v>-81.25</v>
@@ -29227,7 +29227,7 @@
         <v>-81.25</v>
       </c>
       <c r="L209">
-        <v>-0.11083999999999999</v>
+        <v>-0.11104</v>
       </c>
       <c r="M209">
         <v>-81.25</v>
@@ -29251,7 +29251,7 @@
         <v>-81.25</v>
       </c>
       <c r="T209">
-        <v>-0.11081000000000001</v>
+        <v>-0.11090999999999999</v>
       </c>
       <c r="U209">
         <v>-81.25</v>
@@ -29269,7 +29269,7 @@
         <v>-81.25</v>
       </c>
       <c r="Z209">
-        <v>-0.11081000000000001</v>
+        <v>-0.11078</v>
       </c>
       <c r="AA209">
         <v>-81.25</v>
@@ -29281,7 +29281,7 @@
         <v>-81.25</v>
       </c>
       <c r="AD209">
-        <v>-0.11083999999999999</v>
+        <v>-0.11082</v>
       </c>
       <c r="AE209">
         <v>-81.25</v>
@@ -29317,7 +29317,7 @@
         <v>-81.25</v>
       </c>
       <c r="AP209">
-        <v>-0.11083999999999999</v>
+        <v>-0.1108</v>
       </c>
       <c r="AQ209">
         <v>-81.25</v>
@@ -29337,13 +29337,13 @@
         <v>-78.125</v>
       </c>
       <c r="B210">
-        <v>-0.10231999999999999</v>
+        <v>-0.10206999999999999</v>
       </c>
       <c r="C210">
         <v>-79.6875</v>
       </c>
       <c r="D210">
-        <v>-0.1087</v>
+        <v>-0.10871</v>
       </c>
       <c r="E210">
         <v>-79.6875</v>
@@ -29367,7 +29367,7 @@
         <v>-79.6875</v>
       </c>
       <c r="L210">
-        <v>-0.10866000000000001</v>
+        <v>-0.10886</v>
       </c>
       <c r="M210">
         <v>-79.6875</v>
@@ -29477,13 +29477,13 @@
         <v>-76.5625</v>
       </c>
       <c r="B211">
-        <v>-0.10026</v>
+        <v>-0.10002999999999999</v>
       </c>
       <c r="C211">
         <v>-78.125</v>
       </c>
       <c r="D211">
-        <v>-0.10650999999999999</v>
+        <v>-0.1065</v>
       </c>
       <c r="E211">
         <v>-78.125</v>
@@ -29561,7 +29561,7 @@
         <v>-78.125</v>
       </c>
       <c r="AD211">
-        <v>-0.10648000000000001</v>
+        <v>-0.10642</v>
       </c>
       <c r="AE211">
         <v>-78.125</v>
@@ -29573,7 +29573,7 @@
         <v>-78.125</v>
       </c>
       <c r="AH211">
-        <v>-0.10650999999999999</v>
+        <v>-0.1065</v>
       </c>
       <c r="AI211">
         <v>-78.125</v>
@@ -29597,7 +29597,7 @@
         <v>-78.125</v>
       </c>
       <c r="AP211">
-        <v>-0.10648000000000001</v>
+        <v>-0.1065</v>
       </c>
       <c r="AQ211">
         <v>-78.125</v>
@@ -29617,13 +29617,13 @@
         <v>-75</v>
       </c>
       <c r="B212">
-        <v>-9.8199999999999996E-2</v>
+        <v>-9.7970000000000002E-2</v>
       </c>
       <c r="C212">
         <v>-76.5625</v>
       </c>
       <c r="D212">
-        <v>-0.10435</v>
+        <v>-0.10437</v>
       </c>
       <c r="E212">
         <v>-76.5625</v>
@@ -29647,7 +29647,7 @@
         <v>-76.5625</v>
       </c>
       <c r="L212">
-        <v>-0.1043</v>
+        <v>-0.1042</v>
       </c>
       <c r="M212">
         <v>-76.5625</v>
@@ -29671,7 +29671,7 @@
         <v>-76.5625</v>
       </c>
       <c r="T212">
-        <v>-0.10428999999999999</v>
+        <v>-0.10409</v>
       </c>
       <c r="U212">
         <v>-76.5625</v>
@@ -29757,7 +29757,7 @@
         <v>-73.4375</v>
       </c>
       <c r="B213">
-        <v>-9.6140000000000003E-2</v>
+        <v>-9.5920000000000005E-2</v>
       </c>
       <c r="C213">
         <v>-75</v>
@@ -29787,7 +29787,7 @@
         <v>-75</v>
       </c>
       <c r="L213">
-        <v>-0.10215</v>
+        <v>-0.10224999999999999</v>
       </c>
       <c r="M213">
         <v>-75</v>
@@ -29841,7 +29841,7 @@
         <v>-75</v>
       </c>
       <c r="AD213">
-        <v>-0.10215</v>
+        <v>-0.10212</v>
       </c>
       <c r="AE213">
         <v>-75</v>
@@ -29877,7 +29877,7 @@
         <v>-75</v>
       </c>
       <c r="AP213">
-        <v>-0.10215</v>
+        <v>-0.10213</v>
       </c>
       <c r="AQ213">
         <v>-75</v>
@@ -29897,7 +29897,7 @@
         <v>-71.875</v>
       </c>
       <c r="B214">
-        <v>-9.4079999999999997E-2</v>
+        <v>-9.3859999999999999E-2</v>
       </c>
       <c r="C214">
         <v>-73.4375</v>
@@ -29927,7 +29927,7 @@
         <v>-73.4375</v>
       </c>
       <c r="L214">
-        <v>-9.9989999999999996E-2</v>
+        <v>-0.10009</v>
       </c>
       <c r="M214">
         <v>-73.4375</v>
@@ -29981,7 +29981,7 @@
         <v>-73.4375</v>
       </c>
       <c r="AD214">
-        <v>-9.9989999999999996E-2</v>
+        <v>-9.9979999999999999E-2</v>
       </c>
       <c r="AE214">
         <v>-73.4375</v>
@@ -30017,7 +30017,7 @@
         <v>-73.4375</v>
       </c>
       <c r="AP214">
-        <v>-9.9989999999999996E-2</v>
+        <v>-9.9970000000000003E-2</v>
       </c>
       <c r="AQ214">
         <v>-73.4375</v>
@@ -30037,7 +30037,7 @@
         <v>-70.3125</v>
       </c>
       <c r="B215">
-        <v>-9.2030000000000001E-2</v>
+        <v>-9.1810000000000003E-2</v>
       </c>
       <c r="C215">
         <v>-71.875</v>
@@ -30067,7 +30067,7 @@
         <v>-71.875</v>
       </c>
       <c r="L215">
-        <v>-9.7820000000000004E-2</v>
+        <v>-9.7720000000000001E-2</v>
       </c>
       <c r="M215">
         <v>-71.875</v>
@@ -30091,7 +30091,7 @@
         <v>-71.875</v>
       </c>
       <c r="T215">
-        <v>-9.7809999999999994E-2</v>
+        <v>-9.7710000000000005E-2</v>
       </c>
       <c r="U215">
         <v>-71.875</v>
@@ -30121,7 +30121,7 @@
         <v>-71.875</v>
       </c>
       <c r="AD215">
-        <v>-9.7820000000000004E-2</v>
+        <v>-9.7809999999999994E-2</v>
       </c>
       <c r="AE215">
         <v>-71.875</v>
@@ -30157,7 +30157,7 @@
         <v>-71.875</v>
       </c>
       <c r="AP215">
-        <v>-9.7820000000000004E-2</v>
+        <v>-9.7799999999999998E-2</v>
       </c>
       <c r="AQ215">
         <v>-71.875</v>
@@ -30177,7 +30177,7 @@
         <v>-68.75</v>
       </c>
       <c r="B216">
-        <v>-8.9990000000000001E-2</v>
+        <v>-8.9770000000000003E-2</v>
       </c>
       <c r="C216">
         <v>-70.3125</v>
@@ -30207,7 +30207,7 @@
         <v>-70.3125</v>
       </c>
       <c r="L216">
-        <v>-9.5680000000000001E-2</v>
+        <v>-9.5880000000000007E-2</v>
       </c>
       <c r="M216">
         <v>-70.3125</v>
@@ -30231,7 +30231,7 @@
         <v>-70.3125</v>
       </c>
       <c r="T216">
-        <v>-9.5659999999999995E-2</v>
+        <v>-9.5759999999999998E-2</v>
       </c>
       <c r="U216">
         <v>-70.3125</v>
@@ -30261,7 +30261,7 @@
         <v>-70.3125</v>
       </c>
       <c r="AD216">
-        <v>-9.5680000000000001E-2</v>
+        <v>-9.5699999999999993E-2</v>
       </c>
       <c r="AE216">
         <v>-70.3125</v>
@@ -30297,7 +30297,7 @@
         <v>-70.3125</v>
       </c>
       <c r="AP216">
-        <v>-9.5680000000000001E-2</v>
+        <v>-9.5710000000000003E-2</v>
       </c>
       <c r="AQ216">
         <v>-70.3125</v>
@@ -30314,10 +30314,10 @@
     </row>
     <row r="217" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>-65.625</v>
+        <v>-67.1875</v>
       </c>
       <c r="B217">
-        <v>0</v>
+        <v>-8.7720000000000006E-2</v>
       </c>
       <c r="C217">
         <v>-68.75</v>
@@ -30347,7 +30347,7 @@
         <v>-68.75</v>
       </c>
       <c r="L217">
-        <v>-9.3530000000000002E-2</v>
+        <v>-9.3630000000000005E-2</v>
       </c>
       <c r="M217">
         <v>-68.75</v>
@@ -30371,7 +30371,7 @@
         <v>-68.75</v>
       </c>
       <c r="T217">
-        <v>-9.3509999999999996E-2</v>
+        <v>-9.3310000000000004E-2</v>
       </c>
       <c r="U217">
         <v>-68.75</v>
@@ -30401,7 +30401,7 @@
         <v>-68.75</v>
       </c>
       <c r="AD217">
-        <v>-9.3530000000000002E-2</v>
+        <v>-9.3520000000000006E-2</v>
       </c>
       <c r="AE217">
         <v>-68.75</v>
@@ -30437,7 +30437,7 @@
         <v>-68.75</v>
       </c>
       <c r="AP217">
-        <v>-9.3530000000000002E-2</v>
+        <v>-9.3579999999999997E-2</v>
       </c>
       <c r="AQ217">
         <v>-68.75</v>
@@ -30454,10 +30454,10 @@
     </row>
     <row r="218" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A218">
-        <v>-64.0625</v>
+        <v>-65.625</v>
       </c>
       <c r="B218">
-        <v>0</v>
+        <v>-8.566E-2</v>
       </c>
       <c r="C218">
         <v>-67.1875</v>
@@ -30487,7 +30487,7 @@
         <v>-67.1875</v>
       </c>
       <c r="L218">
-        <v>-9.1380000000000003E-2</v>
+        <v>-9.128E-2</v>
       </c>
       <c r="M218">
         <v>-67.1875</v>
@@ -30511,7 +30511,7 @@
         <v>-67.1875</v>
       </c>
       <c r="T218">
-        <v>-9.1359999999999997E-2</v>
+        <v>-9.1560000000000002E-2</v>
       </c>
       <c r="U218">
         <v>-67.1875</v>
@@ -30594,10 +30594,10 @@
     </row>
     <row r="219" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A219">
-        <v>-62.5</v>
+        <v>-64.0625</v>
       </c>
       <c r="B219">
-        <v>0</v>
+        <v>-8.3610000000000004E-2</v>
       </c>
       <c r="C219">
         <v>-65.625</v>
@@ -30627,7 +30627,7 @@
         <v>-65.625</v>
       </c>
       <c r="L219">
-        <v>-8.9209999999999998E-2</v>
+        <v>-8.9010000000000006E-2</v>
       </c>
       <c r="M219">
         <v>-65.625</v>
@@ -30651,7 +30651,7 @@
         <v>-65.625</v>
       </c>
       <c r="T219">
-        <v>-8.9200000000000002E-2</v>
+        <v>-8.8999999999999996E-2</v>
       </c>
       <c r="U219">
         <v>-65.625</v>
@@ -30681,7 +30681,7 @@
         <v>-65.625</v>
       </c>
       <c r="AD219">
-        <v>-8.9209999999999998E-2</v>
+        <v>-8.9200000000000002E-2</v>
       </c>
       <c r="AE219">
         <v>-65.625</v>
@@ -30693,7 +30693,7 @@
         <v>-65.625</v>
       </c>
       <c r="AH219">
-        <v>-8.9249999999999996E-2</v>
+        <v>-8.9260000000000006E-2</v>
       </c>
       <c r="AI219">
         <v>-65.625</v>
@@ -30717,7 +30717,7 @@
         <v>-65.625</v>
       </c>
       <c r="AP219">
-        <v>-8.9209999999999998E-2</v>
+        <v>-8.9249999999999996E-2</v>
       </c>
       <c r="AQ219">
         <v>-65.625</v>
@@ -30734,16 +30734,16 @@
     </row>
     <row r="220" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A220">
-        <v>-60.9375</v>
+        <v>-62.5</v>
       </c>
       <c r="B220">
-        <v>0</v>
+        <v>-8.1549999999999997E-2</v>
       </c>
       <c r="C220">
         <v>-64.0625</v>
       </c>
       <c r="D220">
-        <v>-8.7099999999999997E-2</v>
+        <v>-8.7120000000000003E-2</v>
       </c>
       <c r="E220">
         <v>-64.0625</v>
@@ -30767,7 +30767,7 @@
         <v>-64.0625</v>
       </c>
       <c r="L220">
-        <v>-8.7080000000000005E-2</v>
+        <v>-8.6980000000000002E-2</v>
       </c>
       <c r="M220">
         <v>-64.0625</v>
@@ -30821,7 +30821,7 @@
         <v>-64.0625</v>
       </c>
       <c r="AD220">
-        <v>-8.7080000000000005E-2</v>
+        <v>-8.7059999999999998E-2</v>
       </c>
       <c r="AE220">
         <v>-64.0625</v>
@@ -30833,7 +30833,7 @@
         <v>-64.0625</v>
       </c>
       <c r="AH220">
-        <v>-8.7099999999999997E-2</v>
+        <v>-8.7110000000000007E-2</v>
       </c>
       <c r="AI220">
         <v>-64.0625</v>
@@ -30874,10 +30874,10 @@
     </row>
     <row r="221" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>-59.375</v>
+        <v>-60.9375</v>
       </c>
       <c r="B221">
-        <v>0</v>
+        <v>-7.9509999999999997E-2</v>
       </c>
       <c r="C221">
         <v>-62.5</v>
@@ -30907,7 +30907,7 @@
         <v>-62.5</v>
       </c>
       <c r="L221">
-        <v>-8.4919999999999995E-2</v>
+        <v>-8.5019999999999998E-2</v>
       </c>
       <c r="M221">
         <v>-62.5</v>
@@ -30931,7 +30931,7 @@
         <v>-62.5</v>
       </c>
       <c r="T221">
-        <v>-8.4900000000000003E-2</v>
+        <v>-8.48E-2</v>
       </c>
       <c r="U221">
         <v>-62.5</v>
@@ -30961,7 +30961,7 @@
         <v>-62.5</v>
       </c>
       <c r="AD221">
-        <v>-8.4919999999999995E-2</v>
+        <v>-8.4930000000000005E-2</v>
       </c>
       <c r="AE221">
         <v>-62.5</v>
@@ -30997,7 +30997,7 @@
         <v>-62.5</v>
       </c>
       <c r="AP221">
-        <v>-8.4919999999999995E-2</v>
+        <v>-8.4909999999999999E-2</v>
       </c>
       <c r="AQ221">
         <v>-62.5</v>
@@ -31014,10 +31014,10 @@
     </row>
     <row r="222" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A222">
-        <v>-57.8125</v>
+        <v>-59.375</v>
       </c>
       <c r="B222">
-        <v>0</v>
+        <v>-7.7460000000000001E-2</v>
       </c>
       <c r="C222">
         <v>-60.9375</v>
@@ -31047,7 +31047,7 @@
         <v>-60.9375</v>
       </c>
       <c r="L222">
-        <v>-8.2790000000000002E-2</v>
+        <v>-8.2589999999999997E-2</v>
       </c>
       <c r="M222">
         <v>-60.9375</v>
@@ -31071,7 +31071,7 @@
         <v>-60.9375</v>
       </c>
       <c r="T222">
-        <v>-8.2769999999999996E-2</v>
+        <v>-8.2869999999999999E-2</v>
       </c>
       <c r="U222">
         <v>-60.9375</v>
@@ -31101,7 +31101,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AD222">
-        <v>-8.2790000000000002E-2</v>
+        <v>-8.2799999999999999E-2</v>
       </c>
       <c r="AE222">
         <v>-60.9375</v>
@@ -31113,7 +31113,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AH222">
-        <v>-8.2799999999999999E-2</v>
+        <v>-8.2809999999999995E-2</v>
       </c>
       <c r="AI222">
         <v>-60.9375</v>
@@ -31137,7 +31137,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AP222">
-        <v>-8.2790000000000002E-2</v>
+        <v>-8.276E-2</v>
       </c>
       <c r="AQ222">
         <v>-60.9375</v>
@@ -31154,10 +31154,10 @@
     </row>
     <row r="223" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A223">
-        <v>-56.25</v>
+        <v>-57.8125</v>
       </c>
       <c r="B223">
-        <v>0</v>
+        <v>-7.5410000000000005E-2</v>
       </c>
       <c r="C223">
         <v>-59.375</v>
@@ -31187,7 +31187,7 @@
         <v>-59.375</v>
       </c>
       <c r="L223">
-        <v>-8.0640000000000003E-2</v>
+        <v>-8.0839999999999995E-2</v>
       </c>
       <c r="M223">
         <v>-59.375</v>
@@ -31211,7 +31211,7 @@
         <v>-59.375</v>
       </c>
       <c r="T223">
-        <v>-8.0619999999999997E-2</v>
+        <v>-8.0420000000000005E-2</v>
       </c>
       <c r="U223">
         <v>-59.375</v>
@@ -31229,7 +31229,7 @@
         <v>-59.375</v>
       </c>
       <c r="Z223">
-        <v>-8.0619999999999997E-2</v>
+        <v>-8.0610000000000001E-2</v>
       </c>
       <c r="AA223">
         <v>-59.375</v>
@@ -31241,7 +31241,7 @@
         <v>-59.375</v>
       </c>
       <c r="AD223">
-        <v>-8.0640000000000003E-2</v>
+        <v>-8.0610000000000001E-2</v>
       </c>
       <c r="AE223">
         <v>-59.375</v>
@@ -31277,7 +31277,7 @@
         <v>-59.375</v>
       </c>
       <c r="AP223">
-        <v>-8.0640000000000003E-2</v>
+        <v>-8.0619999999999997E-2</v>
       </c>
       <c r="AQ223">
         <v>-59.375</v>
@@ -31294,10 +31294,10 @@
     </row>
     <row r="224" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A224">
-        <v>-54.6875</v>
+        <v>-56.25</v>
       </c>
       <c r="B224">
-        <v>0</v>
+        <v>-7.3370000000000005E-2</v>
       </c>
       <c r="C224">
         <v>-57.8125</v>
@@ -31327,7 +31327,7 @@
         <v>-57.8125</v>
       </c>
       <c r="L224">
-        <v>-7.85E-2</v>
+        <v>-7.8299999999999995E-2</v>
       </c>
       <c r="M224">
         <v>-57.8125</v>
@@ -31351,7 +31351,7 @@
         <v>-57.8125</v>
       </c>
       <c r="T224">
-        <v>-7.8490000000000004E-2</v>
+        <v>-7.8390000000000001E-2</v>
       </c>
       <c r="U224">
         <v>-57.8125</v>
@@ -31381,7 +31381,7 @@
         <v>-57.8125</v>
       </c>
       <c r="AD224">
-        <v>-7.85E-2</v>
+        <v>-7.8200000000000006E-2</v>
       </c>
       <c r="AE224">
         <v>-57.8125</v>
@@ -31417,7 +31417,7 @@
         <v>-57.8125</v>
       </c>
       <c r="AP224">
-        <v>-7.85E-2</v>
+        <v>-7.8299999999999995E-2</v>
       </c>
       <c r="AQ224">
         <v>-57.8125</v>
@@ -31434,10 +31434,10 @@
     </row>
     <row r="225" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A225">
-        <v>-53.125</v>
+        <v>-54.6875</v>
       </c>
       <c r="B225">
-        <v>0</v>
+        <v>-7.1330000000000005E-2</v>
       </c>
       <c r="C225">
         <v>-56.25</v>
@@ -31491,7 +31491,7 @@
         <v>-56.25</v>
       </c>
       <c r="T225">
-        <v>-7.6359999999999997E-2</v>
+        <v>-7.6259999999999994E-2</v>
       </c>
       <c r="U225">
         <v>-56.25</v>
@@ -31521,7 +31521,7 @@
         <v>-56.25</v>
       </c>
       <c r="AD225">
-        <v>-7.6359999999999997E-2</v>
+        <v>-7.639E-2</v>
       </c>
       <c r="AE225">
         <v>-56.25</v>
@@ -31533,7 +31533,7 @@
         <v>-56.25</v>
       </c>
       <c r="AH225">
-        <v>-7.639E-2</v>
+        <v>-7.6399999999999996E-2</v>
       </c>
       <c r="AI225">
         <v>-56.25</v>
@@ -31557,7 +31557,7 @@
         <v>-56.25</v>
       </c>
       <c r="AP225">
-        <v>-7.6359999999999997E-2</v>
+        <v>-7.6399999999999996E-2</v>
       </c>
       <c r="AQ225">
         <v>-56.25</v>
@@ -31574,10 +31574,10 @@
     </row>
     <row r="226" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>-51.5625</v>
+        <v>-53.125</v>
       </c>
       <c r="B226">
-        <v>0</v>
+        <v>-6.9269999999999998E-2</v>
       </c>
       <c r="C226">
         <v>-54.6875</v>
@@ -31607,7 +31607,7 @@
         <v>-54.6875</v>
       </c>
       <c r="L226">
-        <v>-7.424E-2</v>
+        <v>-7.4440000000000006E-2</v>
       </c>
       <c r="M226">
         <v>-54.6875</v>
@@ -31631,7 +31631,7 @@
         <v>-54.6875</v>
       </c>
       <c r="T226">
-        <v>-7.4219999999999994E-2</v>
+        <v>-7.442E-2</v>
       </c>
       <c r="U226">
         <v>-54.6875</v>
@@ -31649,7 +31649,7 @@
         <v>-54.6875</v>
       </c>
       <c r="Z226">
-        <v>-7.4219999999999994E-2</v>
+        <v>-7.4209999999999998E-2</v>
       </c>
       <c r="AA226">
         <v>-54.6875</v>
@@ -31661,7 +31661,7 @@
         <v>-54.6875</v>
       </c>
       <c r="AD226">
-        <v>-7.424E-2</v>
+        <v>-7.4260000000000007E-2</v>
       </c>
       <c r="AE226">
         <v>-54.6875</v>
@@ -31697,7 +31697,7 @@
         <v>-54.6875</v>
       </c>
       <c r="AP226">
-        <v>-7.424E-2</v>
+        <v>-7.4249999999999997E-2</v>
       </c>
       <c r="AQ226">
         <v>-54.6875</v>
@@ -31714,10 +31714,10 @@
     </row>
     <row r="227" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A227">
-        <v>-50</v>
+        <v>-51.5625</v>
       </c>
       <c r="B227">
-        <v>0</v>
+        <v>-6.7239999999999994E-2</v>
       </c>
       <c r="C227">
         <v>-53.125</v>
@@ -31747,7 +31747,7 @@
         <v>-53.125</v>
       </c>
       <c r="L227">
-        <v>-7.2090000000000001E-2</v>
+        <v>-7.2190000000000004E-2</v>
       </c>
       <c r="M227">
         <v>-53.125</v>
@@ -31854,10 +31854,10 @@
     </row>
     <row r="228" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>-48.4375</v>
+        <v>-50</v>
       </c>
       <c r="B228">
-        <v>0</v>
+        <v>-6.5129999999999993E-2</v>
       </c>
       <c r="C228">
         <v>-51.5625</v>
@@ -31911,7 +31911,7 @@
         <v>-51.5625</v>
       </c>
       <c r="T228">
-        <v>-6.9959999999999994E-2</v>
+        <v>-6.9760000000000003E-2</v>
       </c>
       <c r="U228">
         <v>-51.5625</v>
@@ -31941,7 +31941,7 @@
         <v>-51.5625</v>
       </c>
       <c r="AD228">
-        <v>-6.9980000000000001E-2</v>
+        <v>-6.9970000000000004E-2</v>
       </c>
       <c r="AE228">
         <v>-51.5625</v>
@@ -31953,13 +31953,13 @@
         <v>-51.5625</v>
       </c>
       <c r="AH228">
-        <v>-6.9980000000000001E-2</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="AI228">
         <v>-51.5625</v>
       </c>
       <c r="AJ228">
-        <v>-6.9959999999999994E-2</v>
+        <v>-6.9989999999999997E-2</v>
       </c>
       <c r="AK228">
         <v>-51.5625</v>
@@ -31977,7 +31977,7 @@
         <v>-51.5625</v>
       </c>
       <c r="AP228">
-        <v>-6.9980000000000001E-2</v>
+        <v>-6.9959999999999994E-2</v>
       </c>
       <c r="AQ228">
         <v>-51.5625</v>
@@ -31994,10 +31994,10 @@
     </row>
     <row r="229" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A229">
-        <v>-46.875</v>
+        <v>-48.4375</v>
       </c>
       <c r="B229">
-        <v>0</v>
+        <v>-6.3089999999999993E-2</v>
       </c>
       <c r="C229">
         <v>-50</v>
@@ -32027,7 +32027,7 @@
         <v>-50</v>
       </c>
       <c r="L229">
-        <v>-6.7780000000000007E-2</v>
+        <v>-6.7979999999999999E-2</v>
       </c>
       <c r="M229">
         <v>-50</v>
@@ -32051,7 +32051,7 @@
         <v>-50</v>
       </c>
       <c r="T229">
-        <v>-6.7760000000000001E-2</v>
+        <v>-6.7559999999999995E-2</v>
       </c>
       <c r="U229">
         <v>-50</v>
@@ -32081,7 +32081,7 @@
         <v>-50</v>
       </c>
       <c r="AD229">
-        <v>-6.7780000000000007E-2</v>
+        <v>-6.7760000000000001E-2</v>
       </c>
       <c r="AE229">
         <v>-50</v>
@@ -32099,7 +32099,7 @@
         <v>-50</v>
       </c>
       <c r="AJ229">
-        <v>-6.7780000000000007E-2</v>
+        <v>-6.7739999999999995E-2</v>
       </c>
       <c r="AK229">
         <v>-50</v>
@@ -32117,7 +32117,7 @@
         <v>-50</v>
       </c>
       <c r="AP229">
-        <v>-6.7780000000000007E-2</v>
+        <v>-6.7760000000000001E-2</v>
       </c>
       <c r="AQ229">
         <v>-50</v>
@@ -32134,10 +32134,10 @@
     </row>
     <row r="230" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>-45.3125</v>
+        <v>-46.875</v>
       </c>
       <c r="B230">
-        <v>0</v>
+        <v>-6.1039999999999997E-2</v>
       </c>
       <c r="C230">
         <v>-48.4375</v>
@@ -32167,7 +32167,7 @@
         <v>-48.4375</v>
       </c>
       <c r="L230">
-        <v>-6.565E-2</v>
+        <v>-6.5549999999999997E-2</v>
       </c>
       <c r="M230">
         <v>-48.4375</v>
@@ -32191,7 +32191,7 @@
         <v>-48.4375</v>
       </c>
       <c r="T230">
-        <v>-6.5629999999999994E-2</v>
+        <v>-6.5530000000000005E-2</v>
       </c>
       <c r="U230">
         <v>-48.4375</v>
@@ -32221,7 +32221,7 @@
         <v>-48.4375</v>
       </c>
       <c r="AD230">
-        <v>-6.565E-2</v>
+        <v>-6.5699999999999995E-2</v>
       </c>
       <c r="AE230">
         <v>-48.4375</v>
@@ -32257,7 +32257,7 @@
         <v>-48.4375</v>
       </c>
       <c r="AP230">
-        <v>-6.565E-2</v>
+        <v>-6.5619999999999998E-2</v>
       </c>
       <c r="AQ230">
         <v>-48.4375</v>
@@ -32274,10 +32274,10 @@
     </row>
     <row r="231" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>-43.75</v>
+        <v>-45.3125</v>
       </c>
       <c r="B231">
-        <v>0</v>
+        <v>-5.8999999999999997E-2</v>
       </c>
       <c r="C231">
         <v>-46.875</v>
@@ -32307,7 +32307,7 @@
         <v>-46.875</v>
       </c>
       <c r="L231">
-        <v>-6.3509999999999997E-2</v>
+        <v>-6.3409999999999994E-2</v>
       </c>
       <c r="M231">
         <v>-46.875</v>
@@ -32331,7 +32331,7 @@
         <v>-46.875</v>
       </c>
       <c r="T231">
-        <v>-6.3500000000000001E-2</v>
+        <v>-6.3600000000000004E-2</v>
       </c>
       <c r="U231">
         <v>-46.875</v>
@@ -32361,7 +32361,7 @@
         <v>-46.875</v>
       </c>
       <c r="AD231">
-        <v>-6.3509999999999997E-2</v>
+        <v>-6.3519999999999993E-2</v>
       </c>
       <c r="AE231">
         <v>-46.875</v>
@@ -32373,7 +32373,7 @@
         <v>-46.875</v>
       </c>
       <c r="AH231">
-        <v>-6.3509999999999997E-2</v>
+        <v>-6.3519999999999993E-2</v>
       </c>
       <c r="AI231">
         <v>-46.875</v>
@@ -32397,7 +32397,7 @@
         <v>-46.875</v>
       </c>
       <c r="AP231">
-        <v>-6.3509999999999997E-2</v>
+        <v>-6.3500000000000001E-2</v>
       </c>
       <c r="AQ231">
         <v>-46.875</v>
@@ -32414,10 +32414,10 @@
     </row>
     <row r="232" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A232">
-        <v>-42.1875</v>
+        <v>-43.75</v>
       </c>
       <c r="B232">
-        <v>0</v>
+        <v>-5.6950000000000001E-2</v>
       </c>
       <c r="C232">
         <v>-45.3125</v>
@@ -32447,7 +32447,7 @@
         <v>-45.3125</v>
       </c>
       <c r="L232">
-        <v>-6.1379999999999997E-2</v>
+        <v>-6.1280000000000001E-2</v>
       </c>
       <c r="M232">
         <v>-45.3125</v>
@@ -32471,7 +32471,7 @@
         <v>-45.3125</v>
       </c>
       <c r="T232">
-        <v>-6.1379999999999997E-2</v>
+        <v>-6.1580000000000003E-2</v>
       </c>
       <c r="U232">
         <v>-45.3125</v>
@@ -32501,7 +32501,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AD232">
-        <v>-6.1379999999999997E-2</v>
+        <v>-6.139E-2</v>
       </c>
       <c r="AE232">
         <v>-45.3125</v>
@@ -32537,7 +32537,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AP232">
-        <v>-6.1379999999999997E-2</v>
+        <v>-6.1370000000000001E-2</v>
       </c>
       <c r="AQ232">
         <v>-45.3125</v>
@@ -32554,10 +32554,10 @@
     </row>
     <row r="233" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>-40.625</v>
+        <v>-42.1875</v>
       </c>
       <c r="B233">
-        <v>0</v>
+        <v>-5.4919999999999997E-2</v>
       </c>
       <c r="C233">
         <v>-43.75</v>
@@ -32587,7 +32587,7 @@
         <v>-43.75</v>
       </c>
       <c r="L233">
-        <v>-5.9270000000000003E-2</v>
+        <v>-5.9470000000000002E-2</v>
       </c>
       <c r="M233">
         <v>-43.75</v>
@@ -32641,7 +32641,7 @@
         <v>-43.75</v>
       </c>
       <c r="AD233">
-        <v>-5.9270000000000003E-2</v>
+        <v>-5.9279999999999999E-2</v>
       </c>
       <c r="AE233">
         <v>-43.75</v>
@@ -32677,7 +32677,7 @@
         <v>-43.75</v>
       </c>
       <c r="AP233">
-        <v>-5.9270000000000003E-2</v>
+        <v>-5.926E-2</v>
       </c>
       <c r="AQ233">
         <v>-43.75</v>
@@ -32694,10 +32694,10 @@
     </row>
     <row r="234" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A234">
-        <v>-39.0625</v>
+        <v>-40.625</v>
       </c>
       <c r="B234">
-        <v>0</v>
+        <v>-5.2880000000000003E-2</v>
       </c>
       <c r="C234">
         <v>-42.1875</v>
@@ -32727,7 +32727,7 @@
         <v>-42.1875</v>
       </c>
       <c r="L234">
-        <v>-5.7149999999999999E-2</v>
+        <v>-5.7049999999999997E-2</v>
       </c>
       <c r="M234">
         <v>-42.1875</v>
@@ -32751,7 +32751,7 @@
         <v>-42.1875</v>
       </c>
       <c r="T234">
-        <v>-5.713E-2</v>
+        <v>-5.7029999999999997E-2</v>
       </c>
       <c r="U234">
         <v>-42.1875</v>
@@ -32781,7 +32781,7 @@
         <v>-42.1875</v>
       </c>
       <c r="AD234">
-        <v>-5.7149999999999999E-2</v>
+        <v>-5.7140000000000003E-2</v>
       </c>
       <c r="AE234">
         <v>-42.1875</v>
@@ -32834,10 +32834,10 @@
     </row>
     <row r="235" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A235">
-        <v>-37.5</v>
+        <v>-39.0625</v>
       </c>
       <c r="B235">
-        <v>0</v>
+        <v>-5.083E-2</v>
       </c>
       <c r="C235">
         <v>-40.625</v>
@@ -32867,7 +32867,7 @@
         <v>-40.625</v>
       </c>
       <c r="L235">
-        <v>-5.5019999999999999E-2</v>
+        <v>-5.4919999999999997E-2</v>
       </c>
       <c r="M235">
         <v>-40.625</v>
@@ -32891,7 +32891,7 @@
         <v>-40.625</v>
       </c>
       <c r="T235">
-        <v>-5.5E-2</v>
+        <v>-5.4800000000000001E-2</v>
       </c>
       <c r="U235">
         <v>-40.625</v>
@@ -32933,7 +32933,7 @@
         <v>-40.625</v>
       </c>
       <c r="AH235">
-        <v>-5.5019999999999999E-2</v>
+        <v>-5.5010000000000003E-2</v>
       </c>
       <c r="AI235">
         <v>-40.625</v>
@@ -32957,7 +32957,7 @@
         <v>-40.625</v>
       </c>
       <c r="AP235">
-        <v>-5.5019999999999999E-2</v>
+        <v>-5.5030000000000003E-2</v>
       </c>
       <c r="AQ235">
         <v>-40.625</v>
@@ -32974,10 +32974,10 @@
     </row>
     <row r="236" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A236">
-        <v>-35.9375</v>
+        <v>-37.5</v>
       </c>
       <c r="B236">
-        <v>0</v>
+        <v>-4.8779999999999997E-2</v>
       </c>
       <c r="C236">
         <v>-39.0625</v>
@@ -33007,7 +33007,7 @@
         <v>-39.0625</v>
       </c>
       <c r="L236">
-        <v>-5.2900000000000003E-2</v>
+        <v>-5.2999999999999999E-2</v>
       </c>
       <c r="M236">
         <v>-39.0625</v>
@@ -33031,7 +33031,7 @@
         <v>-39.0625</v>
       </c>
       <c r="T236">
-        <v>-5.289E-2</v>
+        <v>-5.2789999999999997E-2</v>
       </c>
       <c r="U236">
         <v>-39.0625</v>
@@ -33049,7 +33049,7 @@
         <v>-39.0625</v>
       </c>
       <c r="Z236">
-        <v>-5.289E-2</v>
+        <v>-5.2900000000000003E-2</v>
       </c>
       <c r="AA236">
         <v>-39.0625</v>
@@ -33061,7 +33061,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AD236">
-        <v>-5.2900000000000003E-2</v>
+        <v>-5.2909999999999999E-2</v>
       </c>
       <c r="AE236">
         <v>-39.0625</v>
@@ -33097,7 +33097,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AP236">
-        <v>-5.2900000000000003E-2</v>
+        <v>-5.2920000000000002E-2</v>
       </c>
       <c r="AQ236">
         <v>-39.0625</v>
@@ -33114,10 +33114,10 @@
     </row>
     <row r="237" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>-34.375</v>
+        <v>-35.9375</v>
       </c>
       <c r="B237">
-        <v>0</v>
+        <v>-4.6739999999999997E-2</v>
       </c>
       <c r="C237">
         <v>-37.5</v>
@@ -33147,7 +33147,7 @@
         <v>-37.5</v>
       </c>
       <c r="L237">
-        <v>-5.0750000000000003E-2</v>
+        <v>-5.0650000000000001E-2</v>
       </c>
       <c r="M237">
         <v>-37.5</v>
@@ -33171,7 +33171,7 @@
         <v>-37.5</v>
       </c>
       <c r="T237">
-        <v>-5.074E-2</v>
+        <v>-5.0540000000000002E-2</v>
       </c>
       <c r="U237">
         <v>-37.5</v>
@@ -33201,7 +33201,7 @@
         <v>-37.5</v>
       </c>
       <c r="AD237">
-        <v>-5.0750000000000003E-2</v>
+        <v>-5.074E-2</v>
       </c>
       <c r="AE237">
         <v>-37.5</v>
@@ -33237,7 +33237,7 @@
         <v>-37.5</v>
       </c>
       <c r="AP237">
-        <v>-5.0750000000000003E-2</v>
+        <v>-5.0720000000000001E-2</v>
       </c>
       <c r="AQ237">
         <v>-37.5</v>
@@ -33254,10 +33254,10 @@
     </row>
     <row r="238" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>-32.8125</v>
+        <v>-34.375</v>
       </c>
       <c r="B238">
-        <v>0</v>
+        <v>-4.4690000000000001E-2</v>
       </c>
       <c r="C238">
         <v>-35.9375</v>
@@ -33287,7 +33287,7 @@
         <v>-35.9375</v>
       </c>
       <c r="L238">
-        <v>-4.8640000000000003E-2</v>
+        <v>-4.8739999999999999E-2</v>
       </c>
       <c r="M238">
         <v>-35.9375</v>
@@ -33311,7 +33311,7 @@
         <v>-35.9375</v>
       </c>
       <c r="T238">
-        <v>-4.8619999999999997E-2</v>
+        <v>-4.8820000000000002E-2</v>
       </c>
       <c r="U238">
         <v>-35.9375</v>
@@ -33353,13 +33353,13 @@
         <v>-35.9375</v>
       </c>
       <c r="AH238">
-        <v>-4.8640000000000003E-2</v>
+        <v>-4.8649999999999999E-2</v>
       </c>
       <c r="AI238">
         <v>-35.9375</v>
       </c>
       <c r="AJ238">
-        <v>-4.8640000000000003E-2</v>
+        <v>-4.8649999999999999E-2</v>
       </c>
       <c r="AK238">
         <v>-35.9375</v>
@@ -33394,10 +33394,10 @@
     </row>
     <row r="239" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A239">
-        <v>-31.25</v>
+        <v>-32.8125</v>
       </c>
       <c r="B239">
-        <v>0</v>
+        <v>-4.265E-2</v>
       </c>
       <c r="C239">
         <v>-34.375</v>
@@ -33427,7 +33427,7 @@
         <v>-34.375</v>
       </c>
       <c r="L239">
-        <v>-4.6510000000000003E-2</v>
+        <v>-4.641E-2</v>
       </c>
       <c r="M239">
         <v>-34.375</v>
@@ -33451,7 +33451,7 @@
         <v>-34.375</v>
       </c>
       <c r="T239">
-        <v>-4.6510000000000003E-2</v>
+        <v>-4.6309999999999997E-2</v>
       </c>
       <c r="U239">
         <v>-34.375</v>
@@ -33481,7 +33481,7 @@
         <v>-34.375</v>
       </c>
       <c r="AD239">
-        <v>-4.6510000000000003E-2</v>
+        <v>-4.6519999999999999E-2</v>
       </c>
       <c r="AE239">
         <v>-34.375</v>
@@ -33517,7 +33517,7 @@
         <v>-34.375</v>
       </c>
       <c r="AP239">
-        <v>-4.6510000000000003E-2</v>
+        <v>-4.6530000000000002E-2</v>
       </c>
       <c r="AQ239">
         <v>-34.375</v>
@@ -33534,10 +33534,10 @@
     </row>
     <row r="240" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A240">
-        <v>-29.6875</v>
+        <v>-31.25</v>
       </c>
       <c r="B240">
-        <v>0</v>
+        <v>-4.0620000000000003E-2</v>
       </c>
       <c r="C240">
         <v>-32.8125</v>
@@ -33567,7 +33567,7 @@
         <v>-32.8125</v>
       </c>
       <c r="L240">
-        <v>-4.4389999999999999E-2</v>
+        <v>-4.4490000000000002E-2</v>
       </c>
       <c r="M240">
         <v>-32.8125</v>
@@ -33591,7 +33591,7 @@
         <v>-32.8125</v>
       </c>
       <c r="T240">
-        <v>-4.437E-2</v>
+        <v>-4.4269999999999997E-2</v>
       </c>
       <c r="U240">
         <v>-32.8125</v>
@@ -33609,7 +33609,7 @@
         <v>-32.8125</v>
       </c>
       <c r="Z240">
-        <v>-4.437E-2</v>
+        <v>-4.4380000000000003E-2</v>
       </c>
       <c r="AA240">
         <v>-32.8125</v>
@@ -33621,7 +33621,7 @@
         <v>-32.8125</v>
       </c>
       <c r="AD240">
-        <v>-4.4389999999999999E-2</v>
+        <v>-4.4400000000000002E-2</v>
       </c>
       <c r="AE240">
         <v>-32.8125</v>
@@ -33657,7 +33657,7 @@
         <v>-32.8125</v>
       </c>
       <c r="AP240">
-        <v>-4.4389999999999999E-2</v>
+        <v>-4.4409999999999998E-2</v>
       </c>
       <c r="AQ240">
         <v>-32.8125</v>
@@ -33674,10 +33674,10 @@
     </row>
     <row r="241" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A241">
-        <v>-28.125</v>
+        <v>-29.6875</v>
       </c>
       <c r="B241">
-        <v>0</v>
+        <v>-3.857E-2</v>
       </c>
       <c r="C241">
         <v>-31.25</v>
@@ -33761,7 +33761,7 @@
         <v>-31.25</v>
       </c>
       <c r="AD241">
-        <v>-4.2270000000000002E-2</v>
+        <v>-4.2279999999999998E-2</v>
       </c>
       <c r="AE241">
         <v>-31.25</v>
@@ -33797,7 +33797,7 @@
         <v>-31.25</v>
       </c>
       <c r="AP241">
-        <v>-4.2270000000000002E-2</v>
+        <v>-4.2259999999999999E-2</v>
       </c>
       <c r="AQ241">
         <v>-31.25</v>
@@ -33814,10 +33814,10 @@
     </row>
     <row r="242" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A242">
-        <v>-26.5625</v>
+        <v>-28.125</v>
       </c>
       <c r="B242">
-        <v>0</v>
+        <v>-3.6519999999999997E-2</v>
       </c>
       <c r="C242">
         <v>-29.6875</v>
@@ -33847,7 +33847,7 @@
         <v>-29.6875</v>
       </c>
       <c r="L242">
-        <v>-4.0160000000000001E-2</v>
+        <v>-3.9960000000000002E-2</v>
       </c>
       <c r="M242">
         <v>-29.6875</v>
@@ -33871,7 +33871,7 @@
         <v>-29.6875</v>
       </c>
       <c r="T242">
-        <v>-4.0140000000000002E-2</v>
+        <v>-4.0340000000000001E-2</v>
       </c>
       <c r="U242">
         <v>-29.6875</v>
@@ -33954,10 +33954,10 @@
     </row>
     <row r="243" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A243">
-        <v>-25</v>
+        <v>-26.5625</v>
       </c>
       <c r="B243">
-        <v>0</v>
+        <v>-3.4470000000000001E-2</v>
       </c>
       <c r="C243">
         <v>-28.125</v>
@@ -33987,7 +33987,7 @@
         <v>-28.125</v>
       </c>
       <c r="L243">
-        <v>-3.8019999999999998E-2</v>
+        <v>-3.7819999999999999E-2</v>
       </c>
       <c r="M243">
         <v>-28.125</v>
@@ -34011,7 +34011,7 @@
         <v>-28.125</v>
       </c>
       <c r="T243">
-        <v>-3.8010000000000002E-2</v>
+        <v>-3.8109999999999998E-2</v>
       </c>
       <c r="U243">
         <v>-28.125</v>
@@ -34041,7 +34041,7 @@
         <v>-28.125</v>
       </c>
       <c r="AD243">
-        <v>-3.8019999999999998E-2</v>
+        <v>-3.8010000000000002E-2</v>
       </c>
       <c r="AE243">
         <v>-28.125</v>
@@ -34053,7 +34053,7 @@
         <v>-28.125</v>
       </c>
       <c r="AH243">
-        <v>-3.8019999999999998E-2</v>
+        <v>-3.8010000000000002E-2</v>
       </c>
       <c r="AI243">
         <v>-28.125</v>
@@ -34077,7 +34077,7 @@
         <v>-28.125</v>
       </c>
       <c r="AP243">
-        <v>-3.8019999999999998E-2</v>
+        <v>-3.805E-2</v>
       </c>
       <c r="AQ243">
         <v>-28.125</v>
@@ -34094,10 +34094,10 @@
     </row>
     <row r="244" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A244">
-        <v>-23.4375</v>
+        <v>-25</v>
       </c>
       <c r="B244">
-        <v>0</v>
+        <v>-3.243E-2</v>
       </c>
       <c r="C244">
         <v>-26.5625</v>
@@ -34127,7 +34127,7 @@
         <v>-26.5625</v>
       </c>
       <c r="L244">
-        <v>-3.5909999999999997E-2</v>
+        <v>-3.6110000000000003E-2</v>
       </c>
       <c r="M244">
         <v>-26.5625</v>
@@ -34151,7 +34151,7 @@
         <v>-26.5625</v>
       </c>
       <c r="T244">
-        <v>-3.5889999999999998E-2</v>
+        <v>-3.569E-2</v>
       </c>
       <c r="U244">
         <v>-26.5625</v>
@@ -34181,7 +34181,7 @@
         <v>-26.5625</v>
       </c>
       <c r="AD244">
-        <v>-3.5909999999999997E-2</v>
+        <v>-3.5920000000000001E-2</v>
       </c>
       <c r="AE244">
         <v>-26.5625</v>
@@ -34217,7 +34217,7 @@
         <v>-26.5625</v>
       </c>
       <c r="AP244">
-        <v>-3.5909999999999997E-2</v>
+        <v>-3.5959999999999999E-2</v>
       </c>
       <c r="AQ244">
         <v>-26.5625</v>
@@ -34234,10 +34234,10 @@
     </row>
     <row r="245" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A245">
-        <v>-21.875</v>
+        <v>-23.4375</v>
       </c>
       <c r="B245">
-        <v>0</v>
+        <v>-2.4410000000000001E-2</v>
       </c>
       <c r="C245">
         <v>-25</v>
@@ -34267,7 +34267,7 @@
         <v>-25</v>
       </c>
       <c r="L245">
-        <v>-3.3779999999999998E-2</v>
+        <v>-3.3579999999999999E-2</v>
       </c>
       <c r="M245">
         <v>-25</v>
@@ -34291,7 +34291,7 @@
         <v>-25</v>
       </c>
       <c r="T245">
-        <v>-3.3779999999999998E-2</v>
+        <v>-3.3579999999999999E-2</v>
       </c>
       <c r="U245">
         <v>-25</v>
@@ -34321,7 +34321,7 @@
         <v>-25</v>
       </c>
       <c r="AD245">
-        <v>-3.3779999999999998E-2</v>
+        <v>-3.3759999999999998E-2</v>
       </c>
       <c r="AE245">
         <v>-25</v>
@@ -34357,7 +34357,7 @@
         <v>-25</v>
       </c>
       <c r="AP245">
-        <v>-3.3779999999999998E-2</v>
+        <v>-3.3799999999999997E-2</v>
       </c>
       <c r="AQ245">
         <v>-25</v>
@@ -34374,7 +34374,7 @@
     </row>
     <row r="246" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A246">
-        <v>-20.3125</v>
+        <v>-21.875</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -34431,7 +34431,7 @@
         <v>-23.4375</v>
       </c>
       <c r="T246">
-        <v>-3.1640000000000001E-2</v>
+        <v>-3.1440000000000003E-2</v>
       </c>
       <c r="U246">
         <v>-23.4375</v>
@@ -34449,7 +34449,7 @@
         <v>-23.4375</v>
       </c>
       <c r="Z246">
-        <v>-3.1640000000000001E-2</v>
+        <v>-3.1699999999999999E-2</v>
       </c>
       <c r="AA246">
         <v>-23.4375</v>
@@ -34461,7 +34461,7 @@
         <v>-23.4375</v>
       </c>
       <c r="AD246">
-        <v>-3.1660000000000001E-2</v>
+        <v>-3.1620000000000002E-2</v>
       </c>
       <c r="AE246">
         <v>-23.4375</v>
@@ -34497,7 +34497,7 @@
         <v>-23.4375</v>
       </c>
       <c r="AP246">
-        <v>-3.1660000000000001E-2</v>
+        <v>-3.1640000000000001E-2</v>
       </c>
       <c r="AQ246">
         <v>-23.4375</v>
@@ -34514,7 +34514,7 @@
     </row>
     <row r="247" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>-18.75</v>
+        <v>-20.3125</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -34547,7 +34547,7 @@
         <v>-21.875</v>
       </c>
       <c r="L247">
-        <v>-2.954E-2</v>
+        <v>-2.964E-2</v>
       </c>
       <c r="M247">
         <v>-21.875</v>
@@ -34654,7 +34654,7 @@
     </row>
     <row r="248" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>-17.1875</v>
+        <v>-18.75</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -34687,7 +34687,7 @@
         <v>-20.3125</v>
       </c>
       <c r="L248">
-        <v>-2.741E-2</v>
+        <v>-2.7210000000000002E-2</v>
       </c>
       <c r="M248">
         <v>-20.3125</v>
@@ -34711,7 +34711,7 @@
         <v>-20.3125</v>
       </c>
       <c r="T248">
-        <v>-2.741E-2</v>
+        <v>-2.7609999999999999E-2</v>
       </c>
       <c r="U248">
         <v>-20.3125</v>
@@ -34794,7 +34794,7 @@
     </row>
     <row r="249" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>-15.625</v>
+        <v>-17.1875</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -34851,7 +34851,7 @@
         <v>-18.75</v>
       </c>
       <c r="T249">
-        <v>-2.528E-2</v>
+        <v>-2.538E-2</v>
       </c>
       <c r="U249">
         <v>-18.75</v>
@@ -34881,7 +34881,7 @@
         <v>-18.75</v>
       </c>
       <c r="AD249">
-        <v>-2.53E-2</v>
+        <v>-2.52E-2</v>
       </c>
       <c r="AE249">
         <v>-18.75</v>
@@ -34917,7 +34917,7 @@
         <v>-18.75</v>
       </c>
       <c r="AP249">
-        <v>-2.53E-2</v>
+        <v>-2.5100000000000001E-2</v>
       </c>
       <c r="AQ249">
         <v>-18.75</v>
@@ -34934,7 +34934,7 @@
     </row>
     <row r="250" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>-14.0625</v>
+        <v>-15.625</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -34967,7 +34967,7 @@
         <v>-17.1875</v>
       </c>
       <c r="L250">
-        <v>-2.316E-2</v>
+        <v>-2.3060000000000001E-2</v>
       </c>
       <c r="M250">
         <v>-17.1875</v>
@@ -34991,7 +34991,7 @@
         <v>-17.1875</v>
       </c>
       <c r="T250">
-        <v>-2.316E-2</v>
+        <v>-2.3060000000000001E-2</v>
       </c>
       <c r="U250">
         <v>-17.1875</v>
@@ -35074,7 +35074,7 @@
     </row>
     <row r="251" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>-12.5</v>
+        <v>-14.0625</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -35107,7 +35107,7 @@
         <v>-15.625</v>
       </c>
       <c r="L251">
-        <v>-2.103E-2</v>
+        <v>-2.1129999999999999E-2</v>
       </c>
       <c r="M251">
         <v>-15.625</v>
@@ -35131,7 +35131,7 @@
         <v>-15.625</v>
       </c>
       <c r="T251">
-        <v>-2.095E-2</v>
+        <v>-2.1049999999999999E-2</v>
       </c>
       <c r="U251">
         <v>-15.625</v>
@@ -35179,7 +35179,7 @@
         <v>-15.625</v>
       </c>
       <c r="AJ251">
-        <v>-2.102E-2</v>
+        <v>-2.103E-2</v>
       </c>
       <c r="AK251">
         <v>-15.625</v>
@@ -35214,7 +35214,7 @@
     </row>
     <row r="252" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>-10.9375</v>
+        <v>-12.5</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -35247,7 +35247,7 @@
         <v>-14.0625</v>
       </c>
       <c r="L252">
-        <v>-1.753E-2</v>
+        <v>-1.7430000000000001E-2</v>
       </c>
       <c r="M252">
         <v>-14.0625</v>
@@ -35354,7 +35354,7 @@
     </row>
     <row r="253" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>-9.375</v>
+        <v>-10.9375</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -35387,7 +35387,7 @@
         <v>-12.5</v>
       </c>
       <c r="L253">
-        <v>-1.2529999999999999E-2</v>
+        <v>-1.2330000000000001E-2</v>
       </c>
       <c r="M253">
         <v>-12.5</v>
@@ -35494,7 +35494,7 @@
     </row>
     <row r="254" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>-7.8125</v>
+        <v>-9.375</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -35527,7 +35527,7 @@
         <v>-10.9375</v>
       </c>
       <c r="L254">
-        <v>-5.4200000000000003E-3</v>
+        <v>-5.2199999999999998E-3</v>
       </c>
       <c r="M254">
         <v>-10.9375</v>
@@ -35551,7 +35551,7 @@
         <v>-10.9375</v>
       </c>
       <c r="T254">
-        <v>-1.39E-3</v>
+        <v>-1.5900000000000001E-3</v>
       </c>
       <c r="U254">
         <v>-10.9375</v>
@@ -35634,7 +35634,7 @@
     </row>
     <row r="255" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A255">
-        <v>-6.25</v>
+        <v>-7.8125</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -35667,7 +35667,7 @@
         <v>-9.375</v>
       </c>
       <c r="L255" s="1">
-        <v>-4.4945400000000001E-4</v>
+        <v>-6.4945400000000005E-4</v>
       </c>
       <c r="M255">
         <v>-9.375</v>
@@ -35774,7 +35774,7 @@
     </row>
     <row r="256" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A256">
-        <v>-4.6875</v>
+        <v>-6.25</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -35914,7 +35914,7 @@
     </row>
     <row r="257" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A257">
-        <v>-3.125</v>
+        <v>-4.6875</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -36054,7 +36054,7 @@
     </row>
     <row r="258" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A258">
-        <v>-1.5625</v>
+        <v>-3.125</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -36194,7 +36194,7 @@
     </row>
     <row r="259" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A259">
-        <v>0</v>
+        <v>-1.5625</v>
       </c>
       <c r="B259">
         <v>0</v>

--- a/IV_2.5K_T1.xlsx
+++ b/IV_2.5K_T1.xlsx
@@ -1749,7 +1749,7 @@
         <v>10.9375</v>
       </c>
       <c r="AT12">
-        <v>9.2999999999999992E-3</v>
+        <v>9.4999999999999998E-3</v>
       </c>
     </row>
     <row r="13" spans="1:46" x14ac:dyDescent="0.25">
@@ -1889,7 +1889,7 @@
         <v>12.5</v>
       </c>
       <c r="AT13">
-        <v>1.67E-2</v>
+        <v>1.6799999999999999E-2</v>
       </c>
     </row>
     <row r="14" spans="1:46" x14ac:dyDescent="0.25">
@@ -2029,7 +2029,7 @@
         <v>14.0625</v>
       </c>
       <c r="AT14">
-        <v>1.8890000000000001E-2</v>
+        <v>1.9089999999999999E-2</v>
       </c>
     </row>
     <row r="15" spans="1:46" x14ac:dyDescent="0.25">
@@ -2151,7 +2151,7 @@
         <v>15.625</v>
       </c>
       <c r="AN15" s="1">
-        <v>-8.1466700000000004E-5</v>
+        <v>1.8533300000000001E-5</v>
       </c>
       <c r="AO15">
         <v>15.625</v>
@@ -2169,7 +2169,7 @@
         <v>15.625</v>
       </c>
       <c r="AT15">
-        <v>2.0400000000000001E-2</v>
+        <v>2.0500000000000001E-2</v>
       </c>
     </row>
     <row r="16" spans="1:46" x14ac:dyDescent="0.25">
@@ -2291,7 +2291,7 @@
         <v>17.1875</v>
       </c>
       <c r="AN16">
-        <v>2.0379999999999999E-2</v>
+        <v>2.0279999999999999E-2</v>
       </c>
       <c r="AO16">
         <v>17.1875</v>
@@ -2431,7 +2431,7 @@
         <v>18.75</v>
       </c>
       <c r="AN17">
-        <v>2.511E-2</v>
+        <v>2.5010000000000001E-2</v>
       </c>
       <c r="AO17">
         <v>18.75</v>
@@ -2449,7 +2449,7 @@
         <v>18.75</v>
       </c>
       <c r="AT17">
-        <v>2.555E-2</v>
+        <v>2.5749999999999999E-2</v>
       </c>
     </row>
     <row r="18" spans="1:46" x14ac:dyDescent="0.25">
@@ -2571,7 +2571,7 @@
         <v>20.3125</v>
       </c>
       <c r="AN18">
-        <v>2.7689999999999999E-2</v>
+        <v>2.7789999999999999E-2</v>
       </c>
       <c r="AO18">
         <v>20.3125</v>
@@ -2589,7 +2589,7 @@
         <v>20.3125</v>
       </c>
       <c r="AT18">
-        <v>2.7689999999999999E-2</v>
+        <v>2.7890000000000002E-2</v>
       </c>
     </row>
     <row r="19" spans="1:46" x14ac:dyDescent="0.25">
@@ -2711,7 +2711,7 @@
         <v>21.875</v>
       </c>
       <c r="AN19">
-        <v>2.9819999999999999E-2</v>
+        <v>2.9919999999999999E-2</v>
       </c>
       <c r="AO19">
         <v>21.875</v>
@@ -2729,7 +2729,7 @@
         <v>21.875</v>
       </c>
       <c r="AT19">
-        <v>2.9819999999999999E-2</v>
+        <v>2.962E-2</v>
       </c>
     </row>
     <row r="20" spans="1:46" x14ac:dyDescent="0.25">
@@ -3009,7 +3009,7 @@
         <v>25</v>
       </c>
       <c r="AT21">
-        <v>3.4049999999999997E-2</v>
+        <v>3.415E-2</v>
       </c>
     </row>
     <row r="22" spans="1:46" x14ac:dyDescent="0.25">
@@ -3131,7 +3131,7 @@
         <v>26.5625</v>
       </c>
       <c r="AN22">
-        <v>3.6170000000000001E-2</v>
+        <v>3.6269999999999997E-2</v>
       </c>
       <c r="AO22">
         <v>26.5625</v>
@@ -3149,7 +3149,7 @@
         <v>26.5625</v>
       </c>
       <c r="AT22">
-        <v>3.6170000000000001E-2</v>
+        <v>3.6269999999999997E-2</v>
       </c>
     </row>
     <row r="23" spans="1:46" x14ac:dyDescent="0.25">
@@ -3271,7 +3271,7 @@
         <v>28.125</v>
       </c>
       <c r="AN23">
-        <v>3.8300000000000001E-2</v>
+        <v>3.8399999999999997E-2</v>
       </c>
       <c r="AO23">
         <v>28.125</v>
@@ -3411,7 +3411,7 @@
         <v>29.6875</v>
       </c>
       <c r="AN24">
-        <v>4.0419999999999998E-2</v>
+        <v>4.052E-2</v>
       </c>
       <c r="AO24">
         <v>29.6875</v>
@@ -3429,7 +3429,7 @@
         <v>29.6875</v>
       </c>
       <c r="AT24">
-        <v>4.0419999999999998E-2</v>
+        <v>4.052E-2</v>
       </c>
     </row>
     <row r="25" spans="1:46" x14ac:dyDescent="0.25">
@@ -3569,7 +3569,7 @@
         <v>31.25</v>
       </c>
       <c r="AT25">
-        <v>4.2529999999999998E-2</v>
+        <v>4.233E-2</v>
       </c>
     </row>
     <row r="26" spans="1:46" x14ac:dyDescent="0.25">
@@ -3691,7 +3691,7 @@
         <v>32.8125</v>
       </c>
       <c r="AN26">
-        <v>4.4659999999999998E-2</v>
+        <v>4.4560000000000002E-2</v>
       </c>
       <c r="AO26">
         <v>32.8125</v>
@@ -3709,7 +3709,7 @@
         <v>32.8125</v>
       </c>
       <c r="AT26">
-        <v>4.4659999999999998E-2</v>
+        <v>4.4760000000000001E-2</v>
       </c>
     </row>
     <row r="27" spans="1:46" x14ac:dyDescent="0.25">
@@ -3831,7 +3831,7 @@
         <v>34.375</v>
       </c>
       <c r="AN27">
-        <v>4.6780000000000002E-2</v>
+        <v>4.6879999999999998E-2</v>
       </c>
       <c r="AO27">
         <v>34.375</v>
@@ -3849,7 +3849,7 @@
         <v>34.375</v>
       </c>
       <c r="AT27">
-        <v>4.6780000000000002E-2</v>
+        <v>4.6580000000000003E-2</v>
       </c>
     </row>
     <row r="28" spans="1:46" x14ac:dyDescent="0.25">
@@ -3971,7 +3971,7 @@
         <v>35.9375</v>
       </c>
       <c r="AN28">
-        <v>4.8899999999999999E-2</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="AO28">
         <v>35.9375</v>
@@ -3989,7 +3989,7 @@
         <v>35.9375</v>
       </c>
       <c r="AT28">
-        <v>4.8899999999999999E-2</v>
+        <v>4.8800000000000003E-2</v>
       </c>
     </row>
     <row r="29" spans="1:46" x14ac:dyDescent="0.25">
@@ -4111,7 +4111,7 @@
         <v>37.5</v>
       </c>
       <c r="AN29">
-        <v>5.1040000000000002E-2</v>
+        <v>5.1139999999999998E-2</v>
       </c>
       <c r="AO29">
         <v>37.5</v>
@@ -4129,7 +4129,7 @@
         <v>37.5</v>
       </c>
       <c r="AT29">
-        <v>5.1040000000000002E-2</v>
+        <v>5.1240000000000001E-2</v>
       </c>
     </row>
     <row r="30" spans="1:46" x14ac:dyDescent="0.25">
@@ -4227,7 +4227,7 @@
         <v>39.0625</v>
       </c>
       <c r="AF30">
-        <v>5.314E-2</v>
+        <v>5.3120000000000001E-2</v>
       </c>
       <c r="AG30">
         <v>39.0625</v>
@@ -4269,7 +4269,7 @@
         <v>39.0625</v>
       </c>
       <c r="AT30">
-        <v>5.3159999999999999E-2</v>
+        <v>5.3060000000000003E-2</v>
       </c>
     </row>
     <row r="31" spans="1:46" x14ac:dyDescent="0.25">
@@ -4391,7 +4391,7 @@
         <v>40.625</v>
       </c>
       <c r="AN31">
-        <v>5.5289999999999999E-2</v>
+        <v>5.5190000000000003E-2</v>
       </c>
       <c r="AO31">
         <v>40.625</v>
@@ -4507,7 +4507,7 @@
         <v>42.1875</v>
       </c>
       <c r="AF32">
-        <v>5.7389999999999997E-2</v>
+        <v>5.7340000000000002E-2</v>
       </c>
       <c r="AG32">
         <v>42.1875</v>
@@ -4549,7 +4549,7 @@
         <v>42.1875</v>
       </c>
       <c r="AT32">
-        <v>5.7410000000000003E-2</v>
+        <v>5.7209999999999997E-2</v>
       </c>
     </row>
     <row r="33" spans="1:46" x14ac:dyDescent="0.25">
@@ -4671,7 +4671,7 @@
         <v>43.75</v>
       </c>
       <c r="AN33">
-        <v>5.9540000000000003E-2</v>
+        <v>5.944E-2</v>
       </c>
       <c r="AO33">
         <v>43.75</v>
@@ -4689,7 +4689,7 @@
         <v>43.75</v>
       </c>
       <c r="AT33">
-        <v>5.9540000000000003E-2</v>
+        <v>5.944E-2</v>
       </c>
     </row>
     <row r="34" spans="1:46" x14ac:dyDescent="0.25">
@@ -4787,7 +4787,7 @@
         <v>45.3125</v>
       </c>
       <c r="AF34">
-        <v>6.164E-2</v>
+        <v>6.1620000000000001E-2</v>
       </c>
       <c r="AG34">
         <v>45.3125</v>
@@ -4829,7 +4829,7 @@
         <v>45.3125</v>
       </c>
       <c r="AT34">
-        <v>6.166E-2</v>
+        <v>6.1760000000000002E-2</v>
       </c>
     </row>
     <row r="35" spans="1:46" x14ac:dyDescent="0.25">
@@ -4927,7 +4927,7 @@
         <v>46.875</v>
       </c>
       <c r="AF35">
-        <v>6.3769999999999993E-2</v>
+        <v>6.3780000000000003E-2</v>
       </c>
       <c r="AG35">
         <v>46.875</v>
@@ -4951,7 +4951,7 @@
         <v>46.875</v>
       </c>
       <c r="AN35">
-        <v>6.3789999999999999E-2</v>
+        <v>6.3890000000000002E-2</v>
       </c>
       <c r="AO35">
         <v>46.875</v>
@@ -4969,7 +4969,7 @@
         <v>46.875</v>
       </c>
       <c r="AT35">
-        <v>6.3789999999999999E-2</v>
+        <v>6.3990000000000005E-2</v>
       </c>
     </row>
     <row r="36" spans="1:46" x14ac:dyDescent="0.25">
@@ -5067,7 +5067,7 @@
         <v>48.4375</v>
       </c>
       <c r="AF36">
-        <v>6.5909999999999996E-2</v>
+        <v>6.5920000000000006E-2</v>
       </c>
       <c r="AG36">
         <v>48.4375</v>
@@ -5091,7 +5091,7 @@
         <v>48.4375</v>
       </c>
       <c r="AN36">
-        <v>6.5920000000000006E-2</v>
+        <v>6.5820000000000004E-2</v>
       </c>
       <c r="AO36">
         <v>48.4375</v>
@@ -5109,7 +5109,7 @@
         <v>48.4375</v>
       </c>
       <c r="AT36">
-        <v>6.5920000000000006E-2</v>
+        <v>6.6019999999999995E-2</v>
       </c>
     </row>
     <row r="37" spans="1:46" x14ac:dyDescent="0.25">
@@ -5207,7 +5207,7 @@
         <v>50</v>
       </c>
       <c r="AF37">
-        <v>6.8099999999999994E-2</v>
+        <v>6.8199999999999997E-2</v>
       </c>
       <c r="AG37">
         <v>50</v>
@@ -5249,7 +5249,7 @@
         <v>50</v>
       </c>
       <c r="AT37">
-        <v>6.812E-2</v>
+        <v>6.7919999999999994E-2</v>
       </c>
     </row>
     <row r="38" spans="1:46" x14ac:dyDescent="0.25">
@@ -5347,7 +5347,7 @@
         <v>51.5625</v>
       </c>
       <c r="AF38">
-        <v>7.0220000000000005E-2</v>
+        <v>7.0209999999999995E-2</v>
       </c>
       <c r="AG38">
         <v>51.5625</v>
@@ -5389,7 +5389,7 @@
         <v>51.5625</v>
       </c>
       <c r="AT38">
-        <v>7.0230000000000001E-2</v>
+        <v>7.0029999999999995E-2</v>
       </c>
     </row>
     <row r="39" spans="1:46" x14ac:dyDescent="0.25">
@@ -5487,7 +5487,7 @@
         <v>53.125</v>
       </c>
       <c r="AF39">
-        <v>7.2349999999999998E-2</v>
+        <v>7.2359999999999994E-2</v>
       </c>
       <c r="AG39">
         <v>53.125</v>
@@ -5511,7 +5511,7 @@
         <v>53.125</v>
       </c>
       <c r="AN39">
-        <v>7.238E-2</v>
+        <v>7.2279999999999997E-2</v>
       </c>
       <c r="AO39">
         <v>53.125</v>
@@ -5651,7 +5651,7 @@
         <v>54.6875</v>
       </c>
       <c r="AN40">
-        <v>7.4510000000000007E-2</v>
+        <v>7.4410000000000004E-2</v>
       </c>
       <c r="AO40">
         <v>54.6875</v>
@@ -5669,7 +5669,7 @@
         <v>54.6875</v>
       </c>
       <c r="AT40">
-        <v>7.4510000000000007E-2</v>
+        <v>7.4410000000000004E-2</v>
       </c>
     </row>
     <row r="41" spans="1:46" x14ac:dyDescent="0.25">
@@ -5767,7 +5767,7 @@
         <v>56.25</v>
       </c>
       <c r="AF41">
-        <v>7.6609999999999998E-2</v>
+        <v>7.6619999999999994E-2</v>
       </c>
       <c r="AG41">
         <v>56.25</v>
@@ -5809,7 +5809,7 @@
         <v>56.25</v>
       </c>
       <c r="AT41">
-        <v>7.6649999999999996E-2</v>
+        <v>7.6550000000000007E-2</v>
       </c>
     </row>
     <row r="42" spans="1:46" x14ac:dyDescent="0.25">
@@ -5949,7 +5949,7 @@
         <v>57.8125</v>
       </c>
       <c r="AT42">
-        <v>7.8780000000000003E-2</v>
+        <v>7.8979999999999995E-2</v>
       </c>
     </row>
     <row r="43" spans="1:46" x14ac:dyDescent="0.25">
@@ -6047,7 +6047,7 @@
         <v>59.375</v>
       </c>
       <c r="AF43">
-        <v>8.09E-2</v>
+        <v>8.0909999999999996E-2</v>
       </c>
       <c r="AG43">
         <v>59.375</v>
@@ -6071,7 +6071,7 @@
         <v>59.375</v>
       </c>
       <c r="AN43">
-        <v>8.0930000000000002E-2</v>
+        <v>8.0829999999999999E-2</v>
       </c>
       <c r="AO43">
         <v>59.375</v>
@@ -6089,7 +6089,7 @@
         <v>59.375</v>
       </c>
       <c r="AT43">
-        <v>8.0930000000000002E-2</v>
+        <v>8.1129999999999994E-2</v>
       </c>
     </row>
     <row r="44" spans="1:46" x14ac:dyDescent="0.25">
@@ -6187,7 +6187,7 @@
         <v>60.9375</v>
       </c>
       <c r="AF44">
-        <v>8.3030000000000007E-2</v>
+        <v>8.3040000000000003E-2</v>
       </c>
       <c r="AG44">
         <v>60.9375</v>
@@ -6229,7 +6229,7 @@
         <v>60.9375</v>
       </c>
       <c r="AT44">
-        <v>8.3059999999999995E-2</v>
+        <v>8.2960000000000006E-2</v>
       </c>
     </row>
     <row r="45" spans="1:46" x14ac:dyDescent="0.25">
@@ -6351,7 +6351,7 @@
         <v>62.5</v>
       </c>
       <c r="AN45">
-        <v>8.5220000000000004E-2</v>
+        <v>8.5319999999999993E-2</v>
       </c>
       <c r="AO45">
         <v>62.5</v>
@@ -6369,7 +6369,7 @@
         <v>62.5</v>
       </c>
       <c r="AT45">
-        <v>8.5220000000000004E-2</v>
+        <v>8.5419999999999996E-2</v>
       </c>
     </row>
     <row r="46" spans="1:46" x14ac:dyDescent="0.25">
@@ -6467,7 +6467,7 @@
         <v>64.0625</v>
       </c>
       <c r="AF46">
-        <v>8.7319999999999995E-2</v>
+        <v>8.7309999999999999E-2</v>
       </c>
       <c r="AG46">
         <v>64.0625</v>
@@ -6491,7 +6491,7 @@
         <v>64.0625</v>
       </c>
       <c r="AN46">
-        <v>8.7359999999999993E-2</v>
+        <v>8.7459999999999996E-2</v>
       </c>
       <c r="AO46">
         <v>64.0625</v>
@@ -6509,7 +6509,7 @@
         <v>64.0625</v>
       </c>
       <c r="AT46">
-        <v>8.7359999999999993E-2</v>
+        <v>8.7459999999999996E-2</v>
       </c>
     </row>
     <row r="47" spans="1:46" x14ac:dyDescent="0.25">
@@ -6607,7 +6607,7 @@
         <v>65.625</v>
       </c>
       <c r="AF47">
-        <v>8.949E-2</v>
+        <v>8.9480000000000004E-2</v>
       </c>
       <c r="AG47">
         <v>65.625</v>
@@ -6631,7 +6631,7 @@
         <v>65.625</v>
       </c>
       <c r="AN47">
-        <v>8.9520000000000002E-2</v>
+        <v>8.9419999999999999E-2</v>
       </c>
       <c r="AO47">
         <v>65.625</v>
@@ -6649,7 +6649,7 @@
         <v>65.625</v>
       </c>
       <c r="AT47">
-        <v>8.9520000000000002E-2</v>
+        <v>8.9319999999999997E-2</v>
       </c>
     </row>
     <row r="48" spans="1:46" x14ac:dyDescent="0.25">
@@ -6747,7 +6747,7 @@
         <v>67.1875</v>
       </c>
       <c r="AF48">
-        <v>9.1639999999999999E-2</v>
+        <v>9.1649999999999995E-2</v>
       </c>
       <c r="AG48">
         <v>67.1875</v>
@@ -6771,7 +6771,7 @@
         <v>67.1875</v>
       </c>
       <c r="AN48">
-        <v>9.1649999999999995E-2</v>
+        <v>9.1749999999999998E-2</v>
       </c>
       <c r="AO48">
         <v>67.1875</v>
@@ -6789,7 +6789,7 @@
         <v>67.1875</v>
       </c>
       <c r="AT48">
-        <v>9.1649999999999995E-2</v>
+        <v>9.1450000000000004E-2</v>
       </c>
     </row>
     <row r="49" spans="1:46" x14ac:dyDescent="0.25">
@@ -6887,7 +6887,7 @@
         <v>68.75</v>
       </c>
       <c r="AF49">
-        <v>9.3770000000000006E-2</v>
+        <v>9.3780000000000002E-2</v>
       </c>
       <c r="AG49">
         <v>68.75</v>
@@ -6929,7 +6929,7 @@
         <v>68.75</v>
       </c>
       <c r="AT49">
-        <v>9.3799999999999994E-2</v>
+        <v>9.3700000000000006E-2</v>
       </c>
     </row>
     <row r="50" spans="1:46" x14ac:dyDescent="0.25">
@@ -7027,7 +7027,7 @@
         <v>70.3125</v>
       </c>
       <c r="AF50">
-        <v>9.5920000000000005E-2</v>
+        <v>9.5930000000000001E-2</v>
       </c>
       <c r="AG50">
         <v>70.3125</v>
@@ -7069,7 +7069,7 @@
         <v>70.3125</v>
       </c>
       <c r="AT50">
-        <v>9.5949999999999994E-2</v>
+        <v>9.6149999999999999E-2</v>
       </c>
     </row>
     <row r="51" spans="1:46" x14ac:dyDescent="0.25">
@@ -7167,7 +7167,7 @@
         <v>71.875</v>
       </c>
       <c r="AF51">
-        <v>9.8080000000000001E-2</v>
+        <v>9.8089999999999997E-2</v>
       </c>
       <c r="AG51">
         <v>71.875</v>
@@ -7209,7 +7209,7 @@
         <v>71.875</v>
       </c>
       <c r="AT51">
-        <v>9.8110000000000003E-2</v>
+        <v>9.7909999999999997E-2</v>
       </c>
     </row>
     <row r="52" spans="1:46" x14ac:dyDescent="0.25">
@@ -7307,7 +7307,7 @@
         <v>73.4375</v>
       </c>
       <c r="AF52">
-        <v>0.10025000000000001</v>
+        <v>0.1003</v>
       </c>
       <c r="AG52">
         <v>73.4375</v>
@@ -7447,7 +7447,7 @@
         <v>75</v>
       </c>
       <c r="AF53">
-        <v>0.10241</v>
+        <v>0.1024</v>
       </c>
       <c r="AG53">
         <v>75</v>
@@ -7471,7 +7471,7 @@
         <v>75</v>
       </c>
       <c r="AN53">
-        <v>0.10242999999999999</v>
+        <v>0.10253</v>
       </c>
       <c r="AO53">
         <v>75</v>
@@ -7489,7 +7489,7 @@
         <v>75</v>
       </c>
       <c r="AT53">
-        <v>0.10242999999999999</v>
+        <v>0.10263</v>
       </c>
     </row>
     <row r="54" spans="1:46" x14ac:dyDescent="0.25">
@@ -7611,7 +7611,7 @@
         <v>76.5625</v>
       </c>
       <c r="AN54">
-        <v>0.10460999999999999</v>
+        <v>0.10471</v>
       </c>
       <c r="AO54">
         <v>76.5625</v>
@@ -7727,7 +7727,7 @@
         <v>78.125</v>
       </c>
       <c r="AF55">
-        <v>0.10675999999999999</v>
+        <v>0.10675</v>
       </c>
       <c r="AG55">
         <v>78.125</v>
@@ -7751,7 +7751,7 @@
         <v>78.125</v>
       </c>
       <c r="AN55">
-        <v>0.10679</v>
+        <v>0.10689</v>
       </c>
       <c r="AO55">
         <v>78.125</v>
@@ -7769,7 +7769,7 @@
         <v>78.125</v>
       </c>
       <c r="AT55">
-        <v>0.10679</v>
+        <v>0.10659</v>
       </c>
     </row>
     <row r="56" spans="1:46" x14ac:dyDescent="0.25">
@@ -7867,7 +7867,7 @@
         <v>79.6875</v>
       </c>
       <c r="AF56">
-        <v>0.10894</v>
+        <v>0.10895000000000001</v>
       </c>
       <c r="AG56">
         <v>79.6875</v>
@@ -7891,7 +7891,7 @@
         <v>79.6875</v>
       </c>
       <c r="AN56">
-        <v>0.10895000000000001</v>
+        <v>0.10885</v>
       </c>
       <c r="AO56">
         <v>79.6875</v>
@@ -7909,7 +7909,7 @@
         <v>79.6875</v>
       </c>
       <c r="AT56">
-        <v>0.10895000000000001</v>
+        <v>0.10875</v>
       </c>
     </row>
     <row r="57" spans="1:46" x14ac:dyDescent="0.25">
@@ -8007,7 +8007,7 @@
         <v>81.25</v>
       </c>
       <c r="AF57">
-        <v>0.1111</v>
+        <v>0.11119999999999999</v>
       </c>
       <c r="AG57">
         <v>81.25</v>
@@ -8031,7 +8031,7 @@
         <v>81.25</v>
       </c>
       <c r="AN57">
-        <v>0.11113000000000001</v>
+        <v>0.11103</v>
       </c>
       <c r="AO57">
         <v>81.25</v>
@@ -8049,7 +8049,7 @@
         <v>81.25</v>
       </c>
       <c r="AT57">
-        <v>0.11113000000000001</v>
+        <v>0.11093</v>
       </c>
     </row>
     <row r="58" spans="1:46" x14ac:dyDescent="0.25">
@@ -8147,7 +8147,7 @@
         <v>82.8125</v>
       </c>
       <c r="AF58">
-        <v>0.11328000000000001</v>
+        <v>0.11327</v>
       </c>
       <c r="AG58">
         <v>82.8125</v>
@@ -8171,7 +8171,7 @@
         <v>82.8125</v>
       </c>
       <c r="AN58">
-        <v>0.11330999999999999</v>
+        <v>0.11341</v>
       </c>
       <c r="AO58">
         <v>82.8125</v>
@@ -8189,7 +8189,7 @@
         <v>82.8125</v>
       </c>
       <c r="AT58">
-        <v>0.11330999999999999</v>
+        <v>0.11321000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:46" x14ac:dyDescent="0.25">
@@ -8287,7 +8287,7 @@
         <v>84.375</v>
       </c>
       <c r="AF59">
-        <v>0.11550000000000001</v>
+        <v>0.1154</v>
       </c>
       <c r="AG59">
         <v>84.375</v>
@@ -8311,7 +8311,7 @@
         <v>84.375</v>
       </c>
       <c r="AN59">
-        <v>0.11551</v>
+        <v>0.11561</v>
       </c>
       <c r="AO59">
         <v>84.375</v>
@@ -8329,7 +8329,7 @@
         <v>84.375</v>
       </c>
       <c r="AT59">
-        <v>0.11551</v>
+        <v>0.11531</v>
       </c>
     </row>
     <row r="60" spans="1:46" x14ac:dyDescent="0.25">
@@ -8427,7 +8427,7 @@
         <v>85.9375</v>
       </c>
       <c r="AF60">
-        <v>0.11768000000000001</v>
+        <v>0.11767</v>
       </c>
       <c r="AG60">
         <v>85.9375</v>
@@ -8451,7 +8451,7 @@
         <v>85.9375</v>
       </c>
       <c r="AN60">
-        <v>0.11771</v>
+        <v>0.11761000000000001</v>
       </c>
       <c r="AO60">
         <v>85.9375</v>
@@ -8469,7 +8469,7 @@
         <v>85.9375</v>
       </c>
       <c r="AT60">
-        <v>0.11771</v>
+        <v>0.11781</v>
       </c>
     </row>
     <row r="61" spans="1:46" x14ac:dyDescent="0.25">
@@ -8567,7 +8567,7 @@
         <v>87.5</v>
       </c>
       <c r="AF61">
-        <v>0.11989</v>
+        <v>0.11982</v>
       </c>
       <c r="AG61">
         <v>87.5</v>
@@ -8591,7 +8591,7 @@
         <v>87.5</v>
       </c>
       <c r="AN61">
-        <v>0.11992</v>
+        <v>0.11982</v>
       </c>
       <c r="AO61">
         <v>87.5</v>
@@ -8609,7 +8609,7 @@
         <v>87.5</v>
       </c>
       <c r="AT61">
-        <v>0.11992</v>
+        <v>0.12002</v>
       </c>
     </row>
     <row r="62" spans="1:46" x14ac:dyDescent="0.25">
@@ -8707,7 +8707,7 @@
         <v>89.0625</v>
       </c>
       <c r="AF62">
-        <v>0.12209</v>
+        <v>0.1221</v>
       </c>
       <c r="AG62">
         <v>89.0625</v>
@@ -8749,7 +8749,7 @@
         <v>89.0625</v>
       </c>
       <c r="AT62">
-        <v>0.12212000000000001</v>
+        <v>0.12232</v>
       </c>
     </row>
     <row r="63" spans="1:46" x14ac:dyDescent="0.25">
@@ -8847,7 +8847,7 @@
         <v>90.625</v>
       </c>
       <c r="AF63">
-        <v>0.12429999999999999</v>
+        <v>0.12431</v>
       </c>
       <c r="AG63">
         <v>90.625</v>
@@ -8871,7 +8871,7 @@
         <v>90.625</v>
       </c>
       <c r="AN63">
-        <v>0.12435</v>
+        <v>0.12425</v>
       </c>
       <c r="AO63">
         <v>90.625</v>
@@ -8889,7 +8889,7 @@
         <v>90.625</v>
       </c>
       <c r="AT63">
-        <v>0.12435</v>
+        <v>0.12415</v>
       </c>
     </row>
     <row r="64" spans="1:46" x14ac:dyDescent="0.25">
@@ -8987,7 +8987,7 @@
         <v>92.1875</v>
       </c>
       <c r="AF64">
-        <v>0.12653</v>
+        <v>0.12651999999999999</v>
       </c>
       <c r="AG64">
         <v>92.1875</v>
@@ -9029,7 +9029,7 @@
         <v>92.1875</v>
       </c>
       <c r="AT64">
-        <v>0.12656000000000001</v>
+        <v>0.12645999999999999</v>
       </c>
     </row>
     <row r="65" spans="1:46" x14ac:dyDescent="0.25">
@@ -9127,7 +9127,7 @@
         <v>93.75</v>
       </c>
       <c r="AF65">
-        <v>0.12873999999999999</v>
+        <v>0.12873000000000001</v>
       </c>
       <c r="AG65">
         <v>93.75</v>
@@ -9169,7 +9169,7 @@
         <v>93.75</v>
       </c>
       <c r="AT65">
-        <v>0.12878999999999999</v>
+        <v>0.12859000000000001</v>
       </c>
     </row>
     <row r="66" spans="1:46" x14ac:dyDescent="0.25">
@@ -9267,7 +9267,7 @@
         <v>95.3125</v>
       </c>
       <c r="AF66">
-        <v>0.13097</v>
+        <v>0.13098000000000001</v>
       </c>
       <c r="AG66">
         <v>95.3125</v>
@@ -9291,7 +9291,7 @@
         <v>95.3125</v>
       </c>
       <c r="AN66">
-        <v>0.13102</v>
+        <v>0.13111999999999999</v>
       </c>
       <c r="AO66">
         <v>95.3125</v>
@@ -9309,7 +9309,7 @@
         <v>95.3125</v>
       </c>
       <c r="AT66">
-        <v>0.13102</v>
+        <v>0.13081999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:46" x14ac:dyDescent="0.25">
@@ -9407,7 +9407,7 @@
         <v>96.875</v>
       </c>
       <c r="AF67">
-        <v>0.13322000000000001</v>
+        <v>0.13322999999999999</v>
       </c>
       <c r="AG67">
         <v>96.875</v>
@@ -9431,7 +9431,7 @@
         <v>96.875</v>
       </c>
       <c r="AN67">
-        <v>0.13325999999999999</v>
+        <v>0.13336000000000001</v>
       </c>
       <c r="AO67">
         <v>96.875</v>
@@ -9449,7 +9449,7 @@
         <v>96.875</v>
       </c>
       <c r="AT67">
-        <v>0.13325999999999999</v>
+        <v>0.13336000000000001</v>
       </c>
     </row>
     <row r="68" spans="1:46" x14ac:dyDescent="0.25">
@@ -9547,7 +9547,7 @@
         <v>98.4375</v>
       </c>
       <c r="AF68">
-        <v>0.13544</v>
+        <v>0.13539999999999999</v>
       </c>
       <c r="AG68">
         <v>98.4375</v>
@@ -9571,7 +9571,7 @@
         <v>98.4375</v>
       </c>
       <c r="AN68">
-        <v>0.13549</v>
+        <v>0.13558999999999999</v>
       </c>
       <c r="AO68">
         <v>98.4375</v>
@@ -9687,7 +9687,7 @@
         <v>100</v>
       </c>
       <c r="AF69">
-        <v>0.13743</v>
+        <v>0.13739999999999999</v>
       </c>
       <c r="AG69">
         <v>100</v>
@@ -9711,7 +9711,7 @@
         <v>100</v>
       </c>
       <c r="AN69">
-        <v>0.13746</v>
+        <v>0.13736000000000001</v>
       </c>
       <c r="AO69">
         <v>100</v>
@@ -9729,7 +9729,7 @@
         <v>100</v>
       </c>
       <c r="AT69">
-        <v>0.13746</v>
+        <v>0.13736000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:46" x14ac:dyDescent="0.25">
@@ -9827,7 +9827,7 @@
         <v>98.4375</v>
       </c>
       <c r="AF70">
-        <v>0.13528000000000001</v>
+        <v>0.13528999999999999</v>
       </c>
       <c r="AG70">
         <v>98.4375</v>
@@ -9851,7 +9851,7 @@
         <v>98.4375</v>
       </c>
       <c r="AN70">
-        <v>0.13532</v>
+        <v>0.13542000000000001</v>
       </c>
       <c r="AO70">
         <v>98.4375</v>
@@ -9967,7 +9967,7 @@
         <v>96.875</v>
       </c>
       <c r="AF71">
-        <v>0.13305</v>
+        <v>0.13300000000000001</v>
       </c>
       <c r="AG71">
         <v>96.875</v>
@@ -9991,7 +9991,7 @@
         <v>96.875</v>
       </c>
       <c r="AN71">
-        <v>0.13309000000000001</v>
+        <v>0.13319</v>
       </c>
       <c r="AO71">
         <v>96.875</v>
@@ -10009,7 +10009,7 @@
         <v>96.875</v>
       </c>
       <c r="AT71">
-        <v>0.13309000000000001</v>
+        <v>0.13319</v>
       </c>
     </row>
     <row r="72" spans="1:46" x14ac:dyDescent="0.25">
@@ -10107,7 +10107,7 @@
         <v>95.3125</v>
       </c>
       <c r="AF72">
-        <v>0.13081999999999999</v>
+        <v>0.1308</v>
       </c>
       <c r="AG72">
         <v>95.3125</v>
@@ -10149,7 +10149,7 @@
         <v>95.3125</v>
       </c>
       <c r="AT72">
-        <v>0.13086</v>
+        <v>0.13066</v>
       </c>
     </row>
     <row r="73" spans="1:46" x14ac:dyDescent="0.25">
@@ -10247,7 +10247,7 @@
         <v>93.75</v>
       </c>
       <c r="AF73">
-        <v>0.12861</v>
+        <v>0.12862000000000001</v>
       </c>
       <c r="AG73">
         <v>93.75</v>
@@ -10271,7 +10271,7 @@
         <v>93.75</v>
       </c>
       <c r="AN73">
-        <v>0.12862999999999999</v>
+        <v>0.12873000000000001</v>
       </c>
       <c r="AO73">
         <v>93.75</v>
@@ -10289,7 +10289,7 @@
         <v>93.75</v>
       </c>
       <c r="AT73">
-        <v>0.12862999999999999</v>
+        <v>0.12842999999999999</v>
       </c>
     </row>
     <row r="74" spans="1:46" x14ac:dyDescent="0.25">
@@ -10387,7 +10387,7 @@
         <v>92.1875</v>
       </c>
       <c r="AF74">
-        <v>0.12637999999999999</v>
+        <v>0.12640000000000001</v>
       </c>
       <c r="AG74">
         <v>92.1875</v>
@@ -10411,7 +10411,7 @@
         <v>92.1875</v>
       </c>
       <c r="AN74">
-        <v>0.12640000000000001</v>
+        <v>0.1263</v>
       </c>
       <c r="AO74">
         <v>92.1875</v>
@@ -10527,7 +10527,7 @@
         <v>90.625</v>
       </c>
       <c r="AF75">
-        <v>0.12415</v>
+        <v>0.12411999999999999</v>
       </c>
       <c r="AG75">
         <v>90.625</v>
@@ -10551,7 +10551,7 @@
         <v>90.625</v>
       </c>
       <c r="AN75">
-        <v>0.12417</v>
+        <v>0.12407</v>
       </c>
       <c r="AO75">
         <v>90.625</v>
@@ -10569,7 +10569,7 @@
         <v>90.625</v>
       </c>
       <c r="AT75">
-        <v>0.12417</v>
+        <v>0.12397</v>
       </c>
     </row>
     <row r="76" spans="1:46" x14ac:dyDescent="0.25">
@@ -10691,7 +10691,7 @@
         <v>89.0625</v>
       </c>
       <c r="AN76">
-        <v>0.12196</v>
+        <v>0.12186</v>
       </c>
       <c r="AO76">
         <v>89.0625</v>
@@ -10709,7 +10709,7 @@
         <v>89.0625</v>
       </c>
       <c r="AT76">
-        <v>0.12196</v>
+        <v>0.12216</v>
       </c>
     </row>
     <row r="77" spans="1:46" x14ac:dyDescent="0.25">
@@ -10831,7 +10831,7 @@
         <v>87.5</v>
       </c>
       <c r="AN77">
-        <v>0.11973</v>
+        <v>0.11963</v>
       </c>
       <c r="AO77">
         <v>87.5</v>
@@ -10849,7 +10849,7 @@
         <v>87.5</v>
       </c>
       <c r="AT77">
-        <v>0.11973</v>
+        <v>0.11953</v>
       </c>
     </row>
     <row r="78" spans="1:46" x14ac:dyDescent="0.25">
@@ -10947,7 +10947,7 @@
         <v>85.9375</v>
       </c>
       <c r="AF78">
-        <v>0.11749999999999999</v>
+        <v>0.1174</v>
       </c>
       <c r="AG78">
         <v>85.9375</v>
@@ -10989,7 +10989,7 @@
         <v>85.9375</v>
       </c>
       <c r="AT78">
-        <v>0.11753</v>
+        <v>0.11763</v>
       </c>
     </row>
     <row r="79" spans="1:46" x14ac:dyDescent="0.25">
@@ -11129,7 +11129,7 @@
         <v>84.375</v>
       </c>
       <c r="AT79">
-        <v>0.11532000000000001</v>
+        <v>0.11522</v>
       </c>
     </row>
     <row r="80" spans="1:46" x14ac:dyDescent="0.25">
@@ -11269,7 +11269,7 @@
         <v>82.8125</v>
       </c>
       <c r="AT80">
-        <v>0.11312</v>
+        <v>0.11322</v>
       </c>
     </row>
     <row r="81" spans="1:46" x14ac:dyDescent="0.25">
@@ -11367,7 +11367,7 @@
         <v>81.25</v>
       </c>
       <c r="AF81">
-        <v>0.11092</v>
+        <v>0.11090999999999999</v>
       </c>
       <c r="AG81">
         <v>81.25</v>
@@ -11391,7 +11391,7 @@
         <v>81.25</v>
       </c>
       <c r="AN81">
-        <v>0.11094</v>
+        <v>0.11083999999999999</v>
       </c>
       <c r="AO81">
         <v>81.25</v>
@@ -11409,7 +11409,7 @@
         <v>81.25</v>
       </c>
       <c r="AT81">
-        <v>0.11094</v>
+        <v>0.11114</v>
       </c>
     </row>
     <row r="82" spans="1:46" x14ac:dyDescent="0.25">
@@ -11531,7 +11531,7 @@
         <v>79.6875</v>
       </c>
       <c r="AN82">
-        <v>0.10876</v>
+        <v>0.10866000000000001</v>
       </c>
       <c r="AO82">
         <v>79.6875</v>
@@ -11549,7 +11549,7 @@
         <v>79.6875</v>
       </c>
       <c r="AT82">
-        <v>0.10876</v>
+        <v>0.10866000000000001</v>
       </c>
     </row>
     <row r="83" spans="1:46" x14ac:dyDescent="0.25">
@@ -11689,7 +11689,7 @@
         <v>78.125</v>
       </c>
       <c r="AT83">
-        <v>0.10656</v>
+        <v>0.10636</v>
       </c>
     </row>
     <row r="84" spans="1:46" x14ac:dyDescent="0.25">
@@ -11787,7 +11787,7 @@
         <v>76.5625</v>
       </c>
       <c r="AF84" s="1">
-        <v>0.10440000000000001</v>
+        <v>0.1045</v>
       </c>
       <c r="AG84">
         <v>76.5625</v>
@@ -11829,7 +11829,7 @@
         <v>76.5625</v>
       </c>
       <c r="AT84">
-        <v>0.10440000000000001</v>
+        <v>0.1046</v>
       </c>
     </row>
     <row r="85" spans="1:46" x14ac:dyDescent="0.25">
@@ -11951,7 +11951,7 @@
         <v>75</v>
       </c>
       <c r="AN85">
-        <v>0.10222000000000001</v>
+        <v>0.10231999999999999</v>
       </c>
       <c r="AO85">
         <v>75</v>
@@ -12091,7 +12091,7 @@
         <v>73.4375</v>
       </c>
       <c r="AN86">
-        <v>0.10007000000000001</v>
+        <v>0.10017</v>
       </c>
       <c r="AO86">
         <v>73.4375</v>
@@ -12109,7 +12109,7 @@
         <v>73.4375</v>
       </c>
       <c r="AT86">
-        <v>0.10007000000000001</v>
+        <v>0.10017</v>
       </c>
     </row>
     <row r="87" spans="1:46" x14ac:dyDescent="0.25">
@@ -12207,7 +12207,7 @@
         <v>71.875</v>
       </c>
       <c r="AF87" s="1">
-        <v>9.7890000000000005E-2</v>
+        <v>9.7900000000000001E-2</v>
       </c>
       <c r="AG87">
         <v>71.875</v>
@@ -12249,7 +12249,7 @@
         <v>71.875</v>
       </c>
       <c r="AT87">
-        <v>9.7890000000000005E-2</v>
+        <v>9.8089999999999997E-2</v>
       </c>
     </row>
     <row r="88" spans="1:46" x14ac:dyDescent="0.25">
@@ -12371,7 +12371,7 @@
         <v>70.3125</v>
       </c>
       <c r="AN88">
-        <v>9.5740000000000006E-2</v>
+        <v>9.5839999999999995E-2</v>
       </c>
       <c r="AO88">
         <v>70.3125</v>
@@ -12487,7 +12487,7 @@
         <v>68.75</v>
       </c>
       <c r="AF89">
-        <v>9.3590000000000007E-2</v>
+        <v>9.3579999999999997E-2</v>
       </c>
       <c r="AG89">
         <v>68.75</v>
@@ -12511,7 +12511,7 @@
         <v>68.75</v>
       </c>
       <c r="AN89">
-        <v>9.3590000000000007E-2</v>
+        <v>9.3689999999999996E-2</v>
       </c>
       <c r="AO89">
         <v>68.75</v>
@@ -12529,7 +12529,7 @@
         <v>68.75</v>
       </c>
       <c r="AT89">
-        <v>9.3590000000000007E-2</v>
+        <v>9.3789999999999998E-2</v>
       </c>
     </row>
     <row r="90" spans="1:46" x14ac:dyDescent="0.25">
@@ -12627,7 +12627,7 @@
         <v>67.1875</v>
       </c>
       <c r="AF90">
-        <v>9.1429999999999997E-2</v>
+        <v>9.1499999999999998E-2</v>
       </c>
       <c r="AG90">
         <v>67.1875</v>
@@ -12791,7 +12791,7 @@
         <v>65.625</v>
       </c>
       <c r="AN91">
-        <v>8.9279999999999998E-2</v>
+        <v>8.9179999999999995E-2</v>
       </c>
       <c r="AO91">
         <v>65.625</v>
@@ -12809,7 +12809,7 @@
         <v>65.625</v>
       </c>
       <c r="AT91">
-        <v>8.9279999999999998E-2</v>
+        <v>8.9179999999999995E-2</v>
       </c>
     </row>
     <row r="92" spans="1:46" x14ac:dyDescent="0.25">
@@ -12907,7 +12907,7 @@
         <v>64.0625</v>
       </c>
       <c r="AF92">
-        <v>8.7129999999999999E-2</v>
+        <v>8.7169999999999997E-2</v>
       </c>
       <c r="AG92">
         <v>64.0625</v>
@@ -12931,7 +12931,7 @@
         <v>64.0625</v>
       </c>
       <c r="AN92">
-        <v>8.7129999999999999E-2</v>
+        <v>8.7230000000000002E-2</v>
       </c>
       <c r="AO92">
         <v>64.0625</v>
@@ -12949,7 +12949,7 @@
         <v>64.0625</v>
       </c>
       <c r="AT92">
-        <v>8.7129999999999999E-2</v>
+        <v>8.6929999999999993E-2</v>
       </c>
     </row>
     <row r="93" spans="1:46" x14ac:dyDescent="0.25">
@@ -13071,7 +13071,7 @@
         <v>62.5</v>
       </c>
       <c r="AN93">
-        <v>8.4970000000000004E-2</v>
+        <v>8.4870000000000001E-2</v>
       </c>
       <c r="AO93">
         <v>62.5</v>
@@ -13089,7 +13089,7 @@
         <v>62.5</v>
       </c>
       <c r="AT93">
-        <v>8.4970000000000004E-2</v>
+        <v>8.4870000000000001E-2</v>
       </c>
     </row>
     <row r="94" spans="1:46" x14ac:dyDescent="0.25">
@@ -13187,7 +13187,7 @@
         <v>60.9375</v>
       </c>
       <c r="AF94">
-        <v>8.2830000000000001E-2</v>
+        <v>8.2849999999999993E-2</v>
       </c>
       <c r="AG94">
         <v>60.9375</v>
@@ -13211,7 +13211,7 @@
         <v>60.9375</v>
       </c>
       <c r="AN94">
-        <v>8.2830000000000001E-2</v>
+        <v>8.2930000000000004E-2</v>
       </c>
       <c r="AO94">
         <v>60.9375</v>
@@ -13229,7 +13229,7 @@
         <v>60.9375</v>
       </c>
       <c r="AT94">
-        <v>8.2830000000000001E-2</v>
+        <v>8.2629999999999995E-2</v>
       </c>
     </row>
     <row r="95" spans="1:46" x14ac:dyDescent="0.25">
@@ -13327,7 +13327,7 @@
         <v>59.375</v>
       </c>
       <c r="AF95">
-        <v>8.0689999999999998E-2</v>
+        <v>8.0680000000000002E-2</v>
       </c>
       <c r="AG95">
         <v>59.375</v>
@@ -13351,7 +13351,7 @@
         <v>59.375</v>
       </c>
       <c r="AN95">
-        <v>8.0689999999999998E-2</v>
+        <v>8.0790000000000001E-2</v>
       </c>
       <c r="AO95">
         <v>59.375</v>
@@ -13369,7 +13369,7 @@
         <v>59.375</v>
       </c>
       <c r="AT95">
-        <v>8.0689999999999998E-2</v>
+        <v>8.0589999999999995E-2</v>
       </c>
     </row>
     <row r="96" spans="1:46" x14ac:dyDescent="0.25">
@@ -13467,7 +13467,7 @@
         <v>57.8125</v>
       </c>
       <c r="AF96">
-        <v>7.8549999999999995E-2</v>
+        <v>7.8539999999999999E-2</v>
       </c>
       <c r="AG96">
         <v>57.8125</v>
@@ -13491,7 +13491,7 @@
         <v>57.8125</v>
       </c>
       <c r="AN96">
-        <v>7.8549999999999995E-2</v>
+        <v>7.8450000000000006E-2</v>
       </c>
       <c r="AO96">
         <v>57.8125</v>
@@ -13509,7 +13509,7 @@
         <v>57.8125</v>
       </c>
       <c r="AT96">
-        <v>7.8549999999999995E-2</v>
+        <v>7.8350000000000003E-2</v>
       </c>
     </row>
     <row r="97" spans="1:46" x14ac:dyDescent="0.25">
@@ -13631,7 +13631,7 @@
         <v>56.25</v>
       </c>
       <c r="AN97">
-        <v>7.6399999999999996E-2</v>
+        <v>7.6300000000000007E-2</v>
       </c>
       <c r="AO97">
         <v>56.25</v>
@@ -13649,7 +13649,7 @@
         <v>56.25</v>
       </c>
       <c r="AT97">
-        <v>7.6399999999999996E-2</v>
+        <v>7.6600000000000001E-2</v>
       </c>
     </row>
     <row r="98" spans="1:46" x14ac:dyDescent="0.25">
@@ -13747,7 +13747,7 @@
         <v>54.6875</v>
       </c>
       <c r="AF98">
-        <v>7.4270000000000003E-2</v>
+        <v>7.4279999999999999E-2</v>
       </c>
       <c r="AG98">
         <v>54.6875</v>
@@ -13771,7 +13771,7 @@
         <v>54.6875</v>
       </c>
       <c r="AN98">
-        <v>7.4289999999999995E-2</v>
+        <v>7.4190000000000006E-2</v>
       </c>
       <c r="AO98">
         <v>54.6875</v>
@@ -13789,7 +13789,7 @@
         <v>54.6875</v>
       </c>
       <c r="AT98">
-        <v>7.4289999999999995E-2</v>
+        <v>7.4490000000000001E-2</v>
       </c>
     </row>
     <row r="99" spans="1:46" x14ac:dyDescent="0.25">
@@ -13911,7 +13911,7 @@
         <v>53.125</v>
       </c>
       <c r="AN99">
-        <v>7.2120000000000004E-2</v>
+        <v>7.2220000000000006E-2</v>
       </c>
       <c r="AO99">
         <v>53.125</v>
@@ -14027,7 +14027,7 @@
         <v>51.5625</v>
       </c>
       <c r="AF100">
-        <v>7.0010000000000003E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AG100">
         <v>51.5625</v>
@@ -14167,7 +14167,7 @@
         <v>50</v>
       </c>
       <c r="AF101">
-        <v>6.7809999999999995E-2</v>
+        <v>6.7820000000000005E-2</v>
       </c>
       <c r="AG101">
         <v>50</v>
@@ -14191,7 +14191,7 @@
         <v>50</v>
       </c>
       <c r="AN101">
-        <v>6.7809999999999995E-2</v>
+        <v>6.7710000000000006E-2</v>
       </c>
       <c r="AO101">
         <v>50</v>
@@ -14209,7 +14209,7 @@
         <v>50</v>
       </c>
       <c r="AT101">
-        <v>6.7809999999999995E-2</v>
+        <v>6.7610000000000003E-2</v>
       </c>
     </row>
     <row r="102" spans="1:46" x14ac:dyDescent="0.25">
@@ -14349,7 +14349,7 @@
         <v>48.4375</v>
       </c>
       <c r="AT102">
-        <v>6.5680000000000002E-2</v>
+        <v>6.5479999999999997E-2</v>
       </c>
     </row>
     <row r="103" spans="1:46" x14ac:dyDescent="0.25">
@@ -14471,7 +14471,7 @@
         <v>46.875</v>
       </c>
       <c r="AN103">
-        <v>6.3549999999999995E-2</v>
+        <v>6.3649999999999998E-2</v>
       </c>
       <c r="AO103">
         <v>46.875</v>
@@ -14489,7 +14489,7 @@
         <v>46.875</v>
       </c>
       <c r="AT103">
-        <v>6.3549999999999995E-2</v>
+        <v>6.3649999999999998E-2</v>
       </c>
     </row>
     <row r="104" spans="1:46" x14ac:dyDescent="0.25">
@@ -14587,7 +14587,7 @@
         <v>45.3125</v>
       </c>
       <c r="AF104">
-        <v>6.1429999999999998E-2</v>
+        <v>6.1420000000000002E-2</v>
       </c>
       <c r="AG104">
         <v>45.3125</v>
@@ -14611,7 +14611,7 @@
         <v>45.3125</v>
       </c>
       <c r="AN104">
-        <v>6.1429999999999998E-2</v>
+        <v>6.1530000000000001E-2</v>
       </c>
       <c r="AO104">
         <v>45.3125</v>
@@ -14629,7 +14629,7 @@
         <v>45.3125</v>
       </c>
       <c r="AT104">
-        <v>6.1429999999999998E-2</v>
+        <v>6.1629999999999997E-2</v>
       </c>
     </row>
     <row r="105" spans="1:46" x14ac:dyDescent="0.25">
@@ -14751,7 +14751,7 @@
         <v>43.75</v>
       </c>
       <c r="AN105">
-        <v>5.9299999999999999E-2</v>
+        <v>5.9400000000000001E-2</v>
       </c>
       <c r="AO105">
         <v>43.75</v>
@@ -14769,7 +14769,7 @@
         <v>43.75</v>
       </c>
       <c r="AT105">
-        <v>5.9299999999999999E-2</v>
+        <v>5.91E-2</v>
       </c>
     </row>
     <row r="106" spans="1:46" x14ac:dyDescent="0.25">
@@ -14891,7 +14891,7 @@
         <v>42.1875</v>
       </c>
       <c r="AN106">
-        <v>5.7180000000000002E-2</v>
+        <v>5.7079999999999999E-2</v>
       </c>
       <c r="AO106">
         <v>42.1875</v>
@@ -14909,7 +14909,7 @@
         <v>42.1875</v>
       </c>
       <c r="AT106">
-        <v>5.7180000000000002E-2</v>
+        <v>5.7079999999999999E-2</v>
       </c>
     </row>
     <row r="107" spans="1:46" x14ac:dyDescent="0.25">
@@ -15031,7 +15031,7 @@
         <v>40.625</v>
       </c>
       <c r="AN107">
-        <v>5.5050000000000002E-2</v>
+        <v>5.5149999999999998E-2</v>
       </c>
       <c r="AO107">
         <v>40.625</v>
@@ -15147,7 +15147,7 @@
         <v>39.0625</v>
       </c>
       <c r="AF108">
-        <v>5.2920000000000002E-2</v>
+        <v>5.2909999999999999E-2</v>
       </c>
       <c r="AG108">
         <v>39.0625</v>
@@ -15189,7 +15189,7 @@
         <v>39.0625</v>
       </c>
       <c r="AT108">
-        <v>5.2920000000000002E-2</v>
+        <v>5.2720000000000003E-2</v>
       </c>
     </row>
     <row r="109" spans="1:46" x14ac:dyDescent="0.25">
@@ -15329,7 +15329,7 @@
         <v>37.5</v>
       </c>
       <c r="AT109">
-        <v>5.0790000000000002E-2</v>
+        <v>5.0990000000000001E-2</v>
       </c>
     </row>
     <row r="110" spans="1:46" x14ac:dyDescent="0.25">
@@ -15451,7 +15451,7 @@
         <v>35.9375</v>
       </c>
       <c r="AN110">
-        <v>4.8649999999999999E-2</v>
+        <v>4.8750000000000002E-2</v>
       </c>
       <c r="AO110">
         <v>35.9375</v>
@@ -15469,7 +15469,7 @@
         <v>35.9375</v>
       </c>
       <c r="AT110">
-        <v>4.8649999999999999E-2</v>
+        <v>4.8750000000000002E-2</v>
       </c>
     </row>
     <row r="111" spans="1:46" x14ac:dyDescent="0.25">
@@ -15567,7 +15567,7 @@
         <v>34.375</v>
       </c>
       <c r="AF111">
-        <v>4.6519999999999999E-2</v>
+        <v>4.6530000000000002E-2</v>
       </c>
       <c r="AG111">
         <v>34.375</v>
@@ -15591,7 +15591,7 @@
         <v>34.375</v>
       </c>
       <c r="AN111">
-        <v>4.6539999999999998E-2</v>
+        <v>4.6440000000000002E-2</v>
       </c>
       <c r="AO111">
         <v>34.375</v>
@@ -15609,7 +15609,7 @@
         <v>34.375</v>
       </c>
       <c r="AT111">
-        <v>4.6539999999999998E-2</v>
+        <v>4.6339999999999999E-2</v>
       </c>
     </row>
     <row r="112" spans="1:46" x14ac:dyDescent="0.25">
@@ -15707,7 +15707,7 @@
         <v>32.8125</v>
       </c>
       <c r="AF112">
-        <v>4.4409999999999998E-2</v>
+        <v>4.4420000000000001E-2</v>
       </c>
       <c r="AG112">
         <v>32.8125</v>
@@ -15731,7 +15731,7 @@
         <v>32.8125</v>
       </c>
       <c r="AN112">
-        <v>4.4409999999999998E-2</v>
+        <v>4.4310000000000002E-2</v>
       </c>
       <c r="AO112">
         <v>32.8125</v>
@@ -15749,7 +15749,7 @@
         <v>32.8125</v>
       </c>
       <c r="AT112">
-        <v>4.4409999999999998E-2</v>
+        <v>4.4209999999999999E-2</v>
       </c>
     </row>
     <row r="113" spans="1:46" x14ac:dyDescent="0.25">
@@ -15871,7 +15871,7 @@
         <v>31.25</v>
       </c>
       <c r="AN113">
-        <v>4.2290000000000001E-2</v>
+        <v>4.2189999999999998E-2</v>
       </c>
       <c r="AO113">
         <v>31.25</v>
@@ -15889,7 +15889,7 @@
         <v>31.25</v>
       </c>
       <c r="AT113">
-        <v>4.2290000000000001E-2</v>
+        <v>4.249E-2</v>
       </c>
     </row>
     <row r="114" spans="1:46" x14ac:dyDescent="0.25">
@@ -16029,7 +16029,7 @@
         <v>29.6875</v>
       </c>
       <c r="AT114">
-        <v>4.0169999999999997E-2</v>
+        <v>4.0370000000000003E-2</v>
       </c>
     </row>
     <row r="115" spans="1:46" x14ac:dyDescent="0.25">
@@ -16127,7 +16127,7 @@
         <v>28.125</v>
       </c>
       <c r="AF115">
-        <v>3.8039999999999997E-2</v>
+        <v>3.8019999999999998E-2</v>
       </c>
       <c r="AG115">
         <v>28.125</v>
@@ -16169,7 +16169,7 @@
         <v>28.125</v>
       </c>
       <c r="AT115">
-        <v>3.8039999999999997E-2</v>
+        <v>3.7839999999999999E-2</v>
       </c>
     </row>
     <row r="116" spans="1:46" x14ac:dyDescent="0.25">
@@ -16309,7 +16309,7 @@
         <v>26.5625</v>
       </c>
       <c r="AT116">
-        <v>3.5920000000000001E-2</v>
+        <v>3.6020000000000003E-2</v>
       </c>
     </row>
     <row r="117" spans="1:46" x14ac:dyDescent="0.25">
@@ -16431,7 +16431,7 @@
         <v>25</v>
       </c>
       <c r="AN117">
-        <v>3.3790000000000001E-2</v>
+        <v>3.3689999999999998E-2</v>
       </c>
       <c r="AO117">
         <v>25</v>
@@ -16449,7 +16449,7 @@
         <v>25</v>
       </c>
       <c r="AT117">
-        <v>3.3790000000000001E-2</v>
+        <v>3.3989999999999999E-2</v>
       </c>
     </row>
     <row r="118" spans="1:46" x14ac:dyDescent="0.25">
@@ -16571,7 +16571,7 @@
         <v>23.4375</v>
       </c>
       <c r="AN118">
-        <v>3.168E-2</v>
+        <v>3.1579999999999997E-2</v>
       </c>
       <c r="AO118">
         <v>23.4375</v>
@@ -16589,7 +16589,7 @@
         <v>23.4375</v>
       </c>
       <c r="AT118">
-        <v>3.168E-2</v>
+        <v>3.1879999999999999E-2</v>
       </c>
     </row>
     <row r="119" spans="1:46" x14ac:dyDescent="0.25">
@@ -16729,7 +16729,7 @@
         <v>21.875</v>
       </c>
       <c r="AT119">
-        <v>2.9559999999999999E-2</v>
+        <v>2.9360000000000001E-2</v>
       </c>
     </row>
     <row r="120" spans="1:46" x14ac:dyDescent="0.25">
@@ -16851,7 +16851,7 @@
         <v>20.3125</v>
       </c>
       <c r="AN120">
-        <v>2.743E-2</v>
+        <v>2.733E-2</v>
       </c>
       <c r="AO120">
         <v>20.3125</v>
@@ -16869,7 +16869,7 @@
         <v>20.3125</v>
       </c>
       <c r="AT120">
-        <v>2.743E-2</v>
+        <v>2.733E-2</v>
       </c>
     </row>
     <row r="121" spans="1:46" x14ac:dyDescent="0.25">
@@ -16991,7 +16991,7 @@
         <v>18.75</v>
       </c>
       <c r="AN121">
-        <v>2.5309999999999999E-2</v>
+        <v>2.521E-2</v>
       </c>
       <c r="AO121">
         <v>18.75</v>
@@ -17009,7 +17009,7 @@
         <v>18.75</v>
       </c>
       <c r="AT121">
-        <v>2.5309999999999999E-2</v>
+        <v>2.511E-2</v>
       </c>
     </row>
     <row r="122" spans="1:46" x14ac:dyDescent="0.25">
@@ -17131,7 +17131,7 @@
         <v>17.1875</v>
       </c>
       <c r="AN122">
-        <v>2.3199999999999998E-2</v>
+        <v>2.3300000000000001E-2</v>
       </c>
       <c r="AO122">
         <v>17.1875</v>
@@ -17289,7 +17289,7 @@
         <v>15.625</v>
       </c>
       <c r="AT123">
-        <v>2.1049999999999999E-2</v>
+        <v>2.1250000000000002E-2</v>
       </c>
     </row>
     <row r="124" spans="1:46" x14ac:dyDescent="0.25">
@@ -17411,7 +17411,7 @@
         <v>14.0625</v>
       </c>
       <c r="AN124">
-        <v>1.8929999999999999E-2</v>
+        <v>1.883E-2</v>
       </c>
       <c r="AO124">
         <v>14.0625</v>
@@ -17429,7 +17429,7 @@
         <v>14.0625</v>
       </c>
       <c r="AT124">
-        <v>1.8929999999999999E-2</v>
+        <v>1.9029999999999998E-2</v>
       </c>
     </row>
     <row r="125" spans="1:46" x14ac:dyDescent="0.25">
@@ -17551,7 +17551,7 @@
         <v>12.5</v>
       </c>
       <c r="AN125">
-        <v>1.678E-2</v>
+        <v>1.6879999999999999E-2</v>
       </c>
       <c r="AO125">
         <v>12.5</v>
@@ -17569,7 +17569,7 @@
         <v>12.5</v>
       </c>
       <c r="AT125">
-        <v>1.678E-2</v>
+        <v>1.668E-2</v>
       </c>
     </row>
     <row r="126" spans="1:46" x14ac:dyDescent="0.25">
@@ -17709,7 +17709,7 @@
         <v>10.9375</v>
       </c>
       <c r="AT126">
-        <v>1.43E-2</v>
+        <v>1.4200000000000001E-2</v>
       </c>
     </row>
     <row r="127" spans="1:46" x14ac:dyDescent="0.25">
@@ -17849,7 +17849,7 @@
         <v>9.375</v>
       </c>
       <c r="AT127">
-        <v>1.24E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
     </row>
     <row r="128" spans="1:46" x14ac:dyDescent="0.25">
@@ -17971,7 +17971,7 @@
         <v>7.8125</v>
       </c>
       <c r="AN128">
-        <v>3.96E-3</v>
+        <v>4.0600000000000002E-3</v>
       </c>
       <c r="AO128">
         <v>7.8125</v>
@@ -17989,7 +17989,7 @@
         <v>7.8125</v>
       </c>
       <c r="AT128">
-        <v>9.9799999999999993E-3</v>
+        <v>1.008E-2</v>
       </c>
     </row>
     <row r="129" spans="1:46" x14ac:dyDescent="0.25">
@@ -18129,7 +18129,7 @@
         <v>6.25</v>
       </c>
       <c r="AT129">
-        <v>7.6800000000000002E-3</v>
+        <v>7.4799999999999997E-3</v>
       </c>
     </row>
     <row r="130" spans="1:46" x14ac:dyDescent="0.25">
@@ -19249,7 +19249,7 @@
         <v>-6.25</v>
       </c>
       <c r="AT137">
-        <v>-6.5700000000000003E-3</v>
+        <v>-6.77E-3</v>
       </c>
     </row>
     <row r="138" spans="1:46" x14ac:dyDescent="0.25">
@@ -19389,7 +19389,7 @@
         <v>-7.8125</v>
       </c>
       <c r="AT138">
-        <v>-9.8600000000000007E-3</v>
+        <v>-9.6600000000000002E-3</v>
       </c>
     </row>
     <row r="139" spans="1:46" x14ac:dyDescent="0.25">
@@ -19529,7 +19529,7 @@
         <v>-9.375</v>
       </c>
       <c r="AT139">
-        <v>-1.247E-2</v>
+        <v>-1.257E-2</v>
       </c>
     </row>
     <row r="140" spans="1:46" x14ac:dyDescent="0.25">
@@ -19669,7 +19669,7 @@
         <v>-10.9375</v>
       </c>
       <c r="AT140">
-        <v>-1.485E-2</v>
+        <v>-1.465E-2</v>
       </c>
     </row>
     <row r="141" spans="1:46" x14ac:dyDescent="0.25">
@@ -19791,7 +19791,7 @@
         <v>-12.5</v>
       </c>
       <c r="AN141">
-        <v>-1.6729999999999998E-2</v>
+        <v>-1.6830000000000001E-2</v>
       </c>
       <c r="AO141">
         <v>-12.5</v>
@@ -19809,7 +19809,7 @@
         <v>-12.5</v>
       </c>
       <c r="AT141">
-        <v>-1.6729999999999998E-2</v>
+        <v>-1.6830000000000001E-2</v>
       </c>
     </row>
     <row r="142" spans="1:46" x14ac:dyDescent="0.25">
@@ -19931,7 +19931,7 @@
         <v>-14.0625</v>
       </c>
       <c r="AN142">
-        <v>-1.916E-2</v>
+        <v>-1.9259999999999999E-2</v>
       </c>
       <c r="AO142">
         <v>-14.0625</v>
@@ -19949,7 +19949,7 @@
         <v>-14.0625</v>
       </c>
       <c r="AT142">
-        <v>-1.916E-2</v>
+        <v>-1.8960000000000001E-2</v>
       </c>
     </row>
     <row r="143" spans="1:46" x14ac:dyDescent="0.25">
@@ -20071,7 +20071,7 @@
         <v>-15.625</v>
       </c>
       <c r="AN143">
-        <v>-2.129E-2</v>
+        <v>-2.1389999999999999E-2</v>
       </c>
       <c r="AO143">
         <v>-15.625</v>
@@ -20089,7 +20089,7 @@
         <v>-15.625</v>
       </c>
       <c r="AT143">
-        <v>-2.129E-2</v>
+        <v>-2.1389999999999999E-2</v>
       </c>
     </row>
     <row r="144" spans="1:46" x14ac:dyDescent="0.25">
@@ -20211,7 +20211,7 @@
         <v>-17.1875</v>
       </c>
       <c r="AN144">
-        <v>-2.3439999999999999E-2</v>
+        <v>-2.334E-2</v>
       </c>
       <c r="AO144">
         <v>-17.1875</v>
@@ -20229,7 +20229,7 @@
         <v>-17.1875</v>
       </c>
       <c r="AT144">
-        <v>-2.3439999999999999E-2</v>
+        <v>-2.324E-2</v>
       </c>
     </row>
     <row r="145" spans="1:46" x14ac:dyDescent="0.25">
@@ -20351,7 +20351,7 @@
         <v>-18.75</v>
       </c>
       <c r="AN145">
-        <v>-2.554E-2</v>
+        <v>-2.5440000000000001E-2</v>
       </c>
       <c r="AO145">
         <v>-18.75</v>
@@ -20369,7 +20369,7 @@
         <v>-18.75</v>
       </c>
       <c r="AT145">
-        <v>-2.554E-2</v>
+        <v>-2.5739999999999999E-2</v>
       </c>
     </row>
     <row r="146" spans="1:46" x14ac:dyDescent="0.25">
@@ -20491,7 +20491,7 @@
         <v>-20.3125</v>
       </c>
       <c r="AN146">
-        <v>-2.767E-2</v>
+        <v>-2.777E-2</v>
       </c>
       <c r="AO146">
         <v>-20.3125</v>
@@ -20509,7 +20509,7 @@
         <v>-20.3125</v>
       </c>
       <c r="AT146">
-        <v>-2.767E-2</v>
+        <v>-2.7869999999999999E-2</v>
       </c>
     </row>
     <row r="147" spans="1:46" x14ac:dyDescent="0.25">
@@ -20631,7 +20631,7 @@
         <v>-21.875</v>
       </c>
       <c r="AN147">
-        <v>-2.9790000000000001E-2</v>
+        <v>-2.989E-2</v>
       </c>
       <c r="AO147">
         <v>-21.875</v>
@@ -20649,7 +20649,7 @@
         <v>-21.875</v>
       </c>
       <c r="AT147">
-        <v>-2.9790000000000001E-2</v>
+        <v>-2.9590000000000002E-2</v>
       </c>
     </row>
     <row r="148" spans="1:46" x14ac:dyDescent="0.25">
@@ -20747,7 +20747,7 @@
         <v>-23.4375</v>
       </c>
       <c r="AF148">
-        <v>-3.1919999999999997E-2</v>
+        <v>-3.193E-2</v>
       </c>
       <c r="AG148">
         <v>-23.4375</v>
@@ -20771,7 +20771,7 @@
         <v>-23.4375</v>
       </c>
       <c r="AN148">
-        <v>-3.1919999999999997E-2</v>
+        <v>-3.202E-2</v>
       </c>
       <c r="AO148">
         <v>-23.4375</v>
@@ -20789,7 +20789,7 @@
         <v>-23.4375</v>
       </c>
       <c r="AT148">
-        <v>-3.1919999999999997E-2</v>
+        <v>-3.202E-2</v>
       </c>
     </row>
     <row r="149" spans="1:46" x14ac:dyDescent="0.25">
@@ -20887,7 +20887,7 @@
         <v>-25</v>
       </c>
       <c r="AF149">
-        <v>-3.4029999999999998E-2</v>
+        <v>-3.4049999999999997E-2</v>
       </c>
       <c r="AG149">
         <v>-25</v>
@@ -20911,7 +20911,7 @@
         <v>-25</v>
       </c>
       <c r="AN149">
-        <v>-3.4029999999999998E-2</v>
+        <v>-3.4130000000000001E-2</v>
       </c>
       <c r="AO149">
         <v>-25</v>
@@ -20929,7 +20929,7 @@
         <v>-25</v>
       </c>
       <c r="AT149">
-        <v>-3.4029999999999998E-2</v>
+        <v>-3.3829999999999999E-2</v>
       </c>
     </row>
     <row r="150" spans="1:46" x14ac:dyDescent="0.25">
@@ -21027,7 +21027,7 @@
         <v>-26.5625</v>
       </c>
       <c r="AF150">
-        <v>-3.6150000000000002E-2</v>
+        <v>-3.6139999999999999E-2</v>
       </c>
       <c r="AG150">
         <v>-26.5625</v>
@@ -21051,7 +21051,7 @@
         <v>-26.5625</v>
       </c>
       <c r="AN150">
-        <v>-3.6170000000000001E-2</v>
+        <v>-3.6069999999999998E-2</v>
       </c>
       <c r="AO150">
         <v>-26.5625</v>
@@ -21167,7 +21167,7 @@
         <v>-28.125</v>
       </c>
       <c r="AF151">
-        <v>-3.8269999999999998E-2</v>
+        <v>-3.823E-2</v>
       </c>
       <c r="AG151">
         <v>-28.125</v>
@@ -21209,7 +21209,7 @@
         <v>-28.125</v>
       </c>
       <c r="AT151">
-        <v>-3.8269999999999998E-2</v>
+        <v>-3.8170000000000003E-2</v>
       </c>
     </row>
     <row r="152" spans="1:46" x14ac:dyDescent="0.25">
@@ -21307,7 +21307,7 @@
         <v>-29.6875</v>
       </c>
       <c r="AF152">
-        <v>-4.0399999999999998E-2</v>
+        <v>-4.0379999999999999E-2</v>
       </c>
       <c r="AG152">
         <v>-29.6875</v>
@@ -21349,7 +21349,7 @@
         <v>-29.6875</v>
       </c>
       <c r="AT152">
-        <v>-4.0419999999999998E-2</v>
+        <v>-4.052E-2</v>
       </c>
     </row>
     <row r="153" spans="1:46" x14ac:dyDescent="0.25">
@@ -21447,7 +21447,7 @@
         <v>-31.25</v>
       </c>
       <c r="AF153">
-        <v>-4.2520000000000002E-2</v>
+        <v>-4.2509999999999999E-2</v>
       </c>
       <c r="AG153">
         <v>-31.25</v>
@@ -21489,7 +21489,7 @@
         <v>-31.25</v>
       </c>
       <c r="AT153">
-        <v>-4.2529999999999998E-2</v>
+        <v>-4.2729999999999997E-2</v>
       </c>
     </row>
     <row r="154" spans="1:46" x14ac:dyDescent="0.25">
@@ -21611,7 +21611,7 @@
         <v>-32.8125</v>
       </c>
       <c r="AN154">
-        <v>-4.4650000000000002E-2</v>
+        <v>-4.4749999999999998E-2</v>
       </c>
       <c r="AO154">
         <v>-32.8125</v>
@@ -21867,7 +21867,7 @@
         <v>-35.9375</v>
       </c>
       <c r="AF156">
-        <v>-4.8899999999999999E-2</v>
+        <v>-4.8910000000000002E-2</v>
       </c>
       <c r="AG156">
         <v>-35.9375</v>
@@ -21891,7 +21891,7 @@
         <v>-35.9375</v>
       </c>
       <c r="AN156">
-        <v>-4.8899999999999999E-2</v>
+        <v>-4.8800000000000003E-2</v>
       </c>
       <c r="AO156">
         <v>-35.9375</v>
@@ -21909,7 +21909,7 @@
         <v>-35.9375</v>
       </c>
       <c r="AT156">
-        <v>-4.8899999999999999E-2</v>
+        <v>-4.9000000000000002E-2</v>
       </c>
     </row>
     <row r="157" spans="1:46" x14ac:dyDescent="0.25">
@@ -22031,7 +22031,7 @@
         <v>-37.5</v>
       </c>
       <c r="AN157">
-        <v>-5.101E-2</v>
+        <v>-5.1110000000000003E-2</v>
       </c>
       <c r="AO157">
         <v>-37.5</v>
@@ -22049,7 +22049,7 @@
         <v>-37.5</v>
       </c>
       <c r="AT157">
-        <v>-5.101E-2</v>
+        <v>-5.1110000000000003E-2</v>
       </c>
     </row>
     <row r="158" spans="1:46" x14ac:dyDescent="0.25">
@@ -22147,7 +22147,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AF158">
-        <v>-5.3159999999999999E-2</v>
+        <v>-5.3170000000000002E-2</v>
       </c>
       <c r="AG158">
         <v>-39.0625</v>
@@ -22189,7 +22189,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AT158">
-        <v>-5.3159999999999999E-2</v>
+        <v>-5.3260000000000002E-2</v>
       </c>
     </row>
     <row r="159" spans="1:46" x14ac:dyDescent="0.25">
@@ -22311,7 +22311,7 @@
         <v>-40.625</v>
       </c>
       <c r="AN159">
-        <v>-5.5280000000000003E-2</v>
+        <v>-5.518E-2</v>
       </c>
       <c r="AO159">
         <v>-40.625</v>
@@ -22329,7 +22329,7 @@
         <v>-40.625</v>
       </c>
       <c r="AT159">
-        <v>-5.5280000000000003E-2</v>
+        <v>-5.5079999999999997E-2</v>
       </c>
     </row>
     <row r="160" spans="1:46" x14ac:dyDescent="0.25">
@@ -22469,7 +22469,7 @@
         <v>-42.1875</v>
       </c>
       <c r="AT160">
-        <v>-5.7410000000000003E-2</v>
+        <v>-5.7610000000000001E-2</v>
       </c>
     </row>
     <row r="161" spans="1:46" x14ac:dyDescent="0.25">
@@ -22591,7 +22591,7 @@
         <v>-43.75</v>
       </c>
       <c r="AN161">
-        <v>-5.9540000000000003E-2</v>
+        <v>-5.9639999999999999E-2</v>
       </c>
       <c r="AO161">
         <v>-43.75</v>
@@ -22731,7 +22731,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AN162">
-        <v>-6.166E-2</v>
+        <v>-6.1559999999999997E-2</v>
       </c>
       <c r="AO162">
         <v>-45.3125</v>
@@ -22749,7 +22749,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AT162">
-        <v>-6.166E-2</v>
+        <v>-6.1559999999999997E-2</v>
       </c>
     </row>
     <row r="163" spans="1:46" x14ac:dyDescent="0.25">
@@ -22871,7 +22871,7 @@
         <v>-46.875</v>
       </c>
       <c r="AN163">
-        <v>-6.3769999999999993E-2</v>
+        <v>-6.3670000000000004E-2</v>
       </c>
       <c r="AO163">
         <v>-46.875</v>
@@ -23011,7 +23011,7 @@
         <v>-48.4375</v>
       </c>
       <c r="AN164">
-        <v>-6.5909999999999996E-2</v>
+        <v>-6.6009999999999999E-2</v>
       </c>
       <c r="AO164">
         <v>-48.4375</v>
@@ -23029,7 +23029,7 @@
         <v>-48.4375</v>
       </c>
       <c r="AT164">
-        <v>-6.5909999999999996E-2</v>
+        <v>-6.5710000000000005E-2</v>
       </c>
     </row>
     <row r="165" spans="1:46" x14ac:dyDescent="0.25">
@@ -23151,7 +23151,7 @@
         <v>-50</v>
       </c>
       <c r="AN165">
-        <v>-6.8040000000000003E-2</v>
+        <v>-6.8140000000000006E-2</v>
       </c>
       <c r="AO165">
         <v>-50</v>
@@ -23169,7 +23169,7 @@
         <v>-50</v>
       </c>
       <c r="AT165">
-        <v>-6.8040000000000003E-2</v>
+        <v>-6.8140000000000006E-2</v>
       </c>
     </row>
     <row r="166" spans="1:46" x14ac:dyDescent="0.25">
@@ -23449,7 +23449,7 @@
         <v>-53.125</v>
       </c>
       <c r="AT167">
-        <v>-7.2349999999999998E-2</v>
+        <v>-7.2450000000000001E-2</v>
       </c>
     </row>
     <row r="168" spans="1:46" x14ac:dyDescent="0.25">
@@ -23729,7 +23729,7 @@
         <v>-56.25</v>
       </c>
       <c r="AT169">
-        <v>-7.6630000000000004E-2</v>
+        <v>-7.6429999999999998E-2</v>
       </c>
     </row>
     <row r="170" spans="1:46" x14ac:dyDescent="0.25">
@@ -23851,7 +23851,7 @@
         <v>-57.8125</v>
       </c>
       <c r="AN170">
-        <v>-7.8759999999999997E-2</v>
+        <v>-7.886E-2</v>
       </c>
       <c r="AO170">
         <v>-57.8125</v>
@@ -23869,7 +23869,7 @@
         <v>-57.8125</v>
       </c>
       <c r="AT170">
-        <v>-7.8759999999999997E-2</v>
+        <v>-7.8560000000000005E-2</v>
       </c>
     </row>
     <row r="171" spans="1:46" x14ac:dyDescent="0.25">
@@ -23967,7 +23967,7 @@
         <v>-59.375</v>
       </c>
       <c r="AF171">
-        <v>-8.09E-2</v>
+        <v>-8.0890000000000004E-2</v>
       </c>
       <c r="AG171">
         <v>-59.375</v>
@@ -23991,7 +23991,7 @@
         <v>-59.375</v>
       </c>
       <c r="AN171">
-        <v>-8.09E-2</v>
+        <v>-8.1000000000000003E-2</v>
       </c>
       <c r="AO171">
         <v>-59.375</v>
@@ -24009,7 +24009,7 @@
         <v>-59.375</v>
       </c>
       <c r="AT171">
-        <v>-8.09E-2</v>
+        <v>-8.0699999999999994E-2</v>
       </c>
     </row>
     <row r="172" spans="1:46" x14ac:dyDescent="0.25">
@@ -24271,7 +24271,7 @@
         <v>-62.5</v>
       </c>
       <c r="AN173">
-        <v>-8.5180000000000006E-2</v>
+        <v>-8.5279999999999995E-2</v>
       </c>
       <c r="AO173">
         <v>-62.5</v>
@@ -24289,7 +24289,7 @@
         <v>-62.5</v>
       </c>
       <c r="AT173">
-        <v>-8.5180000000000006E-2</v>
+        <v>-8.5379999999999998E-2</v>
       </c>
     </row>
     <row r="174" spans="1:46" x14ac:dyDescent="0.25">
@@ -24387,7 +24387,7 @@
         <v>-64.0625</v>
       </c>
       <c r="AF174">
-        <v>-8.7340000000000001E-2</v>
+        <v>-8.7349999999999997E-2</v>
       </c>
       <c r="AG174">
         <v>-64.0625</v>
@@ -24411,7 +24411,7 @@
         <v>-64.0625</v>
       </c>
       <c r="AN174">
-        <v>-8.7340000000000001E-2</v>
+        <v>-8.7440000000000004E-2</v>
       </c>
       <c r="AO174">
         <v>-64.0625</v>
@@ -24429,7 +24429,7 @@
         <v>-64.0625</v>
       </c>
       <c r="AT174">
-        <v>-8.7340000000000001E-2</v>
+        <v>-8.7139999999999995E-2</v>
       </c>
     </row>
     <row r="175" spans="1:46" x14ac:dyDescent="0.25">
@@ -24551,7 +24551,7 @@
         <v>-65.625</v>
       </c>
       <c r="AN175">
-        <v>-8.949E-2</v>
+        <v>-8.9389999999999997E-2</v>
       </c>
       <c r="AO175">
         <v>-65.625</v>
@@ -24569,7 +24569,7 @@
         <v>-65.625</v>
       </c>
       <c r="AT175">
-        <v>-8.949E-2</v>
+        <v>-8.9389999999999997E-2</v>
       </c>
     </row>
     <row r="176" spans="1:46" x14ac:dyDescent="0.25">
@@ -24667,7 +24667,7 @@
         <v>-67.1875</v>
       </c>
       <c r="AF176">
-        <v>-9.1639999999999999E-2</v>
+        <v>-9.1649999999999995E-2</v>
       </c>
       <c r="AG176">
         <v>-67.1875</v>
@@ -24691,7 +24691,7 @@
         <v>-67.1875</v>
       </c>
       <c r="AN176">
-        <v>-9.1639999999999999E-2</v>
+        <v>-9.1539999999999996E-2</v>
       </c>
       <c r="AO176">
         <v>-67.1875</v>
@@ -24807,7 +24807,7 @@
         <v>-68.75</v>
       </c>
       <c r="AF177">
-        <v>-9.3770000000000006E-2</v>
+        <v>-9.3780000000000002E-2</v>
       </c>
       <c r="AG177">
         <v>-68.75</v>
@@ -24831,7 +24831,7 @@
         <v>-68.75</v>
       </c>
       <c r="AN177">
-        <v>-9.3789999999999998E-2</v>
+        <v>-9.3890000000000001E-2</v>
       </c>
       <c r="AO177">
         <v>-68.75</v>
@@ -24849,7 +24849,7 @@
         <v>-68.75</v>
       </c>
       <c r="AT177">
-        <v>-9.3789999999999998E-2</v>
+        <v>-9.3689999999999996E-2</v>
       </c>
     </row>
     <row r="178" spans="1:46" x14ac:dyDescent="0.25">
@@ -24947,7 +24947,7 @@
         <v>-70.3125</v>
       </c>
       <c r="AF178">
-        <v>-9.5920000000000005E-2</v>
+        <v>-9.5930000000000001E-2</v>
       </c>
       <c r="AG178">
         <v>-70.3125</v>
@@ -24971,7 +24971,7 @@
         <v>-70.3125</v>
       </c>
       <c r="AN178">
-        <v>-9.5920000000000005E-2</v>
+        <v>-9.5820000000000002E-2</v>
       </c>
       <c r="AO178">
         <v>-70.3125</v>
@@ -24989,7 +24989,7 @@
         <v>-70.3125</v>
       </c>
       <c r="AT178">
-        <v>-9.5920000000000005E-2</v>
+        <v>-9.6019999999999994E-2</v>
       </c>
     </row>
     <row r="179" spans="1:46" x14ac:dyDescent="0.25">
@@ -25087,7 +25087,7 @@
         <v>-71.875</v>
       </c>
       <c r="AF179">
-        <v>-9.8070000000000004E-2</v>
+        <v>-9.8080000000000001E-2</v>
       </c>
       <c r="AG179">
         <v>-71.875</v>
@@ -25129,7 +25129,7 @@
         <v>-71.875</v>
       </c>
       <c r="AT179">
-        <v>-9.8070000000000004E-2</v>
+        <v>-9.8269999999999996E-2</v>
       </c>
     </row>
     <row r="180" spans="1:46" x14ac:dyDescent="0.25">
@@ -25227,7 +25227,7 @@
         <v>-73.4375</v>
       </c>
       <c r="AF180">
-        <v>-0.10023</v>
+        <v>-0.10024</v>
       </c>
       <c r="AG180">
         <v>-73.4375</v>
@@ -25269,7 +25269,7 @@
         <v>-73.4375</v>
       </c>
       <c r="AT180">
-        <v>-0.10023</v>
+        <v>-0.10043000000000001</v>
       </c>
     </row>
     <row r="181" spans="1:46" x14ac:dyDescent="0.25">
@@ -25367,7 +25367,7 @@
         <v>-75</v>
       </c>
       <c r="AF181">
-        <v>-0.1024</v>
+        <v>-0.10249999999999999</v>
       </c>
       <c r="AG181">
         <v>-75</v>
@@ -25391,7 +25391,7 @@
         <v>-75</v>
       </c>
       <c r="AN181">
-        <v>-0.10238</v>
+        <v>-0.10228</v>
       </c>
       <c r="AO181">
         <v>-75</v>
@@ -25507,7 +25507,7 @@
         <v>-76.5625</v>
       </c>
       <c r="AF182">
-        <v>-0.10453999999999999</v>
+        <v>-0.10455</v>
       </c>
       <c r="AG182">
         <v>-76.5625</v>
@@ -25647,7 +25647,7 @@
         <v>-78.125</v>
       </c>
       <c r="AF183">
-        <v>-0.10671</v>
+        <v>-0.10672</v>
       </c>
       <c r="AG183">
         <v>-78.125</v>
@@ -25787,7 +25787,7 @@
         <v>-79.6875</v>
       </c>
       <c r="AF184">
-        <v>-0.10889</v>
+        <v>-0.10891000000000001</v>
       </c>
       <c r="AG184">
         <v>-79.6875</v>
@@ -25829,7 +25829,7 @@
         <v>-79.6875</v>
       </c>
       <c r="AT184">
-        <v>-0.10889</v>
+        <v>-0.10909000000000001</v>
       </c>
     </row>
     <row r="185" spans="1:46" x14ac:dyDescent="0.25">
@@ -25927,7 +25927,7 @@
         <v>-81.25</v>
       </c>
       <c r="AF185">
-        <v>-0.11107</v>
+        <v>-0.11108</v>
       </c>
       <c r="AG185">
         <v>-81.25</v>
@@ -25969,7 +25969,7 @@
         <v>-81.25</v>
       </c>
       <c r="AT185">
-        <v>-0.11107</v>
+        <v>-0.11126999999999999</v>
       </c>
     </row>
     <row r="186" spans="1:46" x14ac:dyDescent="0.25">
@@ -26067,7 +26067,7 @@
         <v>-82.8125</v>
       </c>
       <c r="AF186">
-        <v>-0.11325</v>
+        <v>-0.11323999999999999</v>
       </c>
       <c r="AG186">
         <v>-82.8125</v>
@@ -26091,7 +26091,7 @@
         <v>-82.8125</v>
       </c>
       <c r="AN186">
-        <v>-0.11325</v>
+        <v>-0.11335000000000001</v>
       </c>
       <c r="AO186">
         <v>-82.8125</v>
@@ -26109,7 +26109,7 @@
         <v>-82.8125</v>
       </c>
       <c r="AT186">
-        <v>-0.11325</v>
+        <v>-0.11305</v>
       </c>
     </row>
     <row r="187" spans="1:46" x14ac:dyDescent="0.25">
@@ -26207,7 +26207,7 @@
         <v>-84.375</v>
       </c>
       <c r="AF187">
-        <v>-0.11543</v>
+        <v>-0.11544</v>
       </c>
       <c r="AG187">
         <v>-84.375</v>
@@ -26231,7 +26231,7 @@
         <v>-84.375</v>
       </c>
       <c r="AN187">
-        <v>-0.11545</v>
+        <v>-0.11555</v>
       </c>
       <c r="AO187">
         <v>-84.375</v>
@@ -26249,7 +26249,7 @@
         <v>-84.375</v>
       </c>
       <c r="AT187">
-        <v>-0.11545</v>
+        <v>-0.11565</v>
       </c>
     </row>
     <row r="188" spans="1:46" x14ac:dyDescent="0.25">
@@ -26347,7 +26347,7 @@
         <v>-85.9375</v>
       </c>
       <c r="AF188">
-        <v>-0.11761000000000001</v>
+        <v>-0.11762</v>
       </c>
       <c r="AG188">
         <v>-85.9375</v>
@@ -26371,7 +26371,7 @@
         <v>-85.9375</v>
       </c>
       <c r="AN188">
-        <v>-0.11763</v>
+        <v>-0.11753</v>
       </c>
       <c r="AO188">
         <v>-85.9375</v>
@@ -26389,7 +26389,7 @@
         <v>-85.9375</v>
       </c>
       <c r="AT188">
-        <v>-0.11763</v>
+        <v>-0.11743000000000001</v>
       </c>
     </row>
     <row r="189" spans="1:46" x14ac:dyDescent="0.25">
@@ -26487,7 +26487,7 @@
         <v>-87.5</v>
       </c>
       <c r="AF189">
-        <v>-0.11981</v>
+        <v>-0.11982</v>
       </c>
       <c r="AG189">
         <v>-87.5</v>
@@ -26511,7 +26511,7 @@
         <v>-87.5</v>
       </c>
       <c r="AN189">
-        <v>-0.11982</v>
+        <v>-0.11971999999999999</v>
       </c>
       <c r="AO189">
         <v>-87.5</v>
@@ -26627,7 +26627,7 @@
         <v>-89.0625</v>
       </c>
       <c r="AF190">
-        <v>-0.12202</v>
+        <v>-0.122</v>
       </c>
       <c r="AG190">
         <v>-89.0625</v>
@@ -26651,7 +26651,7 @@
         <v>-89.0625</v>
       </c>
       <c r="AN190">
-        <v>-0.12204</v>
+        <v>-0.12214</v>
       </c>
       <c r="AO190">
         <v>-89.0625</v>
@@ -26669,7 +26669,7 @@
         <v>-89.0625</v>
       </c>
       <c r="AT190">
-        <v>-0.12204</v>
+        <v>-0.12214</v>
       </c>
     </row>
     <row r="191" spans="1:46" x14ac:dyDescent="0.25">
@@ -26767,7 +26767,7 @@
         <v>-90.625</v>
       </c>
       <c r="AF191">
-        <v>-0.12422</v>
+        <v>-0.12422999999999999</v>
       </c>
       <c r="AG191">
         <v>-90.625</v>
@@ -26809,7 +26809,7 @@
         <v>-90.625</v>
       </c>
       <c r="AT191">
-        <v>-0.12422999999999999</v>
+        <v>-0.12413</v>
       </c>
     </row>
     <row r="192" spans="1:46" x14ac:dyDescent="0.25">
@@ -26907,7 +26907,7 @@
         <v>-92.1875</v>
       </c>
       <c r="AF192">
-        <v>-0.12645000000000001</v>
+        <v>-0.12644</v>
       </c>
       <c r="AG192">
         <v>-92.1875</v>
@@ -26931,7 +26931,7 @@
         <v>-92.1875</v>
       </c>
       <c r="AN192">
-        <v>-0.12645000000000001</v>
+        <v>-0.12655</v>
       </c>
       <c r="AO192">
         <v>-92.1875</v>
@@ -26949,7 +26949,7 @@
         <v>-92.1875</v>
       </c>
       <c r="AT192">
-        <v>-0.12645000000000001</v>
+        <v>-0.12625</v>
       </c>
     </row>
     <row r="193" spans="1:46" x14ac:dyDescent="0.25">
@@ -27047,7 +27047,7 @@
         <v>-93.75</v>
       </c>
       <c r="AF193">
-        <v>-0.12866</v>
+        <v>-0.12867000000000001</v>
       </c>
       <c r="AG193">
         <v>-93.75</v>
@@ -27071,7 +27071,7 @@
         <v>-93.75</v>
       </c>
       <c r="AN193">
-        <v>-0.12867999999999999</v>
+        <v>-0.12858</v>
       </c>
       <c r="AO193">
         <v>-93.75</v>
@@ -27089,7 +27089,7 @@
         <v>-93.75</v>
       </c>
       <c r="AT193">
-        <v>-0.12867999999999999</v>
+        <v>-0.12878000000000001</v>
       </c>
     </row>
     <row r="194" spans="1:46" x14ac:dyDescent="0.25">
@@ -27187,7 +27187,7 @@
         <v>-95.3125</v>
       </c>
       <c r="AF194">
-        <v>-0.13089000000000001</v>
+        <v>-0.13089999999999999</v>
       </c>
       <c r="AG194">
         <v>-95.3125</v>
@@ -27211,7 +27211,7 @@
         <v>-95.3125</v>
       </c>
       <c r="AN194">
-        <v>-0.13089000000000001</v>
+        <v>-0.13099</v>
       </c>
       <c r="AO194">
         <v>-95.3125</v>
@@ -27229,7 +27229,7 @@
         <v>-95.3125</v>
       </c>
       <c r="AT194">
-        <v>-0.13089000000000001</v>
+        <v>-0.13099</v>
       </c>
     </row>
     <row r="195" spans="1:46" x14ac:dyDescent="0.25">
@@ -27327,7 +27327,7 @@
         <v>-96.875</v>
       </c>
       <c r="AF195">
-        <v>-0.1331</v>
+        <v>-0.13320000000000001</v>
       </c>
       <c r="AG195">
         <v>-96.875</v>
@@ -27351,7 +27351,7 @@
         <v>-96.875</v>
       </c>
       <c r="AN195">
-        <v>-0.13311999999999999</v>
+        <v>-0.13302</v>
       </c>
       <c r="AO195">
         <v>-96.875</v>
@@ -27369,7 +27369,7 @@
         <v>-96.875</v>
       </c>
       <c r="AT195">
-        <v>-0.13311999999999999</v>
+        <v>-0.13302</v>
       </c>
     </row>
     <row r="196" spans="1:46" x14ac:dyDescent="0.25">
@@ -27509,7 +27509,7 @@
         <v>-98.4375</v>
       </c>
       <c r="AT196">
-        <v>-0.13535</v>
+        <v>-0.13525000000000001</v>
       </c>
     </row>
     <row r="197" spans="1:46" x14ac:dyDescent="0.25">
@@ -27607,7 +27607,7 @@
         <v>-100</v>
       </c>
       <c r="AF197">
-        <v>-0.13733000000000001</v>
+        <v>-0.13733999999999999</v>
       </c>
       <c r="AG197">
         <v>-100</v>
@@ -27631,7 +27631,7 @@
         <v>-100</v>
       </c>
       <c r="AN197">
-        <v>-0.13733000000000001</v>
+        <v>-0.13743</v>
       </c>
       <c r="AO197">
         <v>-100</v>
@@ -27649,7 +27649,7 @@
         <v>-100</v>
       </c>
       <c r="AT197">
-        <v>-0.13733000000000001</v>
+        <v>-0.13743</v>
       </c>
     </row>
     <row r="198" spans="1:46" x14ac:dyDescent="0.25">
@@ -27771,7 +27771,7 @@
         <v>-98.4375</v>
       </c>
       <c r="AN198">
-        <v>-0.13519</v>
+        <v>-0.13528999999999999</v>
       </c>
       <c r="AO198">
         <v>-98.4375</v>
@@ -27789,7 +27789,7 @@
         <v>-98.4375</v>
       </c>
       <c r="AT198">
-        <v>-0.13519</v>
+        <v>-0.13499</v>
       </c>
     </row>
     <row r="199" spans="1:46" x14ac:dyDescent="0.25">
@@ -27887,7 +27887,7 @@
         <v>-96.875</v>
       </c>
       <c r="AF199">
-        <v>-0.13295999999999999</v>
+        <v>-0.13297</v>
       </c>
       <c r="AG199">
         <v>-96.875</v>
@@ -27911,7 +27911,7 @@
         <v>-96.875</v>
       </c>
       <c r="AN199">
-        <v>-0.13297</v>
+        <v>-0.13306999999999999</v>
       </c>
       <c r="AO199">
         <v>-96.875</v>
@@ -27929,7 +27929,7 @@
         <v>-96.875</v>
       </c>
       <c r="AT199">
-        <v>-0.13297</v>
+        <v>-0.13306999999999999</v>
       </c>
     </row>
     <row r="200" spans="1:46" x14ac:dyDescent="0.25">
@@ -28027,7 +28027,7 @@
         <v>-95.3125</v>
       </c>
       <c r="AF200">
-        <v>-0.13073000000000001</v>
+        <v>-0.13074</v>
       </c>
       <c r="AG200">
         <v>-95.3125</v>
@@ -28051,7 +28051,7 @@
         <v>-95.3125</v>
       </c>
       <c r="AN200">
-        <v>-0.13074</v>
+        <v>-0.13064000000000001</v>
       </c>
       <c r="AO200">
         <v>-95.3125</v>
@@ -28191,7 +28191,7 @@
         <v>-93.75</v>
       </c>
       <c r="AN201">
-        <v>-0.12853000000000001</v>
+        <v>-0.12862999999999999</v>
       </c>
       <c r="AO201">
         <v>-93.75</v>
@@ -28209,7 +28209,7 @@
         <v>-93.75</v>
       </c>
       <c r="AT201">
-        <v>-0.12853000000000001</v>
+        <v>-0.12842999999999999</v>
       </c>
     </row>
     <row r="202" spans="1:46" x14ac:dyDescent="0.25">
@@ -28331,7 +28331,7 @@
         <v>-92.1875</v>
       </c>
       <c r="AN202">
-        <v>-0.1263</v>
+        <v>-0.12620000000000001</v>
       </c>
       <c r="AO202">
         <v>-92.1875</v>
@@ -28349,7 +28349,7 @@
         <v>-92.1875</v>
       </c>
       <c r="AT202">
-        <v>-0.1263</v>
+        <v>-0.12620000000000001</v>
       </c>
     </row>
     <row r="203" spans="1:46" x14ac:dyDescent="0.25">
@@ -28471,7 +28471,7 @@
         <v>-90.625</v>
       </c>
       <c r="AN203">
-        <v>-0.12407</v>
+        <v>-0.12397</v>
       </c>
       <c r="AO203">
         <v>-90.625</v>
@@ -28489,7 +28489,7 @@
         <v>-90.625</v>
       </c>
       <c r="AT203">
-        <v>-0.12407</v>
+        <v>-0.12386999999999999</v>
       </c>
     </row>
     <row r="204" spans="1:46" x14ac:dyDescent="0.25">
@@ -28629,7 +28629,7 @@
         <v>-89.0625</v>
       </c>
       <c r="AT204">
-        <v>-0.12186</v>
+        <v>-0.12196</v>
       </c>
     </row>
     <row r="205" spans="1:46" x14ac:dyDescent="0.25">
@@ -28751,7 +28751,7 @@
         <v>-87.5</v>
       </c>
       <c r="AN205">
-        <v>-0.11963</v>
+        <v>-0.11973</v>
       </c>
       <c r="AO205">
         <v>-87.5</v>
@@ -28769,7 +28769,7 @@
         <v>-87.5</v>
       </c>
       <c r="AT205">
-        <v>-0.11963</v>
+        <v>-0.11983000000000001</v>
       </c>
     </row>
     <row r="206" spans="1:46" x14ac:dyDescent="0.25">
@@ -28891,7 +28891,7 @@
         <v>-85.9375</v>
       </c>
       <c r="AN206">
-        <v>-0.11743000000000001</v>
+        <v>-0.11753</v>
       </c>
       <c r="AO206">
         <v>-85.9375</v>
@@ -28909,7 +28909,7 @@
         <v>-85.9375</v>
       </c>
       <c r="AT206">
-        <v>-0.11743000000000001</v>
+        <v>-0.11723</v>
       </c>
     </row>
     <row r="207" spans="1:46" x14ac:dyDescent="0.25">
@@ -29007,7 +29007,7 @@
         <v>-84.375</v>
       </c>
       <c r="AF207">
-        <v>-0.11522</v>
+        <v>-0.11521000000000001</v>
       </c>
       <c r="AG207">
         <v>-84.375</v>
@@ -29031,7 +29031,7 @@
         <v>-84.375</v>
       </c>
       <c r="AN207">
-        <v>-0.11524</v>
+        <v>-0.11514000000000001</v>
       </c>
       <c r="AO207">
         <v>-84.375</v>
@@ -29049,7 +29049,7 @@
         <v>-84.375</v>
       </c>
       <c r="AT207">
-        <v>-0.11524</v>
+        <v>-0.11534</v>
       </c>
     </row>
     <row r="208" spans="1:46" x14ac:dyDescent="0.25">
@@ -29171,7 +29171,7 @@
         <v>-82.8125</v>
       </c>
       <c r="AN208">
-        <v>-0.11304</v>
+        <v>-0.11314</v>
       </c>
       <c r="AO208">
         <v>-82.8125</v>
@@ -29189,7 +29189,7 @@
         <v>-82.8125</v>
       </c>
       <c r="AT208">
-        <v>-0.11304</v>
+        <v>-0.11323999999999999</v>
       </c>
     </row>
     <row r="209" spans="1:46" x14ac:dyDescent="0.25">
@@ -29287,7 +29287,7 @@
         <v>-81.25</v>
       </c>
       <c r="AF209">
-        <v>-0.11086</v>
+        <v>-0.11087</v>
       </c>
       <c r="AG209">
         <v>-81.25</v>
@@ -29329,7 +29329,7 @@
         <v>-81.25</v>
       </c>
       <c r="AT209">
-        <v>-0.11086</v>
+        <v>-0.11076</v>
       </c>
     </row>
     <row r="210" spans="1:46" x14ac:dyDescent="0.25">
@@ -29451,7 +29451,7 @@
         <v>-79.6875</v>
       </c>
       <c r="AN210">
-        <v>-0.10868</v>
+        <v>-0.10878</v>
       </c>
       <c r="AO210">
         <v>-79.6875</v>
@@ -29469,7 +29469,7 @@
         <v>-79.6875</v>
       </c>
       <c r="AT210">
-        <v>-0.10868</v>
+        <v>-0.10888</v>
       </c>
     </row>
     <row r="211" spans="1:46" x14ac:dyDescent="0.25">
@@ -29591,7 +29591,7 @@
         <v>-78.125</v>
       </c>
       <c r="AN211">
-        <v>-0.1065</v>
+        <v>-0.10639999999999999</v>
       </c>
       <c r="AO211">
         <v>-78.125</v>
@@ -29609,7 +29609,7 @@
         <v>-78.125</v>
       </c>
       <c r="AT211">
-        <v>-0.1065</v>
+        <v>-0.10630000000000001</v>
       </c>
     </row>
     <row r="212" spans="1:46" x14ac:dyDescent="0.25">
@@ -29731,7 +29731,7 @@
         <v>-76.5625</v>
       </c>
       <c r="AN212">
-        <v>-0.10433000000000001</v>
+        <v>-0.10423</v>
       </c>
       <c r="AO212">
         <v>-76.5625</v>
@@ -29749,7 +29749,7 @@
         <v>-76.5625</v>
       </c>
       <c r="AT212">
-        <v>-0.10433000000000001</v>
+        <v>-0.10423</v>
       </c>
     </row>
     <row r="213" spans="1:46" x14ac:dyDescent="0.25">
@@ -29847,7 +29847,7 @@
         <v>-75</v>
       </c>
       <c r="AF213">
-        <v>-0.10215</v>
+        <v>-0.10213999999999999</v>
       </c>
       <c r="AG213">
         <v>-75</v>
@@ -29871,7 +29871,7 @@
         <v>-75</v>
       </c>
       <c r="AN213">
-        <v>-0.10215</v>
+        <v>-0.10205</v>
       </c>
       <c r="AO213">
         <v>-75</v>
@@ -29987,7 +29987,7 @@
         <v>-73.4375</v>
       </c>
       <c r="AF214">
-        <v>-9.9989999999999996E-2</v>
+        <v>-9.9970000000000003E-2</v>
       </c>
       <c r="AG214">
         <v>-73.4375</v>
@@ -30029,7 +30029,7 @@
         <v>-73.4375</v>
       </c>
       <c r="AT214">
-        <v>-0.1</v>
+        <v>-9.9900000000000003E-2</v>
       </c>
     </row>
     <row r="215" spans="1:46" x14ac:dyDescent="0.25">
@@ -30127,7 +30127,7 @@
         <v>-71.875</v>
       </c>
       <c r="AF215">
-        <v>-9.7820000000000004E-2</v>
+        <v>-9.783E-2</v>
       </c>
       <c r="AG215">
         <v>-71.875</v>
@@ -30169,7 +30169,7 @@
         <v>-71.875</v>
       </c>
       <c r="AT215">
-        <v>-9.7839999999999996E-2</v>
+        <v>-9.7739999999999994E-2</v>
       </c>
     </row>
     <row r="216" spans="1:46" x14ac:dyDescent="0.25">
@@ -30267,7 +30267,7 @@
         <v>-70.3125</v>
       </c>
       <c r="AF216">
-        <v>-9.5680000000000001E-2</v>
+        <v>-9.5689999999999997E-2</v>
       </c>
       <c r="AG216">
         <v>-70.3125</v>
@@ -30291,7 +30291,7 @@
         <v>-70.3125</v>
       </c>
       <c r="AN216">
-        <v>-9.5680000000000001E-2</v>
+        <v>-9.5579999999999998E-2</v>
       </c>
       <c r="AO216">
         <v>-70.3125</v>
@@ -30309,7 +30309,7 @@
         <v>-70.3125</v>
       </c>
       <c r="AT216">
-        <v>-9.5680000000000001E-2</v>
+        <v>-9.5780000000000004E-2</v>
       </c>
     </row>
     <row r="217" spans="1:46" x14ac:dyDescent="0.25">
@@ -30407,7 +30407,7 @@
         <v>-68.75</v>
       </c>
       <c r="AF217">
-        <v>-9.3530000000000002E-2</v>
+        <v>-9.3539999999999998E-2</v>
       </c>
       <c r="AG217">
         <v>-68.75</v>
@@ -30449,7 +30449,7 @@
         <v>-68.75</v>
       </c>
       <c r="AT217">
-        <v>-9.3530000000000002E-2</v>
+        <v>-9.3429999999999999E-2</v>
       </c>
     </row>
     <row r="218" spans="1:46" x14ac:dyDescent="0.25">
@@ -30547,7 +30547,7 @@
         <v>-67.1875</v>
       </c>
       <c r="AF218">
-        <v>-9.1380000000000003E-2</v>
+        <v>-9.1389999999999999E-2</v>
       </c>
       <c r="AG218">
         <v>-67.1875</v>
@@ -30589,7 +30589,7 @@
         <v>-67.1875</v>
       </c>
       <c r="AT218">
-        <v>-9.1380000000000003E-2</v>
+        <v>-9.1579999999999995E-2</v>
       </c>
     </row>
     <row r="219" spans="1:46" x14ac:dyDescent="0.25">
@@ -30687,7 +30687,7 @@
         <v>-65.625</v>
       </c>
       <c r="AF219">
-        <v>-8.9209999999999998E-2</v>
+        <v>-8.9219999999999994E-2</v>
       </c>
       <c r="AG219">
         <v>-65.625</v>
@@ -30711,7 +30711,7 @@
         <v>-65.625</v>
       </c>
       <c r="AN219">
-        <v>-8.9209999999999998E-2</v>
+        <v>-8.931E-2</v>
       </c>
       <c r="AO219">
         <v>-65.625</v>
@@ -30729,7 +30729,7 @@
         <v>-65.625</v>
       </c>
       <c r="AT219">
-        <v>-8.9209999999999998E-2</v>
+        <v>-8.9010000000000006E-2</v>
       </c>
     </row>
     <row r="220" spans="1:46" x14ac:dyDescent="0.25">
@@ -30827,7 +30827,7 @@
         <v>-64.0625</v>
       </c>
       <c r="AF220">
-        <v>-8.7080000000000005E-2</v>
+        <v>-8.7090000000000001E-2</v>
       </c>
       <c r="AG220">
         <v>-64.0625</v>
@@ -30851,7 +30851,7 @@
         <v>-64.0625</v>
       </c>
       <c r="AN220">
-        <v>-8.7080000000000005E-2</v>
+        <v>-8.6980000000000002E-2</v>
       </c>
       <c r="AO220">
         <v>-64.0625</v>
@@ -30869,7 +30869,7 @@
         <v>-64.0625</v>
       </c>
       <c r="AT220">
-        <v>-8.7080000000000005E-2</v>
+        <v>-8.6980000000000002E-2</v>
       </c>
     </row>
     <row r="221" spans="1:46" x14ac:dyDescent="0.25">
@@ -30967,7 +30967,7 @@
         <v>-62.5</v>
       </c>
       <c r="AF221">
-        <v>-8.4919999999999995E-2</v>
+        <v>-8.4930000000000005E-2</v>
       </c>
       <c r="AG221">
         <v>-62.5</v>
@@ -31009,7 +31009,7 @@
         <v>-62.5</v>
       </c>
       <c r="AT221">
-        <v>-8.4919999999999995E-2</v>
+        <v>-8.4720000000000004E-2</v>
       </c>
     </row>
     <row r="222" spans="1:46" x14ac:dyDescent="0.25">
@@ -31107,7 +31107,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AF222">
-        <v>-8.2790000000000002E-2</v>
+        <v>-8.2780000000000006E-2</v>
       </c>
       <c r="AG222">
         <v>-60.9375</v>
@@ -31131,7 +31131,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AN222">
-        <v>-8.2790000000000002E-2</v>
+        <v>-8.2890000000000005E-2</v>
       </c>
       <c r="AO222">
         <v>-60.9375</v>
@@ -31149,7 +31149,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AT222">
-        <v>-8.2790000000000002E-2</v>
+        <v>-8.2890000000000005E-2</v>
       </c>
     </row>
     <row r="223" spans="1:46" x14ac:dyDescent="0.25">
@@ -31247,7 +31247,7 @@
         <v>-59.375</v>
       </c>
       <c r="AF223">
-        <v>-8.0640000000000003E-2</v>
+        <v>-8.0649999999999999E-2</v>
       </c>
       <c r="AG223">
         <v>-59.375</v>
@@ -31271,7 +31271,7 @@
         <v>-59.375</v>
       </c>
       <c r="AN223">
-        <v>-8.0640000000000003E-2</v>
+        <v>-8.054E-2</v>
       </c>
       <c r="AO223">
         <v>-59.375</v>
@@ -31387,7 +31387,7 @@
         <v>-57.8125</v>
       </c>
       <c r="AF224">
-        <v>-7.85E-2</v>
+        <v>-7.8509999999999996E-2</v>
       </c>
       <c r="AG224">
         <v>-57.8125</v>
@@ -31411,7 +31411,7 @@
         <v>-57.8125</v>
       </c>
       <c r="AN224">
-        <v>-7.85E-2</v>
+        <v>-7.8399999999999997E-2</v>
       </c>
       <c r="AO224">
         <v>-57.8125</v>
@@ -31429,7 +31429,7 @@
         <v>-57.8125</v>
       </c>
       <c r="AT224">
-        <v>-7.85E-2</v>
+        <v>-7.8399999999999997E-2</v>
       </c>
     </row>
     <row r="225" spans="1:46" x14ac:dyDescent="0.25">
@@ -31527,7 +31527,7 @@
         <v>-56.25</v>
       </c>
       <c r="AF225">
-        <v>-7.6369999999999993E-2</v>
+        <v>-7.6410000000000006E-2</v>
       </c>
       <c r="AG225">
         <v>-56.25</v>
@@ -31569,7 +31569,7 @@
         <v>-56.25</v>
       </c>
       <c r="AT225">
-        <v>-7.6359999999999997E-2</v>
+        <v>-7.6160000000000005E-2</v>
       </c>
     </row>
     <row r="226" spans="1:46" x14ac:dyDescent="0.25">
@@ -31667,7 +31667,7 @@
         <v>-54.6875</v>
       </c>
       <c r="AF226">
-        <v>-7.424E-2</v>
+        <v>-7.4310000000000001E-2</v>
       </c>
       <c r="AG226">
         <v>-54.6875</v>
@@ -31691,7 +31691,7 @@
         <v>-54.6875</v>
       </c>
       <c r="AN226">
-        <v>-7.424E-2</v>
+        <v>-7.4340000000000003E-2</v>
       </c>
       <c r="AO226">
         <v>-54.6875</v>
@@ -31709,7 +31709,7 @@
         <v>-54.6875</v>
       </c>
       <c r="AT226">
-        <v>-7.424E-2</v>
+        <v>-7.4440000000000006E-2</v>
       </c>
     </row>
     <row r="227" spans="1:46" x14ac:dyDescent="0.25">
@@ -31807,7 +31807,7 @@
         <v>-53.125</v>
       </c>
       <c r="AF227">
-        <v>-7.2090000000000001E-2</v>
+        <v>-7.2080000000000005E-2</v>
       </c>
       <c r="AG227">
         <v>-53.125</v>
@@ -31947,7 +31947,7 @@
         <v>-51.5625</v>
       </c>
       <c r="AF228">
-        <v>-6.9959999999999994E-2</v>
+        <v>-6.9989999999999997E-2</v>
       </c>
       <c r="AG228">
         <v>-51.5625</v>
@@ -31971,7 +31971,7 @@
         <v>-51.5625</v>
       </c>
       <c r="AN228">
-        <v>-6.9959999999999994E-2</v>
+        <v>-6.9860000000000005E-2</v>
       </c>
       <c r="AO228">
         <v>-51.5625</v>
@@ -31989,7 +31989,7 @@
         <v>-51.5625</v>
       </c>
       <c r="AT228">
-        <v>-6.9959999999999994E-2</v>
+        <v>-7.016E-2</v>
       </c>
     </row>
     <row r="229" spans="1:46" x14ac:dyDescent="0.25">
@@ -32087,7 +32087,7 @@
         <v>-50</v>
       </c>
       <c r="AF229">
-        <v>-6.7780000000000007E-2</v>
+        <v>-6.7790000000000003E-2</v>
       </c>
       <c r="AG229">
         <v>-50</v>
@@ -32111,7 +32111,7 @@
         <v>-50</v>
       </c>
       <c r="AN229">
-        <v>-6.7760000000000001E-2</v>
+        <v>-6.7860000000000004E-2</v>
       </c>
       <c r="AO229">
         <v>-50</v>
@@ -32129,7 +32129,7 @@
         <v>-50</v>
       </c>
       <c r="AT229">
-        <v>-6.7760000000000001E-2</v>
+        <v>-6.7860000000000004E-2</v>
       </c>
     </row>
     <row r="230" spans="1:46" x14ac:dyDescent="0.25">
@@ -32227,7 +32227,7 @@
         <v>-48.4375</v>
       </c>
       <c r="AF230">
-        <v>-6.565E-2</v>
+        <v>-6.5619999999999998E-2</v>
       </c>
       <c r="AG230">
         <v>-48.4375</v>
@@ -32269,7 +32269,7 @@
         <v>-48.4375</v>
       </c>
       <c r="AT230">
-        <v>-6.565E-2</v>
+        <v>-6.5850000000000006E-2</v>
       </c>
     </row>
     <row r="231" spans="1:46" x14ac:dyDescent="0.25">
@@ -32367,7 +32367,7 @@
         <v>-46.875</v>
       </c>
       <c r="AF231">
-        <v>-6.3509999999999997E-2</v>
+        <v>-6.3519999999999993E-2</v>
       </c>
       <c r="AG231">
         <v>-46.875</v>
@@ -32391,7 +32391,7 @@
         <v>-46.875</v>
       </c>
       <c r="AN231">
-        <v>-6.3500000000000001E-2</v>
+        <v>-6.3600000000000004E-2</v>
       </c>
       <c r="AO231">
         <v>-46.875</v>
@@ -32409,7 +32409,7 @@
         <v>-46.875</v>
       </c>
       <c r="AT231">
-        <v>-6.3500000000000001E-2</v>
+        <v>-6.3399999999999998E-2</v>
       </c>
     </row>
     <row r="232" spans="1:46" x14ac:dyDescent="0.25">
@@ -32507,7 +32507,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AF232">
-        <v>-6.1379999999999997E-2</v>
+        <v>-6.139E-2</v>
       </c>
       <c r="AG232">
         <v>-45.3125</v>
@@ -32531,7 +32531,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AN232">
-        <v>-6.1379999999999997E-2</v>
+        <v>-6.1280000000000001E-2</v>
       </c>
       <c r="AO232">
         <v>-45.3125</v>
@@ -32549,7 +32549,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AT232">
-        <v>-6.1379999999999997E-2</v>
+        <v>-6.1179999999999998E-2</v>
       </c>
     </row>
     <row r="233" spans="1:46" x14ac:dyDescent="0.25">
@@ -32647,7 +32647,7 @@
         <v>-43.75</v>
       </c>
       <c r="AF233">
-        <v>-5.9249999999999997E-2</v>
+        <v>-5.926E-2</v>
       </c>
       <c r="AG233">
         <v>-43.75</v>
@@ -32787,7 +32787,7 @@
         <v>-42.1875</v>
       </c>
       <c r="AF234">
-        <v>-5.713E-2</v>
+        <v>-5.7140000000000003E-2</v>
       </c>
       <c r="AG234">
         <v>-42.1875</v>
@@ -32829,7 +32829,7 @@
         <v>-42.1875</v>
       </c>
       <c r="AT234">
-        <v>-5.713E-2</v>
+        <v>-5.6930000000000001E-2</v>
       </c>
     </row>
     <row r="235" spans="1:46" x14ac:dyDescent="0.25">
@@ -32927,7 +32927,7 @@
         <v>-40.625</v>
       </c>
       <c r="AF235">
-        <v>-5.5019999999999999E-2</v>
+        <v>-5.5039999999999999E-2</v>
       </c>
       <c r="AG235">
         <v>-40.625</v>
@@ -32951,7 +32951,7 @@
         <v>-40.625</v>
       </c>
       <c r="AN235">
-        <v>-5.5E-2</v>
+        <v>-5.5100000000000003E-2</v>
       </c>
       <c r="AO235">
         <v>-40.625</v>
@@ -33067,7 +33067,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AF236">
-        <v>-5.289E-2</v>
+        <v>-5.2900000000000003E-2</v>
       </c>
       <c r="AG236">
         <v>-39.0625</v>
@@ -33109,7 +33109,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AT236">
-        <v>-5.289E-2</v>
+        <v>-5.2990000000000002E-2</v>
       </c>
     </row>
     <row r="237" spans="1:46" x14ac:dyDescent="0.25">
@@ -33207,7 +33207,7 @@
         <v>-37.5</v>
       </c>
       <c r="AF237">
-        <v>-5.0750000000000003E-2</v>
+        <v>-5.076E-2</v>
       </c>
       <c r="AG237">
         <v>-37.5</v>
@@ -33249,7 +33249,7 @@
         <v>-37.5</v>
       </c>
       <c r="AT237">
-        <v>-5.074E-2</v>
+        <v>-5.0939999999999999E-2</v>
       </c>
     </row>
     <row r="238" spans="1:46" x14ac:dyDescent="0.25">
@@ -33347,7 +33347,7 @@
         <v>-35.9375</v>
       </c>
       <c r="AF238">
-        <v>-4.8640000000000003E-2</v>
+        <v>-4.8649999999999999E-2</v>
       </c>
       <c r="AG238">
         <v>-35.9375</v>
@@ -33371,7 +33371,7 @@
         <v>-35.9375</v>
       </c>
       <c r="AN238">
-        <v>-4.8619999999999997E-2</v>
+        <v>-4.8520000000000001E-2</v>
       </c>
       <c r="AO238">
         <v>-35.9375</v>
@@ -33487,7 +33487,7 @@
         <v>-34.375</v>
       </c>
       <c r="AF239">
-        <v>-4.6510000000000003E-2</v>
+        <v>-4.6519999999999999E-2</v>
       </c>
       <c r="AG239">
         <v>-34.375</v>
@@ -33529,7 +33529,7 @@
         <v>-34.375</v>
       </c>
       <c r="AT239">
-        <v>-4.6489999999999997E-2</v>
+        <v>-4.6589999999999999E-2</v>
       </c>
     </row>
     <row r="240" spans="1:46" x14ac:dyDescent="0.25">
@@ -33627,7 +33627,7 @@
         <v>-32.8125</v>
       </c>
       <c r="AF240">
-        <v>-4.4389999999999999E-2</v>
+        <v>-4.4380000000000003E-2</v>
       </c>
       <c r="AG240">
         <v>-32.8125</v>
@@ -33651,7 +33651,7 @@
         <v>-32.8125</v>
       </c>
       <c r="AN240">
-        <v>-4.437E-2</v>
+        <v>-4.4269999999999997E-2</v>
       </c>
       <c r="AO240">
         <v>-32.8125</v>
@@ -33669,7 +33669,7 @@
         <v>-32.8125</v>
       </c>
       <c r="AT240">
-        <v>-4.437E-2</v>
+        <v>-4.4569999999999999E-2</v>
       </c>
     </row>
     <row r="241" spans="1:46" x14ac:dyDescent="0.25">
@@ -33767,7 +33767,7 @@
         <v>-31.25</v>
       </c>
       <c r="AF241">
-        <v>-4.2259999999999999E-2</v>
+        <v>-4.2270000000000002E-2</v>
       </c>
       <c r="AG241">
         <v>-31.25</v>
@@ -33791,7 +33791,7 @@
         <v>-31.25</v>
       </c>
       <c r="AN241">
-        <v>-4.2259999999999999E-2</v>
+        <v>-4.2160000000000003E-2</v>
       </c>
       <c r="AO241">
         <v>-31.25</v>
@@ -33809,7 +33809,7 @@
         <v>-31.25</v>
       </c>
       <c r="AT241">
-        <v>-4.2259999999999999E-2</v>
+        <v>-4.2459999999999998E-2</v>
       </c>
     </row>
     <row r="242" spans="1:46" x14ac:dyDescent="0.25">
@@ -33907,7 +33907,7 @@
         <v>-29.6875</v>
       </c>
       <c r="AF242">
-        <v>-4.0140000000000002E-2</v>
+        <v>-4.0149999999999998E-2</v>
       </c>
       <c r="AG242">
         <v>-29.6875</v>
@@ -33949,7 +33949,7 @@
         <v>-29.6875</v>
       </c>
       <c r="AT242">
-        <v>-4.0140000000000002E-2</v>
+        <v>-4.0039999999999999E-2</v>
       </c>
     </row>
     <row r="243" spans="1:46" x14ac:dyDescent="0.25">
@@ -34047,7 +34047,7 @@
         <v>-28.125</v>
       </c>
       <c r="AF243">
-        <v>-3.8010000000000002E-2</v>
+        <v>-3.8019999999999998E-2</v>
       </c>
       <c r="AG243">
         <v>-28.125</v>
@@ -34071,7 +34071,7 @@
         <v>-28.125</v>
       </c>
       <c r="AN243">
-        <v>-3.8010000000000002E-2</v>
+        <v>-3.7909999999999999E-2</v>
       </c>
       <c r="AO243">
         <v>-28.125</v>
@@ -34089,7 +34089,7 @@
         <v>-28.125</v>
       </c>
       <c r="AT243">
-        <v>-3.8010000000000002E-2</v>
+        <v>-3.7909999999999999E-2</v>
       </c>
     </row>
     <row r="244" spans="1:46" x14ac:dyDescent="0.25">
@@ -34187,7 +34187,7 @@
         <v>-26.5625</v>
       </c>
       <c r="AF244">
-        <v>-3.5889999999999998E-2</v>
+        <v>-3.5900000000000001E-2</v>
       </c>
       <c r="AG244">
         <v>-26.5625</v>
@@ -34211,7 +34211,7 @@
         <v>-26.5625</v>
       </c>
       <c r="AN244">
-        <v>-3.5889999999999998E-2</v>
+        <v>-3.5790000000000002E-2</v>
       </c>
       <c r="AO244">
         <v>-26.5625</v>
@@ -34229,7 +34229,7 @@
         <v>-26.5625</v>
       </c>
       <c r="AT244">
-        <v>-3.5889999999999998E-2</v>
+        <v>-3.6089999999999997E-2</v>
       </c>
     </row>
     <row r="245" spans="1:46" x14ac:dyDescent="0.25">
@@ -34351,7 +34351,7 @@
         <v>-25</v>
       </c>
       <c r="AN245">
-        <v>-3.3759999999999998E-2</v>
+        <v>-3.3860000000000001E-2</v>
       </c>
       <c r="AO245">
         <v>-25</v>
@@ -34369,7 +34369,7 @@
         <v>-25</v>
       </c>
       <c r="AT245">
-        <v>-3.3759999999999998E-2</v>
+        <v>-3.3660000000000002E-2</v>
       </c>
     </row>
     <row r="246" spans="1:46" x14ac:dyDescent="0.25">
@@ -34467,7 +34467,7 @@
         <v>-23.4375</v>
       </c>
       <c r="AF246">
-        <v>-3.1660000000000001E-2</v>
+        <v>-3.1669999999999997E-2</v>
       </c>
       <c r="AG246">
         <v>-23.4375</v>
@@ -34747,7 +34747,7 @@
         <v>-20.3125</v>
       </c>
       <c r="AF248">
-        <v>-2.741E-2</v>
+        <v>-2.742E-2</v>
       </c>
       <c r="AG248">
         <v>-20.3125</v>
@@ -34771,7 +34771,7 @@
         <v>-20.3125</v>
       </c>
       <c r="AN248">
-        <v>-2.7400000000000001E-2</v>
+        <v>-2.7300000000000001E-2</v>
       </c>
       <c r="AO248">
         <v>-20.3125</v>
@@ -34789,7 +34789,7 @@
         <v>-20.3125</v>
       </c>
       <c r="AT248">
-        <v>-2.7400000000000001E-2</v>
+        <v>-2.7199999999999998E-2</v>
       </c>
     </row>
     <row r="249" spans="1:46" x14ac:dyDescent="0.25">
@@ -34887,7 +34887,7 @@
         <v>-18.75</v>
       </c>
       <c r="AF249">
-        <v>-2.528E-2</v>
+        <v>-2.53E-2</v>
       </c>
       <c r="AG249">
         <v>-18.75</v>
@@ -34911,7 +34911,7 @@
         <v>-18.75</v>
       </c>
       <c r="AN249">
-        <v>-2.528E-2</v>
+        <v>-2.538E-2</v>
       </c>
       <c r="AO249">
         <v>-18.75</v>
@@ -34929,7 +34929,7 @@
         <v>-18.75</v>
       </c>
       <c r="AT249">
-        <v>-2.528E-2</v>
+        <v>-2.5479999999999999E-2</v>
       </c>
     </row>
     <row r="250" spans="1:46" x14ac:dyDescent="0.25">
@@ -35069,7 +35069,7 @@
         <v>-17.1875</v>
       </c>
       <c r="AT250">
-        <v>-2.316E-2</v>
+        <v>-2.3359999999999999E-2</v>
       </c>
     </row>
     <row r="251" spans="1:46" x14ac:dyDescent="0.25">
@@ -35209,7 +35209,7 @@
         <v>-15.625</v>
       </c>
       <c r="AT251">
-        <v>-2.103E-2</v>
+        <v>-2.1129999999999999E-2</v>
       </c>
     </row>
     <row r="252" spans="1:46" x14ac:dyDescent="0.25">
@@ -35349,7 +35349,7 @@
         <v>-14.0625</v>
       </c>
       <c r="AT252">
-        <v>-1.8919999999999999E-2</v>
+        <v>-1.9019999999999999E-2</v>
       </c>
     </row>
     <row r="253" spans="1:46" x14ac:dyDescent="0.25">
@@ -35471,7 +35471,7 @@
         <v>-12.5</v>
       </c>
       <c r="AN253">
-        <v>-1.678E-2</v>
+        <v>-1.668E-2</v>
       </c>
       <c r="AO253">
         <v>-12.5</v>
@@ -35489,7 +35489,7 @@
         <v>-12.5</v>
       </c>
       <c r="AT253">
-        <v>-1.678E-2</v>
+        <v>-1.6979999999999999E-2</v>
       </c>
     </row>
     <row r="254" spans="1:46" x14ac:dyDescent="0.25">
@@ -35611,7 +35611,7 @@
         <v>-10.9375</v>
       </c>
       <c r="AN254">
-        <v>-1.465E-2</v>
+        <v>-1.4749999999999999E-2</v>
       </c>
       <c r="AO254">
         <v>-10.9375</v>
@@ -35769,7 +35769,7 @@
         <v>-9.375</v>
       </c>
       <c r="AT255">
-        <v>-1.247E-2</v>
+        <v>-1.257E-2</v>
       </c>
     </row>
     <row r="256" spans="1:46" x14ac:dyDescent="0.25">
@@ -35891,7 +35891,7 @@
         <v>-7.8125</v>
       </c>
       <c r="AN256">
-        <v>-1.001E-2</v>
+        <v>-9.9100000000000004E-3</v>
       </c>
       <c r="AO256">
         <v>-7.8125</v>
@@ -35909,7 +35909,7 @@
         <v>-7.8125</v>
       </c>
       <c r="AT256">
-        <v>-1.001E-2</v>
+        <v>-9.9100000000000004E-3</v>
       </c>
     </row>
     <row r="257" spans="1:46" x14ac:dyDescent="0.25">
@@ -36049,7 +36049,7 @@
         <v>-6.25</v>
       </c>
       <c r="AT257">
-        <v>-8.2000000000000007E-3</v>
+        <v>-8.3000000000000001E-3</v>
       </c>
     </row>
     <row r="258" spans="1:46" x14ac:dyDescent="0.25">
@@ -36189,7 +36189,7 @@
         <v>-4.6875</v>
       </c>
       <c r="AT258">
-        <v>-6.3E-3</v>
+        <v>-6.4999999999999997E-3</v>
       </c>
     </row>
     <row r="259" spans="1:46" x14ac:dyDescent="0.25">
@@ -36311,7 +36311,7 @@
         <v>-3.125</v>
       </c>
       <c r="AN259">
-        <v>-1.6800000000000001E-3</v>
+        <v>-1.7799999999999999E-3</v>
       </c>
       <c r="AO259">
         <v>-3.125</v>
@@ -36329,7 +36329,7 @@
         <v>-3.125</v>
       </c>
       <c r="AT259">
-        <v>-4.4299999999999999E-3</v>
+        <v>-4.3299999999999996E-3</v>
       </c>
     </row>
     <row r="260" spans="1:46" x14ac:dyDescent="0.25">
@@ -36463,7 +36463,7 @@
         <v>-1.5625</v>
       </c>
       <c r="AT260">
-        <v>-1.9E-3</v>
+        <v>-1.6999999999999999E-3</v>
       </c>
     </row>
   </sheetData>

--- a/IV_2.5K_T1.xlsx
+++ b/IV_2.5K_T1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Dataset_2\New folder 2\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -2705,7 +2705,7 @@
         <v>21.875</v>
       </c>
       <c r="AL19">
-        <v>2.9819999999999999E-2</v>
+        <v>2.98E-2</v>
       </c>
       <c r="AM19">
         <v>21.875</v>
@@ -2839,7 +2839,7 @@
         <v>23.4375</v>
       </c>
       <c r="AJ20">
-        <v>3.1919999999999997E-2</v>
+        <v>3.1910000000000001E-2</v>
       </c>
       <c r="AK20">
         <v>23.4375</v>
@@ -3119,7 +3119,7 @@
         <v>26.5625</v>
       </c>
       <c r="AJ22">
-        <v>3.6150000000000002E-2</v>
+        <v>3.6119999999999999E-2</v>
       </c>
       <c r="AK22">
         <v>26.5625</v>
@@ -3143,7 +3143,7 @@
         <v>26.5625</v>
       </c>
       <c r="AR22">
-        <v>3.6170000000000001E-2</v>
+        <v>3.6179999999999997E-2</v>
       </c>
       <c r="AS22">
         <v>26.5625</v>
@@ -3283,7 +3283,7 @@
         <v>28.125</v>
       </c>
       <c r="AR23">
-        <v>3.8300000000000001E-2</v>
+        <v>3.832E-2</v>
       </c>
       <c r="AS23">
         <v>28.125</v>
@@ -3417,7 +3417,7 @@
         <v>29.6875</v>
       </c>
       <c r="AP24">
-        <v>4.0399999999999998E-2</v>
+        <v>4.0379999999999999E-2</v>
       </c>
       <c r="AQ24">
         <v>29.6875</v>
@@ -3545,7 +3545,7 @@
         <v>31.25</v>
       </c>
       <c r="AL25">
-        <v>4.2529999999999998E-2</v>
+        <v>4.2520000000000002E-2</v>
       </c>
       <c r="AM25">
         <v>31.25</v>
@@ -3703,7 +3703,7 @@
         <v>32.8125</v>
       </c>
       <c r="AR26">
-        <v>4.4659999999999998E-2</v>
+        <v>4.4670000000000001E-2</v>
       </c>
       <c r="AS26">
         <v>32.8125</v>
@@ -3801,7 +3801,7 @@
         <v>34.375</v>
       </c>
       <c r="AD27">
-        <v>4.6760000000000003E-2</v>
+        <v>4.675E-2</v>
       </c>
       <c r="AE27">
         <v>34.375</v>
@@ -4221,7 +4221,7 @@
         <v>39.0625</v>
       </c>
       <c r="AD30">
-        <v>5.314E-2</v>
+        <v>5.3159999999999999E-2</v>
       </c>
       <c r="AE30">
         <v>39.0625</v>
@@ -4361,7 +4361,7 @@
         <v>40.625</v>
       </c>
       <c r="AD31">
-        <v>5.5280000000000003E-2</v>
+        <v>5.5289999999999999E-2</v>
       </c>
       <c r="AE31">
         <v>40.625</v>
@@ -4385,7 +4385,7 @@
         <v>40.625</v>
       </c>
       <c r="AL31">
-        <v>5.5289999999999999E-2</v>
+        <v>5.5309999999999998E-2</v>
       </c>
       <c r="AM31">
         <v>40.625</v>
@@ -4525,7 +4525,7 @@
         <v>42.1875</v>
       </c>
       <c r="AL32">
-        <v>5.7410000000000003E-2</v>
+        <v>5.7419999999999999E-2</v>
       </c>
       <c r="AM32">
         <v>42.1875</v>
@@ -4629,7 +4629,7 @@
         <v>43.75</v>
       </c>
       <c r="Z33">
-        <v>5.9540000000000003E-2</v>
+        <v>5.9549999999999999E-2</v>
       </c>
       <c r="AA33">
         <v>43.75</v>
@@ -4769,7 +4769,7 @@
         <v>45.3125</v>
       </c>
       <c r="Z34">
-        <v>6.166E-2</v>
+        <v>6.1650000000000003E-2</v>
       </c>
       <c r="AA34">
         <v>45.3125</v>
@@ -4823,7 +4823,7 @@
         <v>45.3125</v>
       </c>
       <c r="AR34">
-        <v>6.166E-2</v>
+        <v>6.164E-2</v>
       </c>
       <c r="AS34">
         <v>45.3125</v>
@@ -4963,7 +4963,7 @@
         <v>46.875</v>
       </c>
       <c r="AR35">
-        <v>6.3789999999999999E-2</v>
+        <v>6.3810000000000006E-2</v>
       </c>
       <c r="AS35">
         <v>46.875</v>
@@ -5043,7 +5043,7 @@
         <v>48.4375</v>
       </c>
       <c r="X36">
-        <v>6.5909999999999996E-2</v>
+        <v>6.59E-2</v>
       </c>
       <c r="Y36">
         <v>48.4375</v>
@@ -5329,7 +5329,7 @@
         <v>51.5625</v>
       </c>
       <c r="Z38">
-        <v>7.0230000000000001E-2</v>
+        <v>7.0209999999999995E-2</v>
       </c>
       <c r="AA38">
         <v>51.5625</v>
@@ -5383,7 +5383,7 @@
         <v>51.5625</v>
       </c>
       <c r="AR38">
-        <v>7.0230000000000001E-2</v>
+        <v>7.0209999999999995E-2</v>
       </c>
       <c r="AS38">
         <v>51.5625</v>
@@ -5493,7 +5493,7 @@
         <v>53.125</v>
       </c>
       <c r="AH39">
-        <v>7.2400000000000006E-2</v>
+        <v>7.22E-2</v>
       </c>
       <c r="AI39">
         <v>53.125</v>
@@ -5523,7 +5523,7 @@
         <v>53.125</v>
       </c>
       <c r="AR39">
-        <v>7.238E-2</v>
+        <v>7.2359999999999994E-2</v>
       </c>
       <c r="AS39">
         <v>53.125</v>
@@ -5737,7 +5737,7 @@
         <v>56.25</v>
       </c>
       <c r="V41">
-        <v>7.6630000000000004E-2</v>
+        <v>7.6619999999999994E-2</v>
       </c>
       <c r="W41">
         <v>56.25</v>
@@ -5773,7 +5773,7 @@
         <v>56.25</v>
       </c>
       <c r="AH41">
-        <v>7.6660000000000006E-2</v>
+        <v>7.6649999999999996E-2</v>
       </c>
       <c r="AI41">
         <v>56.25</v>
@@ -5785,7 +5785,7 @@
         <v>56.25</v>
       </c>
       <c r="AL41">
-        <v>7.6649999999999996E-2</v>
+        <v>7.664E-2</v>
       </c>
       <c r="AM41">
         <v>56.25</v>
@@ -5865,7 +5865,7 @@
         <v>57.8125</v>
       </c>
       <c r="R42">
-        <v>7.8799999999999995E-2</v>
+        <v>7.8789999999999999E-2</v>
       </c>
       <c r="S42">
         <v>57.8125</v>
@@ -5877,7 +5877,7 @@
         <v>57.8125</v>
       </c>
       <c r="V42">
-        <v>7.8759999999999997E-2</v>
+        <v>7.8750000000000001E-2</v>
       </c>
       <c r="W42">
         <v>57.8125</v>
@@ -5943,7 +5943,7 @@
         <v>57.8125</v>
       </c>
       <c r="AR42">
-        <v>7.8780000000000003E-2</v>
+        <v>7.8750000000000001E-2</v>
       </c>
       <c r="AS42">
         <v>57.8125</v>
@@ -6157,7 +6157,7 @@
         <v>60.9375</v>
       </c>
       <c r="V44">
-        <v>8.3040000000000003E-2</v>
+        <v>8.3049999999999999E-2</v>
       </c>
       <c r="W44">
         <v>60.9375</v>
@@ -6223,7 +6223,7 @@
         <v>60.9375</v>
       </c>
       <c r="AR44">
-        <v>8.3059999999999995E-2</v>
+        <v>8.3049999999999999E-2</v>
       </c>
       <c r="AS44">
         <v>60.9375</v>
@@ -6363,7 +6363,7 @@
         <v>62.5</v>
       </c>
       <c r="AR45">
-        <v>8.5209999999999994E-2</v>
+        <v>8.5199999999999998E-2</v>
       </c>
       <c r="AS45">
         <v>62.5</v>
@@ -6437,7 +6437,7 @@
         <v>64.0625</v>
       </c>
       <c r="V46">
-        <v>8.7359999999999993E-2</v>
+        <v>8.7349999999999997E-2</v>
       </c>
       <c r="W46">
         <v>64.0625</v>
@@ -6473,13 +6473,13 @@
         <v>64.0625</v>
       </c>
       <c r="AH46">
-        <v>8.7370000000000003E-2</v>
+        <v>8.7379999999999999E-2</v>
       </c>
       <c r="AI46">
         <v>64.0625</v>
       </c>
       <c r="AJ46">
-        <v>8.7319999999999995E-2</v>
+        <v>8.7300000000000003E-2</v>
       </c>
       <c r="AK46">
         <v>64.0625</v>
@@ -6643,7 +6643,7 @@
         <v>65.625</v>
       </c>
       <c r="AR47">
-        <v>8.9499999999999996E-2</v>
+        <v>8.9510000000000006E-2</v>
       </c>
       <c r="AS47">
         <v>65.625</v>
@@ -6663,13 +6663,13 @@
         <v>67.1875</v>
       </c>
       <c r="D48" s="1">
-        <v>9.1689999999999994E-2</v>
+        <v>9.171E-2</v>
       </c>
       <c r="E48">
         <v>67.1875</v>
       </c>
       <c r="F48">
-        <v>9.1649999999999995E-2</v>
+        <v>9.1639999999999999E-2</v>
       </c>
       <c r="G48">
         <v>67.1875</v>
@@ -6753,7 +6753,7 @@
         <v>67.1875</v>
       </c>
       <c r="AH48">
-        <v>9.1689999999999994E-2</v>
+        <v>9.171E-2</v>
       </c>
       <c r="AI48">
         <v>67.1875</v>
@@ -6845,7 +6845,7 @@
         <v>68.75</v>
       </c>
       <c r="R49">
-        <v>9.3820000000000001E-2</v>
+        <v>9.3810000000000004E-2</v>
       </c>
       <c r="S49">
         <v>68.75</v>
@@ -6857,7 +6857,7 @@
         <v>68.75</v>
       </c>
       <c r="V49">
-        <v>9.3799999999999994E-2</v>
+        <v>9.3820000000000001E-2</v>
       </c>
       <c r="W49">
         <v>68.75</v>
@@ -6893,7 +6893,7 @@
         <v>68.75</v>
       </c>
       <c r="AH49">
-        <v>9.3820000000000001E-2</v>
+        <v>9.3799999999999994E-2</v>
       </c>
       <c r="AI49">
         <v>68.75</v>
@@ -6923,7 +6923,7 @@
         <v>68.75</v>
       </c>
       <c r="AR49">
-        <v>9.3799999999999994E-2</v>
+        <v>9.3810000000000004E-2</v>
       </c>
       <c r="AS49">
         <v>68.75</v>
@@ -6949,7 +6949,7 @@
         <v>70.3125</v>
       </c>
       <c r="F50">
-        <v>9.5949999999999994E-2</v>
+        <v>9.5939999999999998E-2</v>
       </c>
       <c r="G50">
         <v>70.3125</v>
@@ -6997,7 +6997,7 @@
         <v>70.3125</v>
       </c>
       <c r="V50">
-        <v>9.5949999999999994E-2</v>
+        <v>9.5939999999999998E-2</v>
       </c>
       <c r="W50">
         <v>70.3125</v>
@@ -7033,7 +7033,7 @@
         <v>70.3125</v>
       </c>
       <c r="AH50">
-        <v>9.5979999999999996E-2</v>
+        <v>9.5990000000000006E-2</v>
       </c>
       <c r="AI50">
         <v>70.3125</v>
@@ -7083,7 +7083,7 @@
         <v>71.875</v>
       </c>
       <c r="D51" s="1">
-        <v>9.8150000000000001E-2</v>
+        <v>9.8129999999999995E-2</v>
       </c>
       <c r="E51">
         <v>71.875</v>
@@ -7173,7 +7173,7 @@
         <v>71.875</v>
       </c>
       <c r="AH51">
-        <v>9.8150000000000001E-2</v>
+        <v>9.8159999999999997E-2</v>
       </c>
       <c r="AI51">
         <v>71.875</v>
@@ -7203,7 +7203,7 @@
         <v>71.875</v>
       </c>
       <c r="AR51">
-        <v>9.8110000000000003E-2</v>
+        <v>9.8129999999999995E-2</v>
       </c>
       <c r="AS51">
         <v>71.875</v>
@@ -7277,7 +7277,7 @@
         <v>73.4375</v>
       </c>
       <c r="V52">
-        <v>0.10026</v>
+        <v>0.10025000000000001</v>
       </c>
       <c r="W52">
         <v>73.4375</v>
@@ -7313,7 +7313,7 @@
         <v>73.4375</v>
       </c>
       <c r="AH52">
-        <v>0.1003</v>
+        <v>0.1004</v>
       </c>
       <c r="AI52">
         <v>73.4375</v>
@@ -7363,7 +7363,7 @@
         <v>75</v>
       </c>
       <c r="D53" s="1">
-        <v>0.10246</v>
+        <v>0.10248</v>
       </c>
       <c r="E53">
         <v>75</v>
@@ -7423,7 +7423,7 @@
         <v>75</v>
       </c>
       <c r="X53">
-        <v>0.10242999999999999</v>
+        <v>0.10244</v>
       </c>
       <c r="Y53">
         <v>75</v>
@@ -7453,7 +7453,7 @@
         <v>75</v>
       </c>
       <c r="AH53">
-        <v>0.10246</v>
+        <v>0.10244</v>
       </c>
       <c r="AI53">
         <v>75</v>
@@ -7465,7 +7465,7 @@
         <v>75</v>
       </c>
       <c r="AL53">
-        <v>0.10242999999999999</v>
+        <v>0.10241</v>
       </c>
       <c r="AM53">
         <v>75</v>
@@ -7503,7 +7503,7 @@
         <v>76.5625</v>
       </c>
       <c r="D54" s="1">
-        <v>0.10462</v>
+        <v>0.10463</v>
       </c>
       <c r="E54">
         <v>76.5625</v>
@@ -7557,7 +7557,7 @@
         <v>76.5625</v>
       </c>
       <c r="V54">
-        <v>0.10459</v>
+        <v>0.10457</v>
       </c>
       <c r="W54">
         <v>76.5625</v>
@@ -7623,7 +7623,7 @@
         <v>76.5625</v>
       </c>
       <c r="AR54">
-        <v>0.10459</v>
+        <v>0.10456</v>
       </c>
       <c r="AS54">
         <v>76.5625</v>
@@ -7745,7 +7745,7 @@
         <v>78.125</v>
       </c>
       <c r="AL55">
-        <v>0.10679</v>
+        <v>0.10678</v>
       </c>
       <c r="AM55">
         <v>78.125</v>
@@ -7825,7 +7825,7 @@
         <v>79.6875</v>
       </c>
       <c r="R56">
-        <v>0.10897</v>
+        <v>0.10899</v>
       </c>
       <c r="S56">
         <v>79.6875</v>
@@ -7843,7 +7843,7 @@
         <v>79.6875</v>
       </c>
       <c r="X56">
-        <v>0.10895000000000001</v>
+        <v>0.10894</v>
       </c>
       <c r="Y56">
         <v>79.6875</v>
@@ -7903,7 +7903,7 @@
         <v>79.6875</v>
       </c>
       <c r="AR56">
-        <v>0.10895000000000001</v>
+        <v>0.10892</v>
       </c>
       <c r="AS56">
         <v>79.6875</v>
@@ -7977,7 +7977,7 @@
         <v>81.25</v>
       </c>
       <c r="V57">
-        <v>0.11112</v>
+        <v>0.11114</v>
       </c>
       <c r="W57">
         <v>81.25</v>
@@ -8099,7 +8099,7 @@
         <v>82.8125</v>
       </c>
       <c r="P58">
-        <v>0.11328000000000001</v>
+        <v>0.11329</v>
       </c>
       <c r="Q58">
         <v>82.8125</v>
@@ -8165,7 +8165,7 @@
         <v>82.8125</v>
       </c>
       <c r="AL58">
-        <v>0.11330999999999999</v>
+        <v>0.11332</v>
       </c>
       <c r="AM58">
         <v>82.8125</v>
@@ -8323,7 +8323,7 @@
         <v>84.375</v>
       </c>
       <c r="AR59">
-        <v>0.11551</v>
+        <v>0.11552999999999999</v>
       </c>
       <c r="AS59">
         <v>84.375</v>
@@ -8379,7 +8379,7 @@
         <v>85.9375</v>
       </c>
       <c r="P60">
-        <v>0.11768000000000001</v>
+        <v>0.11766</v>
       </c>
       <c r="Q60">
         <v>85.9375</v>
@@ -8397,7 +8397,7 @@
         <v>85.9375</v>
       </c>
       <c r="V60">
-        <v>0.11768000000000001</v>
+        <v>0.11771</v>
       </c>
       <c r="W60">
         <v>85.9375</v>
@@ -8433,7 +8433,7 @@
         <v>85.9375</v>
       </c>
       <c r="AH60">
-        <v>0.11772000000000001</v>
+        <v>0.1177</v>
       </c>
       <c r="AI60">
         <v>85.9375</v>
@@ -8537,7 +8537,7 @@
         <v>87.5</v>
       </c>
       <c r="V61">
-        <v>0.11989</v>
+        <v>0.11988</v>
       </c>
       <c r="W61">
         <v>87.5</v>
@@ -8573,7 +8573,7 @@
         <v>87.5</v>
       </c>
       <c r="AH61">
-        <v>0.11994</v>
+        <v>0.11991</v>
       </c>
       <c r="AI61">
         <v>87.5</v>
@@ -8603,7 +8603,7 @@
         <v>87.5</v>
       </c>
       <c r="AR61">
-        <v>0.11992</v>
+        <v>0.11990000000000001</v>
       </c>
       <c r="AS61">
         <v>87.5</v>
@@ -8713,7 +8713,7 @@
         <v>89.0625</v>
       </c>
       <c r="AH62">
-        <v>0.12213</v>
+        <v>0.12211</v>
       </c>
       <c r="AI62">
         <v>89.0625</v>
@@ -8763,13 +8763,13 @@
         <v>90.625</v>
       </c>
       <c r="D63">
-        <v>0.12435</v>
+        <v>0.12433</v>
       </c>
       <c r="E63">
         <v>90.625</v>
       </c>
       <c r="F63">
-        <v>0.12432</v>
+        <v>0.12431</v>
       </c>
       <c r="G63">
         <v>90.625</v>
@@ -8817,7 +8817,7 @@
         <v>90.625</v>
       </c>
       <c r="V63">
-        <v>0.12432</v>
+        <v>0.12433</v>
       </c>
       <c r="W63">
         <v>90.625</v>
@@ -8883,7 +8883,7 @@
         <v>90.625</v>
       </c>
       <c r="AR63">
-        <v>0.12435</v>
+        <v>0.12432</v>
       </c>
       <c r="AS63">
         <v>90.625</v>
@@ -8903,7 +8903,7 @@
         <v>92.1875</v>
       </c>
       <c r="D64">
-        <v>0.12658</v>
+        <v>0.12659999999999999</v>
       </c>
       <c r="E64">
         <v>92.1875</v>
@@ -8993,7 +8993,7 @@
         <v>92.1875</v>
       </c>
       <c r="AH64">
-        <v>0.12658</v>
+        <v>0.12655</v>
       </c>
       <c r="AI64">
         <v>92.1875</v>
@@ -9023,7 +9023,7 @@
         <v>92.1875</v>
       </c>
       <c r="AR64">
-        <v>0.12656000000000001</v>
+        <v>0.12651999999999999</v>
       </c>
       <c r="AS64">
         <v>92.1875</v>
@@ -9043,7 +9043,7 @@
         <v>93.75</v>
       </c>
       <c r="D65">
-        <v>0.12878999999999999</v>
+        <v>0.12881000000000001</v>
       </c>
       <c r="E65">
         <v>93.75</v>
@@ -9213,7 +9213,7 @@
         <v>95.3125</v>
       </c>
       <c r="N66">
-        <v>0.13095000000000001</v>
+        <v>0.13092000000000001</v>
       </c>
       <c r="O66">
         <v>95.3125</v>
@@ -9237,7 +9237,7 @@
         <v>95.3125</v>
       </c>
       <c r="V66">
-        <v>0.13097</v>
+        <v>0.13098000000000001</v>
       </c>
       <c r="W66">
         <v>95.3125</v>
@@ -9273,7 +9273,7 @@
         <v>95.3125</v>
       </c>
       <c r="AH66">
-        <v>0.13102</v>
+        <v>0.13103000000000001</v>
       </c>
       <c r="AI66">
         <v>95.3125</v>
@@ -9303,7 +9303,7 @@
         <v>95.3125</v>
       </c>
       <c r="AR66">
-        <v>0.13102</v>
+        <v>0.13105</v>
       </c>
       <c r="AS66">
         <v>95.3125</v>
@@ -9493,7 +9493,7 @@
         <v>98.4375</v>
       </c>
       <c r="N68">
-        <v>0.13544</v>
+        <v>0.13542999999999999</v>
       </c>
       <c r="O68">
         <v>98.4375</v>
@@ -9517,7 +9517,7 @@
         <v>98.4375</v>
       </c>
       <c r="V68">
-        <v>0.13546</v>
+        <v>0.13547999999999999</v>
       </c>
       <c r="W68">
         <v>98.4375</v>
@@ -9553,7 +9553,7 @@
         <v>98.4375</v>
       </c>
       <c r="AH68">
-        <v>0.13549</v>
+        <v>0.13550000000000001</v>
       </c>
       <c r="AI68">
         <v>98.4375</v>
@@ -9693,7 +9693,7 @@
         <v>100</v>
       </c>
       <c r="AH69">
-        <v>0.13744000000000001</v>
+        <v>0.13744999999999999</v>
       </c>
       <c r="AI69">
         <v>100</v>
@@ -9705,7 +9705,7 @@
         <v>100</v>
       </c>
       <c r="AL69">
-        <v>0.13746</v>
+        <v>0.13744999999999999</v>
       </c>
       <c r="AM69">
         <v>100</v>
@@ -9749,7 +9749,7 @@
         <v>98.4375</v>
       </c>
       <c r="F70">
-        <v>0.13528000000000001</v>
+        <v>0.13525000000000001</v>
       </c>
       <c r="G70">
         <v>98.4375</v>
@@ -9761,7 +9761,7 @@
         <v>98.4375</v>
       </c>
       <c r="J70">
-        <v>0.13525000000000001</v>
+        <v>0.13524</v>
       </c>
       <c r="K70">
         <v>98.4375</v>
@@ -9925,7 +9925,7 @@
         <v>96.875</v>
       </c>
       <c r="R71">
-        <v>0.13309000000000001</v>
+        <v>0.13308</v>
       </c>
       <c r="S71">
         <v>96.875</v>
@@ -9985,7 +9985,7 @@
         <v>96.875</v>
       </c>
       <c r="AL71">
-        <v>0.13309000000000001</v>
+        <v>0.1331</v>
       </c>
       <c r="AM71">
         <v>96.875</v>
@@ -10065,7 +10065,7 @@
         <v>95.3125</v>
       </c>
       <c r="R72">
-        <v>0.13086</v>
+        <v>0.13084000000000001</v>
       </c>
       <c r="S72">
         <v>95.3125</v>
@@ -10193,7 +10193,7 @@
         <v>93.75</v>
       </c>
       <c r="N73">
-        <v>0.12858</v>
+        <v>0.12856999999999999</v>
       </c>
       <c r="O73">
         <v>93.75</v>
@@ -10265,7 +10265,7 @@
         <v>93.75</v>
       </c>
       <c r="AL73">
-        <v>0.12862999999999999</v>
+        <v>0.12864999999999999</v>
       </c>
       <c r="AM73">
         <v>93.75</v>
@@ -10363,7 +10363,7 @@
         <v>92.1875</v>
       </c>
       <c r="X74">
-        <v>0.12640000000000001</v>
+        <v>0.12640999999999999</v>
       </c>
       <c r="Y74">
         <v>92.1875</v>
@@ -10405,7 +10405,7 @@
         <v>92.1875</v>
       </c>
       <c r="AL74">
-        <v>0.12640000000000001</v>
+        <v>0.1263</v>
       </c>
       <c r="AM74">
         <v>92.1875</v>
@@ -10473,7 +10473,7 @@
         <v>90.625</v>
       </c>
       <c r="N75">
-        <v>0.12411999999999999</v>
+        <v>0.12411</v>
       </c>
       <c r="O75">
         <v>90.625</v>
@@ -10497,7 +10497,7 @@
         <v>90.625</v>
       </c>
       <c r="V75">
-        <v>0.12414</v>
+        <v>0.12415</v>
       </c>
       <c r="W75">
         <v>90.625</v>
@@ -10545,7 +10545,7 @@
         <v>90.625</v>
       </c>
       <c r="AL75">
-        <v>0.12417</v>
+        <v>0.12418</v>
       </c>
       <c r="AM75">
         <v>90.625</v>
@@ -10741,7 +10741,7 @@
         <v>87.5</v>
       </c>
       <c r="J77">
-        <v>0.11967999999999999</v>
+        <v>0.11967</v>
       </c>
       <c r="K77">
         <v>87.5</v>
@@ -10777,13 +10777,13 @@
         <v>87.5</v>
       </c>
       <c r="V77" s="1">
-        <v>0.1197</v>
+        <v>0.11990000000000001</v>
       </c>
       <c r="W77">
         <v>87.5</v>
       </c>
       <c r="X77">
-        <v>0.11974</v>
+        <v>0.11975</v>
       </c>
       <c r="Y77">
         <v>87.5</v>
@@ -10813,7 +10813,7 @@
         <v>87.5</v>
       </c>
       <c r="AH77">
-        <v>0.11974</v>
+        <v>0.11976000000000001</v>
       </c>
       <c r="AI77">
         <v>87.5</v>
@@ -10881,7 +10881,7 @@
         <v>85.9375</v>
       </c>
       <c r="J78">
-        <v>0.11748</v>
+        <v>0.11745</v>
       </c>
       <c r="K78">
         <v>85.9375</v>
@@ -11057,7 +11057,7 @@
         <v>84.375</v>
       </c>
       <c r="V79" s="1">
-        <v>0.1153</v>
+        <v>0.11509999999999999</v>
       </c>
       <c r="W79">
         <v>84.375</v>
@@ -11161,7 +11161,7 @@
         <v>82.8125</v>
       </c>
       <c r="J80">
-        <v>0.11309</v>
+        <v>0.11311</v>
       </c>
       <c r="K80">
         <v>82.8125</v>
@@ -11185,7 +11185,7 @@
         <v>82.8125</v>
       </c>
       <c r="R80">
-        <v>0.11314</v>
+        <v>0.11310000000000001</v>
       </c>
       <c r="S80">
         <v>82.8125</v>
@@ -11197,7 +11197,7 @@
         <v>82.8125</v>
       </c>
       <c r="V80" s="1">
-        <v>0.11310000000000001</v>
+        <v>0.1132</v>
       </c>
       <c r="W80">
         <v>82.8125</v>
@@ -11233,7 +11233,7 @@
         <v>82.8125</v>
       </c>
       <c r="AH80">
-        <v>0.11314</v>
+        <v>0.11312</v>
       </c>
       <c r="AI80">
         <v>82.8125</v>
@@ -11373,7 +11373,7 @@
         <v>81.25</v>
       </c>
       <c r="AH81" s="1">
-        <v>0.11096</v>
+        <v>0.11094999999999999</v>
       </c>
       <c r="AI81">
         <v>81.25</v>
@@ -11465,7 +11465,7 @@
         <v>79.6875</v>
       </c>
       <c r="R82">
-        <v>0.10876</v>
+        <v>0.10875</v>
       </c>
       <c r="S82">
         <v>79.6875</v>
@@ -11569,7 +11569,7 @@
         <v>78.125</v>
       </c>
       <c r="F83" s="1">
-        <v>0.10655000000000001</v>
+        <v>0.10653</v>
       </c>
       <c r="G83">
         <v>78.125</v>
@@ -11581,7 +11581,7 @@
         <v>78.125</v>
       </c>
       <c r="J83">
-        <v>0.10653</v>
+        <v>0.10655000000000001</v>
       </c>
       <c r="K83">
         <v>78.125</v>
@@ -11599,13 +11599,13 @@
         <v>78.125</v>
       </c>
       <c r="P83">
-        <v>0.10656</v>
+        <v>0.10655000000000001</v>
       </c>
       <c r="Q83">
         <v>78.125</v>
       </c>
       <c r="R83">
-        <v>0.10657999999999999</v>
+        <v>0.10655000000000001</v>
       </c>
       <c r="S83">
         <v>78.125</v>
@@ -11721,7 +11721,7 @@
         <v>76.5625</v>
       </c>
       <c r="J84">
-        <v>0.10435</v>
+        <v>0.10435999999999999</v>
       </c>
       <c r="K84">
         <v>76.5625</v>
@@ -11733,7 +11733,7 @@
         <v>76.5625</v>
       </c>
       <c r="N84" s="1">
-        <v>0.10437</v>
+        <v>0.10435</v>
       </c>
       <c r="O84">
         <v>76.5625</v>
@@ -11745,7 +11745,7 @@
         <v>76.5625</v>
       </c>
       <c r="R84">
-        <v>0.10440000000000001</v>
+        <v>0.10441</v>
       </c>
       <c r="S84">
         <v>76.5625</v>
@@ -11885,7 +11885,7 @@
         <v>75</v>
       </c>
       <c r="R85">
-        <v>0.10223</v>
+        <v>0.10221</v>
       </c>
       <c r="S85">
         <v>75</v>
@@ -11897,7 +11897,7 @@
         <v>75</v>
       </c>
       <c r="V85" s="1">
-        <v>0.10222000000000001</v>
+        <v>0.10224</v>
       </c>
       <c r="W85">
         <v>75</v>
@@ -11933,7 +11933,7 @@
         <v>75</v>
       </c>
       <c r="AH85" s="1">
-        <v>0.10223</v>
+        <v>0.10221</v>
       </c>
       <c r="AI85">
         <v>75</v>
@@ -12019,7 +12019,7 @@
         <v>73.4375</v>
       </c>
       <c r="P86">
-        <v>0.10007000000000001</v>
+        <v>0.10006</v>
       </c>
       <c r="Q86">
         <v>73.4375</v>
@@ -12073,7 +12073,7 @@
         <v>73.4375</v>
       </c>
       <c r="AH86" s="1">
-        <v>0.10009</v>
+        <v>0.10009999999999999</v>
       </c>
       <c r="AI86">
         <v>73.4375</v>
@@ -12153,7 +12153,7 @@
         <v>71.875</v>
       </c>
       <c r="N87" s="1">
-        <v>9.7869999999999999E-2</v>
+        <v>9.7890000000000005E-2</v>
       </c>
       <c r="O87">
         <v>71.875</v>
@@ -12165,7 +12165,7 @@
         <v>71.875</v>
       </c>
       <c r="R87" s="1">
-        <v>9.7900000000000001E-2</v>
+        <v>9.8100000000000007E-2</v>
       </c>
       <c r="S87">
         <v>71.875</v>
@@ -12177,7 +12177,7 @@
         <v>71.875</v>
       </c>
       <c r="V87">
-        <v>9.7890000000000005E-2</v>
+        <v>9.7869999999999999E-2</v>
       </c>
       <c r="W87">
         <v>71.875</v>
@@ -12213,7 +12213,7 @@
         <v>71.875</v>
       </c>
       <c r="AH87" s="1">
-        <v>9.7900000000000001E-2</v>
+        <v>9.7799999999999998E-2</v>
       </c>
       <c r="AI87">
         <v>71.875</v>
@@ -12243,7 +12243,7 @@
         <v>71.875</v>
       </c>
       <c r="AR87">
-        <v>9.7900000000000001E-2</v>
+        <v>9.7909999999999997E-2</v>
       </c>
       <c r="AS87">
         <v>71.875</v>
@@ -12281,7 +12281,7 @@
         <v>70.3125</v>
       </c>
       <c r="J88">
-        <v>9.5710000000000003E-2</v>
+        <v>9.572E-2</v>
       </c>
       <c r="K88">
         <v>70.3125</v>
@@ -12353,7 +12353,7 @@
         <v>70.3125</v>
       </c>
       <c r="AH88" s="1">
-        <v>9.5740000000000006E-2</v>
+        <v>9.5759999999999998E-2</v>
       </c>
       <c r="AI88">
         <v>70.3125</v>
@@ -12493,7 +12493,7 @@
         <v>68.75</v>
       </c>
       <c r="AH89">
-        <v>9.3590000000000007E-2</v>
+        <v>9.3549999999999994E-2</v>
       </c>
       <c r="AI89">
         <v>68.75</v>
@@ -12523,7 +12523,7 @@
         <v>68.75</v>
       </c>
       <c r="AR89">
-        <v>9.3590000000000007E-2</v>
+        <v>9.3600000000000003E-2</v>
       </c>
       <c r="AS89">
         <v>68.75</v>
@@ -12585,7 +12585,7 @@
         <v>67.1875</v>
       </c>
       <c r="R90" s="1">
-        <v>9.146E-2</v>
+        <v>9.1509999999999994E-2</v>
       </c>
       <c r="S90">
         <v>67.1875</v>
@@ -12597,7 +12597,7 @@
         <v>67.1875</v>
       </c>
       <c r="V90">
-        <v>9.1429999999999997E-2</v>
+        <v>9.1420000000000001E-2</v>
       </c>
       <c r="W90">
         <v>67.1875</v>
@@ -12725,7 +12725,7 @@
         <v>65.625</v>
       </c>
       <c r="R91" s="1">
-        <v>8.9300000000000004E-2</v>
+        <v>8.9319999999999997E-2</v>
       </c>
       <c r="S91">
         <v>65.625</v>
@@ -12737,7 +12737,7 @@
         <v>65.625</v>
       </c>
       <c r="V91">
-        <v>8.9260000000000006E-2</v>
+        <v>8.9300000000000004E-2</v>
       </c>
       <c r="W91">
         <v>65.625</v>
@@ -12829,7 +12829,7 @@
         <v>64.0625</v>
       </c>
       <c r="F92">
-        <v>8.7129999999999999E-2</v>
+        <v>8.7139999999999995E-2</v>
       </c>
       <c r="G92">
         <v>64.0625</v>
@@ -12877,7 +12877,7 @@
         <v>64.0625</v>
       </c>
       <c r="V92">
-        <v>8.7129999999999999E-2</v>
+        <v>8.7139999999999995E-2</v>
       </c>
       <c r="W92">
         <v>64.0625</v>
@@ -12913,13 +12913,13 @@
         <v>64.0625</v>
       </c>
       <c r="AH92">
-        <v>8.7150000000000005E-2</v>
+        <v>8.7139999999999995E-2</v>
       </c>
       <c r="AI92">
         <v>64.0625</v>
       </c>
       <c r="AJ92">
-        <v>8.7129999999999999E-2</v>
+        <v>8.7150000000000005E-2</v>
       </c>
       <c r="AK92">
         <v>64.0625</v>
@@ -12969,7 +12969,7 @@
         <v>62.5</v>
       </c>
       <c r="F93">
-        <v>8.498E-2</v>
+        <v>8.4949999999999998E-2</v>
       </c>
       <c r="G93">
         <v>62.5</v>
@@ -12981,7 +12981,7 @@
         <v>62.5</v>
       </c>
       <c r="J93">
-        <v>8.4949999999999998E-2</v>
+        <v>8.4959999999999994E-2</v>
       </c>
       <c r="K93">
         <v>62.5</v>
@@ -13005,7 +13005,7 @@
         <v>62.5</v>
       </c>
       <c r="R93" s="1">
-        <v>8.5000000000000006E-2</v>
+        <v>8.48E-2</v>
       </c>
       <c r="S93">
         <v>62.5</v>
@@ -13199,7 +13199,7 @@
         <v>60.9375</v>
       </c>
       <c r="AJ94">
-        <v>8.2830000000000001E-2</v>
+        <v>8.2839999999999997E-2</v>
       </c>
       <c r="AK94">
         <v>60.9375</v>
@@ -13249,7 +13249,7 @@
         <v>59.375</v>
       </c>
       <c r="F95">
-        <v>8.0689999999999998E-2</v>
+        <v>8.0699999999999994E-2</v>
       </c>
       <c r="G95">
         <v>59.375</v>
@@ -13285,7 +13285,7 @@
         <v>59.375</v>
       </c>
       <c r="R95" s="1">
-        <v>8.0689999999999998E-2</v>
+        <v>8.072E-2</v>
       </c>
       <c r="S95">
         <v>59.375</v>
@@ -13413,7 +13413,7 @@
         <v>57.8125</v>
       </c>
       <c r="N96" s="1">
-        <v>7.8520000000000006E-2</v>
+        <v>7.8539999999999999E-2</v>
       </c>
       <c r="O96">
         <v>57.8125</v>
@@ -13425,7 +13425,7 @@
         <v>57.8125</v>
       </c>
       <c r="R96" s="1">
-        <v>7.8549999999999995E-2</v>
+        <v>7.8579999999999997E-2</v>
       </c>
       <c r="S96">
         <v>57.8125</v>
@@ -13437,7 +13437,7 @@
         <v>57.8125</v>
       </c>
       <c r="V96">
-        <v>7.8549999999999995E-2</v>
+        <v>7.8570000000000001E-2</v>
       </c>
       <c r="W96">
         <v>57.8125</v>
@@ -13529,19 +13529,19 @@
         <v>56.25</v>
       </c>
       <c r="F97">
-        <v>7.6399999999999996E-2</v>
+        <v>7.6410000000000006E-2</v>
       </c>
       <c r="G97">
         <v>56.25</v>
       </c>
       <c r="H97">
-        <v>7.639E-2</v>
+        <v>7.6399999999999996E-2</v>
       </c>
       <c r="I97">
         <v>56.25</v>
       </c>
       <c r="J97">
-        <v>7.639E-2</v>
+        <v>7.6380000000000003E-2</v>
       </c>
       <c r="K97">
         <v>56.25</v>
@@ -13565,7 +13565,7 @@
         <v>56.25</v>
       </c>
       <c r="R97" s="1">
-        <v>7.6399999999999996E-2</v>
+        <v>7.6100000000000001E-2</v>
       </c>
       <c r="S97">
         <v>56.25</v>
@@ -13619,7 +13619,7 @@
         <v>56.25</v>
       </c>
       <c r="AJ97">
-        <v>7.6420000000000002E-2</v>
+        <v>7.6429999999999998E-2</v>
       </c>
       <c r="AK97">
         <v>56.25</v>
@@ -13759,7 +13759,7 @@
         <v>54.6875</v>
       </c>
       <c r="AJ98">
-        <v>7.4270000000000003E-2</v>
+        <v>7.4279999999999999E-2</v>
       </c>
       <c r="AK98">
         <v>54.6875</v>
@@ -13803,7 +13803,7 @@
         <v>53.125</v>
       </c>
       <c r="D99" s="1">
-        <v>7.2139999999999996E-2</v>
+        <v>7.2109999999999994E-2</v>
       </c>
       <c r="E99">
         <v>53.125</v>
@@ -13815,7 +13815,7 @@
         <v>53.125</v>
       </c>
       <c r="H99">
-        <v>7.2120000000000004E-2</v>
+        <v>7.2139999999999996E-2</v>
       </c>
       <c r="I99">
         <v>53.125</v>
@@ -13943,7 +13943,7 @@
         <v>51.5625</v>
       </c>
       <c r="D100" s="1">
-        <v>7.0010000000000003E-2</v>
+        <v>7.0029999999999995E-2</v>
       </c>
       <c r="E100">
         <v>51.5625</v>
@@ -13961,7 +13961,7 @@
         <v>51.5625</v>
       </c>
       <c r="J100">
-        <v>6.9989999999999997E-2</v>
+        <v>6.9959999999999994E-2</v>
       </c>
       <c r="K100">
         <v>51.5625</v>
@@ -13985,7 +13985,7 @@
         <v>51.5625</v>
       </c>
       <c r="R100">
-        <v>7.0010000000000003E-2</v>
+        <v>7.0019999999999999E-2</v>
       </c>
       <c r="S100">
         <v>51.5625</v>
@@ -14039,13 +14039,13 @@
         <v>51.5625</v>
       </c>
       <c r="AJ100">
-        <v>7.0010000000000003E-2</v>
+        <v>7.0019999999999999E-2</v>
       </c>
       <c r="AK100">
         <v>51.5625</v>
       </c>
       <c r="AL100">
-        <v>7.0010000000000003E-2</v>
+        <v>7.0019999999999999E-2</v>
       </c>
       <c r="AM100">
         <v>51.5625</v>
@@ -14095,7 +14095,7 @@
         <v>50</v>
       </c>
       <c r="H101">
-        <v>6.7799999999999999E-2</v>
+        <v>6.7900000000000002E-2</v>
       </c>
       <c r="I101">
         <v>50</v>
@@ -14119,13 +14119,13 @@
         <v>50</v>
       </c>
       <c r="P101">
-        <v>6.7809999999999995E-2</v>
+        <v>6.7820000000000005E-2</v>
       </c>
       <c r="Q101">
         <v>50</v>
       </c>
       <c r="R101">
-        <v>6.7809999999999995E-2</v>
+        <v>6.7820000000000005E-2</v>
       </c>
       <c r="S101">
         <v>50</v>
@@ -14179,7 +14179,7 @@
         <v>50</v>
       </c>
       <c r="AJ101">
-        <v>6.7809999999999995E-2</v>
+        <v>6.7820000000000005E-2</v>
       </c>
       <c r="AK101">
         <v>50</v>
@@ -14253,7 +14253,7 @@
         <v>48.4375</v>
       </c>
       <c r="N102">
-        <v>6.5659999999999996E-2</v>
+        <v>6.5670000000000006E-2</v>
       </c>
       <c r="O102">
         <v>48.4375</v>
@@ -14265,7 +14265,7 @@
         <v>48.4375</v>
       </c>
       <c r="R102">
-        <v>6.5680000000000002E-2</v>
+        <v>6.5689999999999998E-2</v>
       </c>
       <c r="S102">
         <v>48.4375</v>
@@ -14319,13 +14319,13 @@
         <v>48.4375</v>
       </c>
       <c r="AJ102">
-        <v>6.5680000000000002E-2</v>
+        <v>6.5689999999999998E-2</v>
       </c>
       <c r="AK102">
         <v>48.4375</v>
       </c>
       <c r="AL102">
-        <v>6.5680000000000002E-2</v>
+        <v>6.5699999999999995E-2</v>
       </c>
       <c r="AM102">
         <v>48.4375</v>
@@ -14399,13 +14399,13 @@
         <v>46.875</v>
       </c>
       <c r="P103">
-        <v>6.3549999999999995E-2</v>
+        <v>6.3560000000000005E-2</v>
       </c>
       <c r="Q103">
         <v>46.875</v>
       </c>
       <c r="R103">
-        <v>6.3549999999999995E-2</v>
+        <v>6.3519999999999993E-2</v>
       </c>
       <c r="S103">
         <v>46.875</v>
@@ -14417,7 +14417,7 @@
         <v>46.875</v>
       </c>
       <c r="V103">
-        <v>6.3549999999999995E-2</v>
+        <v>6.3539999999999999E-2</v>
       </c>
       <c r="W103">
         <v>46.875</v>
@@ -14459,7 +14459,7 @@
         <v>46.875</v>
       </c>
       <c r="AJ103">
-        <v>6.3549999999999995E-2</v>
+        <v>6.3530000000000003E-2</v>
       </c>
       <c r="AK103">
         <v>46.875</v>
@@ -14509,7 +14509,7 @@
         <v>45.3125</v>
       </c>
       <c r="F104" s="1">
-        <v>6.1429999999999998E-2</v>
+        <v>6.1420000000000002E-2</v>
       </c>
       <c r="G104">
         <v>45.3125</v>
@@ -14593,7 +14593,7 @@
         <v>45.3125</v>
       </c>
       <c r="AH104">
-        <v>6.1409999999999999E-2</v>
+        <v>6.1420000000000002E-2</v>
       </c>
       <c r="AI104">
         <v>45.3125</v>
@@ -14605,7 +14605,7 @@
         <v>45.3125</v>
       </c>
       <c r="AL104">
-        <v>6.1429999999999998E-2</v>
+        <v>6.1440000000000002E-2</v>
       </c>
       <c r="AM104">
         <v>45.3125</v>
@@ -14679,13 +14679,13 @@
         <v>43.75</v>
       </c>
       <c r="P105">
-        <v>5.9299999999999999E-2</v>
+        <v>5.9319999999999998E-2</v>
       </c>
       <c r="Q105">
         <v>43.75</v>
       </c>
       <c r="R105">
-        <v>5.9299999999999999E-2</v>
+        <v>5.9270000000000003E-2</v>
       </c>
       <c r="S105">
         <v>43.75</v>
@@ -14739,13 +14739,13 @@
         <v>43.75</v>
       </c>
       <c r="AJ105">
-        <v>5.9299999999999999E-2</v>
+        <v>5.9279999999999999E-2</v>
       </c>
       <c r="AK105">
         <v>43.75</v>
       </c>
       <c r="AL105">
-        <v>5.9299999999999999E-2</v>
+        <v>5.9279999999999999E-2</v>
       </c>
       <c r="AM105">
         <v>43.75</v>
@@ -14795,7 +14795,7 @@
         <v>42.1875</v>
       </c>
       <c r="H106">
-        <v>5.7149999999999999E-2</v>
+        <v>5.7140000000000003E-2</v>
       </c>
       <c r="I106">
         <v>42.1875</v>
@@ -14813,7 +14813,7 @@
         <v>42.1875</v>
       </c>
       <c r="N106">
-        <v>5.7149999999999999E-2</v>
+        <v>5.7119999999999997E-2</v>
       </c>
       <c r="O106">
         <v>42.1875</v>
@@ -14825,7 +14825,7 @@
         <v>42.1875</v>
       </c>
       <c r="R106">
-        <v>5.7169999999999999E-2</v>
+        <v>5.7180000000000002E-2</v>
       </c>
       <c r="S106">
         <v>42.1875</v>
@@ -14885,7 +14885,7 @@
         <v>42.1875</v>
       </c>
       <c r="AL106">
-        <v>5.7180000000000002E-2</v>
+        <v>5.7209999999999997E-2</v>
       </c>
       <c r="AM106">
         <v>42.1875</v>
@@ -14929,7 +14929,7 @@
         <v>40.625</v>
       </c>
       <c r="F107">
-        <v>5.5030000000000003E-2</v>
+        <v>5.5019999999999999E-2</v>
       </c>
       <c r="G107">
         <v>40.625</v>
@@ -15093,7 +15093,7 @@
         <v>39.0625</v>
       </c>
       <c r="N108">
-        <v>5.2900000000000003E-2</v>
+        <v>5.2909999999999999E-2</v>
       </c>
       <c r="O108">
         <v>39.0625</v>
@@ -15105,7 +15105,7 @@
         <v>39.0625</v>
       </c>
       <c r="R108">
-        <v>5.2920000000000002E-2</v>
+        <v>5.2909999999999999E-2</v>
       </c>
       <c r="S108">
         <v>39.0625</v>
@@ -15159,7 +15159,7 @@
         <v>39.0625</v>
       </c>
       <c r="AJ108">
-        <v>5.2920000000000002E-2</v>
+        <v>5.2900000000000003E-2</v>
       </c>
       <c r="AK108">
         <v>39.0625</v>
@@ -15183,7 +15183,7 @@
         <v>39.0625</v>
       </c>
       <c r="AR108">
-        <v>5.2920000000000002E-2</v>
+        <v>5.2940000000000001E-2</v>
       </c>
       <c r="AS108">
         <v>39.0625</v>
@@ -15209,7 +15209,7 @@
         <v>37.5</v>
       </c>
       <c r="F109">
-        <v>5.0790000000000002E-2</v>
+        <v>5.0819999999999997E-2</v>
       </c>
       <c r="G109">
         <v>37.5</v>
@@ -15263,7 +15263,7 @@
         <v>37.5</v>
       </c>
       <c r="X109">
-        <v>5.0790000000000002E-2</v>
+        <v>5.0810000000000001E-2</v>
       </c>
       <c r="Y109">
         <v>37.5</v>
@@ -15299,7 +15299,7 @@
         <v>37.5</v>
       </c>
       <c r="AJ109">
-        <v>5.0790000000000002E-2</v>
+        <v>5.0810000000000001E-2</v>
       </c>
       <c r="AK109">
         <v>37.5</v>
@@ -15433,7 +15433,7 @@
         <v>35.9375</v>
       </c>
       <c r="AH110">
-        <v>4.8649999999999999E-2</v>
+        <v>4.8660000000000002E-2</v>
       </c>
       <c r="AI110">
         <v>35.9375</v>
@@ -15543,7 +15543,7 @@
         <v>34.375</v>
       </c>
       <c r="X111">
-        <v>4.6519999999999999E-2</v>
+        <v>4.6510000000000003E-2</v>
       </c>
       <c r="Y111">
         <v>34.375</v>
@@ -15573,19 +15573,19 @@
         <v>34.375</v>
       </c>
       <c r="AH111">
-        <v>4.6519999999999999E-2</v>
+        <v>4.6530000000000002E-2</v>
       </c>
       <c r="AI111">
         <v>34.375</v>
       </c>
       <c r="AJ111">
-        <v>4.6539999999999998E-2</v>
+        <v>4.6519999999999999E-2</v>
       </c>
       <c r="AK111">
         <v>34.375</v>
       </c>
       <c r="AL111">
-        <v>4.6539999999999998E-2</v>
+        <v>4.6519999999999999E-2</v>
       </c>
       <c r="AM111">
         <v>34.375</v>
@@ -15629,7 +15629,7 @@
         <v>32.8125</v>
       </c>
       <c r="F112">
-        <v>4.4409999999999998E-2</v>
+        <v>4.4420000000000001E-2</v>
       </c>
       <c r="G112">
         <v>32.8125</v>
@@ -15665,7 +15665,7 @@
         <v>32.8125</v>
       </c>
       <c r="R112">
-        <v>4.4409999999999998E-2</v>
+        <v>4.4400000000000002E-2</v>
       </c>
       <c r="S112">
         <v>32.8125</v>
@@ -15725,7 +15725,7 @@
         <v>32.8125</v>
       </c>
       <c r="AL112">
-        <v>4.4409999999999998E-2</v>
+        <v>4.4420000000000001E-2</v>
       </c>
       <c r="AM112">
         <v>32.8125</v>
@@ -15763,7 +15763,7 @@
         <v>31.25</v>
       </c>
       <c r="D113">
-        <v>4.2290000000000001E-2</v>
+        <v>4.2299999999999997E-2</v>
       </c>
       <c r="E113">
         <v>31.25</v>
@@ -15793,7 +15793,7 @@
         <v>31.25</v>
       </c>
       <c r="N113">
-        <v>4.2270000000000002E-2</v>
+        <v>4.2279999999999998E-2</v>
       </c>
       <c r="O113">
         <v>31.25</v>
@@ -15817,7 +15817,7 @@
         <v>31.25</v>
       </c>
       <c r="V113">
-        <v>4.2290000000000001E-2</v>
+        <v>4.2279999999999998E-2</v>
       </c>
       <c r="W113">
         <v>31.25</v>
@@ -15853,19 +15853,19 @@
         <v>31.25</v>
       </c>
       <c r="AH113">
-        <v>4.2290000000000001E-2</v>
+        <v>4.2259999999999999E-2</v>
       </c>
       <c r="AI113">
         <v>31.25</v>
       </c>
       <c r="AJ113">
-        <v>4.2290000000000001E-2</v>
+        <v>4.231E-2</v>
       </c>
       <c r="AK113">
         <v>31.25</v>
       </c>
       <c r="AL113">
-        <v>4.2290000000000001E-2</v>
+        <v>4.2270000000000002E-2</v>
       </c>
       <c r="AM113">
         <v>31.25</v>
@@ -15939,7 +15939,7 @@
         <v>29.6875</v>
       </c>
       <c r="P114">
-        <v>4.0169999999999997E-2</v>
+        <v>4.018E-2</v>
       </c>
       <c r="Q114">
         <v>29.6875</v>
@@ -16073,7 +16073,7 @@
         <v>28.125</v>
       </c>
       <c r="N115">
-        <v>3.8019999999999998E-2</v>
+        <v>3.8030000000000001E-2</v>
       </c>
       <c r="O115">
         <v>28.125</v>
@@ -16103,7 +16103,7 @@
         <v>28.125</v>
       </c>
       <c r="X115">
-        <v>3.8019999999999998E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="Y115">
         <v>28.125</v>
@@ -16139,13 +16139,13 @@
         <v>28.125</v>
       </c>
       <c r="AJ115">
-        <v>3.8039999999999997E-2</v>
+        <v>3.8059999999999997E-2</v>
       </c>
       <c r="AK115">
         <v>28.125</v>
       </c>
       <c r="AL115">
-        <v>3.8039999999999997E-2</v>
+        <v>3.805E-2</v>
       </c>
       <c r="AM115">
         <v>28.125</v>
@@ -16219,7 +16219,7 @@
         <v>26.5625</v>
       </c>
       <c r="P116">
-        <v>3.5920000000000001E-2</v>
+        <v>3.5909999999999997E-2</v>
       </c>
       <c r="Q116">
         <v>26.5625</v>
@@ -16237,7 +16237,7 @@
         <v>26.5625</v>
       </c>
       <c r="V116">
-        <v>3.5920000000000001E-2</v>
+        <v>3.5929999999999997E-2</v>
       </c>
       <c r="W116">
         <v>26.5625</v>
@@ -16279,7 +16279,7 @@
         <v>26.5625</v>
       </c>
       <c r="AJ116">
-        <v>3.5920000000000001E-2</v>
+        <v>3.5929999999999997E-2</v>
       </c>
       <c r="AK116">
         <v>26.5625</v>
@@ -16383,7 +16383,7 @@
         <v>25</v>
       </c>
       <c r="X117">
-        <v>3.3790000000000001E-2</v>
+        <v>3.3779999999999998E-2</v>
       </c>
       <c r="Y117">
         <v>25</v>
@@ -16407,7 +16407,7 @@
         <v>25</v>
       </c>
       <c r="AF117">
-        <v>3.3790000000000001E-2</v>
+        <v>3.3829999999999999E-2</v>
       </c>
       <c r="AG117">
         <v>25</v>
@@ -16419,13 +16419,13 @@
         <v>25</v>
       </c>
       <c r="AJ117">
-        <v>3.3790000000000001E-2</v>
+        <v>3.381E-2</v>
       </c>
       <c r="AK117">
         <v>25</v>
       </c>
       <c r="AL117">
-        <v>3.3790000000000001E-2</v>
+        <v>3.381E-2</v>
       </c>
       <c r="AM117">
         <v>25</v>
@@ -16517,7 +16517,7 @@
         <v>23.4375</v>
       </c>
       <c r="V118">
-        <v>3.168E-2</v>
+        <v>3.1669999999999997E-2</v>
       </c>
       <c r="W118">
         <v>23.4375</v>
@@ -16559,13 +16559,13 @@
         <v>23.4375</v>
       </c>
       <c r="AJ118">
-        <v>3.168E-2</v>
+        <v>3.1699999999999999E-2</v>
       </c>
       <c r="AK118">
         <v>23.4375</v>
       </c>
       <c r="AL118">
-        <v>3.168E-2</v>
+        <v>3.1699999999999999E-2</v>
       </c>
       <c r="AM118">
         <v>23.4375</v>
@@ -16693,7 +16693,7 @@
         <v>21.875</v>
       </c>
       <c r="AH119">
-        <v>2.954E-2</v>
+        <v>2.9499999999999998E-2</v>
       </c>
       <c r="AI119">
         <v>21.875</v>
@@ -16797,7 +16797,7 @@
         <v>20.3125</v>
       </c>
       <c r="V120">
-        <v>2.743E-2</v>
+        <v>2.7400000000000001E-2</v>
       </c>
       <c r="W120">
         <v>20.3125</v>
@@ -16827,7 +16827,7 @@
         <v>20.3125</v>
       </c>
       <c r="AF120">
-        <v>2.743E-2</v>
+        <v>2.7400000000000001E-2</v>
       </c>
       <c r="AG120">
         <v>20.3125</v>
@@ -16839,13 +16839,13 @@
         <v>20.3125</v>
       </c>
       <c r="AJ120">
-        <v>2.743E-2</v>
+        <v>2.742E-2</v>
       </c>
       <c r="AK120">
         <v>20.3125</v>
       </c>
       <c r="AL120">
-        <v>2.743E-2</v>
+        <v>2.7400000000000001E-2</v>
       </c>
       <c r="AM120">
         <v>20.3125</v>
@@ -17113,13 +17113,13 @@
         <v>17.1875</v>
       </c>
       <c r="AH122">
-        <v>2.1950000000000001E-2</v>
+        <v>2.197E-2</v>
       </c>
       <c r="AI122">
         <v>17.1875</v>
       </c>
       <c r="AJ122">
-        <v>2.3179999999999999E-2</v>
+        <v>2.317E-2</v>
       </c>
       <c r="AK122">
         <v>17.1875</v>
@@ -17229,7 +17229,7 @@
         <v>15.625</v>
       </c>
       <c r="Z123">
-        <v>1.925E-2</v>
+        <v>1.9259999999999999E-2</v>
       </c>
       <c r="AA123">
         <v>15.625</v>
@@ -17369,7 +17369,7 @@
         <v>14.0625</v>
       </c>
       <c r="Z124">
-        <v>1.1480000000000001E-2</v>
+        <v>1.145E-2</v>
       </c>
       <c r="AA124">
         <v>14.0625</v>
@@ -17509,7 +17509,7 @@
         <v>12.5</v>
       </c>
       <c r="Z125" s="1">
-        <v>4.84597E-5</v>
+        <v>3.8949999999999998E-5</v>
       </c>
       <c r="AA125">
         <v>12.5</v>
@@ -20875,7 +20875,7 @@
         <v>-25</v>
       </c>
       <c r="AB149">
-        <v>-3.4020000000000002E-2</v>
+        <v>-3.4009999999999999E-2</v>
       </c>
       <c r="AC149">
         <v>-25</v>
@@ -21015,7 +21015,7 @@
         <v>-26.5625</v>
       </c>
       <c r="AB150">
-        <v>-3.6130000000000002E-2</v>
+        <v>-3.61E-2</v>
       </c>
       <c r="AC150">
         <v>-26.5625</v>
@@ -21295,7 +21295,7 @@
         <v>-29.6875</v>
       </c>
       <c r="AB152">
-        <v>-4.0379999999999999E-2</v>
+        <v>-4.0390000000000002E-2</v>
       </c>
       <c r="AC152">
         <v>-29.6875</v>
@@ -21435,7 +21435,7 @@
         <v>-31.25</v>
       </c>
       <c r="AB153">
-        <v>-4.2500000000000003E-2</v>
+        <v>-4.249E-2</v>
       </c>
       <c r="AC153">
         <v>-31.25</v>
@@ -21709,7 +21709,7 @@
         <v>-34.375</v>
       </c>
       <c r="Z155">
-        <v>-4.6730000000000001E-2</v>
+        <v>-4.675E-2</v>
       </c>
       <c r="AA155">
         <v>-34.375</v>
@@ -21763,7 +21763,7 @@
         <v>-34.375</v>
       </c>
       <c r="AR155">
-        <v>-4.6760000000000003E-2</v>
+        <v>-4.6789999999999998E-2</v>
       </c>
       <c r="AS155">
         <v>-34.375</v>
@@ -21849,7 +21849,7 @@
         <v>-35.9375</v>
       </c>
       <c r="Z156">
-        <v>-4.8860000000000001E-2</v>
+        <v>-4.8869999999999997E-2</v>
       </c>
       <c r="AA156">
         <v>-35.9375</v>
@@ -22043,7 +22043,7 @@
         <v>-37.5</v>
       </c>
       <c r="AR157">
-        <v>-5.101E-2</v>
+        <v>-5.0999999999999997E-2</v>
       </c>
       <c r="AS157">
         <v>-37.5</v>
@@ -22099,7 +22099,7 @@
         <v>-39.0625</v>
       </c>
       <c r="P158">
-        <v>-5.3159999999999999E-2</v>
+        <v>-5.3179999999999998E-2</v>
       </c>
       <c r="Q158">
         <v>-39.0625</v>
@@ -22141,7 +22141,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AD158">
-        <v>-5.3129999999999997E-2</v>
+        <v>-5.3170000000000002E-2</v>
       </c>
       <c r="AE158">
         <v>-39.0625</v>
@@ -22183,7 +22183,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AR158">
-        <v>-5.3159999999999999E-2</v>
+        <v>-5.3179999999999998E-2</v>
       </c>
       <c r="AS158">
         <v>-39.0625</v>
@@ -22239,7 +22239,7 @@
         <v>-40.625</v>
       </c>
       <c r="P159">
-        <v>-5.5280000000000003E-2</v>
+        <v>-5.527E-2</v>
       </c>
       <c r="Q159">
         <v>-40.625</v>
@@ -22287,7 +22287,7 @@
         <v>-40.625</v>
       </c>
       <c r="AF159">
-        <v>-5.5280000000000003E-2</v>
+        <v>-5.5300000000000002E-2</v>
       </c>
       <c r="AG159">
         <v>-40.625</v>
@@ -22415,19 +22415,19 @@
         <v>-42.1875</v>
       </c>
       <c r="AB160">
-        <v>-5.738E-2</v>
+        <v>-5.7360000000000001E-2</v>
       </c>
       <c r="AC160">
         <v>-42.1875</v>
       </c>
       <c r="AD160">
-        <v>-5.738E-2</v>
+        <v>-5.74E-2</v>
       </c>
       <c r="AE160">
         <v>-42.1875</v>
       </c>
       <c r="AF160">
-        <v>-5.7410000000000003E-2</v>
+        <v>-5.7419999999999999E-2</v>
       </c>
       <c r="AG160">
         <v>-42.1875</v>
@@ -22573,7 +22573,7 @@
         <v>-43.75</v>
       </c>
       <c r="AH161">
-        <v>-5.951E-2</v>
+        <v>-5.9520000000000003E-2</v>
       </c>
       <c r="AI161">
         <v>-43.75</v>
@@ -22585,7 +22585,7 @@
         <v>-43.75</v>
       </c>
       <c r="AL161">
-        <v>-5.9540000000000003E-2</v>
+        <v>-5.9549999999999999E-2</v>
       </c>
       <c r="AM161">
         <v>-43.75</v>
@@ -22683,7 +22683,7 @@
         <v>-45.3125</v>
       </c>
       <c r="X162">
-        <v>-6.166E-2</v>
+        <v>-6.1670000000000003E-2</v>
       </c>
       <c r="Y162">
         <v>-45.3125</v>
@@ -22701,7 +22701,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AD162">
-        <v>-6.1620000000000001E-2</v>
+        <v>-6.1629999999999997E-2</v>
       </c>
       <c r="AE162">
         <v>-45.3125</v>
@@ -22817,7 +22817,7 @@
         <v>-46.875</v>
       </c>
       <c r="V163">
-        <v>-6.3769999999999993E-2</v>
+        <v>-6.3750000000000001E-2</v>
       </c>
       <c r="W163">
         <v>-46.875</v>
@@ -22835,37 +22835,37 @@
         <v>-46.875</v>
       </c>
       <c r="AB163">
-        <v>-6.3740000000000005E-2</v>
+        <v>-6.3719999999999999E-2</v>
       </c>
       <c r="AC163">
         <v>-46.875</v>
       </c>
       <c r="AD163">
-        <v>-6.3740000000000005E-2</v>
+        <v>-6.3750000000000001E-2</v>
       </c>
       <c r="AE163">
         <v>-46.875</v>
       </c>
       <c r="AF163">
-        <v>-6.3769999999999993E-2</v>
+        <v>-6.3750000000000001E-2</v>
       </c>
       <c r="AG163">
         <v>-46.875</v>
       </c>
       <c r="AH163">
-        <v>-6.3759999999999997E-2</v>
+        <v>-6.3769999999999993E-2</v>
       </c>
       <c r="AI163">
         <v>-46.875</v>
       </c>
       <c r="AJ163">
-        <v>-6.3769999999999993E-2</v>
+        <v>-6.3780000000000003E-2</v>
       </c>
       <c r="AK163">
         <v>-46.875</v>
       </c>
       <c r="AL163">
-        <v>-6.3769999999999993E-2</v>
+        <v>-6.3759999999999997E-2</v>
       </c>
       <c r="AM163">
         <v>-46.875</v>
@@ -23079,13 +23079,13 @@
         <v>-50</v>
       </c>
       <c r="P165">
-        <v>-6.8040000000000003E-2</v>
+        <v>-6.8049999999999999E-2</v>
       </c>
       <c r="Q165">
         <v>-50</v>
       </c>
       <c r="R165">
-        <v>-6.8019999999999997E-2</v>
+        <v>-6.8029999999999993E-2</v>
       </c>
       <c r="S165">
         <v>-50</v>
@@ -23097,7 +23097,7 @@
         <v>-50</v>
       </c>
       <c r="V165">
-        <v>-6.8040000000000003E-2</v>
+        <v>-6.8049999999999999E-2</v>
       </c>
       <c r="W165">
         <v>-50</v>
@@ -23115,19 +23115,19 @@
         <v>-50</v>
       </c>
       <c r="AB165">
-        <v>-6.8010000000000001E-2</v>
+        <v>-6.8019999999999997E-2</v>
       </c>
       <c r="AC165">
         <v>-50</v>
       </c>
       <c r="AD165">
-        <v>-6.8010000000000001E-2</v>
+        <v>-6.8040000000000003E-2</v>
       </c>
       <c r="AE165">
         <v>-50</v>
       </c>
       <c r="AF165">
-        <v>-6.8040000000000003E-2</v>
+        <v>-6.8070000000000006E-2</v>
       </c>
       <c r="AG165">
         <v>-50</v>
@@ -23139,7 +23139,7 @@
         <v>-50</v>
       </c>
       <c r="AJ165">
-        <v>-6.8040000000000003E-2</v>
+        <v>-6.8059999999999996E-2</v>
       </c>
       <c r="AK165">
         <v>-50</v>
@@ -23219,7 +23219,7 @@
         <v>-51.5625</v>
       </c>
       <c r="P166">
-        <v>-7.0230000000000001E-2</v>
+        <v>-7.0220000000000005E-2</v>
       </c>
       <c r="Q166">
         <v>-51.5625</v>
@@ -23261,13 +23261,13 @@
         <v>-51.5625</v>
       </c>
       <c r="AD166">
-        <v>-7.0190000000000002E-2</v>
+        <v>-7.0209999999999995E-2</v>
       </c>
       <c r="AE166">
         <v>-51.5625</v>
       </c>
       <c r="AF166">
-        <v>-7.0230000000000001E-2</v>
+        <v>-7.0199999999999999E-2</v>
       </c>
       <c r="AG166">
         <v>-51.5625</v>
@@ -23413,7 +23413,7 @@
         <v>-53.125</v>
       </c>
       <c r="AH167">
-        <v>-7.2349999999999998E-2</v>
+        <v>-7.2330000000000005E-2</v>
       </c>
       <c r="AI167">
         <v>-53.125</v>
@@ -23425,7 +23425,7 @@
         <v>-53.125</v>
       </c>
       <c r="AL167">
-        <v>-7.2349999999999998E-2</v>
+        <v>-7.2340000000000002E-2</v>
       </c>
       <c r="AM167">
         <v>-53.125</v>
@@ -23499,13 +23499,13 @@
         <v>-54.6875</v>
       </c>
       <c r="P168">
-        <v>-7.4499999999999997E-2</v>
+        <v>-7.4480000000000005E-2</v>
       </c>
       <c r="Q168">
         <v>-54.6875</v>
       </c>
       <c r="R168">
-        <v>-7.4499999999999997E-2</v>
+        <v>-7.4510000000000007E-2</v>
       </c>
       <c r="S168">
         <v>-54.6875</v>
@@ -23523,7 +23523,7 @@
         <v>-54.6875</v>
       </c>
       <c r="X168">
-        <v>-7.4499999999999997E-2</v>
+        <v>-7.4510000000000007E-2</v>
       </c>
       <c r="Y168">
         <v>-54.6875</v>
@@ -23535,7 +23535,7 @@
         <v>-54.6875</v>
       </c>
       <c r="AB168">
-        <v>-7.4469999999999995E-2</v>
+        <v>-7.4480000000000005E-2</v>
       </c>
       <c r="AC168">
         <v>-54.6875</v>
@@ -23559,7 +23559,7 @@
         <v>-54.6875</v>
       </c>
       <c r="AJ168">
-        <v>-7.4499999999999997E-2</v>
+        <v>-7.4510000000000007E-2</v>
       </c>
       <c r="AK168">
         <v>-54.6875</v>
@@ -23583,7 +23583,7 @@
         <v>-54.6875</v>
       </c>
       <c r="AR168">
-        <v>-7.4499999999999997E-2</v>
+        <v>-7.4510000000000007E-2</v>
       </c>
       <c r="AS168">
         <v>-54.6875</v>
@@ -23639,13 +23639,13 @@
         <v>-56.25</v>
       </c>
       <c r="P169">
-        <v>-7.6630000000000004E-2</v>
+        <v>-7.6649999999999996E-2</v>
       </c>
       <c r="Q169">
         <v>-56.25</v>
       </c>
       <c r="R169">
-        <v>-7.6630000000000004E-2</v>
+        <v>-7.664E-2</v>
       </c>
       <c r="S169">
         <v>-56.25</v>
@@ -23693,7 +23693,7 @@
         <v>-56.25</v>
       </c>
       <c r="AH169">
-        <v>-7.6630000000000004E-2</v>
+        <v>-7.6649999999999996E-2</v>
       </c>
       <c r="AI169">
         <v>-56.25</v>
@@ -23705,7 +23705,7 @@
         <v>-56.25</v>
       </c>
       <c r="AL169">
-        <v>-7.6630000000000004E-2</v>
+        <v>-7.6609999999999998E-2</v>
       </c>
       <c r="AM169">
         <v>-56.25</v>
@@ -23815,7 +23815,7 @@
         <v>-57.8125</v>
       </c>
       <c r="AB170">
-        <v>-7.8729999999999994E-2</v>
+        <v>-7.8740000000000004E-2</v>
       </c>
       <c r="AC170">
         <v>-57.8125</v>
@@ -23839,13 +23839,13 @@
         <v>-57.8125</v>
       </c>
       <c r="AJ170">
-        <v>-7.8759999999999997E-2</v>
+        <v>-7.8740000000000004E-2</v>
       </c>
       <c r="AK170">
         <v>-57.8125</v>
       </c>
       <c r="AL170">
-        <v>-7.8759999999999997E-2</v>
+        <v>-7.8750000000000001E-2</v>
       </c>
       <c r="AM170">
         <v>-57.8125</v>
@@ -23863,7 +23863,7 @@
         <v>-57.8125</v>
       </c>
       <c r="AR170">
-        <v>-7.8759999999999997E-2</v>
+        <v>-7.8770000000000007E-2</v>
       </c>
       <c r="AS170">
         <v>-57.8125</v>
@@ -23919,13 +23919,13 @@
         <v>-59.375</v>
       </c>
       <c r="P171">
-        <v>-8.09E-2</v>
+        <v>-8.0909999999999996E-2</v>
       </c>
       <c r="Q171">
         <v>-59.375</v>
       </c>
       <c r="R171">
-        <v>-8.09E-2</v>
+        <v>-8.0890000000000004E-2</v>
       </c>
       <c r="S171">
         <v>-59.375</v>
@@ -23955,7 +23955,7 @@
         <v>-59.375</v>
       </c>
       <c r="AB171">
-        <v>-8.0860000000000001E-2</v>
+        <v>-8.0869999999999997E-2</v>
       </c>
       <c r="AC171">
         <v>-59.375</v>
@@ -23973,7 +23973,7 @@
         <v>-59.375</v>
       </c>
       <c r="AH171">
-        <v>-8.09E-2</v>
+        <v>-8.0909999999999996E-2</v>
       </c>
       <c r="AI171">
         <v>-59.375</v>
@@ -24003,7 +24003,7 @@
         <v>-59.375</v>
       </c>
       <c r="AR171">
-        <v>-8.09E-2</v>
+        <v>-8.0909999999999996E-2</v>
       </c>
       <c r="AS171">
         <v>-59.375</v>
@@ -24083,7 +24083,7 @@
         <v>-60.9375</v>
       </c>
       <c r="X172">
-        <v>-8.3030000000000007E-2</v>
+        <v>-8.3040000000000003E-2</v>
       </c>
       <c r="Y172">
         <v>-60.9375</v>
@@ -24119,7 +24119,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AJ172">
-        <v>-8.3040000000000003E-2</v>
+        <v>-8.3019999999999997E-2</v>
       </c>
       <c r="AK172">
         <v>-60.9375</v>
@@ -24163,7 +24163,7 @@
         <v>-62.5</v>
       </c>
       <c r="D173">
-        <v>-8.5180000000000006E-2</v>
+        <v>-8.516E-2</v>
       </c>
       <c r="E173">
         <v>-62.5</v>
@@ -24181,7 +24181,7 @@
         <v>-62.5</v>
       </c>
       <c r="J173">
-        <v>-8.5139999999999993E-2</v>
+        <v>-8.516E-2</v>
       </c>
       <c r="K173">
         <v>-62.5</v>
@@ -24205,7 +24205,7 @@
         <v>-62.5</v>
       </c>
       <c r="R173">
-        <v>-8.5180000000000006E-2</v>
+        <v>-8.5169999999999996E-2</v>
       </c>
       <c r="S173">
         <v>-62.5</v>
@@ -24217,7 +24217,7 @@
         <v>-62.5</v>
       </c>
       <c r="V173">
-        <v>-8.5180000000000006E-2</v>
+        <v>-8.5169999999999996E-2</v>
       </c>
       <c r="W173">
         <v>-62.5</v>
@@ -24283,7 +24283,7 @@
         <v>-62.5</v>
       </c>
       <c r="AR173">
-        <v>-8.5180000000000006E-2</v>
+        <v>-8.5199999999999998E-2</v>
       </c>
       <c r="AS173">
         <v>-62.5</v>
@@ -24357,13 +24357,13 @@
         <v>-64.0625</v>
       </c>
       <c r="V174">
-        <v>-8.7319999999999995E-2</v>
+        <v>-8.7340000000000001E-2</v>
       </c>
       <c r="W174">
         <v>-64.0625</v>
       </c>
       <c r="X174">
-        <v>-8.7319999999999995E-2</v>
+        <v>-8.7330000000000005E-2</v>
       </c>
       <c r="Y174">
         <v>-64.0625</v>
@@ -24399,7 +24399,7 @@
         <v>-64.0625</v>
       </c>
       <c r="AJ174">
-        <v>-8.7340000000000001E-2</v>
+        <v>-8.7330000000000005E-2</v>
       </c>
       <c r="AK174">
         <v>-64.0625</v>
@@ -24443,7 +24443,7 @@
         <v>-65.625</v>
       </c>
       <c r="D175">
-        <v>-8.9469999999999994E-2</v>
+        <v>-8.9480000000000004E-2</v>
       </c>
       <c r="E175">
         <v>-65.625</v>
@@ -24479,7 +24479,7 @@
         <v>-65.625</v>
       </c>
       <c r="P175">
-        <v>-8.9469999999999994E-2</v>
+        <v>-8.949E-2</v>
       </c>
       <c r="Q175">
         <v>-65.625</v>
@@ -24545,7 +24545,7 @@
         <v>-65.625</v>
       </c>
       <c r="AL175">
-        <v>-8.949E-2</v>
+        <v>-8.9510000000000006E-2</v>
       </c>
       <c r="AM175">
         <v>-65.625</v>
@@ -24583,7 +24583,7 @@
         <v>-67.1875</v>
       </c>
       <c r="D176">
-        <v>-9.1619999999999993E-2</v>
+        <v>-9.1600000000000001E-2</v>
       </c>
       <c r="E176">
         <v>-67.1875</v>
@@ -24613,7 +24613,7 @@
         <v>-67.1875</v>
       </c>
       <c r="N176">
-        <v>-9.1590000000000005E-2</v>
+        <v>-9.1609999999999997E-2</v>
       </c>
       <c r="O176">
         <v>-67.1875</v>
@@ -24643,7 +24643,7 @@
         <v>-67.1875</v>
       </c>
       <c r="X176">
-        <v>-9.1619999999999993E-2</v>
+        <v>-9.1600000000000001E-2</v>
       </c>
       <c r="Y176">
         <v>-67.1875</v>
@@ -24655,7 +24655,7 @@
         <v>-67.1875</v>
       </c>
       <c r="AB176">
-        <v>-9.1590000000000005E-2</v>
+        <v>-9.1619999999999993E-2</v>
       </c>
       <c r="AC176">
         <v>-67.1875</v>
@@ -24703,7 +24703,7 @@
         <v>-67.1875</v>
       </c>
       <c r="AR176">
-        <v>-9.1639999999999999E-2</v>
+        <v>-9.1649999999999995E-2</v>
       </c>
       <c r="AS176">
         <v>-67.1875</v>
@@ -24729,7 +24729,7 @@
         <v>-68.75</v>
       </c>
       <c r="F177">
-        <v>-9.3770000000000006E-2</v>
+        <v>-9.3780000000000002E-2</v>
       </c>
       <c r="G177">
         <v>-68.75</v>
@@ -24759,13 +24759,13 @@
         <v>-68.75</v>
       </c>
       <c r="P177">
-        <v>-9.3770000000000006E-2</v>
+        <v>-9.3780000000000002E-2</v>
       </c>
       <c r="Q177">
         <v>-68.75</v>
       </c>
       <c r="R177">
-        <v>-9.3770000000000006E-2</v>
+        <v>-9.375E-2</v>
       </c>
       <c r="S177">
         <v>-68.75</v>
@@ -24783,7 +24783,7 @@
         <v>-68.75</v>
       </c>
       <c r="X177">
-        <v>-9.375E-2</v>
+        <v>-9.3770000000000006E-2</v>
       </c>
       <c r="Y177">
         <v>-68.75</v>
@@ -24863,7 +24863,7 @@
         <v>-70.3125</v>
       </c>
       <c r="D178">
-        <v>-9.5920000000000005E-2</v>
+        <v>-9.5899999999999999E-2</v>
       </c>
       <c r="E178">
         <v>-70.3125</v>
@@ -24893,13 +24893,13 @@
         <v>-70.3125</v>
       </c>
       <c r="N178">
-        <v>-9.5890000000000003E-2</v>
+        <v>-9.5899999999999999E-2</v>
       </c>
       <c r="O178">
         <v>-70.3125</v>
       </c>
       <c r="P178">
-        <v>-9.5920000000000005E-2</v>
+        <v>-9.5909999999999995E-2</v>
       </c>
       <c r="Q178">
         <v>-70.3125</v>
@@ -24953,7 +24953,7 @@
         <v>-70.3125</v>
       </c>
       <c r="AH178">
-        <v>-9.5920000000000005E-2</v>
+        <v>-9.5899999999999999E-2</v>
       </c>
       <c r="AI178">
         <v>-70.3125</v>
@@ -24965,7 +24965,7 @@
         <v>-70.3125</v>
       </c>
       <c r="AL178">
-        <v>-9.5920000000000005E-2</v>
+        <v>-9.5909999999999995E-2</v>
       </c>
       <c r="AM178">
         <v>-70.3125</v>
@@ -25045,7 +25045,7 @@
         <v>-71.875</v>
       </c>
       <c r="R179">
-        <v>-9.8070000000000004E-2</v>
+        <v>-9.8059999999999994E-2</v>
       </c>
       <c r="S179">
         <v>-71.875</v>
@@ -25057,7 +25057,7 @@
         <v>-71.875</v>
       </c>
       <c r="V179">
-        <v>-9.8070000000000004E-2</v>
+        <v>-9.8049999999999998E-2</v>
       </c>
       <c r="W179">
         <v>-71.875</v>
@@ -25075,7 +25075,7 @@
         <v>-71.875</v>
       </c>
       <c r="AB179">
-        <v>-9.8030000000000006E-2</v>
+        <v>-9.8049999999999998E-2</v>
       </c>
       <c r="AC179">
         <v>-71.875</v>
@@ -25149,7 +25149,7 @@
         <v>-73.4375</v>
       </c>
       <c r="F180">
-        <v>-0.10023</v>
+        <v>-0.10024</v>
       </c>
       <c r="G180">
         <v>-73.4375</v>
@@ -25173,7 +25173,7 @@
         <v>-73.4375</v>
       </c>
       <c r="N180">
-        <v>-0.1002</v>
+        <v>-0.10009999999999999</v>
       </c>
       <c r="O180">
         <v>-73.4375</v>
@@ -25185,7 +25185,7 @@
         <v>-73.4375</v>
       </c>
       <c r="R180">
-        <v>-0.10023</v>
+        <v>-0.1002</v>
       </c>
       <c r="S180">
         <v>-73.4375</v>
@@ -25233,7 +25233,7 @@
         <v>-73.4375</v>
       </c>
       <c r="AH180">
-        <v>-0.10023</v>
+        <v>-0.10022</v>
       </c>
       <c r="AI180">
         <v>-73.4375</v>
@@ -25245,7 +25245,7 @@
         <v>-73.4375</v>
       </c>
       <c r="AL180">
-        <v>-0.10023</v>
+        <v>-0.10022</v>
       </c>
       <c r="AM180">
         <v>-73.4375</v>
@@ -25343,7 +25343,7 @@
         <v>-75</v>
       </c>
       <c r="X181">
-        <v>-0.10238</v>
+        <v>-0.10238999999999999</v>
       </c>
       <c r="Y181">
         <v>-75</v>
@@ -25373,7 +25373,7 @@
         <v>-75</v>
       </c>
       <c r="AH181">
-        <v>-0.1024</v>
+        <v>-0.1021</v>
       </c>
       <c r="AI181">
         <v>-75</v>
@@ -25423,7 +25423,7 @@
         <v>-76.5625</v>
       </c>
       <c r="D182">
-        <v>-0.10456</v>
+        <v>-0.10455</v>
       </c>
       <c r="E182">
         <v>-76.5625</v>
@@ -25519,13 +25519,13 @@
         <v>-76.5625</v>
       </c>
       <c r="AJ182">
-        <v>-0.10453999999999999</v>
+        <v>-0.10452</v>
       </c>
       <c r="AK182">
         <v>-76.5625</v>
       </c>
       <c r="AL182">
-        <v>-0.10453999999999999</v>
+        <v>-0.10452</v>
       </c>
       <c r="AM182">
         <v>-76.5625</v>
@@ -25605,7 +25605,7 @@
         <v>-78.125</v>
       </c>
       <c r="R183">
-        <v>-0.10671</v>
+        <v>-0.10673000000000001</v>
       </c>
       <c r="S183">
         <v>-78.125</v>
@@ -25617,13 +25617,13 @@
         <v>-78.125</v>
       </c>
       <c r="V183">
-        <v>-0.10671</v>
+        <v>-0.10672</v>
       </c>
       <c r="W183">
         <v>-78.125</v>
       </c>
       <c r="X183">
-        <v>-0.10668999999999999</v>
+        <v>-0.10671</v>
       </c>
       <c r="Y183">
         <v>-78.125</v>
@@ -25703,7 +25703,7 @@
         <v>-79.6875</v>
       </c>
       <c r="D184">
-        <v>-0.10889</v>
+        <v>-0.1089</v>
       </c>
       <c r="E184">
         <v>-79.6875</v>
@@ -25843,7 +25843,7 @@
         <v>-81.25</v>
       </c>
       <c r="D185">
-        <v>-0.11108999999999999</v>
+        <v>-0.11107</v>
       </c>
       <c r="E185">
         <v>-81.25</v>
@@ -25897,7 +25897,7 @@
         <v>-81.25</v>
       </c>
       <c r="V185">
-        <v>-0.11105</v>
+        <v>-0.11104</v>
       </c>
       <c r="W185">
         <v>-81.25</v>
@@ -25909,7 +25909,7 @@
         <v>-81.25</v>
       </c>
       <c r="Z185">
-        <v>-0.11101999999999999</v>
+        <v>-0.11103</v>
       </c>
       <c r="AA185">
         <v>-81.25</v>
@@ -25945,7 +25945,7 @@
         <v>-81.25</v>
       </c>
       <c r="AL185">
-        <v>-0.11107</v>
+        <v>-0.11108999999999999</v>
       </c>
       <c r="AM185">
         <v>-81.25</v>
@@ -26037,7 +26037,7 @@
         <v>-82.8125</v>
       </c>
       <c r="V186">
-        <v>-0.11323</v>
+        <v>-0.1132</v>
       </c>
       <c r="W186">
         <v>-82.8125</v>
@@ -26079,7 +26079,7 @@
         <v>-82.8125</v>
       </c>
       <c r="AJ186">
-        <v>-0.11325</v>
+        <v>-0.11323999999999999</v>
       </c>
       <c r="AK186">
         <v>-82.8125</v>
@@ -26103,7 +26103,7 @@
         <v>-82.8125</v>
       </c>
       <c r="AR186">
-        <v>-0.11327</v>
+        <v>-0.11329</v>
       </c>
       <c r="AS186">
         <v>-82.8125</v>
@@ -26123,7 +26123,7 @@
         <v>-84.375</v>
       </c>
       <c r="D187">
-        <v>-0.11545</v>
+        <v>-0.11545999999999999</v>
       </c>
       <c r="E187">
         <v>-84.375</v>
@@ -26189,7 +26189,7 @@
         <v>-84.375</v>
       </c>
       <c r="Z187">
-        <v>-0.11537</v>
+        <v>-0.11534999999999999</v>
       </c>
       <c r="AA187">
         <v>-84.375</v>
@@ -26293,7 +26293,7 @@
         <v>-85.9375</v>
       </c>
       <c r="N188">
-        <v>-0.11756</v>
+        <v>-0.11755</v>
       </c>
       <c r="O188">
         <v>-85.9375</v>
@@ -26305,7 +26305,7 @@
         <v>-85.9375</v>
       </c>
       <c r="R188">
-        <v>-0.11763999999999999</v>
+        <v>-0.11766</v>
       </c>
       <c r="S188">
         <v>-85.9375</v>
@@ -26359,7 +26359,7 @@
         <v>-85.9375</v>
       </c>
       <c r="AJ188">
-        <v>-0.11761000000000001</v>
+        <v>-0.1176</v>
       </c>
       <c r="AK188">
         <v>-85.9375</v>
@@ -26445,7 +26445,7 @@
         <v>-87.5</v>
       </c>
       <c r="R189">
-        <v>-0.11984</v>
+        <v>-0.11985</v>
       </c>
       <c r="S189">
         <v>-87.5</v>
@@ -26457,7 +26457,7 @@
         <v>-87.5</v>
       </c>
       <c r="V189">
-        <v>-0.11978</v>
+        <v>-0.11978999999999999</v>
       </c>
       <c r="W189">
         <v>-87.5</v>
@@ -26523,7 +26523,7 @@
         <v>-87.5</v>
       </c>
       <c r="AR189">
-        <v>-0.11984</v>
+        <v>-0.11985</v>
       </c>
       <c r="AS189">
         <v>-87.5</v>
@@ -26585,7 +26585,7 @@
         <v>-89.0625</v>
       </c>
       <c r="R190">
-        <v>-0.12205000000000001</v>
+        <v>-0.12206</v>
       </c>
       <c r="S190">
         <v>-89.0625</v>
@@ -26609,7 +26609,7 @@
         <v>-89.0625</v>
       </c>
       <c r="Z190">
-        <v>-0.12199</v>
+        <v>-0.12198000000000001</v>
       </c>
       <c r="AA190">
         <v>-89.0625</v>
@@ -26639,7 +26639,7 @@
         <v>-89.0625</v>
       </c>
       <c r="AJ190">
-        <v>-0.12202</v>
+        <v>-0.12204</v>
       </c>
       <c r="AK190">
         <v>-89.0625</v>
@@ -26737,7 +26737,7 @@
         <v>-90.625</v>
       </c>
       <c r="V191">
-        <v>-0.1242</v>
+        <v>-0.1244</v>
       </c>
       <c r="W191">
         <v>-90.625</v>
@@ -26823,7 +26823,7 @@
         <v>-92.1875</v>
       </c>
       <c r="D192">
-        <v>-0.12648000000000001</v>
+        <v>-0.1265</v>
       </c>
       <c r="E192">
         <v>-92.1875</v>
@@ -26969,7 +26969,7 @@
         <v>-93.75</v>
       </c>
       <c r="F193">
-        <v>-0.12862999999999999</v>
+        <v>-0.12864</v>
       </c>
       <c r="G193">
         <v>-93.75</v>
@@ -27005,7 +27005,7 @@
         <v>-93.75</v>
       </c>
       <c r="R193">
-        <v>-0.12867999999999999</v>
+        <v>-0.12870000000000001</v>
       </c>
       <c r="S193">
         <v>-93.75</v>
@@ -27059,7 +27059,7 @@
         <v>-93.75</v>
       </c>
       <c r="AJ193">
-        <v>-0.12866</v>
+        <v>-0.12864999999999999</v>
       </c>
       <c r="AK193">
         <v>-93.75</v>
@@ -27115,7 +27115,7 @@
         <v>-95.3125</v>
       </c>
       <c r="H194">
-        <v>-0.13086</v>
+        <v>-0.13084999999999999</v>
       </c>
       <c r="I194">
         <v>-95.3125</v>
@@ -27157,7 +27157,7 @@
         <v>-95.3125</v>
       </c>
       <c r="V194">
-        <v>-0.13086</v>
+        <v>-0.13086999999999999</v>
       </c>
       <c r="W194">
         <v>-95.3125</v>
@@ -27169,7 +27169,7 @@
         <v>-95.3125</v>
       </c>
       <c r="Z194">
-        <v>-0.13084000000000001</v>
+        <v>-0.13081999999999999</v>
       </c>
       <c r="AA194">
         <v>-95.3125</v>
@@ -27243,7 +27243,7 @@
         <v>-96.875</v>
       </c>
       <c r="D195">
-        <v>-0.13311999999999999</v>
+        <v>-0.13311000000000001</v>
       </c>
       <c r="E195">
         <v>-96.875</v>
@@ -27333,13 +27333,13 @@
         <v>-96.875</v>
       </c>
       <c r="AH195">
-        <v>-0.13311999999999999</v>
+        <v>-0.1331</v>
       </c>
       <c r="AI195">
         <v>-96.875</v>
       </c>
       <c r="AJ195">
-        <v>-0.1331</v>
+        <v>-0.13311000000000001</v>
       </c>
       <c r="AK195">
         <v>-96.875</v>
@@ -27443,13 +27443,13 @@
         <v>-98.4375</v>
       </c>
       <c r="X196">
-        <v>-0.13533000000000001</v>
+        <v>-0.13533999999999999</v>
       </c>
       <c r="Y196">
         <v>-98.4375</v>
       </c>
       <c r="Z196">
-        <v>-0.13532</v>
+        <v>-0.13533000000000001</v>
       </c>
       <c r="AA196">
         <v>-98.4375</v>
@@ -27577,7 +27577,7 @@
         <v>-100</v>
       </c>
       <c r="V197">
-        <v>-0.13732</v>
+        <v>-0.13733000000000001</v>
       </c>
       <c r="W197">
         <v>-100</v>
@@ -27619,7 +27619,7 @@
         <v>-100</v>
       </c>
       <c r="AJ197">
-        <v>-0.13733000000000001</v>
+        <v>-0.13733999999999999</v>
       </c>
       <c r="AK197">
         <v>-100</v>
@@ -27699,7 +27699,7 @@
         <v>-98.4375</v>
       </c>
       <c r="P198">
-        <v>-0.13517000000000001</v>
+        <v>-0.13517999999999999</v>
       </c>
       <c r="Q198">
         <v>-98.4375</v>
@@ -27753,7 +27753,7 @@
         <v>-98.4375</v>
       </c>
       <c r="AH198">
-        <v>-0.13519999999999999</v>
+        <v>-0.13539999999999999</v>
       </c>
       <c r="AI198">
         <v>-98.4375</v>
@@ -27845,7 +27845,7 @@
         <v>-96.875</v>
       </c>
       <c r="R199">
-        <v>-0.13297</v>
+        <v>-0.13297999999999999</v>
       </c>
       <c r="S199">
         <v>-96.875</v>
@@ -27857,7 +27857,7 @@
         <v>-96.875</v>
       </c>
       <c r="V199">
-        <v>-0.13294</v>
+        <v>-0.13295000000000001</v>
       </c>
       <c r="W199">
         <v>-96.875</v>
@@ -27949,7 +27949,7 @@
         <v>-95.3125</v>
       </c>
       <c r="F200">
-        <v>-0.13070999999999999</v>
+        <v>-0.13072</v>
       </c>
       <c r="G200">
         <v>-95.3125</v>
@@ -28003,7 +28003,7 @@
         <v>-95.3125</v>
       </c>
       <c r="X200">
-        <v>-0.13070999999999999</v>
+        <v>-0.13072</v>
       </c>
       <c r="Y200">
         <v>-95.3125</v>
@@ -28039,7 +28039,7 @@
         <v>-95.3125</v>
       </c>
       <c r="AJ200">
-        <v>-0.13073000000000001</v>
+        <v>-0.13074</v>
       </c>
       <c r="AK200">
         <v>-95.3125</v>
@@ -28283,7 +28283,7 @@
         <v>-92.1875</v>
       </c>
       <c r="X202">
-        <v>-0.12626999999999999</v>
+        <v>-0.12626000000000001</v>
       </c>
       <c r="Y202">
         <v>-92.1875</v>
@@ -28307,13 +28307,13 @@
         <v>-92.1875</v>
       </c>
       <c r="AF202">
-        <v>-0.12626999999999999</v>
+        <v>-0.12625</v>
       </c>
       <c r="AG202">
         <v>-92.1875</v>
       </c>
       <c r="AH202">
-        <v>-0.1263</v>
+        <v>-0.126</v>
       </c>
       <c r="AI202">
         <v>-92.1875</v>
@@ -28557,7 +28557,7 @@
         <v>-89.0625</v>
       </c>
       <c r="V204">
-        <v>-0.12184</v>
+        <v>-0.12182999999999999</v>
       </c>
       <c r="W204">
         <v>-89.0625</v>
@@ -28587,19 +28587,19 @@
         <v>-89.0625</v>
       </c>
       <c r="AF204">
-        <v>-0.12184</v>
+        <v>-0.12185</v>
       </c>
       <c r="AG204">
         <v>-89.0625</v>
       </c>
       <c r="AH204">
-        <v>-0.12186</v>
+        <v>-0.12185</v>
       </c>
       <c r="AI204">
         <v>-89.0625</v>
       </c>
       <c r="AJ204">
-        <v>-0.12184</v>
+        <v>-0.12182</v>
       </c>
       <c r="AK204">
         <v>-89.0625</v>
@@ -28697,7 +28697,7 @@
         <v>-87.5</v>
       </c>
       <c r="V205">
-        <v>-0.11960999999999999</v>
+        <v>-0.11962</v>
       </c>
       <c r="W205">
         <v>-87.5</v>
@@ -28727,13 +28727,13 @@
         <v>-87.5</v>
       </c>
       <c r="AF205">
-        <v>-0.11963</v>
+        <v>-0.11965000000000001</v>
       </c>
       <c r="AG205">
         <v>-87.5</v>
       </c>
       <c r="AH205">
-        <v>-0.11965000000000001</v>
+        <v>-0.11964</v>
       </c>
       <c r="AI205">
         <v>-87.5</v>
@@ -28837,7 +28837,7 @@
         <v>-85.9375</v>
       </c>
       <c r="V206">
-        <v>-0.11742</v>
+        <v>-0.11743000000000001</v>
       </c>
       <c r="W206">
         <v>-85.9375</v>
@@ -28867,7 +28867,7 @@
         <v>-85.9375</v>
       </c>
       <c r="AF206">
-        <v>-0.11743000000000001</v>
+        <v>-0.11742</v>
       </c>
       <c r="AG206">
         <v>-85.9375</v>
@@ -28879,13 +28879,13 @@
         <v>-85.9375</v>
       </c>
       <c r="AJ206">
-        <v>-0.11743000000000001</v>
+        <v>-0.11742</v>
       </c>
       <c r="AK206">
         <v>-85.9375</v>
       </c>
       <c r="AL206">
-        <v>-0.11743000000000001</v>
+        <v>-0.11744</v>
       </c>
       <c r="AM206">
         <v>-85.9375</v>
@@ -28935,7 +28935,7 @@
         <v>-84.375</v>
       </c>
       <c r="H207">
-        <v>-0.11524</v>
+        <v>-0.11523</v>
       </c>
       <c r="I207">
         <v>-84.375</v>
@@ -28977,7 +28977,7 @@
         <v>-84.375</v>
       </c>
       <c r="V207">
-        <v>-0.11522</v>
+        <v>-0.1152</v>
       </c>
       <c r="W207">
         <v>-84.375</v>
@@ -28989,7 +28989,7 @@
         <v>-84.375</v>
       </c>
       <c r="Z207">
-        <v>-0.11519</v>
+        <v>-0.11521000000000001</v>
       </c>
       <c r="AA207">
         <v>-84.375</v>
@@ -29013,7 +29013,7 @@
         <v>-84.375</v>
       </c>
       <c r="AH207">
-        <v>-0.11525000000000001</v>
+        <v>-0.11524</v>
       </c>
       <c r="AI207">
         <v>-84.375</v>
@@ -29159,7 +29159,7 @@
         <v>-82.8125</v>
       </c>
       <c r="AJ208">
-        <v>-0.11304</v>
+        <v>-0.11302</v>
       </c>
       <c r="AK208">
         <v>-82.8125</v>
@@ -29209,7 +29209,7 @@
         <v>-81.25</v>
       </c>
       <c r="F209">
-        <v>-0.11083999999999999</v>
+        <v>-0.11082</v>
       </c>
       <c r="G209">
         <v>-81.25</v>
@@ -29263,7 +29263,7 @@
         <v>-81.25</v>
       </c>
       <c r="X209">
-        <v>-0.11083999999999999</v>
+        <v>-0.11085</v>
       </c>
       <c r="Y209">
         <v>-81.25</v>
@@ -29293,7 +29293,7 @@
         <v>-81.25</v>
       </c>
       <c r="AH209">
-        <v>-0.11088000000000001</v>
+        <v>-0.11085</v>
       </c>
       <c r="AI209">
         <v>-81.25</v>
@@ -29397,13 +29397,13 @@
         <v>-79.6875</v>
       </c>
       <c r="V210">
-        <v>-0.10866000000000001</v>
+        <v>-0.10865</v>
       </c>
       <c r="W210">
         <v>-79.6875</v>
       </c>
       <c r="X210">
-        <v>-0.10866000000000001</v>
+        <v>-0.10861999999999999</v>
       </c>
       <c r="Y210">
         <v>-79.6875</v>
@@ -29439,13 +29439,13 @@
         <v>-79.6875</v>
       </c>
       <c r="AJ210">
-        <v>-0.10868</v>
+        <v>-0.10867</v>
       </c>
       <c r="AK210">
         <v>-79.6875</v>
       </c>
       <c r="AL210">
-        <v>-0.10868</v>
+        <v>-0.10867</v>
       </c>
       <c r="AM210">
         <v>-79.6875</v>
@@ -29519,7 +29519,7 @@
         <v>-78.125</v>
       </c>
       <c r="P211">
-        <v>-0.1065</v>
+        <v>-0.10650999999999999</v>
       </c>
       <c r="Q211">
         <v>-78.125</v>
@@ -29537,7 +29537,7 @@
         <v>-78.125</v>
       </c>
       <c r="V211">
-        <v>-0.10648000000000001</v>
+        <v>-0.1065</v>
       </c>
       <c r="W211">
         <v>-78.125</v>
@@ -29549,7 +29549,7 @@
         <v>-78.125</v>
       </c>
       <c r="Z211">
-        <v>-0.10647</v>
+        <v>-0.10648000000000001</v>
       </c>
       <c r="AA211">
         <v>-78.125</v>
@@ -29683,7 +29683,7 @@
         <v>-76.5625</v>
       </c>
       <c r="X212">
-        <v>-0.1043</v>
+        <v>-0.10440000000000001</v>
       </c>
       <c r="Y212">
         <v>-76.5625</v>
@@ -29695,7 +29695,7 @@
         <v>-76.5625</v>
       </c>
       <c r="AB212">
-        <v>-0.10432</v>
+        <v>-0.1043</v>
       </c>
       <c r="AC212">
         <v>-76.5625</v>
@@ -29725,7 +29725,7 @@
         <v>-76.5625</v>
       </c>
       <c r="AL212">
-        <v>-0.10433000000000001</v>
+        <v>-0.10432</v>
       </c>
       <c r="AM212">
         <v>-76.5625</v>
@@ -29763,7 +29763,7 @@
         <v>-75</v>
       </c>
       <c r="D213">
-        <v>-0.10217</v>
+        <v>-0.10218000000000001</v>
       </c>
       <c r="E213">
         <v>-75</v>
@@ -29817,7 +29817,7 @@
         <v>-75</v>
       </c>
       <c r="V213">
-        <v>-0.10213999999999999</v>
+        <v>-0.10212</v>
       </c>
       <c r="W213">
         <v>-75</v>
@@ -29835,7 +29835,7 @@
         <v>-75</v>
       </c>
       <c r="AB213">
-        <v>-0.10215</v>
+        <v>-0.10213999999999999</v>
       </c>
       <c r="AC213">
         <v>-75</v>
@@ -29859,7 +29859,7 @@
         <v>-75</v>
       </c>
       <c r="AJ213">
-        <v>-0.10215</v>
+        <v>-0.10213999999999999</v>
       </c>
       <c r="AK213">
         <v>-75</v>
@@ -29939,13 +29939,13 @@
         <v>-73.4375</v>
       </c>
       <c r="P214">
-        <v>-9.9989999999999996E-2</v>
+        <v>-9.9959999999999993E-2</v>
       </c>
       <c r="Q214">
         <v>-73.4375</v>
       </c>
       <c r="R214">
-        <v>-0.10002</v>
+        <v>-0.10001</v>
       </c>
       <c r="S214">
         <v>-73.4375</v>
@@ -29963,19 +29963,19 @@
         <v>-73.4375</v>
       </c>
       <c r="X214">
-        <v>-9.9989999999999996E-2</v>
+        <v>-9.9970000000000003E-2</v>
       </c>
       <c r="Y214">
         <v>-73.4375</v>
       </c>
       <c r="Z214">
-        <v>-9.9970000000000003E-2</v>
+        <v>-9.9989999999999996E-2</v>
       </c>
       <c r="AA214">
         <v>-73.4375</v>
       </c>
       <c r="AB214">
-        <v>-9.9989999999999996E-2</v>
+        <v>-9.9979999999999999E-2</v>
       </c>
       <c r="AC214">
         <v>-73.4375</v>
@@ -29999,7 +29999,7 @@
         <v>-73.4375</v>
       </c>
       <c r="AJ214">
-        <v>-9.9989999999999996E-2</v>
+        <v>-9.9959999999999993E-2</v>
       </c>
       <c r="AK214">
         <v>-73.4375</v>
@@ -30085,7 +30085,7 @@
         <v>-71.875</v>
       </c>
       <c r="R215">
-        <v>-9.7860000000000003E-2</v>
+        <v>-9.7890000000000005E-2</v>
       </c>
       <c r="S215">
         <v>-71.875</v>
@@ -30097,7 +30097,7 @@
         <v>-71.875</v>
       </c>
       <c r="V215">
-        <v>-9.7820000000000004E-2</v>
+        <v>-9.7839999999999996E-2</v>
       </c>
       <c r="W215">
         <v>-71.875</v>
@@ -30115,7 +30115,7 @@
         <v>-71.875</v>
       </c>
       <c r="AB215">
-        <v>-9.7820000000000004E-2</v>
+        <v>-9.7799999999999998E-2</v>
       </c>
       <c r="AC215">
         <v>-71.875</v>
@@ -30133,13 +30133,13 @@
         <v>-71.875</v>
       </c>
       <c r="AH215">
-        <v>-9.7860000000000003E-2</v>
+        <v>-9.7850000000000006E-2</v>
       </c>
       <c r="AI215">
         <v>-71.875</v>
       </c>
       <c r="AJ215">
-        <v>-9.7820000000000004E-2</v>
+        <v>-9.783E-2</v>
       </c>
       <c r="AK215">
         <v>-71.875</v>
@@ -30201,7 +30201,7 @@
         <v>-70.3125</v>
       </c>
       <c r="J216">
-        <v>-9.5680000000000001E-2</v>
+        <v>-9.5670000000000005E-2</v>
       </c>
       <c r="K216">
         <v>-70.3125</v>
@@ -30213,7 +30213,7 @@
         <v>-70.3125</v>
       </c>
       <c r="N216">
-        <v>-9.5659999999999995E-2</v>
+        <v>-9.5649999999999999E-2</v>
       </c>
       <c r="O216">
         <v>-70.3125</v>
@@ -30237,7 +30237,7 @@
         <v>-70.3125</v>
       </c>
       <c r="V216">
-        <v>-9.5659999999999995E-2</v>
+        <v>-9.5670000000000005E-2</v>
       </c>
       <c r="W216">
         <v>-70.3125</v>
@@ -30249,7 +30249,7 @@
         <v>-70.3125</v>
       </c>
       <c r="Z216">
-        <v>-9.5659999999999995E-2</v>
+        <v>-9.5670000000000005E-2</v>
       </c>
       <c r="AA216">
         <v>-70.3125</v>
@@ -30323,7 +30323,7 @@
         <v>-68.75</v>
       </c>
       <c r="D217">
-        <v>-9.3560000000000004E-2</v>
+        <v>-9.3549999999999994E-2</v>
       </c>
       <c r="E217">
         <v>-68.75</v>
@@ -30359,7 +30359,7 @@
         <v>-68.75</v>
       </c>
       <c r="P217">
-        <v>-9.3530000000000002E-2</v>
+        <v>-9.3520000000000006E-2</v>
       </c>
       <c r="Q217">
         <v>-68.75</v>
@@ -30389,13 +30389,13 @@
         <v>-68.75</v>
       </c>
       <c r="Z217">
-        <v>-9.3509999999999996E-2</v>
+        <v>-9.3520000000000006E-2</v>
       </c>
       <c r="AA217">
         <v>-68.75</v>
       </c>
       <c r="AB217">
-        <v>-9.3509999999999996E-2</v>
+        <v>-9.3530000000000002E-2</v>
       </c>
       <c r="AC217">
         <v>-68.75</v>
@@ -30413,7 +30413,7 @@
         <v>-68.75</v>
       </c>
       <c r="AH217">
-        <v>-9.3560000000000004E-2</v>
+        <v>-9.3549999999999994E-2</v>
       </c>
       <c r="AI217">
         <v>-68.75</v>
@@ -30425,7 +30425,7 @@
         <v>-68.75</v>
       </c>
       <c r="AL217">
-        <v>-9.3530000000000002E-2</v>
+        <v>-9.3520000000000006E-2</v>
       </c>
       <c r="AM217">
         <v>-68.75</v>
@@ -30463,7 +30463,7 @@
         <v>-67.1875</v>
       </c>
       <c r="D218">
-        <v>-9.1389999999999999E-2</v>
+        <v>-9.1399999999999995E-2</v>
       </c>
       <c r="E218">
         <v>-67.1875</v>
@@ -30493,13 +30493,13 @@
         <v>-67.1875</v>
       </c>
       <c r="N218">
-        <v>-9.1359999999999997E-2</v>
+        <v>-9.1350000000000001E-2</v>
       </c>
       <c r="O218">
         <v>-67.1875</v>
       </c>
       <c r="P218">
-        <v>-9.1380000000000003E-2</v>
+        <v>-9.1389999999999999E-2</v>
       </c>
       <c r="Q218">
         <v>-67.1875</v>
@@ -30523,7 +30523,7 @@
         <v>-67.1875</v>
       </c>
       <c r="X218">
-        <v>-9.1380000000000003E-2</v>
+        <v>-9.1370000000000007E-2</v>
       </c>
       <c r="Y218">
         <v>-67.1875</v>
@@ -30559,7 +30559,7 @@
         <v>-67.1875</v>
       </c>
       <c r="AJ218">
-        <v>-9.1380000000000003E-2</v>
+        <v>-9.1389999999999999E-2</v>
       </c>
       <c r="AK218">
         <v>-67.1875</v>
@@ -30633,7 +30633,7 @@
         <v>-65.625</v>
       </c>
       <c r="N219">
-        <v>-8.9200000000000002E-2</v>
+        <v>-8.9209999999999998E-2</v>
       </c>
       <c r="O219">
         <v>-65.625</v>
@@ -30657,7 +30657,7 @@
         <v>-65.625</v>
       </c>
       <c r="V219">
-        <v>-8.9200000000000002E-2</v>
+        <v>-8.9209999999999998E-2</v>
       </c>
       <c r="W219">
         <v>-65.625</v>
@@ -30675,7 +30675,7 @@
         <v>-65.625</v>
       </c>
       <c r="AB219">
-        <v>-8.9200000000000002E-2</v>
+        <v>-8.9219999999999994E-2</v>
       </c>
       <c r="AC219">
         <v>-65.625</v>
@@ -30693,7 +30693,7 @@
         <v>-65.625</v>
       </c>
       <c r="AH219">
-        <v>-8.9260000000000006E-2</v>
+        <v>-8.9230000000000004E-2</v>
       </c>
       <c r="AI219">
         <v>-65.625</v>
@@ -30705,7 +30705,7 @@
         <v>-65.625</v>
       </c>
       <c r="AL219">
-        <v>-8.9209999999999998E-2</v>
+        <v>-8.9219999999999994E-2</v>
       </c>
       <c r="AM219">
         <v>-65.625</v>
@@ -30809,7 +30809,7 @@
         <v>-64.0625</v>
       </c>
       <c r="Z220">
-        <v>-8.7069999999999995E-2</v>
+        <v>-8.7080000000000005E-2</v>
       </c>
       <c r="AA220">
         <v>-64.0625</v>
@@ -30839,13 +30839,13 @@
         <v>-64.0625</v>
       </c>
       <c r="AJ220">
-        <v>-8.7080000000000005E-2</v>
+        <v>-8.7069999999999995E-2</v>
       </c>
       <c r="AK220">
         <v>-64.0625</v>
       </c>
       <c r="AL220">
-        <v>-8.7080000000000005E-2</v>
+        <v>-8.7069999999999995E-2</v>
       </c>
       <c r="AM220">
         <v>-64.0625</v>
@@ -30863,7 +30863,7 @@
         <v>-64.0625</v>
       </c>
       <c r="AR220">
-        <v>-8.7099999999999997E-2</v>
+        <v>-8.7120000000000003E-2</v>
       </c>
       <c r="AS220">
         <v>-64.0625</v>
@@ -30883,7 +30883,7 @@
         <v>-62.5</v>
       </c>
       <c r="D221">
-        <v>-8.4930000000000005E-2</v>
+        <v>-8.4900000000000003E-2</v>
       </c>
       <c r="E221">
         <v>-62.5</v>
@@ -30913,13 +30913,13 @@
         <v>-62.5</v>
       </c>
       <c r="N221">
-        <v>-8.4900000000000003E-2</v>
+        <v>-8.5099999999999995E-2</v>
       </c>
       <c r="O221">
         <v>-62.5</v>
       </c>
       <c r="P221">
-        <v>-8.4919999999999995E-2</v>
+        <v>-8.4900000000000003E-2</v>
       </c>
       <c r="Q221">
         <v>-62.5</v>
@@ -30937,13 +30937,13 @@
         <v>-62.5</v>
       </c>
       <c r="V221">
-        <v>-8.4900000000000003E-2</v>
+        <v>-8.4909999999999999E-2</v>
       </c>
       <c r="W221">
         <v>-62.5</v>
       </c>
       <c r="X221">
-        <v>-8.4919999999999995E-2</v>
+        <v>-8.5099999999999995E-2</v>
       </c>
       <c r="Y221">
         <v>-62.5</v>
@@ -30955,7 +30955,7 @@
         <v>-62.5</v>
       </c>
       <c r="AB221">
-        <v>-8.4900000000000003E-2</v>
+        <v>-8.4919999999999995E-2</v>
       </c>
       <c r="AC221">
         <v>-62.5</v>
@@ -30985,7 +30985,7 @@
         <v>-62.5</v>
       </c>
       <c r="AL221">
-        <v>-8.4919999999999995E-2</v>
+        <v>-8.4909999999999999E-2</v>
       </c>
       <c r="AM221">
         <v>-62.5</v>
@@ -31023,13 +31023,13 @@
         <v>-60.9375</v>
       </c>
       <c r="D222">
-        <v>-8.2799999999999999E-2</v>
+        <v>-8.2699999999999996E-2</v>
       </c>
       <c r="E222">
         <v>-60.9375</v>
       </c>
       <c r="F222">
-        <v>-8.2769999999999996E-2</v>
+        <v>-8.2750000000000004E-2</v>
       </c>
       <c r="G222">
         <v>-60.9375</v>
@@ -31089,7 +31089,7 @@
         <v>-60.9375</v>
       </c>
       <c r="Z222">
-        <v>-8.2769999999999996E-2</v>
+        <v>-8.2780000000000006E-2</v>
       </c>
       <c r="AA222">
         <v>-60.9375</v>
@@ -31119,7 +31119,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AJ222">
-        <v>-8.2790000000000002E-2</v>
+        <v>-8.2809999999999995E-2</v>
       </c>
       <c r="AK222">
         <v>-60.9375</v>
@@ -31143,7 +31143,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AR222">
-        <v>-8.2799999999999999E-2</v>
+        <v>-8.2809999999999995E-2</v>
       </c>
       <c r="AS222">
         <v>-60.9375</v>
@@ -31199,13 +31199,13 @@
         <v>-59.375</v>
       </c>
       <c r="P223">
-        <v>-8.0640000000000003E-2</v>
+        <v>-8.0649999999999999E-2</v>
       </c>
       <c r="Q223">
         <v>-59.375</v>
       </c>
       <c r="R223">
-        <v>-8.0649999999999999E-2</v>
+        <v>-8.0629999999999993E-2</v>
       </c>
       <c r="S223">
         <v>-59.375</v>
@@ -31217,7 +31217,7 @@
         <v>-59.375</v>
       </c>
       <c r="V223">
-        <v>-8.0619999999999997E-2</v>
+        <v>-8.0600000000000005E-2</v>
       </c>
       <c r="W223">
         <v>-59.375</v>
@@ -31235,7 +31235,7 @@
         <v>-59.375</v>
       </c>
       <c r="AB223">
-        <v>-8.0619999999999997E-2</v>
+        <v>-8.0640000000000003E-2</v>
       </c>
       <c r="AC223">
         <v>-59.375</v>
@@ -31265,7 +31265,7 @@
         <v>-59.375</v>
       </c>
       <c r="AL223">
-        <v>-8.0640000000000003E-2</v>
+        <v>-8.0649999999999999E-2</v>
       </c>
       <c r="AM223">
         <v>-59.375</v>
@@ -31309,7 +31309,7 @@
         <v>-57.8125</v>
       </c>
       <c r="F224">
-        <v>-7.8490000000000004E-2</v>
+        <v>-7.8479999999999994E-2</v>
       </c>
       <c r="G224">
         <v>-57.8125</v>
@@ -31345,7 +31345,7 @@
         <v>-57.8125</v>
       </c>
       <c r="R224">
-        <v>-7.8520000000000006E-2</v>
+        <v>-7.8530000000000003E-2</v>
       </c>
       <c r="S224">
         <v>-57.8125</v>
@@ -31399,13 +31399,13 @@
         <v>-57.8125</v>
       </c>
       <c r="AJ224">
-        <v>-7.85E-2</v>
+        <v>-7.8509999999999996E-2</v>
       </c>
       <c r="AK224">
         <v>-57.8125</v>
       </c>
       <c r="AL224">
-        <v>-7.85E-2</v>
+        <v>-7.8490000000000004E-2</v>
       </c>
       <c r="AM224">
         <v>-57.8125</v>
@@ -31479,13 +31479,13 @@
         <v>-56.25</v>
       </c>
       <c r="P225">
-        <v>-7.6369999999999993E-2</v>
+        <v>-7.6350000000000001E-2</v>
       </c>
       <c r="Q225">
         <v>-56.25</v>
       </c>
       <c r="R225">
-        <v>-7.639E-2</v>
+        <v>-7.6410000000000006E-2</v>
       </c>
       <c r="S225">
         <v>-56.25</v>
@@ -31497,7 +31497,7 @@
         <v>-56.25</v>
       </c>
       <c r="V225">
-        <v>-7.6359999999999997E-2</v>
+        <v>-7.6350000000000001E-2</v>
       </c>
       <c r="W225">
         <v>-56.25</v>
@@ -31539,13 +31539,13 @@
         <v>-56.25</v>
       </c>
       <c r="AJ225">
-        <v>-7.6369999999999993E-2</v>
+        <v>-7.6380000000000003E-2</v>
       </c>
       <c r="AK225">
         <v>-56.25</v>
       </c>
       <c r="AL225">
-        <v>-7.6359999999999997E-2</v>
+        <v>-7.6350000000000001E-2</v>
       </c>
       <c r="AM225">
         <v>-56.25</v>
@@ -31583,13 +31583,13 @@
         <v>-54.6875</v>
       </c>
       <c r="D226">
-        <v>-7.4260000000000007E-2</v>
+        <v>-7.4270000000000003E-2</v>
       </c>
       <c r="E226">
         <v>-54.6875</v>
       </c>
       <c r="F226">
-        <v>-7.4219999999999994E-2</v>
+        <v>-7.4249999999999997E-2</v>
       </c>
       <c r="G226">
         <v>-54.6875</v>
@@ -31637,7 +31637,7 @@
         <v>-54.6875</v>
       </c>
       <c r="V226">
-        <v>-7.4219999999999994E-2</v>
+        <v>-7.4209999999999998E-2</v>
       </c>
       <c r="W226">
         <v>-54.6875</v>
@@ -31703,7 +31703,7 @@
         <v>-54.6875</v>
       </c>
       <c r="AR226">
-        <v>-7.4260000000000007E-2</v>
+        <v>-7.424E-2</v>
       </c>
       <c r="AS226">
         <v>-54.6875</v>
@@ -31825,7 +31825,7 @@
         <v>-53.125</v>
       </c>
       <c r="AL227">
-        <v>-7.2090000000000001E-2</v>
+        <v>-7.2099999999999997E-2</v>
       </c>
       <c r="AM227">
         <v>-53.125</v>
@@ -31863,7 +31863,7 @@
         <v>-51.5625</v>
       </c>
       <c r="D228">
-        <v>-6.9980000000000001E-2</v>
+        <v>-6.9949999999999998E-2</v>
       </c>
       <c r="E228">
         <v>-51.5625</v>
@@ -31917,7 +31917,7 @@
         <v>-51.5625</v>
       </c>
       <c r="V228">
-        <v>-6.9959999999999994E-2</v>
+        <v>-6.9949999999999998E-2</v>
       </c>
       <c r="W228">
         <v>-51.5625</v>
@@ -31929,7 +31929,7 @@
         <v>-51.5625</v>
       </c>
       <c r="Z228">
-        <v>-6.9959999999999994E-2</v>
+        <v>-6.9949999999999998E-2</v>
       </c>
       <c r="AA228">
         <v>-51.5625</v>
@@ -31983,7 +31983,7 @@
         <v>-51.5625</v>
       </c>
       <c r="AR228">
-        <v>-6.9980000000000001E-2</v>
+        <v>-6.9959999999999994E-2</v>
       </c>
       <c r="AS228">
         <v>-51.5625</v>
@@ -32009,7 +32009,7 @@
         <v>-50</v>
       </c>
       <c r="F229">
-        <v>-6.7760000000000001E-2</v>
+        <v>-6.7750000000000005E-2</v>
       </c>
       <c r="G229">
         <v>-50</v>
@@ -32045,7 +32045,7 @@
         <v>-50</v>
       </c>
       <c r="R229">
-        <v>-6.7780000000000007E-2</v>
+        <v>-6.7790000000000003E-2</v>
       </c>
       <c r="S229">
         <v>-50</v>
@@ -32069,7 +32069,7 @@
         <v>-50</v>
       </c>
       <c r="Z229">
-        <v>-6.7760000000000001E-2</v>
+        <v>-6.7750000000000005E-2</v>
       </c>
       <c r="AA229">
         <v>-50</v>
@@ -32173,7 +32173,7 @@
         <v>-48.4375</v>
       </c>
       <c r="N230">
-        <v>-6.5629999999999994E-2</v>
+        <v>-6.5619999999999998E-2</v>
       </c>
       <c r="O230">
         <v>-48.4375</v>
@@ -32209,7 +32209,7 @@
         <v>-48.4375</v>
       </c>
       <c r="Z230">
-        <v>-6.5629999999999994E-2</v>
+        <v>-6.5600000000000006E-2</v>
       </c>
       <c r="AA230">
         <v>-48.4375</v>
@@ -32263,7 +32263,7 @@
         <v>-48.4375</v>
       </c>
       <c r="AR230">
-        <v>-6.5659999999999996E-2</v>
+        <v>-6.5640000000000004E-2</v>
       </c>
       <c r="AS230">
         <v>-48.4375</v>
@@ -32325,7 +32325,7 @@
         <v>-46.875</v>
       </c>
       <c r="R231">
-        <v>-6.3509999999999997E-2</v>
+        <v>-6.3519999999999993E-2</v>
       </c>
       <c r="S231">
         <v>-46.875</v>
@@ -32343,7 +32343,7 @@
         <v>-46.875</v>
       </c>
       <c r="X231">
-        <v>-6.3509999999999997E-2</v>
+        <v>-6.3530000000000003E-2</v>
       </c>
       <c r="Y231">
         <v>-46.875</v>
@@ -32423,13 +32423,13 @@
         <v>-45.3125</v>
       </c>
       <c r="D232">
-        <v>-6.1400000000000003E-2</v>
+        <v>-6.1409999999999999E-2</v>
       </c>
       <c r="E232">
         <v>-45.3125</v>
       </c>
       <c r="F232">
-        <v>-6.1379999999999997E-2</v>
+        <v>-6.139E-2</v>
       </c>
       <c r="G232">
         <v>-45.3125</v>
@@ -32519,7 +32519,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AJ232">
-        <v>-6.1379999999999997E-2</v>
+        <v>-6.1400000000000003E-2</v>
       </c>
       <c r="AK232">
         <v>-45.3125</v>
@@ -32629,7 +32629,7 @@
         <v>-43.75</v>
       </c>
       <c r="Z233">
-        <v>-5.9270000000000003E-2</v>
+        <v>-5.9290000000000002E-2</v>
       </c>
       <c r="AA233">
         <v>-43.75</v>
@@ -32683,7 +32683,7 @@
         <v>-43.75</v>
       </c>
       <c r="AR233">
-        <v>-5.9270000000000003E-2</v>
+        <v>-5.9290000000000002E-2</v>
       </c>
       <c r="AS233">
         <v>-43.75</v>
@@ -32703,13 +32703,13 @@
         <v>-42.1875</v>
       </c>
       <c r="D234">
-        <v>-5.7149999999999999E-2</v>
+        <v>-5.7140000000000003E-2</v>
       </c>
       <c r="E234">
         <v>-42.1875</v>
       </c>
       <c r="F234">
-        <v>-5.713E-2</v>
+        <v>-5.7149999999999999E-2</v>
       </c>
       <c r="G234">
         <v>-42.1875</v>
@@ -32757,7 +32757,7 @@
         <v>-42.1875</v>
       </c>
       <c r="V234">
-        <v>-5.713E-2</v>
+        <v>-5.7110000000000001E-2</v>
       </c>
       <c r="W234">
         <v>-42.1875</v>
@@ -32769,7 +32769,7 @@
         <v>-42.1875</v>
       </c>
       <c r="Z234">
-        <v>-5.713E-2</v>
+        <v>-5.7140000000000003E-2</v>
       </c>
       <c r="AA234">
         <v>-42.1875</v>
@@ -32793,7 +32793,7 @@
         <v>-42.1875</v>
       </c>
       <c r="AH234">
-        <v>-5.7149999999999999E-2</v>
+        <v>-5.7169999999999999E-2</v>
       </c>
       <c r="AI234">
         <v>-42.1875</v>
@@ -32805,7 +32805,7 @@
         <v>-42.1875</v>
       </c>
       <c r="AL234">
-        <v>-5.713E-2</v>
+        <v>-5.7149999999999999E-2</v>
       </c>
       <c r="AM234">
         <v>-42.1875</v>
@@ -32873,7 +32873,7 @@
         <v>-40.625</v>
       </c>
       <c r="N235">
-        <v>-5.5E-2</v>
+        <v>-5.5199999999999999E-2</v>
       </c>
       <c r="O235">
         <v>-40.625</v>
@@ -32885,7 +32885,7 @@
         <v>-40.625</v>
       </c>
       <c r="R235">
-        <v>-5.5019999999999999E-2</v>
+        <v>-5.5010000000000003E-2</v>
       </c>
       <c r="S235">
         <v>-40.625</v>
@@ -32897,7 +32897,7 @@
         <v>-40.625</v>
       </c>
       <c r="V235">
-        <v>-5.5E-2</v>
+        <v>-5.5100000000000003E-2</v>
       </c>
       <c r="W235">
         <v>-40.625</v>
@@ -32939,7 +32939,7 @@
         <v>-40.625</v>
       </c>
       <c r="AJ235">
-        <v>-5.5019999999999999E-2</v>
+        <v>-5.5030000000000003E-2</v>
       </c>
       <c r="AK235">
         <v>-40.625</v>
@@ -32963,7 +32963,7 @@
         <v>-40.625</v>
       </c>
       <c r="AR235">
-        <v>-5.5019999999999999E-2</v>
+        <v>-5.5030000000000003E-2</v>
       </c>
       <c r="AS235">
         <v>-40.625</v>
@@ -32983,7 +32983,7 @@
         <v>-39.0625</v>
       </c>
       <c r="D236">
-        <v>-5.2900000000000003E-2</v>
+        <v>-5.2909999999999999E-2</v>
       </c>
       <c r="E236">
         <v>-39.0625</v>
@@ -33013,7 +33013,7 @@
         <v>-39.0625</v>
       </c>
       <c r="N236">
-        <v>-5.289E-2</v>
+        <v>-5.2909999999999999E-2</v>
       </c>
       <c r="O236">
         <v>-39.0625</v>
@@ -33073,7 +33073,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AH236">
-        <v>-5.2900000000000003E-2</v>
+        <v>-5.3100000000000001E-2</v>
       </c>
       <c r="AI236">
         <v>-39.0625</v>
@@ -33103,7 +33103,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AR236">
-        <v>-5.2900000000000003E-2</v>
+        <v>-5.28E-2</v>
       </c>
       <c r="AS236">
         <v>-39.0625</v>
@@ -33123,7 +33123,7 @@
         <v>-37.5</v>
       </c>
       <c r="D237">
-        <v>-5.0750000000000003E-2</v>
+        <v>-5.0770000000000003E-2</v>
       </c>
       <c r="E237">
         <v>-37.5</v>
@@ -33153,7 +33153,7 @@
         <v>-37.5</v>
       </c>
       <c r="N237">
-        <v>-5.074E-2</v>
+        <v>-5.0750000000000003E-2</v>
       </c>
       <c r="O237">
         <v>-37.5</v>
@@ -33183,7 +33183,7 @@
         <v>-37.5</v>
       </c>
       <c r="X237">
-        <v>-5.0750000000000003E-2</v>
+        <v>-5.0770000000000003E-2</v>
       </c>
       <c r="Y237">
         <v>-37.5</v>
@@ -33225,7 +33225,7 @@
         <v>-37.5</v>
       </c>
       <c r="AL237">
-        <v>-5.074E-2</v>
+        <v>-5.0750000000000003E-2</v>
       </c>
       <c r="AM237">
         <v>-37.5</v>
@@ -33293,7 +33293,7 @@
         <v>-35.9375</v>
       </c>
       <c r="N238">
-        <v>-4.8619999999999997E-2</v>
+        <v>-4.863E-2</v>
       </c>
       <c r="O238">
         <v>-35.9375</v>
@@ -33305,7 +33305,7 @@
         <v>-35.9375</v>
       </c>
       <c r="R238">
-        <v>-4.8640000000000003E-2</v>
+        <v>-4.8649999999999999E-2</v>
       </c>
       <c r="S238">
         <v>-35.9375</v>
@@ -33323,7 +33323,7 @@
         <v>-35.9375</v>
       </c>
       <c r="X238">
-        <v>-4.8640000000000003E-2</v>
+        <v>-4.8649999999999999E-2</v>
       </c>
       <c r="Y238">
         <v>-35.9375</v>
@@ -33353,7 +33353,7 @@
         <v>-35.9375</v>
       </c>
       <c r="AH238">
-        <v>-4.8649999999999999E-2</v>
+        <v>-4.8660000000000002E-2</v>
       </c>
       <c r="AI238">
         <v>-35.9375</v>
@@ -33383,7 +33383,7 @@
         <v>-35.9375</v>
       </c>
       <c r="AR238">
-        <v>-4.8640000000000003E-2</v>
+        <v>-4.8649999999999999E-2</v>
       </c>
       <c r="AS238">
         <v>-35.9375</v>
@@ -33403,7 +33403,7 @@
         <v>-34.375</v>
       </c>
       <c r="D239">
-        <v>-4.6510000000000003E-2</v>
+        <v>-4.65E-2</v>
       </c>
       <c r="E239">
         <v>-34.375</v>
@@ -33445,7 +33445,7 @@
         <v>-34.375</v>
       </c>
       <c r="R239">
-        <v>-4.6510000000000003E-2</v>
+        <v>-4.6539999999999998E-2</v>
       </c>
       <c r="S239">
         <v>-34.375</v>
@@ -33457,7 +33457,7 @@
         <v>-34.375</v>
       </c>
       <c r="V239">
-        <v>-4.6489999999999997E-2</v>
+        <v>-4.6510000000000003E-2</v>
       </c>
       <c r="W239">
         <v>-34.375</v>
@@ -33499,7 +33499,7 @@
         <v>-34.375</v>
       </c>
       <c r="AJ239">
-        <v>-4.6510000000000003E-2</v>
+        <v>-4.6519999999999999E-2</v>
       </c>
       <c r="AK239">
         <v>-34.375</v>
@@ -33585,7 +33585,7 @@
         <v>-32.8125</v>
       </c>
       <c r="R240">
-        <v>-4.4389999999999999E-2</v>
+        <v>-4.4400000000000002E-2</v>
       </c>
       <c r="S240">
         <v>-32.8125</v>
@@ -33597,7 +33597,7 @@
         <v>-32.8125</v>
       </c>
       <c r="V240">
-        <v>-4.437E-2</v>
+        <v>-4.4350000000000001E-2</v>
       </c>
       <c r="W240">
         <v>-32.8125</v>
@@ -33645,7 +33645,7 @@
         <v>-32.8125</v>
       </c>
       <c r="AL240">
-        <v>-4.437E-2</v>
+        <v>-4.4380000000000003E-2</v>
       </c>
       <c r="AM240">
         <v>-32.8125</v>
@@ -33663,7 +33663,7 @@
         <v>-32.8125</v>
       </c>
       <c r="AR240">
-        <v>-4.4389999999999999E-2</v>
+        <v>-4.437E-2</v>
       </c>
       <c r="AS240">
         <v>-32.8125</v>
@@ -33683,13 +33683,13 @@
         <v>-31.25</v>
       </c>
       <c r="D241">
-        <v>-4.2270000000000002E-2</v>
+        <v>-4.2299999999999997E-2</v>
       </c>
       <c r="E241">
         <v>-31.25</v>
       </c>
       <c r="F241">
-        <v>-4.2259999999999999E-2</v>
+        <v>-4.2270000000000002E-2</v>
       </c>
       <c r="G241">
         <v>-31.25</v>
@@ -33701,7 +33701,7 @@
         <v>-31.25</v>
       </c>
       <c r="J241">
-        <v>-4.2270000000000002E-2</v>
+        <v>-4.2299999999999997E-2</v>
       </c>
       <c r="K241">
         <v>-31.25</v>
@@ -33785,7 +33785,7 @@
         <v>-31.25</v>
       </c>
       <c r="AL241">
-        <v>-4.2259999999999999E-2</v>
+        <v>-4.2250000000000003E-2</v>
       </c>
       <c r="AM241">
         <v>-31.25</v>
@@ -33859,13 +33859,13 @@
         <v>-29.6875</v>
       </c>
       <c r="P242">
-        <v>-4.0140000000000002E-2</v>
+        <v>-4.0160000000000001E-2</v>
       </c>
       <c r="Q242">
         <v>-29.6875</v>
       </c>
       <c r="R242">
-        <v>-4.0140000000000002E-2</v>
+        <v>-4.0149999999999998E-2</v>
       </c>
       <c r="S242">
         <v>-29.6875</v>
@@ -33889,7 +33889,7 @@
         <v>-29.6875</v>
       </c>
       <c r="Z242">
-        <v>-4.0140000000000002E-2</v>
+        <v>-4.0129999999999999E-2</v>
       </c>
       <c r="AA242">
         <v>-29.6875</v>
@@ -33919,13 +33919,13 @@
         <v>-29.6875</v>
       </c>
       <c r="AJ242">
-        <v>-4.0140000000000002E-2</v>
+        <v>-4.0169999999999997E-2</v>
       </c>
       <c r="AK242">
         <v>-29.6875</v>
       </c>
       <c r="AL242">
-        <v>-4.0140000000000002E-2</v>
+        <v>-4.0149999999999998E-2</v>
       </c>
       <c r="AM242">
         <v>-29.6875</v>
@@ -33943,7 +33943,7 @@
         <v>-29.6875</v>
       </c>
       <c r="AR242">
-        <v>-4.0140000000000002E-2</v>
+        <v>-4.0129999999999999E-2</v>
       </c>
       <c r="AS242">
         <v>-29.6875</v>
@@ -33963,7 +33963,7 @@
         <v>-28.125</v>
       </c>
       <c r="D243">
-        <v>-3.8019999999999998E-2</v>
+        <v>-3.8010000000000002E-2</v>
       </c>
       <c r="E243">
         <v>-28.125</v>
@@ -33981,7 +33981,7 @@
         <v>-28.125</v>
       </c>
       <c r="J243">
-        <v>-3.8019999999999998E-2</v>
+        <v>-3.8030000000000001E-2</v>
       </c>
       <c r="K243">
         <v>-28.125</v>
@@ -34017,7 +34017,7 @@
         <v>-28.125</v>
       </c>
       <c r="V243">
-        <v>-3.8010000000000002E-2</v>
+        <v>-3.8019999999999998E-2</v>
       </c>
       <c r="W243">
         <v>-28.125</v>
@@ -34083,7 +34083,7 @@
         <v>-28.125</v>
       </c>
       <c r="AR243">
-        <v>-3.8019999999999998E-2</v>
+        <v>-3.8030000000000001E-2</v>
       </c>
       <c r="AS243">
         <v>-28.125</v>
@@ -34139,13 +34139,13 @@
         <v>-26.5625</v>
       </c>
       <c r="P244">
-        <v>-3.5889999999999998E-2</v>
+        <v>-3.5880000000000002E-2</v>
       </c>
       <c r="Q244">
         <v>-26.5625</v>
       </c>
       <c r="R244">
-        <v>-3.5909999999999997E-2</v>
+        <v>-3.5920000000000001E-2</v>
       </c>
       <c r="S244">
         <v>-26.5625</v>
@@ -34199,13 +34199,13 @@
         <v>-26.5625</v>
       </c>
       <c r="AJ244">
-        <v>-3.5889999999999998E-2</v>
+        <v>-3.5900000000000001E-2</v>
       </c>
       <c r="AK244">
         <v>-26.5625</v>
       </c>
       <c r="AL244">
-        <v>-3.5889999999999998E-2</v>
+        <v>-3.5909999999999997E-2</v>
       </c>
       <c r="AM244">
         <v>-26.5625</v>
@@ -34223,7 +34223,7 @@
         <v>-26.5625</v>
       </c>
       <c r="AR244">
-        <v>-3.5909999999999997E-2</v>
+        <v>-3.5900000000000001E-2</v>
       </c>
       <c r="AS244">
         <v>-26.5625</v>
@@ -34243,7 +34243,7 @@
         <v>-25</v>
       </c>
       <c r="D245">
-        <v>-3.3779999999999998E-2</v>
+        <v>-3.3790000000000001E-2</v>
       </c>
       <c r="E245">
         <v>-25</v>
@@ -34261,7 +34261,7 @@
         <v>-25</v>
       </c>
       <c r="J245">
-        <v>-3.3779999999999998E-2</v>
+        <v>-3.3790000000000001E-2</v>
       </c>
       <c r="K245">
         <v>-25</v>
@@ -34309,7 +34309,7 @@
         <v>-25</v>
       </c>
       <c r="Z245">
-        <v>-3.3779999999999998E-2</v>
+        <v>-3.3770000000000001E-2</v>
       </c>
       <c r="AA245">
         <v>-25</v>
@@ -34383,7 +34383,7 @@
         <v>-23.4375</v>
       </c>
       <c r="D246">
-        <v>-3.1660000000000001E-2</v>
+        <v>-3.1649999999999998E-2</v>
       </c>
       <c r="E246">
         <v>-23.4375</v>
@@ -34437,7 +34437,7 @@
         <v>-23.4375</v>
       </c>
       <c r="V246">
-        <v>-3.1640000000000001E-2</v>
+        <v>-3.1649999999999998E-2</v>
       </c>
       <c r="W246">
         <v>-23.4375</v>
@@ -34473,13 +34473,13 @@
         <v>-23.4375</v>
       </c>
       <c r="AH246">
-        <v>-3.1660000000000001E-2</v>
+        <v>-3.1640000000000001E-2</v>
       </c>
       <c r="AI246">
         <v>-23.4375</v>
       </c>
       <c r="AJ246">
-        <v>-3.1660000000000001E-2</v>
+        <v>-3.1649999999999998E-2</v>
       </c>
       <c r="AK246">
         <v>-23.4375</v>
@@ -34565,7 +34565,7 @@
         <v>-21.875</v>
       </c>
       <c r="R247">
-        <v>-2.954E-2</v>
+        <v>-2.9520000000000001E-2</v>
       </c>
       <c r="S247">
         <v>-21.875</v>
@@ -34613,7 +34613,7 @@
         <v>-21.875</v>
       </c>
       <c r="AH247">
-        <v>-2.954E-2</v>
+        <v>-2.955E-2</v>
       </c>
       <c r="AI247">
         <v>-21.875</v>
@@ -34753,13 +34753,13 @@
         <v>-20.3125</v>
       </c>
       <c r="AH248">
-        <v>-2.741E-2</v>
+        <v>-2.742E-2</v>
       </c>
       <c r="AI248">
         <v>-20.3125</v>
       </c>
       <c r="AJ248">
-        <v>-2.741E-2</v>
+        <v>-2.742E-2</v>
       </c>
       <c r="AK248">
         <v>-20.3125</v>
@@ -34783,7 +34783,7 @@
         <v>-20.3125</v>
       </c>
       <c r="AR248">
-        <v>-2.741E-2</v>
+        <v>-2.7390000000000001E-2</v>
       </c>
       <c r="AS248">
         <v>-20.3125</v>
@@ -34803,7 +34803,7 @@
         <v>-18.75</v>
       </c>
       <c r="D249">
-        <v>-2.53E-2</v>
+        <v>-2.5319999999999999E-2</v>
       </c>
       <c r="E249">
         <v>-18.75</v>
@@ -34857,7 +34857,7 @@
         <v>-18.75</v>
       </c>
       <c r="V249">
-        <v>-2.528E-2</v>
+        <v>-2.5260000000000001E-2</v>
       </c>
       <c r="W249">
         <v>-18.75</v>
@@ -34869,7 +34869,7 @@
         <v>-18.75</v>
       </c>
       <c r="Z249">
-        <v>-2.528E-2</v>
+        <v>-2.5260000000000001E-2</v>
       </c>
       <c r="AA249">
         <v>-18.75</v>
@@ -34893,7 +34893,7 @@
         <v>-18.75</v>
       </c>
       <c r="AH249">
-        <v>-2.53E-2</v>
+        <v>-2.528E-2</v>
       </c>
       <c r="AI249">
         <v>-18.75</v>
@@ -35039,7 +35039,7 @@
         <v>-17.1875</v>
       </c>
       <c r="AJ250">
-        <v>-2.316E-2</v>
+        <v>-2.3179999999999999E-2</v>
       </c>
       <c r="AK250">
         <v>-17.1875</v>
@@ -35289,7 +35289,7 @@
         <v>-14.0625</v>
       </c>
       <c r="Z252">
-        <v>-1.78E-2</v>
+        <v>-1.77E-2</v>
       </c>
       <c r="AA252">
         <v>-14.0625</v>
@@ -35429,7 +35429,7 @@
         <v>-12.5</v>
       </c>
       <c r="Z253">
-        <v>-1.2529999999999999E-2</v>
+        <v>-1.2500000000000001E-2</v>
       </c>
       <c r="AA253">
         <v>-12.5</v>
@@ -35709,7 +35709,7 @@
         <v>-9.375</v>
       </c>
       <c r="Z255" s="1">
-        <v>-3.23064E-5</v>
+        <v>-4.515E-5</v>
       </c>
       <c r="AA255">
         <v>-9.375</v>
